--- a/outputs/VIC_curtailment.xlsx
+++ b/outputs/VIC_curtailment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V68"/>
+  <dimension ref="A1:X68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -481,6 +481,8 @@
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="12" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -531,65 +533,75 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Actual FY23-24</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Actual FY24-25</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>ELI Near Term</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ELI Med Term</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>FY24-25</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>FY25-26</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>FY26-27 (Draft)</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Curt FY1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Curt FY2</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Curt FY3</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Curt Avg</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Offl FY1</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Offl FY2</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Offl FY3</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Offl Avg</t>
         </is>
@@ -638,42 +650,48 @@
         <v>66</v>
       </c>
       <c r="J2" s="5" t="n">
+        <v>0.3710560565867671</v>
+      </c>
+      <c r="K2" s="5" t="n">
+        <v>0.2719808764553837</v>
+      </c>
+      <c r="L2" s="5" t="n">
         <v>0.833539620209753</v>
       </c>
-      <c r="K2" s="5" t="n">
+      <c r="M2" s="5" t="n">
         <v>0.164192244302687</v>
       </c>
-      <c r="L2" s="5" t="n">
+      <c r="N2" s="5" t="n">
         <v>0.8584000000000001</v>
       </c>
-      <c r="M2" s="5" t="n">
+      <c r="O2" s="5" t="n">
         <v>0.8986</v>
       </c>
-      <c r="N2" s="5" t="n">
+      <c r="P2" s="5" t="n">
         <v>0.9114</v>
       </c>
-      <c r="O2" s="6" t="n">
+      <c r="Q2" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="P2" s="6" t="n">
+      <c r="R2" s="6" t="n">
         <v>0.06</v>
       </c>
-      <c r="Q2" s="6" t="n">
+      <c r="S2" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="R2" s="6" t="n">
+      <c r="T2" s="6" t="n">
         <v>0.02666666666666667</v>
       </c>
-      <c r="S2" s="6" t="n">
+      <c r="U2" s="6" t="n">
         <v>0.11</v>
       </c>
-      <c r="T2" s="6" t="n">
+      <c r="V2" s="6" t="n">
         <v>0.17</v>
       </c>
-      <c r="U2" s="6" t="n">
+      <c r="W2" s="6" t="n">
         <v>0.08</v>
       </c>
-      <c r="V2" s="6" t="n">
+      <c r="X2" s="6" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -716,20 +734,22 @@
       <c r="J3" s="5" t="inlineStr"/>
       <c r="K3" s="5" t="inlineStr"/>
       <c r="L3" s="5" t="inlineStr"/>
-      <c r="M3" s="5" t="n">
+      <c r="M3" s="5" t="inlineStr"/>
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="n">
         <v>0.8883</v>
       </c>
-      <c r="N3" s="5" t="n">
+      <c r="P3" s="5" t="n">
         <v>0.9012</v>
       </c>
-      <c r="O3" s="6" t="inlineStr"/>
-      <c r="P3" s="6" t="inlineStr"/>
       <c r="Q3" s="6" t="inlineStr"/>
       <c r="R3" s="6" t="inlineStr"/>
       <c r="S3" s="6" t="inlineStr"/>
       <c r="T3" s="6" t="inlineStr"/>
       <c r="U3" s="6" t="inlineStr"/>
       <c r="V3" s="6" t="inlineStr"/>
+      <c r="W3" s="6" t="inlineStr"/>
+      <c r="X3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -774,42 +794,48 @@
         <v>66</v>
       </c>
       <c r="J4" s="5" t="n">
+        <v>0.1600293147297279</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>0.2827710603192121</v>
+      </c>
+      <c r="L4" s="5" t="n">
         <v>0.547516873654646</v>
       </c>
-      <c r="K4" s="5" t="n">
+      <c r="M4" s="5" t="n">
         <v>0.122422882740379</v>
       </c>
-      <c r="L4" s="5" t="n">
+      <c r="N4" s="5" t="n">
         <v>0.8962</v>
       </c>
-      <c r="M4" s="5" t="n">
+      <c r="O4" s="5" t="n">
         <v>0.9305</v>
       </c>
-      <c r="N4" s="5" t="n">
+      <c r="P4" s="5" t="n">
         <v>0.9307</v>
       </c>
-      <c r="O4" s="6" t="n">
+      <c r="Q4" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="P4" s="6" t="n">
+      <c r="R4" s="6" t="n">
         <v>0.06</v>
       </c>
-      <c r="Q4" s="6" t="n">
+      <c r="S4" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="R4" s="6" t="n">
+      <c r="T4" s="6" t="n">
         <v>0.02666666666666667</v>
       </c>
-      <c r="S4" s="6" t="n">
+      <c r="U4" s="6" t="n">
         <v>0.11</v>
       </c>
-      <c r="T4" s="6" t="n">
+      <c r="V4" s="6" t="n">
         <v>0.17</v>
       </c>
-      <c r="U4" s="6" t="n">
+      <c r="W4" s="6" t="n">
         <v>0.08</v>
       </c>
-      <c r="V4" s="6" t="n">
+      <c r="X4" s="6" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -856,42 +882,48 @@
         <v>66</v>
       </c>
       <c r="J5" s="5" t="n">
+        <v>0.05215670207613177</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>0.05460168559670209</v>
+      </c>
+      <c r="L5" s="5" t="n">
         <v>0.547516873654646</v>
       </c>
-      <c r="K5" s="5" t="n">
+      <c r="M5" s="5" t="n">
         <v>0.122422882740379</v>
       </c>
-      <c r="L5" s="5" t="n">
+      <c r="N5" s="5" t="n">
         <v>0.8962</v>
       </c>
-      <c r="M5" s="5" t="n">
+      <c r="O5" s="5" t="n">
         <v>0.9305</v>
       </c>
-      <c r="N5" s="5" t="n">
+      <c r="P5" s="5" t="n">
         <v>0.9307</v>
       </c>
-      <c r="O5" s="6" t="n">
+      <c r="Q5" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="P5" s="6" t="n">
+      <c r="R5" s="6" t="n">
         <v>0.06</v>
       </c>
-      <c r="Q5" s="6" t="n">
+      <c r="S5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="R5" s="6" t="n">
+      <c r="T5" s="6" t="n">
         <v>0.02666666666666667</v>
       </c>
-      <c r="S5" s="6" t="n">
+      <c r="U5" s="6" t="n">
         <v>0.11</v>
       </c>
-      <c r="T5" s="6" t="n">
+      <c r="V5" s="6" t="n">
         <v>0.17</v>
       </c>
-      <c r="U5" s="6" t="n">
+      <c r="W5" s="6" t="n">
         <v>0.08</v>
       </c>
-      <c r="V5" s="6" t="n">
+      <c r="X5" s="6" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -937,26 +969,24 @@
       <c r="I6" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="J6" s="5" t="n">
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="n">
+        <v>0.2650311526126716</v>
+      </c>
+      <c r="L6" s="5" t="n">
         <v>0.389503957787889</v>
       </c>
-      <c r="K6" s="5" t="n">
+      <c r="M6" s="5" t="n">
         <v>0.08205629867681941</v>
       </c>
-      <c r="L6" s="5" t="n">
+      <c r="N6" s="5" t="n">
         <v>0.9477</v>
       </c>
-      <c r="M6" s="5" t="n">
+      <c r="O6" s="5" t="n">
         <v>0.9463</v>
       </c>
-      <c r="N6" s="5" t="n">
+      <c r="P6" s="5" t="n">
         <v>0.9223</v>
-      </c>
-      <c r="O6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v>0</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>0</v>
@@ -965,17 +995,23 @@
         <v>0</v>
       </c>
       <c r="S6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="6" t="n">
         <v>0.04</v>
-      </c>
-      <c r="T6" s="6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="U6" s="6" t="n">
-        <v>0.1</v>
       </c>
       <c r="V6" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
+      <c r="W6" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X6" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1020,25 +1056,25 @@
         <v>220</v>
       </c>
       <c r="J7" s="5" t="n">
+        <v>0.1954445746044534</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>0.07798287623836642</v>
+      </c>
+      <c r="L7" s="5" t="n">
         <v>0.390717855103594</v>
       </c>
-      <c r="K7" s="5" t="n">
+      <c r="M7" s="5" t="n">
         <v>0.08997768712489811</v>
       </c>
-      <c r="L7" s="5" t="n">
+      <c r="N7" s="5" t="n">
         <v>0.9626</v>
       </c>
-      <c r="M7" s="5" t="n">
+      <c r="O7" s="5" t="n">
         <v>0.949</v>
       </c>
-      <c r="N7" s="5" t="n">
+      <c r="P7" s="5" t="n">
         <v>0.9292</v>
-      </c>
-      <c r="O7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="6" t="n">
-        <v>0</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1047,17 +1083,23 @@
         <v>0</v>
       </c>
       <c r="S7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="6" t="n">
         <v>0.04</v>
-      </c>
-      <c r="T7" s="6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="U7" s="6" t="n">
-        <v>0.1</v>
       </c>
       <c r="V7" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
+      <c r="W7" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X7" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1095,25 +1137,31 @@
         <v>132</v>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="5" t="inlineStr"/>
-      <c r="K8" s="5" t="inlineStr"/>
-      <c r="L8" s="5" t="n">
+      <c r="J8" s="5" t="n">
+        <v>0.1990273759688161</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>0.2408960878187453</v>
+      </c>
+      <c r="L8" s="5" t="inlineStr"/>
+      <c r="M8" s="5" t="inlineStr"/>
+      <c r="N8" s="5" t="n">
         <v>0.9455</v>
       </c>
-      <c r="M8" s="5" t="n">
+      <c r="O8" s="5" t="n">
         <v>0.9402</v>
       </c>
-      <c r="N8" s="5" t="n">
+      <c r="P8" s="5" t="n">
         <v>0.922</v>
       </c>
-      <c r="O8" s="6" t="inlineStr"/>
-      <c r="P8" s="6" t="inlineStr"/>
       <c r="Q8" s="6" t="inlineStr"/>
       <c r="R8" s="6" t="inlineStr"/>
       <c r="S8" s="6" t="inlineStr"/>
       <c r="T8" s="6" t="inlineStr"/>
       <c r="U8" s="6" t="inlineStr"/>
       <c r="V8" s="6" t="inlineStr"/>
+      <c r="W8" s="6" t="inlineStr"/>
+      <c r="X8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1154,20 +1202,22 @@
       <c r="J9" s="5" t="inlineStr"/>
       <c r="K9" s="5" t="inlineStr"/>
       <c r="L9" s="5" t="inlineStr"/>
-      <c r="M9" s="5" t="n">
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="n">
         <v>0.9328</v>
       </c>
-      <c r="N9" s="5" t="n">
+      <c r="P9" s="5" t="n">
         <v>0.9262</v>
       </c>
-      <c r="O9" s="6" t="inlineStr"/>
-      <c r="P9" s="6" t="inlineStr"/>
       <c r="Q9" s="6" t="inlineStr"/>
       <c r="R9" s="6" t="inlineStr"/>
       <c r="S9" s="6" t="inlineStr"/>
       <c r="T9" s="6" t="inlineStr"/>
       <c r="U9" s="6" t="inlineStr"/>
       <c r="V9" s="6" t="inlineStr"/>
+      <c r="W9" s="6" t="inlineStr"/>
+      <c r="X9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1212,42 +1262,48 @@
         <v>66</v>
       </c>
       <c r="J10" s="5" t="n">
+        <v>0.3169574937730341</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>0.1686799728674456</v>
+      </c>
+      <c r="L10" s="5" t="n">
         <v>0.8554020168196</v>
       </c>
-      <c r="K10" s="5" t="n">
+      <c r="M10" s="5" t="n">
         <v>0.072415601225557</v>
       </c>
-      <c r="L10" s="5" t="n">
+      <c r="N10" s="5" t="n">
         <v>0.8506</v>
       </c>
-      <c r="M10" s="5" t="n">
+      <c r="O10" s="5" t="n">
         <v>0.8895</v>
       </c>
-      <c r="N10" s="5" t="n">
+      <c r="P10" s="5" t="n">
         <v>0.9088000000000001</v>
       </c>
-      <c r="O10" s="6" t="n">
+      <c r="Q10" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="P10" s="6" t="n">
+      <c r="R10" s="6" t="n">
         <v>0.06</v>
       </c>
-      <c r="Q10" s="6" t="n">
+      <c r="S10" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="R10" s="6" t="n">
+      <c r="T10" s="6" t="n">
         <v>0.02666666666666667</v>
       </c>
-      <c r="S10" s="6" t="n">
+      <c r="U10" s="6" t="n">
         <v>0.11</v>
       </c>
-      <c r="T10" s="6" t="n">
+      <c r="V10" s="6" t="n">
         <v>0.17</v>
       </c>
-      <c r="U10" s="6" t="n">
+      <c r="W10" s="6" t="n">
         <v>0.08</v>
       </c>
-      <c r="V10" s="6" t="n">
+      <c r="X10" s="6" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -1288,24 +1344,28 @@
       </c>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
-      <c r="L11" s="5" t="n">
+      <c r="K11" s="5" t="n">
+        <v>0.04898598021985823</v>
+      </c>
+      <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="n">
         <v>0.8964</v>
       </c>
-      <c r="M11" s="5" t="n">
+      <c r="O11" s="5" t="n">
         <v>0.9329</v>
       </c>
-      <c r="N11" s="5" t="n">
+      <c r="P11" s="5" t="n">
         <v>0.9330000000000001</v>
       </c>
-      <c r="O11" s="6" t="inlineStr"/>
-      <c r="P11" s="6" t="inlineStr"/>
       <c r="Q11" s="6" t="inlineStr"/>
       <c r="R11" s="6" t="inlineStr"/>
       <c r="S11" s="6" t="inlineStr"/>
       <c r="T11" s="6" t="inlineStr"/>
       <c r="U11" s="6" t="inlineStr"/>
       <c r="V11" s="6" t="inlineStr"/>
+      <c r="W11" s="6" t="inlineStr"/>
+      <c r="X11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1350,42 +1410,48 @@
         <v>220</v>
       </c>
       <c r="J12" s="5" t="n">
+        <v>0.1091648532990047</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>0.1136272868211855</v>
+      </c>
+      <c r="L12" s="5" t="n">
         <v>0.827440107601162</v>
       </c>
-      <c r="K12" s="5" t="n">
+      <c r="M12" s="5" t="n">
         <v>0.0878331516592939</v>
       </c>
-      <c r="L12" s="5" t="n">
+      <c r="N12" s="5" t="n">
         <v>0.8363</v>
       </c>
-      <c r="M12" s="5" t="n">
+      <c r="O12" s="5" t="n">
         <v>0.8784999999999999</v>
       </c>
-      <c r="N12" s="5" t="n">
+      <c r="P12" s="5" t="n">
         <v>0.878</v>
       </c>
-      <c r="O12" s="6" t="n">
+      <c r="Q12" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="P12" s="6" t="n">
+      <c r="R12" s="6" t="n">
         <v>0.06</v>
       </c>
-      <c r="Q12" s="6" t="n">
+      <c r="S12" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="R12" s="6" t="n">
+      <c r="T12" s="6" t="n">
         <v>0.02666666666666667</v>
       </c>
-      <c r="S12" s="6" t="n">
+      <c r="U12" s="6" t="n">
         <v>0.11</v>
       </c>
-      <c r="T12" s="6" t="n">
+      <c r="V12" s="6" t="n">
         <v>0.17</v>
       </c>
-      <c r="U12" s="6" t="n">
+      <c r="W12" s="6" t="n">
         <v>0.08</v>
       </c>
-      <c r="V12" s="6" t="n">
+      <c r="X12" s="6" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -1428,18 +1494,20 @@
       <c r="J13" s="5" t="inlineStr"/>
       <c r="K13" s="5" t="inlineStr"/>
       <c r="L13" s="5" t="inlineStr"/>
-      <c r="M13" s="5" t="n">
+      <c r="M13" s="5" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="5" t="n">
         <v>0.9441000000000001</v>
       </c>
-      <c r="N13" s="5" t="inlineStr"/>
-      <c r="O13" s="6" t="inlineStr"/>
-      <c r="P13" s="6" t="inlineStr"/>
+      <c r="P13" s="5" t="inlineStr"/>
       <c r="Q13" s="6" t="inlineStr"/>
       <c r="R13" s="6" t="inlineStr"/>
       <c r="S13" s="6" t="inlineStr"/>
       <c r="T13" s="6" t="inlineStr"/>
       <c r="U13" s="6" t="inlineStr"/>
       <c r="V13" s="6" t="inlineStr"/>
+      <c r="W13" s="6" t="inlineStr"/>
+      <c r="X13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1478,24 +1546,28 @@
       </c>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="5" t="inlineStr"/>
-      <c r="K14" s="5" t="inlineStr"/>
-      <c r="L14" s="5" t="n">
+      <c r="K14" s="5" t="n">
+        <v>0.1074948342034868</v>
+      </c>
+      <c r="L14" s="5" t="inlineStr"/>
+      <c r="M14" s="5" t="inlineStr"/>
+      <c r="N14" s="5" t="n">
         <v>0.9484</v>
       </c>
-      <c r="M14" s="5" t="n">
+      <c r="O14" s="5" t="n">
         <v>0.9415</v>
       </c>
-      <c r="N14" s="5" t="n">
+      <c r="P14" s="5" t="n">
         <v>0.9248</v>
       </c>
-      <c r="O14" s="6" t="inlineStr"/>
-      <c r="P14" s="6" t="inlineStr"/>
       <c r="Q14" s="6" t="inlineStr"/>
       <c r="R14" s="6" t="inlineStr"/>
       <c r="S14" s="6" t="inlineStr"/>
       <c r="T14" s="6" t="inlineStr"/>
       <c r="U14" s="6" t="inlineStr"/>
       <c r="V14" s="6" t="inlineStr"/>
+      <c r="W14" s="6" t="inlineStr"/>
+      <c r="X14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1540,25 +1612,25 @@
         <v>66</v>
       </c>
       <c r="J15" s="5" t="n">
+        <v>0.3437740975604878</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>0.1415139558510223</v>
+      </c>
+      <c r="L15" s="5" t="n">
         <v>0.389503957787889</v>
       </c>
-      <c r="K15" s="5" t="n">
+      <c r="M15" s="5" t="n">
         <v>0.08205629867681941</v>
       </c>
-      <c r="L15" s="5" t="n">
+      <c r="N15" s="5" t="n">
         <v>0.9477</v>
       </c>
-      <c r="M15" s="5" t="n">
+      <c r="O15" s="5" t="n">
         <v>0.9463</v>
       </c>
-      <c r="N15" s="5" t="n">
+      <c r="P15" s="5" t="n">
         <v>0.9223</v>
-      </c>
-      <c r="O15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" s="6" t="n">
-        <v>0</v>
       </c>
       <c r="Q15" s="6" t="n">
         <v>0</v>
@@ -1567,15 +1639,21 @@
         <v>0</v>
       </c>
       <c r="S15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="6" t="n">
         <v>0.04</v>
       </c>
-      <c r="T15" s="6" t="n">
+      <c r="V15" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="U15" s="6" t="n">
+      <c r="W15" s="6" t="n">
         <v>0.1</v>
       </c>
-      <c r="V15" s="6" t="n">
+      <c r="X15" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -1617,23 +1695,25 @@
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="5" t="inlineStr"/>
       <c r="K16" s="5" t="inlineStr"/>
-      <c r="L16" s="5" t="n">
+      <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="5" t="inlineStr"/>
+      <c r="N16" s="5" t="n">
         <v>1.0015</v>
       </c>
-      <c r="M16" s="5" t="n">
+      <c r="O16" s="5" t="n">
         <v>0.9519</v>
       </c>
-      <c r="N16" s="5" t="n">
+      <c r="P16" s="5" t="n">
         <v>0.928</v>
       </c>
-      <c r="O16" s="6" t="inlineStr"/>
-      <c r="P16" s="6" t="inlineStr"/>
       <c r="Q16" s="6" t="inlineStr"/>
       <c r="R16" s="6" t="inlineStr"/>
       <c r="S16" s="6" t="inlineStr"/>
       <c r="T16" s="6" t="inlineStr"/>
       <c r="U16" s="6" t="inlineStr"/>
       <c r="V16" s="6" t="inlineStr"/>
+      <c r="W16" s="6" t="inlineStr"/>
+      <c r="X16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1678,42 +1758,48 @@
         <v>66</v>
       </c>
       <c r="J17" s="5" t="n">
+        <v>0.3584538984210027</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>0.2739101642738966</v>
+      </c>
+      <c r="L17" s="5" t="n">
         <v>0.833539620209753</v>
       </c>
-      <c r="K17" s="5" t="n">
+      <c r="M17" s="5" t="n">
         <v>0.164192244302687</v>
       </c>
-      <c r="L17" s="5" t="n">
+      <c r="N17" s="5" t="n">
         <v>0.8584000000000001</v>
       </c>
-      <c r="M17" s="5" t="n">
+      <c r="O17" s="5" t="n">
         <v>0.8986</v>
       </c>
-      <c r="N17" s="5" t="n">
+      <c r="P17" s="5" t="n">
         <v>0.9114</v>
       </c>
-      <c r="O17" s="6" t="n">
+      <c r="Q17" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="P17" s="6" t="n">
+      <c r="R17" s="6" t="n">
         <v>0.06</v>
       </c>
-      <c r="Q17" s="6" t="n">
+      <c r="S17" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="R17" s="6" t="n">
+      <c r="T17" s="6" t="n">
         <v>0.02666666666666667</v>
       </c>
-      <c r="S17" s="6" t="n">
+      <c r="U17" s="6" t="n">
         <v>0.11</v>
       </c>
-      <c r="T17" s="6" t="n">
+      <c r="V17" s="6" t="n">
         <v>0.17</v>
       </c>
-      <c r="U17" s="6" t="n">
+      <c r="W17" s="6" t="n">
         <v>0.08</v>
       </c>
-      <c r="V17" s="6" t="n">
+      <c r="X17" s="6" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -1760,25 +1846,25 @@
         <v>66</v>
       </c>
       <c r="J18" s="5" t="n">
+        <v>0.2487248512923422</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>0.1094894731574723</v>
+      </c>
+      <c r="L18" s="5" t="n">
         <v>0.390717855103594</v>
       </c>
-      <c r="K18" s="5" t="n">
+      <c r="M18" s="5" t="n">
         <v>0.08997768712489811</v>
       </c>
-      <c r="L18" s="5" t="n">
+      <c r="N18" s="5" t="n">
         <v>0.9455</v>
       </c>
-      <c r="M18" s="5" t="n">
+      <c r="O18" s="5" t="n">
         <v>0.9402</v>
       </c>
-      <c r="N18" s="5" t="n">
+      <c r="P18" s="5" t="n">
         <v>0.922</v>
-      </c>
-      <c r="O18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" s="6" t="n">
-        <v>0</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
@@ -1787,17 +1873,23 @@
         <v>0</v>
       </c>
       <c r="S18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="6" t="n">
         <v>0.04</v>
-      </c>
-      <c r="T18" s="6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="U18" s="6" t="n">
-        <v>0.1</v>
       </c>
       <c r="V18" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
+      <c r="W18" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X18" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1841,29 +1933,33 @@
       <c r="I19" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="J19" s="5" t="n">
+      <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="n">
+        <v>0.1428920071912686</v>
+      </c>
+      <c r="L19" s="5" t="n">
         <v>0.389503957787889</v>
       </c>
-      <c r="K19" s="5" t="n">
+      <c r="M19" s="5" t="n">
         <v>0.08205629867681941</v>
       </c>
-      <c r="L19" s="5" t="n">
+      <c r="N19" s="5" t="n">
         <v>0.9477</v>
       </c>
-      <c r="M19" s="5" t="n">
+      <c r="O19" s="5" t="n">
         <v>0.9463</v>
       </c>
-      <c r="N19" s="5" t="n">
+      <c r="P19" s="5" t="n">
         <v>0.9223</v>
       </c>
-      <c r="O19" s="6" t="inlineStr"/>
-      <c r="P19" s="6" t="inlineStr"/>
       <c r="Q19" s="6" t="inlineStr"/>
       <c r="R19" s="6" t="inlineStr"/>
       <c r="S19" s="6" t="inlineStr"/>
       <c r="T19" s="6" t="inlineStr"/>
       <c r="U19" s="6" t="inlineStr"/>
       <c r="V19" s="6" t="inlineStr"/>
+      <c r="W19" s="6" t="inlineStr"/>
+      <c r="X19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1908,42 +2004,48 @@
         <v>66</v>
       </c>
       <c r="J20" s="5" t="n">
+        <v>0.3372382246917938</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>0.2486746048568231</v>
+      </c>
+      <c r="L20" s="5" t="n">
         <v>0.8554020168196</v>
       </c>
-      <c r="K20" s="5" t="n">
+      <c r="M20" s="5" t="n">
         <v>0.072415601225557</v>
       </c>
-      <c r="L20" s="5" t="n">
+      <c r="N20" s="5" t="n">
         <v>0.8506</v>
       </c>
-      <c r="M20" s="5" t="n">
+      <c r="O20" s="5" t="n">
         <v>0.8895</v>
       </c>
-      <c r="N20" s="5" t="n">
+      <c r="P20" s="5" t="n">
         <v>0.9088000000000001</v>
       </c>
-      <c r="O20" s="6" t="n">
+      <c r="Q20" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="P20" s="6" t="n">
+      <c r="R20" s="6" t="n">
         <v>0.06</v>
       </c>
-      <c r="Q20" s="6" t="n">
+      <c r="S20" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="R20" s="6" t="n">
+      <c r="T20" s="6" t="n">
         <v>0.02666666666666667</v>
       </c>
-      <c r="S20" s="6" t="n">
+      <c r="U20" s="6" t="n">
         <v>0.11</v>
       </c>
-      <c r="T20" s="6" t="n">
+      <c r="V20" s="6" t="n">
         <v>0.17</v>
       </c>
-      <c r="U20" s="6" t="n">
+      <c r="W20" s="6" t="n">
         <v>0.08</v>
       </c>
-      <c r="V20" s="6" t="n">
+      <c r="X20" s="6" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -1983,25 +2085,31 @@
         <v>241.59</v>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="5" t="inlineStr"/>
-      <c r="K21" s="5" t="inlineStr"/>
-      <c r="L21" s="5" t="n">
+      <c r="J21" s="5" t="n">
+        <v>0.07896687551826564</v>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>0.04879956378773898</v>
+      </c>
+      <c r="L21" s="5" t="inlineStr"/>
+      <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="n">
         <v>0.8856000000000001</v>
       </c>
-      <c r="M21" s="5" t="n">
+      <c r="O21" s="5" t="n">
         <v>0.9031</v>
       </c>
-      <c r="N21" s="5" t="n">
+      <c r="P21" s="5" t="n">
         <v>0.8999</v>
       </c>
-      <c r="O21" s="6" t="inlineStr"/>
-      <c r="P21" s="6" t="inlineStr"/>
       <c r="Q21" s="6" t="inlineStr"/>
       <c r="R21" s="6" t="inlineStr"/>
       <c r="S21" s="6" t="inlineStr"/>
       <c r="T21" s="6" t="inlineStr"/>
       <c r="U21" s="6" t="inlineStr"/>
       <c r="V21" s="6" t="inlineStr"/>
+      <c r="W21" s="6" t="inlineStr"/>
+      <c r="X21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2039,25 +2147,31 @@
         <v>106.6</v>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
-      <c r="L22" s="5" t="n">
+      <c r="J22" s="5" t="n">
+        <v>0.007890464523191421</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>0.005078393583182961</v>
+      </c>
+      <c r="L22" s="5" t="inlineStr"/>
+      <c r="M22" s="5" t="inlineStr"/>
+      <c r="N22" s="5" t="n">
         <v>0.9848</v>
       </c>
-      <c r="M22" s="5" t="n">
+      <c r="O22" s="5" t="n">
         <v>0.9862</v>
       </c>
-      <c r="N22" s="5" t="n">
+      <c r="P22" s="5" t="n">
         <v>0.9913999999999999</v>
       </c>
-      <c r="O22" s="6" t="inlineStr"/>
-      <c r="P22" s="6" t="inlineStr"/>
       <c r="Q22" s="6" t="inlineStr"/>
       <c r="R22" s="6" t="inlineStr"/>
       <c r="S22" s="6" t="inlineStr"/>
       <c r="T22" s="6" t="inlineStr"/>
       <c r="U22" s="6" t="inlineStr"/>
       <c r="V22" s="6" t="inlineStr"/>
+      <c r="W22" s="6" t="inlineStr"/>
+      <c r="X22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2095,25 +2209,31 @@
         <v>109</v>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
-      <c r="L23" s="5" t="n">
+      <c r="J23" s="5" t="n">
+        <v>0.228198922467751</v>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>0.2029431742155934</v>
+      </c>
+      <c r="L23" s="5" t="inlineStr"/>
+      <c r="M23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="n">
         <v>0.9315</v>
       </c>
-      <c r="M23" s="5" t="n">
+      <c r="O23" s="5" t="n">
         <v>0.9465</v>
       </c>
-      <c r="N23" s="5" t="n">
+      <c r="P23" s="5" t="n">
         <v>0.945</v>
       </c>
-      <c r="O23" s="6" t="inlineStr"/>
-      <c r="P23" s="6" t="inlineStr"/>
       <c r="Q23" s="6" t="inlineStr"/>
       <c r="R23" s="6" t="inlineStr"/>
       <c r="S23" s="6" t="inlineStr"/>
       <c r="T23" s="6" t="inlineStr"/>
       <c r="U23" s="6" t="inlineStr"/>
       <c r="V23" s="6" t="inlineStr"/>
+      <c r="W23" s="6" t="inlineStr"/>
+      <c r="X23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2151,25 +2271,31 @@
         <v>180.6</v>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
-      <c r="L24" s="5" t="n">
+      <c r="J24" s="5" t="n">
+        <v>0.04586386696325562</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>0.03247885424318653</v>
+      </c>
+      <c r="L24" s="5" t="inlineStr"/>
+      <c r="M24" s="5" t="inlineStr"/>
+      <c r="N24" s="5" t="n">
         <v>0.9315</v>
       </c>
-      <c r="M24" s="5" t="n">
+      <c r="O24" s="5" t="n">
         <v>0.9465</v>
       </c>
-      <c r="N24" s="5" t="n">
+      <c r="P24" s="5" t="n">
         <v>0.945</v>
       </c>
-      <c r="O24" s="6" t="inlineStr"/>
-      <c r="P24" s="6" t="inlineStr"/>
       <c r="Q24" s="6" t="inlineStr"/>
       <c r="R24" s="6" t="inlineStr"/>
       <c r="S24" s="6" t="inlineStr"/>
       <c r="T24" s="6" t="inlineStr"/>
       <c r="U24" s="6" t="inlineStr"/>
       <c r="V24" s="6" t="inlineStr"/>
+      <c r="W24" s="6" t="inlineStr"/>
+      <c r="X24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2207,25 +2333,31 @@
         <v>204</v>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="5" t="inlineStr"/>
-      <c r="K25" s="5" t="inlineStr"/>
-      <c r="L25" s="5" t="n">
+      <c r="J25" s="5" t="n">
+        <v>0.03468796155479126</v>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>0.02811506234350913</v>
+      </c>
+      <c r="L25" s="5" t="inlineStr"/>
+      <c r="M25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="n">
         <v>0.8733</v>
       </c>
-      <c r="M25" s="5" t="n">
+      <c r="O25" s="5" t="n">
         <v>0.8907</v>
       </c>
-      <c r="N25" s="5" t="n">
+      <c r="P25" s="5" t="n">
         <v>0.89</v>
       </c>
-      <c r="O25" s="6" t="inlineStr"/>
-      <c r="P25" s="6" t="inlineStr"/>
       <c r="Q25" s="6" t="inlineStr"/>
       <c r="R25" s="6" t="inlineStr"/>
       <c r="S25" s="6" t="inlineStr"/>
       <c r="T25" s="6" t="inlineStr"/>
       <c r="U25" s="6" t="inlineStr"/>
       <c r="V25" s="6" t="inlineStr"/>
+      <c r="W25" s="6" t="inlineStr"/>
+      <c r="X25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2265,23 +2397,25 @@
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="5" t="inlineStr"/>
       <c r="K26" s="5" t="inlineStr"/>
-      <c r="L26" s="5" t="n">
+      <c r="L26" s="5" t="inlineStr"/>
+      <c r="M26" s="5" t="inlineStr"/>
+      <c r="N26" s="5" t="n">
         <v>0.9718</v>
       </c>
-      <c r="M26" s="5" t="n">
+      <c r="O26" s="5" t="n">
         <v>0.9825</v>
       </c>
-      <c r="N26" s="5" t="n">
+      <c r="P26" s="5" t="n">
         <v>0.9801</v>
       </c>
-      <c r="O26" s="6" t="inlineStr"/>
-      <c r="P26" s="6" t="inlineStr"/>
       <c r="Q26" s="6" t="inlineStr"/>
       <c r="R26" s="6" t="inlineStr"/>
       <c r="S26" s="6" t="inlineStr"/>
       <c r="T26" s="6" t="inlineStr"/>
       <c r="U26" s="6" t="inlineStr"/>
       <c r="V26" s="6" t="inlineStr"/>
+      <c r="W26" s="6" t="inlineStr"/>
+      <c r="X26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2321,21 +2455,23 @@
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="5" t="inlineStr"/>
       <c r="K27" s="5" t="inlineStr"/>
-      <c r="L27" s="5" t="n">
+      <c r="L27" s="5" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="n">
         <v>0.9718</v>
       </c>
-      <c r="M27" s="5" t="n">
+      <c r="O27" s="5" t="n">
         <v>0.9825</v>
       </c>
-      <c r="N27" s="5" t="inlineStr"/>
-      <c r="O27" s="6" t="inlineStr"/>
-      <c r="P27" s="6" t="inlineStr"/>
+      <c r="P27" s="5" t="inlineStr"/>
       <c r="Q27" s="6" t="inlineStr"/>
       <c r="R27" s="6" t="inlineStr"/>
       <c r="S27" s="6" t="inlineStr"/>
       <c r="T27" s="6" t="inlineStr"/>
       <c r="U27" s="6" t="inlineStr"/>
       <c r="V27" s="6" t="inlineStr"/>
+      <c r="W27" s="6" t="inlineStr"/>
+      <c r="X27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2373,25 +2509,31 @@
         <v>57.6</v>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
-      <c r="L28" s="5" t="n">
+      <c r="J28" s="5" t="n">
+        <v>0.06000630720703115</v>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>0.0990364762086815</v>
+      </c>
+      <c r="L28" s="5" t="inlineStr"/>
+      <c r="M28" s="5" t="inlineStr"/>
+      <c r="N28" s="5" t="n">
         <v>0.9976</v>
       </c>
-      <c r="M28" s="5" t="n">
+      <c r="O28" s="5" t="n">
         <v>0.998</v>
       </c>
-      <c r="N28" s="5" t="n">
+      <c r="P28" s="5" t="n">
         <v>0.9978</v>
       </c>
-      <c r="O28" s="6" t="inlineStr"/>
-      <c r="P28" s="6" t="inlineStr"/>
       <c r="Q28" s="6" t="inlineStr"/>
       <c r="R28" s="6" t="inlineStr"/>
       <c r="S28" s="6" t="inlineStr"/>
       <c r="T28" s="6" t="inlineStr"/>
       <c r="U28" s="6" t="inlineStr"/>
       <c r="V28" s="6" t="inlineStr"/>
+      <c r="W28" s="6" t="inlineStr"/>
+      <c r="X28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2431,23 +2573,25 @@
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="5" t="inlineStr"/>
       <c r="K29" s="5" t="inlineStr"/>
-      <c r="L29" s="5" t="n">
+      <c r="L29" s="5" t="inlineStr"/>
+      <c r="M29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="n">
         <v>0.9993</v>
       </c>
-      <c r="M29" s="5" t="n">
+      <c r="O29" s="5" t="n">
         <v>1.0018</v>
       </c>
-      <c r="N29" s="5" t="n">
+      <c r="P29" s="5" t="n">
         <v>0.9952</v>
       </c>
-      <c r="O29" s="6" t="inlineStr"/>
-      <c r="P29" s="6" t="inlineStr"/>
       <c r="Q29" s="6" t="inlineStr"/>
       <c r="R29" s="6" t="inlineStr"/>
       <c r="S29" s="6" t="inlineStr"/>
       <c r="T29" s="6" t="inlineStr"/>
       <c r="U29" s="6" t="inlineStr"/>
       <c r="V29" s="6" t="inlineStr"/>
+      <c r="W29" s="6" t="inlineStr"/>
+      <c r="X29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2487,23 +2631,25 @@
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="5" t="inlineStr"/>
       <c r="K30" s="5" t="inlineStr"/>
-      <c r="L30" s="5" t="n">
+      <c r="L30" s="5" t="inlineStr"/>
+      <c r="M30" s="5" t="inlineStr"/>
+      <c r="N30" s="5" t="n">
         <v>1.0072</v>
       </c>
-      <c r="M30" s="5" t="n">
+      <c r="O30" s="5" t="n">
         <v>1.0166</v>
       </c>
-      <c r="N30" s="5" t="n">
+      <c r="P30" s="5" t="n">
         <v>1.0065</v>
       </c>
-      <c r="O30" s="6" t="inlineStr"/>
-      <c r="P30" s="6" t="inlineStr"/>
       <c r="Q30" s="6" t="inlineStr"/>
       <c r="R30" s="6" t="inlineStr"/>
       <c r="S30" s="6" t="inlineStr"/>
       <c r="T30" s="6" t="inlineStr"/>
       <c r="U30" s="6" t="inlineStr"/>
       <c r="V30" s="6" t="inlineStr"/>
+      <c r="W30" s="6" t="inlineStr"/>
+      <c r="X30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2541,25 +2687,31 @@
         <v>79.95</v>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="5" t="inlineStr"/>
-      <c r="K31" s="5" t="inlineStr"/>
-      <c r="L31" s="5" t="n">
+      <c r="J31" s="5" t="n">
+        <v>0.05765254706148304</v>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>0.07617724801951264</v>
+      </c>
+      <c r="L31" s="5" t="inlineStr"/>
+      <c r="M31" s="5" t="inlineStr"/>
+      <c r="N31" s="5" t="n">
         <v>0.8833</v>
       </c>
-      <c r="M31" s="5" t="n">
+      <c r="O31" s="5" t="n">
         <v>0.9004</v>
       </c>
-      <c r="N31" s="5" t="n">
+      <c r="P31" s="5" t="n">
         <v>0.9</v>
       </c>
-      <c r="O31" s="6" t="inlineStr"/>
-      <c r="P31" s="6" t="inlineStr"/>
       <c r="Q31" s="6" t="inlineStr"/>
       <c r="R31" s="6" t="inlineStr"/>
       <c r="S31" s="6" t="inlineStr"/>
       <c r="T31" s="6" t="inlineStr"/>
       <c r="U31" s="6" t="inlineStr"/>
       <c r="V31" s="6" t="inlineStr"/>
+      <c r="W31" s="6" t="inlineStr"/>
+      <c r="X31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2599,23 +2751,25 @@
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="5" t="inlineStr"/>
       <c r="K32" s="5" t="inlineStr"/>
-      <c r="L32" s="5" t="n">
+      <c r="L32" s="5" t="inlineStr"/>
+      <c r="M32" s="5" t="inlineStr"/>
+      <c r="N32" s="5" t="n">
         <v>0.8733</v>
       </c>
-      <c r="M32" s="5" t="n">
+      <c r="O32" s="5" t="n">
         <v>0.8959</v>
       </c>
-      <c r="N32" s="5" t="n">
+      <c r="P32" s="5" t="n">
         <v>0.901</v>
       </c>
-      <c r="O32" s="6" t="inlineStr"/>
-      <c r="P32" s="6" t="inlineStr"/>
       <c r="Q32" s="6" t="inlineStr"/>
       <c r="R32" s="6" t="inlineStr"/>
       <c r="S32" s="6" t="inlineStr"/>
       <c r="T32" s="6" t="inlineStr"/>
       <c r="U32" s="6" t="inlineStr"/>
       <c r="V32" s="6" t="inlineStr"/>
+      <c r="W32" s="6" t="inlineStr"/>
+      <c r="X32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2653,25 +2807,31 @@
         <v>168</v>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="5" t="inlineStr"/>
-      <c r="K33" s="5" t="inlineStr"/>
-      <c r="L33" s="5" t="n">
+      <c r="J33" s="5" t="n">
+        <v>0.1090852472782988</v>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>0.1329011055420474</v>
+      </c>
+      <c r="L33" s="5" t="inlineStr"/>
+      <c r="M33" s="5" t="inlineStr"/>
+      <c r="N33" s="5" t="n">
         <v>0.981</v>
       </c>
-      <c r="M33" s="5" t="n">
+      <c r="O33" s="5" t="n">
         <v>0.9845</v>
       </c>
-      <c r="N33" s="5" t="n">
+      <c r="P33" s="5" t="n">
         <v>0.9833</v>
       </c>
-      <c r="O33" s="6" t="inlineStr"/>
-      <c r="P33" s="6" t="inlineStr"/>
       <c r="Q33" s="6" t="inlineStr"/>
       <c r="R33" s="6" t="inlineStr"/>
       <c r="S33" s="6" t="inlineStr"/>
       <c r="T33" s="6" t="inlineStr"/>
       <c r="U33" s="6" t="inlineStr"/>
       <c r="V33" s="6" t="inlineStr"/>
+      <c r="W33" s="6" t="inlineStr"/>
+      <c r="X33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2709,25 +2869,31 @@
         <v>46</v>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="5" t="inlineStr"/>
-      <c r="K34" s="5" t="inlineStr"/>
-      <c r="L34" s="5" t="n">
+      <c r="J34" s="5" t="n">
+        <v>0.07673420102808481</v>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>0.04879482272464053</v>
+      </c>
+      <c r="L34" s="5" t="inlineStr"/>
+      <c r="M34" s="5" t="inlineStr"/>
+      <c r="N34" s="5" t="n">
         <v>0.981</v>
       </c>
-      <c r="M34" s="5" t="n">
+      <c r="O34" s="5" t="n">
         <v>0.9845</v>
       </c>
-      <c r="N34" s="5" t="n">
+      <c r="P34" s="5" t="n">
         <v>0.9833</v>
       </c>
-      <c r="O34" s="6" t="inlineStr"/>
-      <c r="P34" s="6" t="inlineStr"/>
       <c r="Q34" s="6" t="inlineStr"/>
       <c r="R34" s="6" t="inlineStr"/>
       <c r="S34" s="6" t="inlineStr"/>
       <c r="T34" s="6" t="inlineStr"/>
       <c r="U34" s="6" t="inlineStr"/>
       <c r="V34" s="6" t="inlineStr"/>
+      <c r="W34" s="6" t="inlineStr"/>
+      <c r="X34" s="6" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2765,25 +2931,31 @@
         <v>121</v>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="5" t="inlineStr"/>
-      <c r="K35" s="5" t="inlineStr"/>
-      <c r="L35" s="5" t="n">
+      <c r="J35" s="5" t="n">
+        <v>0.08376688909880559</v>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>0.03441493291566089</v>
+      </c>
+      <c r="L35" s="5" t="inlineStr"/>
+      <c r="M35" s="5" t="inlineStr"/>
+      <c r="N35" s="5" t="n">
         <v>0.981</v>
       </c>
-      <c r="M35" s="5" t="n">
+      <c r="O35" s="5" t="n">
         <v>0.9845</v>
       </c>
-      <c r="N35" s="5" t="n">
+      <c r="P35" s="5" t="n">
         <v>0.9833</v>
       </c>
-      <c r="O35" s="6" t="inlineStr"/>
-      <c r="P35" s="6" t="inlineStr"/>
       <c r="Q35" s="6" t="inlineStr"/>
       <c r="R35" s="6" t="inlineStr"/>
       <c r="S35" s="6" t="inlineStr"/>
       <c r="T35" s="6" t="inlineStr"/>
       <c r="U35" s="6" t="inlineStr"/>
       <c r="V35" s="6" t="inlineStr"/>
+      <c r="W35" s="6" t="inlineStr"/>
+      <c r="X35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2821,25 +2993,31 @@
         <v>83.59999999999999</v>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="5" t="inlineStr"/>
-      <c r="K36" s="5" t="inlineStr"/>
-      <c r="L36" s="5" t="n">
+      <c r="J36" s="5" t="n">
+        <v>0.165261756131016</v>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>0.1792215413644107</v>
+      </c>
+      <c r="L36" s="5" t="inlineStr"/>
+      <c r="M36" s="5" t="inlineStr"/>
+      <c r="N36" s="5" t="n">
         <v>0.9475</v>
       </c>
-      <c r="M36" s="5" t="n">
+      <c r="O36" s="5" t="n">
         <v>0.9569</v>
       </c>
-      <c r="N36" s="5" t="n">
+      <c r="P36" s="5" t="n">
         <v>0.9569</v>
       </c>
-      <c r="O36" s="6" t="inlineStr"/>
-      <c r="P36" s="6" t="inlineStr"/>
       <c r="Q36" s="6" t="inlineStr"/>
       <c r="R36" s="6" t="inlineStr"/>
       <c r="S36" s="6" t="inlineStr"/>
       <c r="T36" s="6" t="inlineStr"/>
       <c r="U36" s="6" t="inlineStr"/>
       <c r="V36" s="6" t="inlineStr"/>
+      <c r="W36" s="6" t="inlineStr"/>
+      <c r="X36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2879,19 +3057,21 @@
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="5" t="inlineStr"/>
       <c r="K37" s="5" t="inlineStr"/>
-      <c r="L37" s="5" t="n">
+      <c r="L37" s="5" t="inlineStr"/>
+      <c r="M37" s="5" t="inlineStr"/>
+      <c r="N37" s="5" t="n">
         <v>0.9993</v>
       </c>
-      <c r="M37" s="5" t="inlineStr"/>
-      <c r="N37" s="5" t="inlineStr"/>
-      <c r="O37" s="6" t="inlineStr"/>
-      <c r="P37" s="6" t="inlineStr"/>
+      <c r="O37" s="5" t="inlineStr"/>
+      <c r="P37" s="5" t="inlineStr"/>
       <c r="Q37" s="6" t="inlineStr"/>
       <c r="R37" s="6" t="inlineStr"/>
       <c r="S37" s="6" t="inlineStr"/>
       <c r="T37" s="6" t="inlineStr"/>
       <c r="U37" s="6" t="inlineStr"/>
       <c r="V37" s="6" t="inlineStr"/>
+      <c r="W37" s="6" t="inlineStr"/>
+      <c r="X37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2931,23 +3111,25 @@
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="5" t="inlineStr"/>
       <c r="K38" s="5" t="inlineStr"/>
-      <c r="L38" s="5" t="n">
+      <c r="L38" s="5" t="inlineStr"/>
+      <c r="M38" s="5" t="inlineStr"/>
+      <c r="N38" s="5" t="n">
         <v>0.9993</v>
       </c>
-      <c r="M38" s="5" t="n">
+      <c r="O38" s="5" t="n">
         <v>1.0018</v>
       </c>
-      <c r="N38" s="5" t="n">
+      <c r="P38" s="5" t="n">
         <v>0.9952</v>
       </c>
-      <c r="O38" s="6" t="inlineStr"/>
-      <c r="P38" s="6" t="inlineStr"/>
       <c r="Q38" s="6" t="inlineStr"/>
       <c r="R38" s="6" t="inlineStr"/>
       <c r="S38" s="6" t="inlineStr"/>
       <c r="T38" s="6" t="inlineStr"/>
       <c r="U38" s="6" t="inlineStr"/>
       <c r="V38" s="6" t="inlineStr"/>
+      <c r="W38" s="6" t="inlineStr"/>
+      <c r="X38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2986,24 +3168,28 @@
       </c>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="5" t="inlineStr"/>
-      <c r="K39" s="5" t="inlineStr"/>
-      <c r="L39" s="5" t="n">
+      <c r="K39" s="5" t="n">
+        <v>0.08800887843952154</v>
+      </c>
+      <c r="L39" s="5" t="inlineStr"/>
+      <c r="M39" s="5" t="inlineStr"/>
+      <c r="N39" s="5" t="n">
         <v>0.9808</v>
       </c>
-      <c r="M39" s="5" t="n">
+      <c r="O39" s="5" t="n">
         <v>0.9834000000000001</v>
       </c>
-      <c r="N39" s="5" t="n">
+      <c r="P39" s="5" t="n">
         <v>0.9819</v>
       </c>
-      <c r="O39" s="6" t="inlineStr"/>
-      <c r="P39" s="6" t="inlineStr"/>
       <c r="Q39" s="6" t="inlineStr"/>
       <c r="R39" s="6" t="inlineStr"/>
       <c r="S39" s="6" t="inlineStr"/>
       <c r="T39" s="6" t="inlineStr"/>
       <c r="U39" s="6" t="inlineStr"/>
       <c r="V39" s="6" t="inlineStr"/>
+      <c r="W39" s="6" t="inlineStr"/>
+      <c r="X39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3042,24 +3228,28 @@
       </c>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="5" t="inlineStr"/>
-      <c r="K40" s="5" t="inlineStr"/>
-      <c r="L40" s="5" t="n">
+      <c r="K40" s="5" t="n">
+        <v>0.1119293945604837</v>
+      </c>
+      <c r="L40" s="5" t="inlineStr"/>
+      <c r="M40" s="5" t="inlineStr"/>
+      <c r="N40" s="5" t="n">
         <v>0.9808</v>
       </c>
-      <c r="M40" s="5" t="n">
+      <c r="O40" s="5" t="n">
         <v>0.9834000000000001</v>
       </c>
-      <c r="N40" s="5" t="n">
+      <c r="P40" s="5" t="n">
         <v>0.9819</v>
       </c>
-      <c r="O40" s="6" t="inlineStr"/>
-      <c r="P40" s="6" t="inlineStr"/>
       <c r="Q40" s="6" t="inlineStr"/>
       <c r="R40" s="6" t="inlineStr"/>
       <c r="S40" s="6" t="inlineStr"/>
       <c r="T40" s="6" t="inlineStr"/>
       <c r="U40" s="6" t="inlineStr"/>
       <c r="V40" s="6" t="inlineStr"/>
+      <c r="W40" s="6" t="inlineStr"/>
+      <c r="X40" s="6" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -3098,24 +3288,28 @@
       </c>
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="5" t="inlineStr"/>
-      <c r="K41" s="5" t="inlineStr"/>
-      <c r="L41" s="5" t="n">
+      <c r="K41" s="5" t="n">
+        <v>0.0123018750239543</v>
+      </c>
+      <c r="L41" s="5" t="inlineStr"/>
+      <c r="M41" s="5" t="inlineStr"/>
+      <c r="N41" s="5" t="n">
         <v>0.9808</v>
       </c>
-      <c r="M41" s="5" t="n">
+      <c r="O41" s="5" t="n">
         <v>0.9834000000000001</v>
       </c>
-      <c r="N41" s="5" t="n">
+      <c r="P41" s="5" t="n">
         <v>0.9819</v>
       </c>
-      <c r="O41" s="6" t="inlineStr"/>
-      <c r="P41" s="6" t="inlineStr"/>
       <c r="Q41" s="6" t="inlineStr"/>
       <c r="R41" s="6" t="inlineStr"/>
       <c r="S41" s="6" t="inlineStr"/>
       <c r="T41" s="6" t="inlineStr"/>
       <c r="U41" s="6" t="inlineStr"/>
       <c r="V41" s="6" t="inlineStr"/>
+      <c r="W41" s="6" t="inlineStr"/>
+      <c r="X41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -3156,20 +3350,22 @@
       <c r="J42" s="5" t="inlineStr"/>
       <c r="K42" s="5" t="inlineStr"/>
       <c r="L42" s="5" t="inlineStr"/>
-      <c r="M42" s="5" t="n">
+      <c r="M42" s="5" t="inlineStr"/>
+      <c r="N42" s="5" t="inlineStr"/>
+      <c r="O42" s="5" t="n">
         <v>0.9837</v>
       </c>
-      <c r="N42" s="5" t="n">
+      <c r="P42" s="5" t="n">
         <v>0.9824000000000001</v>
       </c>
-      <c r="O42" s="6" t="inlineStr"/>
-      <c r="P42" s="6" t="inlineStr"/>
       <c r="Q42" s="6" t="inlineStr"/>
       <c r="R42" s="6" t="inlineStr"/>
       <c r="S42" s="6" t="inlineStr"/>
       <c r="T42" s="6" t="inlineStr"/>
       <c r="U42" s="6" t="inlineStr"/>
       <c r="V42" s="6" t="inlineStr"/>
+      <c r="W42" s="6" t="inlineStr"/>
+      <c r="X42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3210,20 +3406,22 @@
       <c r="J43" s="5" t="inlineStr"/>
       <c r="K43" s="5" t="inlineStr"/>
       <c r="L43" s="5" t="inlineStr"/>
-      <c r="M43" s="5" t="n">
+      <c r="M43" s="5" t="inlineStr"/>
+      <c r="N43" s="5" t="inlineStr"/>
+      <c r="O43" s="5" t="n">
         <v>0.9837</v>
       </c>
-      <c r="N43" s="5" t="n">
+      <c r="P43" s="5" t="n">
         <v>0.9824000000000001</v>
       </c>
-      <c r="O43" s="6" t="inlineStr"/>
-      <c r="P43" s="6" t="inlineStr"/>
       <c r="Q43" s="6" t="inlineStr"/>
       <c r="R43" s="6" t="inlineStr"/>
       <c r="S43" s="6" t="inlineStr"/>
       <c r="T43" s="6" t="inlineStr"/>
       <c r="U43" s="6" t="inlineStr"/>
       <c r="V43" s="6" t="inlineStr"/>
+      <c r="W43" s="6" t="inlineStr"/>
+      <c r="X43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3261,25 +3459,31 @@
         <v>96.59999999999999</v>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="5" t="inlineStr"/>
-      <c r="K44" s="5" t="inlineStr"/>
-      <c r="L44" s="5" t="n">
+      <c r="J44" s="5" t="n">
+        <v>0.006730440322401998</v>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>0.1828368307734174</v>
+      </c>
+      <c r="L44" s="5" t="inlineStr"/>
+      <c r="M44" s="5" t="inlineStr"/>
+      <c r="N44" s="5" t="n">
         <v>0.9809</v>
       </c>
-      <c r="M44" s="5" t="n">
+      <c r="O44" s="5" t="n">
         <v>0.9865</v>
       </c>
-      <c r="N44" s="5" t="n">
+      <c r="P44" s="5" t="n">
         <v>0.9829</v>
       </c>
-      <c r="O44" s="6" t="inlineStr"/>
-      <c r="P44" s="6" t="inlineStr"/>
       <c r="Q44" s="6" t="inlineStr"/>
       <c r="R44" s="6" t="inlineStr"/>
       <c r="S44" s="6" t="inlineStr"/>
       <c r="T44" s="6" t="inlineStr"/>
       <c r="U44" s="6" t="inlineStr"/>
       <c r="V44" s="6" t="inlineStr"/>
+      <c r="W44" s="6" t="inlineStr"/>
+      <c r="X44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3319,23 +3523,25 @@
       <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="5" t="inlineStr"/>
       <c r="K45" s="5" t="inlineStr"/>
-      <c r="L45" s="5" t="n">
+      <c r="L45" s="5" t="inlineStr"/>
+      <c r="M45" s="5" t="inlineStr"/>
+      <c r="N45" s="5" t="n">
         <v>0.9718</v>
       </c>
-      <c r="M45" s="5" t="n">
+      <c r="O45" s="5" t="n">
         <v>0.9825</v>
       </c>
-      <c r="N45" s="5" t="n">
+      <c r="P45" s="5" t="n">
         <v>0.9801</v>
       </c>
-      <c r="O45" s="6" t="inlineStr"/>
-      <c r="P45" s="6" t="inlineStr"/>
       <c r="Q45" s="6" t="inlineStr"/>
       <c r="R45" s="6" t="inlineStr"/>
       <c r="S45" s="6" t="inlineStr"/>
       <c r="T45" s="6" t="inlineStr"/>
       <c r="U45" s="6" t="inlineStr"/>
       <c r="V45" s="6" t="inlineStr"/>
+      <c r="W45" s="6" t="inlineStr"/>
+      <c r="X45" s="6" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3373,25 +3579,31 @@
         <v>31.05</v>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="5" t="inlineStr"/>
-      <c r="K46" s="5" t="inlineStr"/>
-      <c r="L46" s="5" t="n">
+      <c r="J46" s="5" t="n">
+        <v>0.1118721818565486</v>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>0.178900785388332</v>
+      </c>
+      <c r="L46" s="5" t="inlineStr"/>
+      <c r="M46" s="5" t="inlineStr"/>
+      <c r="N46" s="5" t="n">
         <v>0.8733</v>
       </c>
-      <c r="M46" s="5" t="n">
+      <c r="O46" s="5" t="n">
         <v>0.8959</v>
       </c>
-      <c r="N46" s="5" t="n">
+      <c r="P46" s="5" t="n">
         <v>0.901</v>
       </c>
-      <c r="O46" s="6" t="inlineStr"/>
-      <c r="P46" s="6" t="inlineStr"/>
       <c r="Q46" s="6" t="inlineStr"/>
       <c r="R46" s="6" t="inlineStr"/>
       <c r="S46" s="6" t="inlineStr"/>
       <c r="T46" s="6" t="inlineStr"/>
       <c r="U46" s="6" t="inlineStr"/>
       <c r="V46" s="6" t="inlineStr"/>
+      <c r="W46" s="6" t="inlineStr"/>
+      <c r="X46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3429,25 +3641,31 @@
         <v>420</v>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="5" t="inlineStr"/>
-      <c r="K47" s="5" t="inlineStr"/>
-      <c r="L47" s="5" t="n">
+      <c r="J47" s="5" t="n">
+        <v>0.07862362779385146</v>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>0.1393456838590317</v>
+      </c>
+      <c r="L47" s="5" t="inlineStr"/>
+      <c r="M47" s="5" t="inlineStr"/>
+      <c r="N47" s="5" t="n">
         <v>0.9781</v>
       </c>
-      <c r="M47" s="5" t="n">
+      <c r="O47" s="5" t="n">
         <v>0.9829</v>
       </c>
-      <c r="N47" s="5" t="n">
+      <c r="P47" s="5" t="n">
         <v>0.983</v>
       </c>
-      <c r="O47" s="6" t="inlineStr"/>
-      <c r="P47" s="6" t="inlineStr"/>
       <c r="Q47" s="6" t="inlineStr"/>
       <c r="R47" s="6" t="inlineStr"/>
       <c r="S47" s="6" t="inlineStr"/>
       <c r="T47" s="6" t="inlineStr"/>
       <c r="U47" s="6" t="inlineStr"/>
       <c r="V47" s="6" t="inlineStr"/>
+      <c r="W47" s="6" t="inlineStr"/>
+      <c r="X47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3487,23 +3705,25 @@
       <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="5" t="inlineStr"/>
       <c r="K48" s="5" t="inlineStr"/>
-      <c r="L48" s="5" t="n">
+      <c r="L48" s="5" t="inlineStr"/>
+      <c r="M48" s="5" t="inlineStr"/>
+      <c r="N48" s="5" t="n">
         <v>0.9718</v>
       </c>
-      <c r="M48" s="5" t="n">
+      <c r="O48" s="5" t="n">
         <v>0.9825</v>
       </c>
-      <c r="N48" s="5" t="n">
+      <c r="P48" s="5" t="n">
         <v>0.9801</v>
       </c>
-      <c r="O48" s="6" t="inlineStr"/>
-      <c r="P48" s="6" t="inlineStr"/>
       <c r="Q48" s="6" t="inlineStr"/>
       <c r="R48" s="6" t="inlineStr"/>
       <c r="S48" s="6" t="inlineStr"/>
       <c r="T48" s="6" t="inlineStr"/>
       <c r="U48" s="6" t="inlineStr"/>
       <c r="V48" s="6" t="inlineStr"/>
+      <c r="W48" s="6" t="inlineStr"/>
+      <c r="X48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -3541,25 +3761,31 @@
         <v>312</v>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="5" t="inlineStr"/>
-      <c r="K49" s="5" t="inlineStr"/>
-      <c r="L49" s="5" t="n">
+      <c r="J49" s="5" t="n">
+        <v>0.09237139852010201</v>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>0.09029336657571219</v>
+      </c>
+      <c r="L49" s="5" t="inlineStr"/>
+      <c r="M49" s="5" t="inlineStr"/>
+      <c r="N49" s="5" t="n">
         <v>0.9475</v>
       </c>
-      <c r="M49" s="5" t="n">
+      <c r="O49" s="5" t="n">
         <v>0.9569</v>
       </c>
-      <c r="N49" s="5" t="n">
+      <c r="P49" s="5" t="n">
         <v>0.9569</v>
       </c>
-      <c r="O49" s="6" t="inlineStr"/>
-      <c r="P49" s="6" t="inlineStr"/>
       <c r="Q49" s="6" t="inlineStr"/>
       <c r="R49" s="6" t="inlineStr"/>
       <c r="S49" s="6" t="inlineStr"/>
       <c r="T49" s="6" t="inlineStr"/>
       <c r="U49" s="6" t="inlineStr"/>
       <c r="V49" s="6" t="inlineStr"/>
+      <c r="W49" s="6" t="inlineStr"/>
+      <c r="X49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3597,25 +3823,31 @@
         <v>157.5</v>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="5" t="inlineStr"/>
-      <c r="K50" s="5" t="inlineStr"/>
-      <c r="L50" s="5" t="n">
+      <c r="J50" s="5" t="n">
+        <v>0.1347524443952343</v>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>0.1060249296605559</v>
+      </c>
+      <c r="L50" s="5" t="inlineStr"/>
+      <c r="M50" s="5" t="inlineStr"/>
+      <c r="N50" s="5" t="n">
         <v>0.9429999999999999</v>
       </c>
-      <c r="M50" s="5" t="n">
+      <c r="O50" s="5" t="n">
         <v>0.9525</v>
       </c>
-      <c r="N50" s="5" t="n">
+      <c r="P50" s="5" t="n">
         <v>0.9519</v>
       </c>
-      <c r="O50" s="6" t="inlineStr"/>
-      <c r="P50" s="6" t="inlineStr"/>
       <c r="Q50" s="6" t="inlineStr"/>
       <c r="R50" s="6" t="inlineStr"/>
       <c r="S50" s="6" t="inlineStr"/>
       <c r="T50" s="6" t="inlineStr"/>
       <c r="U50" s="6" t="inlineStr"/>
       <c r="V50" s="6" t="inlineStr"/>
+      <c r="W50" s="6" t="inlineStr"/>
+      <c r="X50" s="6" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3655,23 +3887,25 @@
       <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="5" t="inlineStr"/>
       <c r="K51" s="5" t="inlineStr"/>
-      <c r="L51" s="5" t="n">
+      <c r="L51" s="5" t="inlineStr"/>
+      <c r="M51" s="5" t="inlineStr"/>
+      <c r="N51" s="5" t="n">
         <v>0.9993</v>
       </c>
-      <c r="M51" s="5" t="n">
+      <c r="O51" s="5" t="n">
         <v>1.0018</v>
       </c>
-      <c r="N51" s="5" t="n">
+      <c r="P51" s="5" t="n">
         <v>0.9952</v>
       </c>
-      <c r="O51" s="6" t="inlineStr"/>
-      <c r="P51" s="6" t="inlineStr"/>
       <c r="Q51" s="6" t="inlineStr"/>
       <c r="R51" s="6" t="inlineStr"/>
       <c r="S51" s="6" t="inlineStr"/>
       <c r="T51" s="6" t="inlineStr"/>
       <c r="U51" s="6" t="inlineStr"/>
       <c r="V51" s="6" t="inlineStr"/>
+      <c r="W51" s="6" t="inlineStr"/>
+      <c r="X51" s="6" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3709,25 +3943,31 @@
         <v>138</v>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="5" t="inlineStr"/>
-      <c r="K52" s="5" t="inlineStr"/>
-      <c r="L52" s="5" t="n">
+      <c r="J52" s="5" t="n">
+        <v>0.05030984963358887</v>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>0.0523074239242165</v>
+      </c>
+      <c r="L52" s="5" t="inlineStr"/>
+      <c r="M52" s="5" t="inlineStr"/>
+      <c r="N52" s="5" t="n">
         <v>0.9855</v>
       </c>
-      <c r="M52" s="5" t="n">
+      <c r="O52" s="5" t="n">
         <v>0.9879</v>
       </c>
-      <c r="N52" s="5" t="n">
+      <c r="P52" s="5" t="n">
         <v>0.9893999999999999</v>
       </c>
-      <c r="O52" s="6" t="inlineStr"/>
-      <c r="P52" s="6" t="inlineStr"/>
       <c r="Q52" s="6" t="inlineStr"/>
       <c r="R52" s="6" t="inlineStr"/>
       <c r="S52" s="6" t="inlineStr"/>
       <c r="T52" s="6" t="inlineStr"/>
       <c r="U52" s="6" t="inlineStr"/>
       <c r="V52" s="6" t="inlineStr"/>
+      <c r="W52" s="6" t="inlineStr"/>
+      <c r="X52" s="6" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -3765,25 +4005,31 @@
         <v>131.2</v>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="5" t="inlineStr"/>
-      <c r="K53" s="5" t="inlineStr"/>
-      <c r="L53" s="5" t="n">
+      <c r="J53" s="5" t="n">
+        <v>0.1905628760534537</v>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>0.2791924245645767</v>
+      </c>
+      <c r="L53" s="5" t="inlineStr"/>
+      <c r="M53" s="5" t="inlineStr"/>
+      <c r="N53" s="5" t="n">
         <v>0.9475</v>
       </c>
-      <c r="M53" s="5" t="n">
+      <c r="O53" s="5" t="n">
         <v>0.9569</v>
       </c>
-      <c r="N53" s="5" t="n">
+      <c r="P53" s="5" t="n">
         <v>0.9569</v>
       </c>
-      <c r="O53" s="6" t="inlineStr"/>
-      <c r="P53" s="6" t="inlineStr"/>
       <c r="Q53" s="6" t="inlineStr"/>
       <c r="R53" s="6" t="inlineStr"/>
       <c r="S53" s="6" t="inlineStr"/>
       <c r="T53" s="6" t="inlineStr"/>
       <c r="U53" s="6" t="inlineStr"/>
       <c r="V53" s="6" t="inlineStr"/>
+      <c r="W53" s="6" t="inlineStr"/>
+      <c r="X53" s="6" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -3821,25 +4067,31 @@
         <v>231.8</v>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="5" t="inlineStr"/>
-      <c r="K54" s="5" t="inlineStr"/>
-      <c r="L54" s="5" t="n">
+      <c r="J54" s="5" t="n">
+        <v>0.1929403130048908</v>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>0.2955409110236449</v>
+      </c>
+      <c r="L54" s="5" t="inlineStr"/>
+      <c r="M54" s="5" t="inlineStr"/>
+      <c r="N54" s="5" t="n">
         <v>0.8619</v>
       </c>
-      <c r="M54" s="5" t="n">
+      <c r="O54" s="5" t="n">
         <v>0.8817</v>
       </c>
-      <c r="N54" s="5" t="n">
+      <c r="P54" s="5" t="n">
         <v>0.8881</v>
       </c>
-      <c r="O54" s="6" t="inlineStr"/>
-      <c r="P54" s="6" t="inlineStr"/>
       <c r="Q54" s="6" t="inlineStr"/>
       <c r="R54" s="6" t="inlineStr"/>
       <c r="S54" s="6" t="inlineStr"/>
       <c r="T54" s="6" t="inlineStr"/>
       <c r="U54" s="6" t="inlineStr"/>
       <c r="V54" s="6" t="inlineStr"/>
+      <c r="W54" s="6" t="inlineStr"/>
+      <c r="X54" s="6" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3877,25 +4129,31 @@
         <v>209</v>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="5" t="inlineStr"/>
-      <c r="K55" s="5" t="inlineStr"/>
-      <c r="L55" s="5" t="n">
+      <c r="J55" s="5" t="n">
+        <v>0.1820130053159992</v>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>0.2502015276870414</v>
+      </c>
+      <c r="L55" s="5" t="inlineStr"/>
+      <c r="M55" s="5" t="inlineStr"/>
+      <c r="N55" s="5" t="n">
         <v>0.8619</v>
       </c>
-      <c r="M55" s="5" t="n">
+      <c r="O55" s="5" t="n">
         <v>0.8817</v>
       </c>
-      <c r="N55" s="5" t="n">
+      <c r="P55" s="5" t="n">
         <v>0.8881</v>
       </c>
-      <c r="O55" s="6" t="inlineStr"/>
-      <c r="P55" s="6" t="inlineStr"/>
       <c r="Q55" s="6" t="inlineStr"/>
       <c r="R55" s="6" t="inlineStr"/>
       <c r="S55" s="6" t="inlineStr"/>
       <c r="T55" s="6" t="inlineStr"/>
       <c r="U55" s="6" t="inlineStr"/>
       <c r="V55" s="6" t="inlineStr"/>
+      <c r="W55" s="6" t="inlineStr"/>
+      <c r="X55" s="6" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3933,25 +4191,31 @@
         <v>67</v>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="5" t="inlineStr"/>
-      <c r="K56" s="5" t="inlineStr"/>
-      <c r="L56" s="5" t="n">
+      <c r="J56" s="5" t="n">
+        <v>0.06059805759477788</v>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>0.0793430622023733</v>
+      </c>
+      <c r="L56" s="5" t="inlineStr"/>
+      <c r="M56" s="5" t="inlineStr"/>
+      <c r="N56" s="5" t="n">
         <v>0.9993</v>
       </c>
-      <c r="M56" s="5" t="n">
+      <c r="O56" s="5" t="n">
         <v>1.0018</v>
       </c>
-      <c r="N56" s="5" t="n">
+      <c r="P56" s="5" t="n">
         <v>0.9952</v>
       </c>
-      <c r="O56" s="6" t="inlineStr"/>
-      <c r="P56" s="6" t="inlineStr"/>
       <c r="Q56" s="6" t="inlineStr"/>
       <c r="R56" s="6" t="inlineStr"/>
       <c r="S56" s="6" t="inlineStr"/>
       <c r="T56" s="6" t="inlineStr"/>
       <c r="U56" s="6" t="inlineStr"/>
       <c r="V56" s="6" t="inlineStr"/>
+      <c r="W56" s="6" t="inlineStr"/>
+      <c r="X56" s="6" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -3994,14 +4258,16 @@
       <c r="L57" s="5" t="inlineStr"/>
       <c r="M57" s="5" t="inlineStr"/>
       <c r="N57" s="5" t="inlineStr"/>
-      <c r="O57" s="6" t="inlineStr"/>
-      <c r="P57" s="6" t="inlineStr"/>
+      <c r="O57" s="5" t="inlineStr"/>
+      <c r="P57" s="5" t="inlineStr"/>
       <c r="Q57" s="6" t="inlineStr"/>
       <c r="R57" s="6" t="inlineStr"/>
       <c r="S57" s="6" t="inlineStr"/>
       <c r="T57" s="6" t="inlineStr"/>
       <c r="U57" s="6" t="inlineStr"/>
       <c r="V57" s="6" t="inlineStr"/>
+      <c r="W57" s="6" t="inlineStr"/>
+      <c r="X57" s="6" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -4040,24 +4306,28 @@
       </c>
       <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="5" t="inlineStr"/>
-      <c r="K58" s="5" t="inlineStr"/>
-      <c r="L58" s="5" t="n">
+      <c r="K58" s="5" t="n">
+        <v>0.1030626282962745</v>
+      </c>
+      <c r="L58" s="5" t="inlineStr"/>
+      <c r="M58" s="5" t="inlineStr"/>
+      <c r="N58" s="5" t="n">
         <v>0.9787</v>
       </c>
-      <c r="M58" s="5" t="n">
+      <c r="O58" s="5" t="n">
         <v>0.9875</v>
       </c>
-      <c r="N58" s="5" t="n">
+      <c r="P58" s="5" t="n">
         <v>0.9837</v>
       </c>
-      <c r="O58" s="6" t="inlineStr"/>
-      <c r="P58" s="6" t="inlineStr"/>
       <c r="Q58" s="6" t="inlineStr"/>
       <c r="R58" s="6" t="inlineStr"/>
       <c r="S58" s="6" t="inlineStr"/>
       <c r="T58" s="6" t="inlineStr"/>
       <c r="U58" s="6" t="inlineStr"/>
       <c r="V58" s="6" t="inlineStr"/>
+      <c r="W58" s="6" t="inlineStr"/>
+      <c r="X58" s="6" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -4095,25 +4365,31 @@
         <v>54</v>
       </c>
       <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="5" t="inlineStr"/>
-      <c r="K59" s="5" t="inlineStr"/>
-      <c r="L59" s="5" t="n">
+      <c r="J59" s="5" t="n">
+        <v>0.1701534557235311</v>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>0.2438491711773283</v>
+      </c>
+      <c r="L59" s="5" t="inlineStr"/>
+      <c r="M59" s="5" t="inlineStr"/>
+      <c r="N59" s="5" t="n">
         <v>0.9388</v>
       </c>
-      <c r="M59" s="5" t="n">
+      <c r="O59" s="5" t="n">
         <v>0.9519</v>
       </c>
-      <c r="N59" s="5" t="n">
+      <c r="P59" s="5" t="n">
         <v>0.951</v>
       </c>
-      <c r="O59" s="6" t="inlineStr"/>
-      <c r="P59" s="6" t="inlineStr"/>
       <c r="Q59" s="6" t="inlineStr"/>
       <c r="R59" s="6" t="inlineStr"/>
       <c r="S59" s="6" t="inlineStr"/>
       <c r="T59" s="6" t="inlineStr"/>
       <c r="U59" s="6" t="inlineStr"/>
       <c r="V59" s="6" t="inlineStr"/>
+      <c r="W59" s="6" t="inlineStr"/>
+      <c r="X59" s="6" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -4151,25 +4427,31 @@
         <v>531</v>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="5" t="inlineStr"/>
-      <c r="K60" s="5" t="inlineStr"/>
-      <c r="L60" s="5" t="n">
+      <c r="J60" s="5" t="n">
+        <v>0.0683590128113456</v>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>0.02031868173035667</v>
+      </c>
+      <c r="L60" s="5" t="inlineStr"/>
+      <c r="M60" s="5" t="inlineStr"/>
+      <c r="N60" s="5" t="n">
         <v>0.9812</v>
       </c>
-      <c r="M60" s="5" t="n">
+      <c r="O60" s="5" t="n">
         <v>0.9845</v>
       </c>
-      <c r="N60" s="5" t="n">
+      <c r="P60" s="5" t="n">
         <v>0.9832</v>
       </c>
-      <c r="O60" s="6" t="inlineStr"/>
-      <c r="P60" s="6" t="inlineStr"/>
       <c r="Q60" s="6" t="inlineStr"/>
       <c r="R60" s="6" t="inlineStr"/>
       <c r="S60" s="6" t="inlineStr"/>
       <c r="T60" s="6" t="inlineStr"/>
       <c r="U60" s="6" t="inlineStr"/>
       <c r="V60" s="6" t="inlineStr"/>
+      <c r="W60" s="6" t="inlineStr"/>
+      <c r="X60" s="6" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -4209,23 +4491,25 @@
       <c r="I61" s="2" t="inlineStr"/>
       <c r="J61" s="5" t="inlineStr"/>
       <c r="K61" s="5" t="inlineStr"/>
-      <c r="L61" s="5" t="n">
+      <c r="L61" s="5" t="inlineStr"/>
+      <c r="M61" s="5" t="inlineStr"/>
+      <c r="N61" s="5" t="n">
         <v>0.9993</v>
       </c>
-      <c r="M61" s="5" t="n">
+      <c r="O61" s="5" t="n">
         <v>1.0018</v>
       </c>
-      <c r="N61" s="5" t="n">
+      <c r="P61" s="5" t="n">
         <v>0.9952</v>
       </c>
-      <c r="O61" s="6" t="inlineStr"/>
-      <c r="P61" s="6" t="inlineStr"/>
       <c r="Q61" s="6" t="inlineStr"/>
       <c r="R61" s="6" t="inlineStr"/>
       <c r="S61" s="6" t="inlineStr"/>
       <c r="T61" s="6" t="inlineStr"/>
       <c r="U61" s="6" t="inlineStr"/>
       <c r="V61" s="6" t="inlineStr"/>
+      <c r="W61" s="6" t="inlineStr"/>
+      <c r="X61" s="6" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -4265,23 +4549,25 @@
       <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="5" t="inlineStr"/>
       <c r="K62" s="5" t="inlineStr"/>
-      <c r="L62" s="5" t="n">
+      <c r="L62" s="5" t="inlineStr"/>
+      <c r="M62" s="5" t="inlineStr"/>
+      <c r="N62" s="5" t="n">
         <v>0.9848</v>
       </c>
-      <c r="M62" s="5" t="n">
+      <c r="O62" s="5" t="n">
         <v>0.9862</v>
       </c>
-      <c r="N62" s="5" t="n">
+      <c r="P62" s="5" t="n">
         <v>0.9913999999999999</v>
       </c>
-      <c r="O62" s="6" t="inlineStr"/>
-      <c r="P62" s="6" t="inlineStr"/>
       <c r="Q62" s="6" t="inlineStr"/>
       <c r="R62" s="6" t="inlineStr"/>
       <c r="S62" s="6" t="inlineStr"/>
       <c r="T62" s="6" t="inlineStr"/>
       <c r="U62" s="6" t="inlineStr"/>
       <c r="V62" s="6" t="inlineStr"/>
+      <c r="W62" s="6" t="inlineStr"/>
+      <c r="X62" s="6" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -4321,23 +4607,25 @@
       <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="5" t="inlineStr"/>
       <c r="K63" s="5" t="inlineStr"/>
-      <c r="L63" s="5" t="n">
+      <c r="L63" s="5" t="inlineStr"/>
+      <c r="M63" s="5" t="inlineStr"/>
+      <c r="N63" s="5" t="n">
         <v>0.9149</v>
       </c>
-      <c r="M63" s="5" t="n">
+      <c r="O63" s="5" t="n">
         <v>0.9329</v>
       </c>
-      <c r="N63" s="5" t="n">
+      <c r="P63" s="5" t="n">
         <v>0.9317</v>
       </c>
-      <c r="O63" s="6" t="inlineStr"/>
-      <c r="P63" s="6" t="inlineStr"/>
       <c r="Q63" s="6" t="inlineStr"/>
       <c r="R63" s="6" t="inlineStr"/>
       <c r="S63" s="6" t="inlineStr"/>
       <c r="T63" s="6" t="inlineStr"/>
       <c r="U63" s="6" t="inlineStr"/>
       <c r="V63" s="6" t="inlineStr"/>
+      <c r="W63" s="6" t="inlineStr"/>
+      <c r="X63" s="6" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -4377,23 +4665,25 @@
       <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="5" t="inlineStr"/>
       <c r="K64" s="5" t="inlineStr"/>
-      <c r="L64" s="5" t="n">
+      <c r="L64" s="5" t="inlineStr"/>
+      <c r="M64" s="5" t="inlineStr"/>
+      <c r="N64" s="5" t="n">
         <v>0.9848</v>
       </c>
-      <c r="M64" s="5" t="n">
+      <c r="O64" s="5" t="n">
         <v>0.9862</v>
       </c>
-      <c r="N64" s="5" t="n">
+      <c r="P64" s="5" t="n">
         <v>0.9913999999999999</v>
       </c>
-      <c r="O64" s="6" t="inlineStr"/>
-      <c r="P64" s="6" t="inlineStr"/>
       <c r="Q64" s="6" t="inlineStr"/>
       <c r="R64" s="6" t="inlineStr"/>
       <c r="S64" s="6" t="inlineStr"/>
       <c r="T64" s="6" t="inlineStr"/>
       <c r="U64" s="6" t="inlineStr"/>
       <c r="V64" s="6" t="inlineStr"/>
+      <c r="W64" s="6" t="inlineStr"/>
+      <c r="X64" s="6" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -4433,23 +4723,25 @@
       <c r="I65" s="2" t="inlineStr"/>
       <c r="J65" s="5" t="inlineStr"/>
       <c r="K65" s="5" t="inlineStr"/>
-      <c r="L65" s="5" t="n">
+      <c r="L65" s="5" t="inlineStr"/>
+      <c r="M65" s="5" t="inlineStr"/>
+      <c r="N65" s="5" t="n">
         <v>0.9718</v>
       </c>
-      <c r="M65" s="5" t="n">
+      <c r="O65" s="5" t="n">
         <v>0.9825</v>
       </c>
-      <c r="N65" s="5" t="n">
+      <c r="P65" s="5" t="n">
         <v>0.9801</v>
       </c>
-      <c r="O65" s="6" t="inlineStr"/>
-      <c r="P65" s="6" t="inlineStr"/>
       <c r="Q65" s="6" t="inlineStr"/>
       <c r="R65" s="6" t="inlineStr"/>
       <c r="S65" s="6" t="inlineStr"/>
       <c r="T65" s="6" t="inlineStr"/>
       <c r="U65" s="6" t="inlineStr"/>
       <c r="V65" s="6" t="inlineStr"/>
+      <c r="W65" s="6" t="inlineStr"/>
+      <c r="X65" s="6" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -4489,23 +4781,25 @@
       <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="5" t="inlineStr"/>
       <c r="K66" s="5" t="inlineStr"/>
-      <c r="L66" s="5" t="n">
+      <c r="L66" s="5" t="inlineStr"/>
+      <c r="M66" s="5" t="inlineStr"/>
+      <c r="N66" s="5" t="n">
         <v>0.9993</v>
       </c>
-      <c r="M66" s="5" t="n">
+      <c r="O66" s="5" t="n">
         <v>1.0018</v>
       </c>
-      <c r="N66" s="5" t="n">
+      <c r="P66" s="5" t="n">
         <v>0.9952</v>
       </c>
-      <c r="O66" s="6" t="inlineStr"/>
-      <c r="P66" s="6" t="inlineStr"/>
       <c r="Q66" s="6" t="inlineStr"/>
       <c r="R66" s="6" t="inlineStr"/>
       <c r="S66" s="6" t="inlineStr"/>
       <c r="T66" s="6" t="inlineStr"/>
       <c r="U66" s="6" t="inlineStr"/>
       <c r="V66" s="6" t="inlineStr"/>
+      <c r="W66" s="6" t="inlineStr"/>
+      <c r="X66" s="6" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -4545,23 +4839,25 @@
       <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="5" t="inlineStr"/>
       <c r="K67" s="5" t="inlineStr"/>
-      <c r="L67" s="5" t="n">
+      <c r="L67" s="5" t="inlineStr"/>
+      <c r="M67" s="5" t="inlineStr"/>
+      <c r="N67" s="5" t="n">
         <v>1.0072</v>
       </c>
-      <c r="M67" s="5" t="n">
+      <c r="O67" s="5" t="n">
         <v>1.0166</v>
       </c>
-      <c r="N67" s="5" t="n">
+      <c r="P67" s="5" t="n">
         <v>1.0065</v>
       </c>
-      <c r="O67" s="6" t="inlineStr"/>
-      <c r="P67" s="6" t="inlineStr"/>
       <c r="Q67" s="6" t="inlineStr"/>
       <c r="R67" s="6" t="inlineStr"/>
       <c r="S67" s="6" t="inlineStr"/>
       <c r="T67" s="6" t="inlineStr"/>
       <c r="U67" s="6" t="inlineStr"/>
       <c r="V67" s="6" t="inlineStr"/>
+      <c r="W67" s="6" t="inlineStr"/>
+      <c r="X67" s="6" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -4599,25 +4895,31 @@
         <v>144.4</v>
       </c>
       <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="5" t="inlineStr"/>
-      <c r="K68" s="5" t="inlineStr"/>
-      <c r="L68" s="5" t="n">
+      <c r="J68" s="5" t="n">
+        <v>0.1520359556040282</v>
+      </c>
+      <c r="K68" s="5" t="n">
+        <v>0.1684419945136396</v>
+      </c>
+      <c r="L68" s="5" t="inlineStr"/>
+      <c r="M68" s="5" t="inlineStr"/>
+      <c r="N68" s="5" t="n">
         <v>0.9425</v>
       </c>
-      <c r="M68" s="5" t="n">
+      <c r="O68" s="5" t="n">
         <v>0.9537</v>
       </c>
-      <c r="N68" s="5" t="n">
+      <c r="P68" s="5" t="n">
         <v>0.9562</v>
       </c>
-      <c r="O68" s="6" t="inlineStr"/>
-      <c r="P68" s="6" t="inlineStr"/>
       <c r="Q68" s="6" t="inlineStr"/>
       <c r="R68" s="6" t="inlineStr"/>
       <c r="S68" s="6" t="inlineStr"/>
       <c r="T68" s="6" t="inlineStr"/>
       <c r="U68" s="6" t="inlineStr"/>
       <c r="V68" s="6" t="inlineStr"/>
+      <c r="W68" s="6" t="inlineStr"/>
+      <c r="X68" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4630,7 +4932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U68"/>
+  <dimension ref="A1:W68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4654,6 +4956,8 @@
     <col width="14" customWidth="1" min="19" max="19"/>
     <col width="14" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4684,80 +4988,90 @@
       </c>
       <c r="F1" s="7" t="inlineStr">
         <is>
+          <t>CURTAILMENT_ACTUAL_FY23-24</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>CURTAILMENT_ACTUAL_FY24-25</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
           <t>ELI_CURTAILMENT_NEAR</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>ELI_CURTAILMENT_MED</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>ISP_CURTAILMENT_FY1</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="K1" s="7" t="inlineStr">
         <is>
           <t>ISP_CURTAILMENT_FY1_LABEL</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="L1" s="7" t="inlineStr">
         <is>
           <t>ISP_CURTAILMENT_FY2</t>
         </is>
       </c>
-      <c r="K1" s="7" t="inlineStr">
+      <c r="M1" s="7" t="inlineStr">
         <is>
           <t>ISP_CURTAILMENT_FY2_LABEL</t>
         </is>
       </c>
-      <c r="L1" s="7" t="inlineStr">
+      <c r="N1" s="7" t="inlineStr">
         <is>
           <t>ISP_CURTAILMENT_FY3</t>
         </is>
       </c>
-      <c r="M1" s="7" t="inlineStr">
+      <c r="O1" s="7" t="inlineStr">
         <is>
           <t>ISP_CURTAILMENT_FY3_LABEL</t>
         </is>
       </c>
-      <c r="N1" s="7" t="inlineStr">
+      <c r="P1" s="7" t="inlineStr">
         <is>
           <t>ISP_CURTAILMENT_AVG</t>
         </is>
       </c>
-      <c r="O1" s="7" t="inlineStr">
+      <c r="Q1" s="7" t="inlineStr">
         <is>
           <t>ISP_OFFLOADING_FY1</t>
         </is>
       </c>
-      <c r="P1" s="7" t="inlineStr">
+      <c r="R1" s="7" t="inlineStr">
         <is>
           <t>ISP_OFFLOADING_FY1_LABEL</t>
         </is>
       </c>
-      <c r="Q1" s="7" t="inlineStr">
+      <c r="S1" s="7" t="inlineStr">
         <is>
           <t>ISP_OFFLOADING_FY2</t>
         </is>
       </c>
-      <c r="R1" s="7" t="inlineStr">
+      <c r="T1" s="7" t="inlineStr">
         <is>
           <t>ISP_OFFLOADING_FY2_LABEL</t>
         </is>
       </c>
-      <c r="S1" s="7" t="inlineStr">
+      <c r="U1" s="7" t="inlineStr">
         <is>
           <t>ISP_OFFLOADING_FY3</t>
         </is>
       </c>
-      <c r="T1" s="7" t="inlineStr">
+      <c r="V1" s="7" t="inlineStr">
         <is>
           <t>ISP_OFFLOADING_FY3_LABEL</t>
         </is>
       </c>
-      <c r="U1" s="7" t="inlineStr">
+      <c r="W1" s="7" t="inlineStr">
         <is>
           <t>ISP_OFFLOADING_AVG</t>
         </is>
@@ -4784,63 +5098,69 @@
         <v>0.9114</v>
       </c>
       <c r="F2" s="5" t="n">
+        <v>0.3710560565867671</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>0.2719808764553837</v>
+      </c>
+      <c r="H2" s="5" t="n">
         <v>0.833539620209753</v>
       </c>
-      <c r="G2" s="5" t="n">
+      <c r="I2" s="5" t="n">
         <v>0.164192244302687</v>
       </c>
-      <c r="H2" s="5" t="n">
+      <c r="J2" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="I2" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="J2" s="5" t="n">
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="L2" s="5" t="n">
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M2" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="N2" s="5" t="n">
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="n">
         <v>0.02666666666666667</v>
       </c>
-      <c r="O2" s="5" t="n">
+      <c r="Q2" s="5" t="n">
         <v>0.11</v>
       </c>
-      <c r="P2" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q2" s="5" t="n">
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="n">
         <v>0.17</v>
       </c>
-      <c r="R2" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="S2" s="5" t="n">
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
         <v>0.08</v>
       </c>
-      <c r="T2" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="U2" s="5" t="n">
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -4865,43 +5185,45 @@
       <c r="F3" s="5" t="inlineStr"/>
       <c r="G3" s="5" t="inlineStr"/>
       <c r="H3" s="5" t="inlineStr"/>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I3" s="5" t="inlineStr"/>
       <c r="J3" s="5" t="inlineStr"/>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L3" s="5" t="inlineStr"/>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N3" s="5" t="inlineStr"/>
-      <c r="O3" s="5" t="inlineStr"/>
-      <c r="P3" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr"/>
       <c r="Q3" s="5" t="inlineStr"/>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr"/>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U3" s="5" t="inlineStr"/>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
@@ -4924,63 +5246,69 @@
         <v>0.9307</v>
       </c>
       <c r="F4" s="5" t="n">
+        <v>0.1600293147297279</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0.2827710603192121</v>
+      </c>
+      <c r="H4" s="5" t="n">
         <v>0.547516873654646</v>
       </c>
-      <c r="G4" s="5" t="n">
+      <c r="I4" s="5" t="n">
         <v>0.122422882740379</v>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="J4" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="J4" s="5" t="n">
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="n">
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M4" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="N4" s="5" t="n">
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="n">
         <v>0.02666666666666667</v>
       </c>
-      <c r="O4" s="5" t="n">
+      <c r="Q4" s="5" t="n">
         <v>0.11</v>
       </c>
-      <c r="P4" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q4" s="5" t="n">
+      <c r="R4" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S4" s="5" t="n">
         <v>0.17</v>
       </c>
-      <c r="R4" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="S4" s="5" t="n">
+      <c r="T4" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U4" s="5" t="n">
         <v>0.08</v>
       </c>
-      <c r="T4" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="U4" s="5" t="n">
+      <c r="V4" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -5005,63 +5333,69 @@
         <v>0.9307</v>
       </c>
       <c r="F5" s="5" t="n">
+        <v>0.05215670207613177</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>0.05460168559670209</v>
+      </c>
+      <c r="H5" s="5" t="n">
         <v>0.547516873654646</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="I5" s="5" t="n">
         <v>0.122422882740379</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="J5" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="n">
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="L5" s="5" t="n">
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M5" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="N5" s="5" t="n">
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P5" s="5" t="n">
         <v>0.02666666666666667</v>
       </c>
-      <c r="O5" s="5" t="n">
+      <c r="Q5" s="5" t="n">
         <v>0.11</v>
       </c>
-      <c r="P5" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q5" s="5" t="n">
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S5" s="5" t="n">
         <v>0.17</v>
       </c>
-      <c r="R5" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="S5" s="5" t="n">
+      <c r="T5" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U5" s="5" t="n">
         <v>0.08</v>
       </c>
-      <c r="T5" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="U5" s="5" t="n">
+      <c r="V5" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W5" s="5" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -5085,26 +5419,22 @@
       <c r="E6" s="5" t="n">
         <v>0.9223</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="n">
+        <v>0.2650311526126716</v>
+      </c>
+      <c r="H6" s="5" t="n">
         <v>0.389503957787889</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="I6" s="5" t="n">
         <v>0.08205629867681941</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
       </c>
       <c r="J6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L6" s="5" t="n">
@@ -5112,37 +5442,45 @@
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N6" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O6" s="5" t="n">
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="5" t="n">
         <v>0.04</v>
       </c>
-      <c r="P6" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q6" s="5" t="n">
+      <c r="R6" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S6" s="5" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="R6" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="S6" s="5" t="n">
+      <c r="T6" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U6" s="5" t="n">
         <v>0.1</v>
       </c>
-      <c r="T6" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="U6" s="5" t="n">
+      <c r="V6" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W6" s="5" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -5167,25 +5505,23 @@
         <v>0.9292</v>
       </c>
       <c r="F7" s="5" t="n">
+        <v>0.1954445746044534</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>0.07798287623836642</v>
+      </c>
+      <c r="H7" s="5" t="n">
         <v>0.390717855103594</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="I7" s="5" t="n">
         <v>0.08997768712489811</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
       </c>
       <c r="J7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L7" s="5" t="n">
@@ -5193,37 +5529,45 @@
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N7" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O7" s="5" t="n">
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="5" t="n">
         <v>0.04</v>
       </c>
-      <c r="P7" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q7" s="5" t="n">
+      <c r="R7" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S7" s="5" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="R7" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="S7" s="5" t="n">
+      <c r="T7" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U7" s="5" t="n">
         <v>0.1</v>
       </c>
-      <c r="T7" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="U7" s="5" t="n">
+      <c r="V7" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W7" s="5" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -5247,46 +5591,52 @@
       <c r="E8" s="5" t="n">
         <v>0.922</v>
       </c>
-      <c r="F8" s="5" t="inlineStr"/>
-      <c r="G8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="n">
+        <v>0.1990273759688161</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0.2408960878187453</v>
+      </c>
       <c r="H8" s="5" t="inlineStr"/>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I8" s="5" t="inlineStr"/>
       <c r="J8" s="5" t="inlineStr"/>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr"/>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N8" s="5" t="inlineStr"/>
-      <c r="O8" s="5" t="inlineStr"/>
-      <c r="P8" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O8" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P8" s="5" t="inlineStr"/>
       <c r="Q8" s="5" t="inlineStr"/>
       <c r="R8" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S8" s="5" t="inlineStr"/>
       <c r="T8" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U8" s="5" t="inlineStr"/>
+      <c r="V8" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
@@ -5309,43 +5659,45 @@
       <c r="F9" s="5" t="inlineStr"/>
       <c r="G9" s="5" t="inlineStr"/>
       <c r="H9" s="5" t="inlineStr"/>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I9" s="5" t="inlineStr"/>
       <c r="J9" s="5" t="inlineStr"/>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L9" s="5" t="inlineStr"/>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N9" s="5" t="inlineStr"/>
-      <c r="O9" s="5" t="inlineStr"/>
-      <c r="P9" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P9" s="5" t="inlineStr"/>
       <c r="Q9" s="5" t="inlineStr"/>
       <c r="R9" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S9" s="5" t="inlineStr"/>
       <c r="T9" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U9" s="5" t="inlineStr"/>
+      <c r="V9" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -5368,63 +5720,69 @@
         <v>0.9088000000000001</v>
       </c>
       <c r="F10" s="5" t="n">
+        <v>0.3169574937730341</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.1686799728674456</v>
+      </c>
+      <c r="H10" s="5" t="n">
         <v>0.8554020168196</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="I10" s="5" t="n">
         <v>0.072415601225557</v>
       </c>
-      <c r="H10" s="5" t="n">
+      <c r="J10" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="n">
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="n">
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N10" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M10" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="N10" s="5" t="n">
+      <c r="O10" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P10" s="5" t="n">
         <v>0.02666666666666667</v>
       </c>
-      <c r="O10" s="5" t="n">
+      <c r="Q10" s="5" t="n">
         <v>0.11</v>
       </c>
-      <c r="P10" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q10" s="5" t="n">
+      <c r="R10" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S10" s="5" t="n">
         <v>0.17</v>
       </c>
-      <c r="R10" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="S10" s="5" t="n">
+      <c r="T10" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U10" s="5" t="n">
         <v>0.08</v>
       </c>
-      <c r="T10" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="U10" s="5" t="n">
+      <c r="V10" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W10" s="5" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -5449,45 +5807,49 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="n">
+        <v>0.04898598021985823</v>
+      </c>
       <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I11" s="5" t="inlineStr"/>
       <c r="J11" s="5" t="inlineStr"/>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L11" s="5" t="inlineStr"/>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N11" s="5" t="inlineStr"/>
-      <c r="O11" s="5" t="inlineStr"/>
-      <c r="P11" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P11" s="5" t="inlineStr"/>
       <c r="Q11" s="5" t="inlineStr"/>
       <c r="R11" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S11" s="5" t="inlineStr"/>
       <c r="T11" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U11" s="5" t="inlineStr"/>
+      <c r="V11" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
@@ -5510,63 +5872,69 @@
         <v>0.878</v>
       </c>
       <c r="F12" s="5" t="n">
+        <v>0.1091648532990047</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.1136272868211855</v>
+      </c>
+      <c r="H12" s="5" t="n">
         <v>0.827440107601162</v>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="I12" s="5" t="n">
         <v>0.0878331516592939</v>
       </c>
-      <c r="H12" s="5" t="n">
+      <c r="J12" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="J12" s="5" t="n">
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="L12" s="5" t="n">
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N12" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M12" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="N12" s="5" t="n">
+      <c r="O12" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P12" s="5" t="n">
         <v>0.02666666666666667</v>
       </c>
-      <c r="O12" s="5" t="n">
+      <c r="Q12" s="5" t="n">
         <v>0.11</v>
       </c>
-      <c r="P12" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q12" s="5" t="n">
+      <c r="R12" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S12" s="5" t="n">
         <v>0.17</v>
       </c>
-      <c r="R12" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="S12" s="5" t="n">
+      <c r="T12" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U12" s="5" t="n">
         <v>0.08</v>
       </c>
-      <c r="T12" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="U12" s="5" t="n">
+      <c r="V12" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W12" s="5" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -5589,43 +5957,45 @@
       <c r="F13" s="5" t="inlineStr"/>
       <c r="G13" s="5" t="inlineStr"/>
       <c r="H13" s="5" t="inlineStr"/>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I13" s="5" t="inlineStr"/>
       <c r="J13" s="5" t="inlineStr"/>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L13" s="5" t="inlineStr"/>
       <c r="M13" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N13" s="5" t="inlineStr"/>
-      <c r="O13" s="5" t="inlineStr"/>
-      <c r="P13" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O13" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P13" s="5" t="inlineStr"/>
       <c r="Q13" s="5" t="inlineStr"/>
       <c r="R13" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S13" s="5" t="inlineStr"/>
       <c r="T13" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U13" s="5" t="inlineStr"/>
+      <c r="V13" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
@@ -5648,45 +6018,49 @@
         <v>0.9248</v>
       </c>
       <c r="F14" s="5" t="inlineStr"/>
-      <c r="G14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="n">
+        <v>0.1074948342034868</v>
+      </c>
       <c r="H14" s="5" t="inlineStr"/>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I14" s="5" t="inlineStr"/>
       <c r="J14" s="5" t="inlineStr"/>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr"/>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N14" s="5" t="inlineStr"/>
-      <c r="O14" s="5" t="inlineStr"/>
-      <c r="P14" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O14" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P14" s="5" t="inlineStr"/>
       <c r="Q14" s="5" t="inlineStr"/>
       <c r="R14" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S14" s="5" t="inlineStr"/>
       <c r="T14" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U14" s="5" t="inlineStr"/>
+      <c r="V14" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
@@ -5709,25 +6083,23 @@
         <v>0.9223</v>
       </c>
       <c r="F15" s="5" t="n">
+        <v>0.3437740975604878</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>0.1415139558510223</v>
+      </c>
+      <c r="H15" s="5" t="n">
         <v>0.389503957787889</v>
       </c>
-      <c r="G15" s="5" t="n">
+      <c r="I15" s="5" t="n">
         <v>0.08205629867681941</v>
-      </c>
-      <c r="H15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
       </c>
       <c r="J15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L15" s="5" t="n">
@@ -5735,37 +6107,45 @@
       </c>
       <c r="M15" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N15" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O15" s="5" t="n">
+      <c r="O15" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="5" t="n">
         <v>0.04</v>
       </c>
-      <c r="P15" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q15" s="5" t="n">
+      <c r="R15" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S15" s="5" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="R15" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="S15" s="5" t="n">
+      <c r="T15" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U15" s="5" t="n">
         <v>0.1</v>
       </c>
-      <c r="T15" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="U15" s="5" t="n">
+      <c r="V15" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W15" s="5" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -5792,43 +6172,45 @@
       <c r="F16" s="5" t="inlineStr"/>
       <c r="G16" s="5" t="inlineStr"/>
       <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I16" s="5" t="inlineStr"/>
       <c r="J16" s="5" t="inlineStr"/>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr"/>
       <c r="M16" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N16" s="5" t="inlineStr"/>
-      <c r="O16" s="5" t="inlineStr"/>
-      <c r="P16" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P16" s="5" t="inlineStr"/>
       <c r="Q16" s="5" t="inlineStr"/>
       <c r="R16" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S16" s="5" t="inlineStr"/>
       <c r="T16" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U16" s="5" t="inlineStr"/>
+      <c r="V16" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -5851,63 +6233,69 @@
         <v>0.9114</v>
       </c>
       <c r="F17" s="5" t="n">
+        <v>0.3584538984210027</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.2739101642738966</v>
+      </c>
+      <c r="H17" s="5" t="n">
         <v>0.833539620209753</v>
       </c>
-      <c r="G17" s="5" t="n">
+      <c r="I17" s="5" t="n">
         <v>0.164192244302687</v>
       </c>
-      <c r="H17" s="5" t="n">
+      <c r="J17" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="n">
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="L17" s="5" t="n">
+      <c r="M17" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N17" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M17" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="N17" s="5" t="n">
+      <c r="O17" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P17" s="5" t="n">
         <v>0.02666666666666667</v>
       </c>
-      <c r="O17" s="5" t="n">
+      <c r="Q17" s="5" t="n">
         <v>0.11</v>
       </c>
-      <c r="P17" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q17" s="5" t="n">
+      <c r="R17" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S17" s="5" t="n">
         <v>0.17</v>
       </c>
-      <c r="R17" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="S17" s="5" t="n">
+      <c r="T17" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U17" s="5" t="n">
         <v>0.08</v>
       </c>
-      <c r="T17" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="U17" s="5" t="n">
+      <c r="V17" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W17" s="5" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -5932,25 +6320,23 @@
         <v>0.922</v>
       </c>
       <c r="F18" s="5" t="n">
+        <v>0.2487248512923422</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.1094894731574723</v>
+      </c>
+      <c r="H18" s="5" t="n">
         <v>0.390717855103594</v>
       </c>
-      <c r="G18" s="5" t="n">
+      <c r="I18" s="5" t="n">
         <v>0.08997768712489811</v>
-      </c>
-      <c r="H18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
       </c>
       <c r="J18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L18" s="5" t="n">
@@ -5958,37 +6344,45 @@
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N18" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O18" s="5" t="n">
+      <c r="O18" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="5" t="n">
         <v>0.04</v>
       </c>
-      <c r="P18" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q18" s="5" t="n">
+      <c r="R18" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S18" s="5" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="R18" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="S18" s="5" t="n">
+      <c r="T18" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U18" s="5" t="n">
         <v>0.1</v>
       </c>
-      <c r="T18" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="U18" s="5" t="n">
+      <c r="V18" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W18" s="5" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -6012,50 +6406,54 @@
       <c r="E19" s="5" t="n">
         <v>0.9223</v>
       </c>
-      <c r="F19" s="5" t="n">
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="n">
+        <v>0.1428920071912686</v>
+      </c>
+      <c r="H19" s="5" t="n">
         <v>0.389503957787889</v>
       </c>
-      <c r="G19" s="5" t="n">
+      <c r="I19" s="5" t="n">
         <v>0.08205629867681941</v>
-      </c>
-      <c r="H19" s="5" t="inlineStr"/>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
       </c>
       <c r="J19" s="5" t="inlineStr"/>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr"/>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N19" s="5" t="inlineStr"/>
-      <c r="O19" s="5" t="inlineStr"/>
-      <c r="P19" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O19" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P19" s="5" t="inlineStr"/>
       <c r="Q19" s="5" t="inlineStr"/>
       <c r="R19" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S19" s="5" t="inlineStr"/>
       <c r="T19" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U19" s="5" t="inlineStr"/>
+      <c r="V19" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -6078,63 +6476,69 @@
         <v>0.9088000000000001</v>
       </c>
       <c r="F20" s="5" t="n">
+        <v>0.3372382246917938</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0.2486746048568231</v>
+      </c>
+      <c r="H20" s="5" t="n">
         <v>0.8554020168196</v>
       </c>
-      <c r="G20" s="5" t="n">
+      <c r="I20" s="5" t="n">
         <v>0.072415601225557</v>
       </c>
-      <c r="H20" s="5" t="n">
+      <c r="J20" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="I20" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="J20" s="5" t="n">
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="L20" s="5" t="n">
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N20" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M20" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="N20" s="5" t="n">
+      <c r="O20" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P20" s="5" t="n">
         <v>0.02666666666666667</v>
       </c>
-      <c r="O20" s="5" t="n">
+      <c r="Q20" s="5" t="n">
         <v>0.11</v>
       </c>
-      <c r="P20" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q20" s="5" t="n">
+      <c r="R20" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S20" s="5" t="n">
         <v>0.17</v>
       </c>
-      <c r="R20" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="S20" s="5" t="n">
+      <c r="T20" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U20" s="5" t="n">
         <v>0.08</v>
       </c>
-      <c r="T20" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="U20" s="5" t="n">
+      <c r="V20" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W20" s="5" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -6158,46 +6562,52 @@
       <c r="E21" s="5" t="n">
         <v>0.8999</v>
       </c>
-      <c r="F21" s="5" t="inlineStr"/>
-      <c r="G21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="n">
+        <v>0.07896687551826564</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0.04879956378773898</v>
+      </c>
       <c r="H21" s="5" t="inlineStr"/>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I21" s="5" t="inlineStr"/>
       <c r="J21" s="5" t="inlineStr"/>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L21" s="5" t="inlineStr"/>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N21" s="5" t="inlineStr"/>
-      <c r="O21" s="5" t="inlineStr"/>
-      <c r="P21" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O21" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P21" s="5" t="inlineStr"/>
       <c r="Q21" s="5" t="inlineStr"/>
       <c r="R21" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S21" s="5" t="inlineStr"/>
       <c r="T21" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U21" s="5" t="inlineStr"/>
+      <c r="V21" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
@@ -6219,46 +6629,52 @@
       <c r="E22" s="5" t="n">
         <v>0.9913999999999999</v>
       </c>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="n">
+        <v>0.007890464523191421</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0.005078393583182961</v>
+      </c>
       <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I22" s="5" t="inlineStr"/>
       <c r="J22" s="5" t="inlineStr"/>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr"/>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N22" s="5" t="inlineStr"/>
-      <c r="O22" s="5" t="inlineStr"/>
-      <c r="P22" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O22" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P22" s="5" t="inlineStr"/>
       <c r="Q22" s="5" t="inlineStr"/>
       <c r="R22" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S22" s="5" t="inlineStr"/>
       <c r="T22" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U22" s="5" t="inlineStr"/>
+      <c r="V22" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
@@ -6280,46 +6696,52 @@
       <c r="E23" s="5" t="n">
         <v>0.945</v>
       </c>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
+      <c r="F23" s="5" t="n">
+        <v>0.228198922467751</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0.2029431742155934</v>
+      </c>
       <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I23" s="5" t="inlineStr"/>
       <c r="J23" s="5" t="inlineStr"/>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr"/>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N23" s="5" t="inlineStr"/>
-      <c r="O23" s="5" t="inlineStr"/>
-      <c r="P23" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O23" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P23" s="5" t="inlineStr"/>
       <c r="Q23" s="5" t="inlineStr"/>
       <c r="R23" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S23" s="5" t="inlineStr"/>
       <c r="T23" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U23" s="5" t="inlineStr"/>
+      <c r="V23" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
@@ -6341,46 +6763,52 @@
       <c r="E24" s="5" t="n">
         <v>0.945</v>
       </c>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="n">
+        <v>0.04586386696325562</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.03247885424318653</v>
+      </c>
       <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I24" s="5" t="inlineStr"/>
       <c r="J24" s="5" t="inlineStr"/>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr"/>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N24" s="5" t="inlineStr"/>
-      <c r="O24" s="5" t="inlineStr"/>
-      <c r="P24" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O24" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P24" s="5" t="inlineStr"/>
       <c r="Q24" s="5" t="inlineStr"/>
       <c r="R24" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S24" s="5" t="inlineStr"/>
       <c r="T24" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U24" s="5" t="inlineStr"/>
+      <c r="V24" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
@@ -6402,46 +6830,52 @@
       <c r="E25" s="5" t="n">
         <v>0.89</v>
       </c>
-      <c r="F25" s="5" t="inlineStr"/>
-      <c r="G25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="n">
+        <v>0.03468796155479126</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0.02811506234350913</v>
+      </c>
       <c r="H25" s="5" t="inlineStr"/>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I25" s="5" t="inlineStr"/>
       <c r="J25" s="5" t="inlineStr"/>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr"/>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N25" s="5" t="inlineStr"/>
-      <c r="O25" s="5" t="inlineStr"/>
-      <c r="P25" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O25" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P25" s="5" t="inlineStr"/>
       <c r="Q25" s="5" t="inlineStr"/>
       <c r="R25" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S25" s="5" t="inlineStr"/>
       <c r="T25" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U25" s="5" t="inlineStr"/>
+      <c r="V25" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
@@ -6466,43 +6900,45 @@
       <c r="F26" s="5" t="inlineStr"/>
       <c r="G26" s="5" t="inlineStr"/>
       <c r="H26" s="5" t="inlineStr"/>
-      <c r="I26" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I26" s="5" t="inlineStr"/>
       <c r="J26" s="5" t="inlineStr"/>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr"/>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N26" s="5" t="inlineStr"/>
-      <c r="O26" s="5" t="inlineStr"/>
-      <c r="P26" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O26" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P26" s="5" t="inlineStr"/>
       <c r="Q26" s="5" t="inlineStr"/>
       <c r="R26" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S26" s="5" t="inlineStr"/>
       <c r="T26" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U26" s="5" t="inlineStr"/>
+      <c r="V26" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
@@ -6525,43 +6961,45 @@
       <c r="F27" s="5" t="inlineStr"/>
       <c r="G27" s="5" t="inlineStr"/>
       <c r="H27" s="5" t="inlineStr"/>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I27" s="5" t="inlineStr"/>
       <c r="J27" s="5" t="inlineStr"/>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr"/>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N27" s="5" t="inlineStr"/>
-      <c r="O27" s="5" t="inlineStr"/>
-      <c r="P27" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O27" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P27" s="5" t="inlineStr"/>
       <c r="Q27" s="5" t="inlineStr"/>
       <c r="R27" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S27" s="5" t="inlineStr"/>
       <c r="T27" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U27" s="5" t="inlineStr"/>
+      <c r="V27" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
@@ -6583,46 +7021,52 @@
       <c r="E28" s="5" t="n">
         <v>0.9978</v>
       </c>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="n">
+        <v>0.06000630720703115</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0.0990364762086815</v>
+      </c>
       <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I28" s="5" t="inlineStr"/>
       <c r="J28" s="5" t="inlineStr"/>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr"/>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N28" s="5" t="inlineStr"/>
-      <c r="O28" s="5" t="inlineStr"/>
-      <c r="P28" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O28" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P28" s="5" t="inlineStr"/>
       <c r="Q28" s="5" t="inlineStr"/>
       <c r="R28" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S28" s="5" t="inlineStr"/>
       <c r="T28" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U28" s="5" t="inlineStr"/>
+      <c r="V28" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
@@ -6647,43 +7091,45 @@
       <c r="F29" s="5" t="inlineStr"/>
       <c r="G29" s="5" t="inlineStr"/>
       <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I29" s="5" t="inlineStr"/>
       <c r="J29" s="5" t="inlineStr"/>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr"/>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N29" s="5" t="inlineStr"/>
-      <c r="O29" s="5" t="inlineStr"/>
-      <c r="P29" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O29" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P29" s="5" t="inlineStr"/>
       <c r="Q29" s="5" t="inlineStr"/>
       <c r="R29" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S29" s="5" t="inlineStr"/>
       <c r="T29" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U29" s="5" t="inlineStr"/>
+      <c r="V29" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
@@ -6708,43 +7154,45 @@
       <c r="F30" s="5" t="inlineStr"/>
       <c r="G30" s="5" t="inlineStr"/>
       <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I30" s="5" t="inlineStr"/>
       <c r="J30" s="5" t="inlineStr"/>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr"/>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N30" s="5" t="inlineStr"/>
-      <c r="O30" s="5" t="inlineStr"/>
-      <c r="P30" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O30" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P30" s="5" t="inlineStr"/>
       <c r="Q30" s="5" t="inlineStr"/>
       <c r="R30" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S30" s="5" t="inlineStr"/>
       <c r="T30" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U30" s="5" t="inlineStr"/>
+      <c r="V30" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
@@ -6766,46 +7214,52 @@
       <c r="E31" s="5" t="n">
         <v>0.9</v>
       </c>
-      <c r="F31" s="5" t="inlineStr"/>
-      <c r="G31" s="5" t="inlineStr"/>
+      <c r="F31" s="5" t="n">
+        <v>0.05765254706148304</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0.07617724801951264</v>
+      </c>
       <c r="H31" s="5" t="inlineStr"/>
-      <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I31" s="5" t="inlineStr"/>
       <c r="J31" s="5" t="inlineStr"/>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr"/>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N31" s="5" t="inlineStr"/>
-      <c r="O31" s="5" t="inlineStr"/>
-      <c r="P31" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O31" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P31" s="5" t="inlineStr"/>
       <c r="Q31" s="5" t="inlineStr"/>
       <c r="R31" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S31" s="5" t="inlineStr"/>
       <c r="T31" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U31" s="5" t="inlineStr"/>
+      <c r="V31" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
@@ -6830,43 +7284,45 @@
       <c r="F32" s="5" t="inlineStr"/>
       <c r="G32" s="5" t="inlineStr"/>
       <c r="H32" s="5" t="inlineStr"/>
-      <c r="I32" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I32" s="5" t="inlineStr"/>
       <c r="J32" s="5" t="inlineStr"/>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr"/>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N32" s="5" t="inlineStr"/>
-      <c r="O32" s="5" t="inlineStr"/>
-      <c r="P32" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O32" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P32" s="5" t="inlineStr"/>
       <c r="Q32" s="5" t="inlineStr"/>
       <c r="R32" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S32" s="5" t="inlineStr"/>
       <c r="T32" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U32" s="5" t="inlineStr"/>
+      <c r="V32" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
@@ -6888,46 +7344,52 @@
       <c r="E33" s="5" t="n">
         <v>0.9833</v>
       </c>
-      <c r="F33" s="5" t="inlineStr"/>
-      <c r="G33" s="5" t="inlineStr"/>
+      <c r="F33" s="5" t="n">
+        <v>0.1090852472782988</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0.1329011055420474</v>
+      </c>
       <c r="H33" s="5" t="inlineStr"/>
-      <c r="I33" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I33" s="5" t="inlineStr"/>
       <c r="J33" s="5" t="inlineStr"/>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr"/>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N33" s="5" t="inlineStr"/>
-      <c r="O33" s="5" t="inlineStr"/>
-      <c r="P33" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O33" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P33" s="5" t="inlineStr"/>
       <c r="Q33" s="5" t="inlineStr"/>
       <c r="R33" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S33" s="5" t="inlineStr"/>
       <c r="T33" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U33" s="5" t="inlineStr"/>
+      <c r="V33" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
@@ -6949,46 +7411,52 @@
       <c r="E34" s="5" t="n">
         <v>0.9833</v>
       </c>
-      <c r="F34" s="5" t="inlineStr"/>
-      <c r="G34" s="5" t="inlineStr"/>
+      <c r="F34" s="5" t="n">
+        <v>0.07673420102808481</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0.04879482272464053</v>
+      </c>
       <c r="H34" s="5" t="inlineStr"/>
-      <c r="I34" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I34" s="5" t="inlineStr"/>
       <c r="J34" s="5" t="inlineStr"/>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr"/>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N34" s="5" t="inlineStr"/>
-      <c r="O34" s="5" t="inlineStr"/>
-      <c r="P34" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O34" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P34" s="5" t="inlineStr"/>
       <c r="Q34" s="5" t="inlineStr"/>
       <c r="R34" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S34" s="5" t="inlineStr"/>
       <c r="T34" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U34" s="5" t="inlineStr"/>
+      <c r="V34" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
@@ -7010,46 +7478,52 @@
       <c r="E35" s="5" t="n">
         <v>0.9833</v>
       </c>
-      <c r="F35" s="5" t="inlineStr"/>
-      <c r="G35" s="5" t="inlineStr"/>
+      <c r="F35" s="5" t="n">
+        <v>0.08376688909880559</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0.03441493291566089</v>
+      </c>
       <c r="H35" s="5" t="inlineStr"/>
-      <c r="I35" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I35" s="5" t="inlineStr"/>
       <c r="J35" s="5" t="inlineStr"/>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr"/>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N35" s="5" t="inlineStr"/>
-      <c r="O35" s="5" t="inlineStr"/>
-      <c r="P35" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O35" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P35" s="5" t="inlineStr"/>
       <c r="Q35" s="5" t="inlineStr"/>
       <c r="R35" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S35" s="5" t="inlineStr"/>
       <c r="T35" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U35" s="5" t="inlineStr"/>
+      <c r="V35" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W35" s="5" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
@@ -7071,46 +7545,52 @@
       <c r="E36" s="5" t="n">
         <v>0.9569</v>
       </c>
-      <c r="F36" s="5" t="inlineStr"/>
-      <c r="G36" s="5" t="inlineStr"/>
+      <c r="F36" s="5" t="n">
+        <v>0.165261756131016</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0.1792215413644107</v>
+      </c>
       <c r="H36" s="5" t="inlineStr"/>
-      <c r="I36" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I36" s="5" t="inlineStr"/>
       <c r="J36" s="5" t="inlineStr"/>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr"/>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N36" s="5" t="inlineStr"/>
-      <c r="O36" s="5" t="inlineStr"/>
-      <c r="P36" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O36" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P36" s="5" t="inlineStr"/>
       <c r="Q36" s="5" t="inlineStr"/>
       <c r="R36" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S36" s="5" t="inlineStr"/>
       <c r="T36" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U36" s="5" t="inlineStr"/>
+      <c r="V36" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
@@ -7131,43 +7611,45 @@
       <c r="F37" s="5" t="inlineStr"/>
       <c r="G37" s="5" t="inlineStr"/>
       <c r="H37" s="5" t="inlineStr"/>
-      <c r="I37" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I37" s="5" t="inlineStr"/>
       <c r="J37" s="5" t="inlineStr"/>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr"/>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N37" s="5" t="inlineStr"/>
-      <c r="O37" s="5" t="inlineStr"/>
-      <c r="P37" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O37" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P37" s="5" t="inlineStr"/>
       <c r="Q37" s="5" t="inlineStr"/>
       <c r="R37" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S37" s="5" t="inlineStr"/>
       <c r="T37" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U37" s="5" t="inlineStr"/>
+      <c r="V37" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
@@ -7192,43 +7674,45 @@
       <c r="F38" s="5" t="inlineStr"/>
       <c r="G38" s="5" t="inlineStr"/>
       <c r="H38" s="5" t="inlineStr"/>
-      <c r="I38" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I38" s="5" t="inlineStr"/>
       <c r="J38" s="5" t="inlineStr"/>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr"/>
       <c r="M38" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N38" s="5" t="inlineStr"/>
-      <c r="O38" s="5" t="inlineStr"/>
-      <c r="P38" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O38" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P38" s="5" t="inlineStr"/>
       <c r="Q38" s="5" t="inlineStr"/>
       <c r="R38" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S38" s="5" t="inlineStr"/>
       <c r="T38" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U38" s="5" t="inlineStr"/>
+      <c r="V38" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
@@ -7251,45 +7735,49 @@
         <v>0.9819</v>
       </c>
       <c r="F39" s="5" t="inlineStr"/>
-      <c r="G39" s="5" t="inlineStr"/>
+      <c r="G39" s="5" t="n">
+        <v>0.08800887843952154</v>
+      </c>
       <c r="H39" s="5" t="inlineStr"/>
-      <c r="I39" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I39" s="5" t="inlineStr"/>
       <c r="J39" s="5" t="inlineStr"/>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr"/>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N39" s="5" t="inlineStr"/>
-      <c r="O39" s="5" t="inlineStr"/>
-      <c r="P39" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O39" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P39" s="5" t="inlineStr"/>
       <c r="Q39" s="5" t="inlineStr"/>
       <c r="R39" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S39" s="5" t="inlineStr"/>
       <c r="T39" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U39" s="5" t="inlineStr"/>
+      <c r="V39" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
@@ -7312,45 +7800,49 @@
         <v>0.9819</v>
       </c>
       <c r="F40" s="5" t="inlineStr"/>
-      <c r="G40" s="5" t="inlineStr"/>
+      <c r="G40" s="5" t="n">
+        <v>0.1119293945604837</v>
+      </c>
       <c r="H40" s="5" t="inlineStr"/>
-      <c r="I40" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I40" s="5" t="inlineStr"/>
       <c r="J40" s="5" t="inlineStr"/>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L40" s="5" t="inlineStr"/>
       <c r="M40" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N40" s="5" t="inlineStr"/>
-      <c r="O40" s="5" t="inlineStr"/>
-      <c r="P40" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O40" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P40" s="5" t="inlineStr"/>
       <c r="Q40" s="5" t="inlineStr"/>
       <c r="R40" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S40" s="5" t="inlineStr"/>
       <c r="T40" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U40" s="5" t="inlineStr"/>
+      <c r="V40" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
@@ -7373,45 +7865,49 @@
         <v>0.9819</v>
       </c>
       <c r="F41" s="5" t="inlineStr"/>
-      <c r="G41" s="5" t="inlineStr"/>
+      <c r="G41" s="5" t="n">
+        <v>0.0123018750239543</v>
+      </c>
       <c r="H41" s="5" t="inlineStr"/>
-      <c r="I41" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I41" s="5" t="inlineStr"/>
       <c r="J41" s="5" t="inlineStr"/>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr"/>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N41" s="5" t="inlineStr"/>
-      <c r="O41" s="5" t="inlineStr"/>
-      <c r="P41" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O41" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P41" s="5" t="inlineStr"/>
       <c r="Q41" s="5" t="inlineStr"/>
       <c r="R41" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S41" s="5" t="inlineStr"/>
       <c r="T41" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U41" s="5" t="inlineStr"/>
+      <c r="V41" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W41" s="5" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
@@ -7434,43 +7930,45 @@
       <c r="F42" s="5" t="inlineStr"/>
       <c r="G42" s="5" t="inlineStr"/>
       <c r="H42" s="5" t="inlineStr"/>
-      <c r="I42" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I42" s="5" t="inlineStr"/>
       <c r="J42" s="5" t="inlineStr"/>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L42" s="5" t="inlineStr"/>
       <c r="M42" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N42" s="5" t="inlineStr"/>
-      <c r="O42" s="5" t="inlineStr"/>
-      <c r="P42" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O42" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P42" s="5" t="inlineStr"/>
       <c r="Q42" s="5" t="inlineStr"/>
       <c r="R42" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S42" s="5" t="inlineStr"/>
       <c r="T42" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U42" s="5" t="inlineStr"/>
+      <c r="V42" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
@@ -7493,43 +7991,45 @@
       <c r="F43" s="5" t="inlineStr"/>
       <c r="G43" s="5" t="inlineStr"/>
       <c r="H43" s="5" t="inlineStr"/>
-      <c r="I43" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I43" s="5" t="inlineStr"/>
       <c r="J43" s="5" t="inlineStr"/>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr"/>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N43" s="5" t="inlineStr"/>
-      <c r="O43" s="5" t="inlineStr"/>
-      <c r="P43" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O43" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P43" s="5" t="inlineStr"/>
       <c r="Q43" s="5" t="inlineStr"/>
       <c r="R43" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S43" s="5" t="inlineStr"/>
       <c r="T43" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U43" s="5" t="inlineStr"/>
+      <c r="V43" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
@@ -7551,46 +8051,52 @@
       <c r="E44" s="5" t="n">
         <v>0.9829</v>
       </c>
-      <c r="F44" s="5" t="inlineStr"/>
-      <c r="G44" s="5" t="inlineStr"/>
+      <c r="F44" s="5" t="n">
+        <v>0.006730440322401998</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>0.1828368307734174</v>
+      </c>
       <c r="H44" s="5" t="inlineStr"/>
-      <c r="I44" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I44" s="5" t="inlineStr"/>
       <c r="J44" s="5" t="inlineStr"/>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L44" s="5" t="inlineStr"/>
       <c r="M44" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N44" s="5" t="inlineStr"/>
-      <c r="O44" s="5" t="inlineStr"/>
-      <c r="P44" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O44" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P44" s="5" t="inlineStr"/>
       <c r="Q44" s="5" t="inlineStr"/>
       <c r="R44" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S44" s="5" t="inlineStr"/>
       <c r="T44" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U44" s="5" t="inlineStr"/>
+      <c r="V44" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W44" s="5" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
@@ -7615,43 +8121,45 @@
       <c r="F45" s="5" t="inlineStr"/>
       <c r="G45" s="5" t="inlineStr"/>
       <c r="H45" s="5" t="inlineStr"/>
-      <c r="I45" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I45" s="5" t="inlineStr"/>
       <c r="J45" s="5" t="inlineStr"/>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr"/>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N45" s="5" t="inlineStr"/>
-      <c r="O45" s="5" t="inlineStr"/>
-      <c r="P45" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O45" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P45" s="5" t="inlineStr"/>
       <c r="Q45" s="5" t="inlineStr"/>
       <c r="R45" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S45" s="5" t="inlineStr"/>
       <c r="T45" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U45" s="5" t="inlineStr"/>
+      <c r="V45" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W45" s="5" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
@@ -7673,46 +8181,52 @@
       <c r="E46" s="5" t="n">
         <v>0.901</v>
       </c>
-      <c r="F46" s="5" t="inlineStr"/>
-      <c r="G46" s="5" t="inlineStr"/>
+      <c r="F46" s="5" t="n">
+        <v>0.1118721818565486</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>0.178900785388332</v>
+      </c>
       <c r="H46" s="5" t="inlineStr"/>
-      <c r="I46" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I46" s="5" t="inlineStr"/>
       <c r="J46" s="5" t="inlineStr"/>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L46" s="5" t="inlineStr"/>
       <c r="M46" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N46" s="5" t="inlineStr"/>
-      <c r="O46" s="5" t="inlineStr"/>
-      <c r="P46" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O46" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P46" s="5" t="inlineStr"/>
       <c r="Q46" s="5" t="inlineStr"/>
       <c r="R46" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S46" s="5" t="inlineStr"/>
       <c r="T46" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U46" s="5" t="inlineStr"/>
+      <c r="V46" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
@@ -7734,46 +8248,52 @@
       <c r="E47" s="5" t="n">
         <v>0.983</v>
       </c>
-      <c r="F47" s="5" t="inlineStr"/>
-      <c r="G47" s="5" t="inlineStr"/>
+      <c r="F47" s="5" t="n">
+        <v>0.07862362779385146</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0.1393456838590317</v>
+      </c>
       <c r="H47" s="5" t="inlineStr"/>
-      <c r="I47" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I47" s="5" t="inlineStr"/>
       <c r="J47" s="5" t="inlineStr"/>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr"/>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N47" s="5" t="inlineStr"/>
-      <c r="O47" s="5" t="inlineStr"/>
-      <c r="P47" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O47" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P47" s="5" t="inlineStr"/>
       <c r="Q47" s="5" t="inlineStr"/>
       <c r="R47" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S47" s="5" t="inlineStr"/>
       <c r="T47" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U47" s="5" t="inlineStr"/>
+      <c r="V47" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W47" s="5" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
@@ -7798,43 +8318,45 @@
       <c r="F48" s="5" t="inlineStr"/>
       <c r="G48" s="5" t="inlineStr"/>
       <c r="H48" s="5" t="inlineStr"/>
-      <c r="I48" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I48" s="5" t="inlineStr"/>
       <c r="J48" s="5" t="inlineStr"/>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L48" s="5" t="inlineStr"/>
       <c r="M48" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N48" s="5" t="inlineStr"/>
-      <c r="O48" s="5" t="inlineStr"/>
-      <c r="P48" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O48" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P48" s="5" t="inlineStr"/>
       <c r="Q48" s="5" t="inlineStr"/>
       <c r="R48" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S48" s="5" t="inlineStr"/>
       <c r="T48" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U48" s="5" t="inlineStr"/>
+      <c r="V48" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W48" s="5" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
@@ -7856,46 +8378,52 @@
       <c r="E49" s="5" t="n">
         <v>0.9569</v>
       </c>
-      <c r="F49" s="5" t="inlineStr"/>
-      <c r="G49" s="5" t="inlineStr"/>
+      <c r="F49" s="5" t="n">
+        <v>0.09237139852010201</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.09029336657571219</v>
+      </c>
       <c r="H49" s="5" t="inlineStr"/>
-      <c r="I49" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I49" s="5" t="inlineStr"/>
       <c r="J49" s="5" t="inlineStr"/>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr"/>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N49" s="5" t="inlineStr"/>
-      <c r="O49" s="5" t="inlineStr"/>
-      <c r="P49" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O49" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P49" s="5" t="inlineStr"/>
       <c r="Q49" s="5" t="inlineStr"/>
       <c r="R49" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S49" s="5" t="inlineStr"/>
       <c r="T49" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U49" s="5" t="inlineStr"/>
+      <c r="V49" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
@@ -7917,46 +8445,52 @@
       <c r="E50" s="5" t="n">
         <v>0.9519</v>
       </c>
-      <c r="F50" s="5" t="inlineStr"/>
-      <c r="G50" s="5" t="inlineStr"/>
+      <c r="F50" s="5" t="n">
+        <v>0.1347524443952343</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0.1060249296605559</v>
+      </c>
       <c r="H50" s="5" t="inlineStr"/>
-      <c r="I50" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I50" s="5" t="inlineStr"/>
       <c r="J50" s="5" t="inlineStr"/>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L50" s="5" t="inlineStr"/>
       <c r="M50" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N50" s="5" t="inlineStr"/>
-      <c r="O50" s="5" t="inlineStr"/>
-      <c r="P50" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O50" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P50" s="5" t="inlineStr"/>
       <c r="Q50" s="5" t="inlineStr"/>
       <c r="R50" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S50" s="5" t="inlineStr"/>
       <c r="T50" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U50" s="5" t="inlineStr"/>
+      <c r="V50" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W50" s="5" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
@@ -7981,43 +8515,45 @@
       <c r="F51" s="5" t="inlineStr"/>
       <c r="G51" s="5" t="inlineStr"/>
       <c r="H51" s="5" t="inlineStr"/>
-      <c r="I51" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I51" s="5" t="inlineStr"/>
       <c r="J51" s="5" t="inlineStr"/>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr"/>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N51" s="5" t="inlineStr"/>
-      <c r="O51" s="5" t="inlineStr"/>
-      <c r="P51" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O51" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P51" s="5" t="inlineStr"/>
       <c r="Q51" s="5" t="inlineStr"/>
       <c r="R51" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S51" s="5" t="inlineStr"/>
       <c r="T51" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U51" s="5" t="inlineStr"/>
+      <c r="V51" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W51" s="5" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
@@ -8039,46 +8575,52 @@
       <c r="E52" s="5" t="n">
         <v>0.9893999999999999</v>
       </c>
-      <c r="F52" s="5" t="inlineStr"/>
-      <c r="G52" s="5" t="inlineStr"/>
+      <c r="F52" s="5" t="n">
+        <v>0.05030984963358887</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0.0523074239242165</v>
+      </c>
       <c r="H52" s="5" t="inlineStr"/>
-      <c r="I52" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I52" s="5" t="inlineStr"/>
       <c r="J52" s="5" t="inlineStr"/>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L52" s="5" t="inlineStr"/>
       <c r="M52" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N52" s="5" t="inlineStr"/>
-      <c r="O52" s="5" t="inlineStr"/>
-      <c r="P52" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O52" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P52" s="5" t="inlineStr"/>
       <c r="Q52" s="5" t="inlineStr"/>
       <c r="R52" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S52" s="5" t="inlineStr"/>
       <c r="T52" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U52" s="5" t="inlineStr"/>
+      <c r="V52" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W52" s="5" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
@@ -8100,46 +8642,52 @@
       <c r="E53" s="5" t="n">
         <v>0.9569</v>
       </c>
-      <c r="F53" s="5" t="inlineStr"/>
-      <c r="G53" s="5" t="inlineStr"/>
+      <c r="F53" s="5" t="n">
+        <v>0.1905628760534537</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0.2791924245645767</v>
+      </c>
       <c r="H53" s="5" t="inlineStr"/>
-      <c r="I53" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I53" s="5" t="inlineStr"/>
       <c r="J53" s="5" t="inlineStr"/>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr"/>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N53" s="5" t="inlineStr"/>
-      <c r="O53" s="5" t="inlineStr"/>
-      <c r="P53" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O53" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P53" s="5" t="inlineStr"/>
       <c r="Q53" s="5" t="inlineStr"/>
       <c r="R53" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S53" s="5" t="inlineStr"/>
       <c r="T53" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U53" s="5" t="inlineStr"/>
+      <c r="V53" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W53" s="5" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
@@ -8161,46 +8709,52 @@
       <c r="E54" s="5" t="n">
         <v>0.8881</v>
       </c>
-      <c r="F54" s="5" t="inlineStr"/>
-      <c r="G54" s="5" t="inlineStr"/>
+      <c r="F54" s="5" t="n">
+        <v>0.1929403130048908</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0.2955409110236449</v>
+      </c>
       <c r="H54" s="5" t="inlineStr"/>
-      <c r="I54" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I54" s="5" t="inlineStr"/>
       <c r="J54" s="5" t="inlineStr"/>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L54" s="5" t="inlineStr"/>
       <c r="M54" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N54" s="5" t="inlineStr"/>
-      <c r="O54" s="5" t="inlineStr"/>
-      <c r="P54" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O54" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P54" s="5" t="inlineStr"/>
       <c r="Q54" s="5" t="inlineStr"/>
       <c r="R54" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S54" s="5" t="inlineStr"/>
       <c r="T54" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U54" s="5" t="inlineStr"/>
+      <c r="V54" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W54" s="5" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
@@ -8222,46 +8776,52 @@
       <c r="E55" s="5" t="n">
         <v>0.8881</v>
       </c>
-      <c r="F55" s="5" t="inlineStr"/>
-      <c r="G55" s="5" t="inlineStr"/>
+      <c r="F55" s="5" t="n">
+        <v>0.1820130053159992</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0.2502015276870414</v>
+      </c>
       <c r="H55" s="5" t="inlineStr"/>
-      <c r="I55" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I55" s="5" t="inlineStr"/>
       <c r="J55" s="5" t="inlineStr"/>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr"/>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N55" s="5" t="inlineStr"/>
-      <c r="O55" s="5" t="inlineStr"/>
-      <c r="P55" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O55" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P55" s="5" t="inlineStr"/>
       <c r="Q55" s="5" t="inlineStr"/>
       <c r="R55" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S55" s="5" t="inlineStr"/>
       <c r="T55" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U55" s="5" t="inlineStr"/>
+      <c r="V55" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W55" s="5" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
@@ -8283,46 +8843,52 @@
       <c r="E56" s="5" t="n">
         <v>0.9952</v>
       </c>
-      <c r="F56" s="5" t="inlineStr"/>
-      <c r="G56" s="5" t="inlineStr"/>
+      <c r="F56" s="5" t="n">
+        <v>0.06059805759477788</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0.0793430622023733</v>
+      </c>
       <c r="H56" s="5" t="inlineStr"/>
-      <c r="I56" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I56" s="5" t="inlineStr"/>
       <c r="J56" s="5" t="inlineStr"/>
       <c r="K56" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L56" s="5" t="inlineStr"/>
       <c r="M56" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N56" s="5" t="inlineStr"/>
-      <c r="O56" s="5" t="inlineStr"/>
-      <c r="P56" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O56" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P56" s="5" t="inlineStr"/>
       <c r="Q56" s="5" t="inlineStr"/>
       <c r="R56" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S56" s="5" t="inlineStr"/>
       <c r="T56" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U56" s="5" t="inlineStr"/>
+      <c r="V56" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W56" s="5" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
@@ -8341,43 +8907,45 @@
       <c r="F57" s="5" t="inlineStr"/>
       <c r="G57" s="5" t="inlineStr"/>
       <c r="H57" s="5" t="inlineStr"/>
-      <c r="I57" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I57" s="5" t="inlineStr"/>
       <c r="J57" s="5" t="inlineStr"/>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L57" s="5" t="inlineStr"/>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N57" s="5" t="inlineStr"/>
-      <c r="O57" s="5" t="inlineStr"/>
-      <c r="P57" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O57" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P57" s="5" t="inlineStr"/>
       <c r="Q57" s="5" t="inlineStr"/>
       <c r="R57" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S57" s="5" t="inlineStr"/>
       <c r="T57" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U57" s="5" t="inlineStr"/>
+      <c r="V57" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W57" s="5" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
@@ -8400,45 +8968,49 @@
         <v>0.9837</v>
       </c>
       <c r="F58" s="5" t="inlineStr"/>
-      <c r="G58" s="5" t="inlineStr"/>
+      <c r="G58" s="5" t="n">
+        <v>0.1030626282962745</v>
+      </c>
       <c r="H58" s="5" t="inlineStr"/>
-      <c r="I58" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I58" s="5" t="inlineStr"/>
       <c r="J58" s="5" t="inlineStr"/>
       <c r="K58" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L58" s="5" t="inlineStr"/>
       <c r="M58" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N58" s="5" t="inlineStr"/>
-      <c r="O58" s="5" t="inlineStr"/>
-      <c r="P58" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O58" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P58" s="5" t="inlineStr"/>
       <c r="Q58" s="5" t="inlineStr"/>
       <c r="R58" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S58" s="5" t="inlineStr"/>
       <c r="T58" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U58" s="5" t="inlineStr"/>
+      <c r="V58" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W58" s="5" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
@@ -8460,46 +9032,52 @@
       <c r="E59" s="5" t="n">
         <v>0.951</v>
       </c>
-      <c r="F59" s="5" t="inlineStr"/>
-      <c r="G59" s="5" t="inlineStr"/>
+      <c r="F59" s="5" t="n">
+        <v>0.1701534557235311</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>0.2438491711773283</v>
+      </c>
       <c r="H59" s="5" t="inlineStr"/>
-      <c r="I59" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I59" s="5" t="inlineStr"/>
       <c r="J59" s="5" t="inlineStr"/>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L59" s="5" t="inlineStr"/>
       <c r="M59" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N59" s="5" t="inlineStr"/>
-      <c r="O59" s="5" t="inlineStr"/>
-      <c r="P59" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O59" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P59" s="5" t="inlineStr"/>
       <c r="Q59" s="5" t="inlineStr"/>
       <c r="R59" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S59" s="5" t="inlineStr"/>
       <c r="T59" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U59" s="5" t="inlineStr"/>
+      <c r="V59" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W59" s="5" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
@@ -8521,46 +9099,52 @@
       <c r="E60" s="5" t="n">
         <v>0.9832</v>
       </c>
-      <c r="F60" s="5" t="inlineStr"/>
-      <c r="G60" s="5" t="inlineStr"/>
+      <c r="F60" s="5" t="n">
+        <v>0.0683590128113456</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>0.02031868173035667</v>
+      </c>
       <c r="H60" s="5" t="inlineStr"/>
-      <c r="I60" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I60" s="5" t="inlineStr"/>
       <c r="J60" s="5" t="inlineStr"/>
       <c r="K60" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L60" s="5" t="inlineStr"/>
       <c r="M60" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N60" s="5" t="inlineStr"/>
-      <c r="O60" s="5" t="inlineStr"/>
-      <c r="P60" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O60" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P60" s="5" t="inlineStr"/>
       <c r="Q60" s="5" t="inlineStr"/>
       <c r="R60" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S60" s="5" t="inlineStr"/>
       <c r="T60" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U60" s="5" t="inlineStr"/>
+      <c r="V60" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W60" s="5" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
@@ -8585,43 +9169,45 @@
       <c r="F61" s="5" t="inlineStr"/>
       <c r="G61" s="5" t="inlineStr"/>
       <c r="H61" s="5" t="inlineStr"/>
-      <c r="I61" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I61" s="5" t="inlineStr"/>
       <c r="J61" s="5" t="inlineStr"/>
       <c r="K61" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L61" s="5" t="inlineStr"/>
       <c r="M61" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N61" s="5" t="inlineStr"/>
-      <c r="O61" s="5" t="inlineStr"/>
-      <c r="P61" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O61" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P61" s="5" t="inlineStr"/>
       <c r="Q61" s="5" t="inlineStr"/>
       <c r="R61" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S61" s="5" t="inlineStr"/>
       <c r="T61" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U61" s="5" t="inlineStr"/>
+      <c r="V61" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W61" s="5" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
@@ -8646,43 +9232,45 @@
       <c r="F62" s="5" t="inlineStr"/>
       <c r="G62" s="5" t="inlineStr"/>
       <c r="H62" s="5" t="inlineStr"/>
-      <c r="I62" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I62" s="5" t="inlineStr"/>
       <c r="J62" s="5" t="inlineStr"/>
       <c r="K62" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L62" s="5" t="inlineStr"/>
       <c r="M62" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N62" s="5" t="inlineStr"/>
-      <c r="O62" s="5" t="inlineStr"/>
-      <c r="P62" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O62" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P62" s="5" t="inlineStr"/>
       <c r="Q62" s="5" t="inlineStr"/>
       <c r="R62" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S62" s="5" t="inlineStr"/>
       <c r="T62" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U62" s="5" t="inlineStr"/>
+      <c r="V62" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W62" s="5" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
@@ -8707,43 +9295,45 @@
       <c r="F63" s="5" t="inlineStr"/>
       <c r="G63" s="5" t="inlineStr"/>
       <c r="H63" s="5" t="inlineStr"/>
-      <c r="I63" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I63" s="5" t="inlineStr"/>
       <c r="J63" s="5" t="inlineStr"/>
       <c r="K63" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L63" s="5" t="inlineStr"/>
       <c r="M63" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N63" s="5" t="inlineStr"/>
-      <c r="O63" s="5" t="inlineStr"/>
-      <c r="P63" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O63" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P63" s="5" t="inlineStr"/>
       <c r="Q63" s="5" t="inlineStr"/>
       <c r="R63" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S63" s="5" t="inlineStr"/>
       <c r="T63" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U63" s="5" t="inlineStr"/>
+      <c r="V63" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W63" s="5" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
@@ -8768,43 +9358,45 @@
       <c r="F64" s="5" t="inlineStr"/>
       <c r="G64" s="5" t="inlineStr"/>
       <c r="H64" s="5" t="inlineStr"/>
-      <c r="I64" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I64" s="5" t="inlineStr"/>
       <c r="J64" s="5" t="inlineStr"/>
       <c r="K64" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L64" s="5" t="inlineStr"/>
       <c r="M64" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N64" s="5" t="inlineStr"/>
-      <c r="O64" s="5" t="inlineStr"/>
-      <c r="P64" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O64" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P64" s="5" t="inlineStr"/>
       <c r="Q64" s="5" t="inlineStr"/>
       <c r="R64" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S64" s="5" t="inlineStr"/>
       <c r="T64" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U64" s="5" t="inlineStr"/>
+      <c r="V64" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W64" s="5" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
@@ -8829,43 +9421,45 @@
       <c r="F65" s="5" t="inlineStr"/>
       <c r="G65" s="5" t="inlineStr"/>
       <c r="H65" s="5" t="inlineStr"/>
-      <c r="I65" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I65" s="5" t="inlineStr"/>
       <c r="J65" s="5" t="inlineStr"/>
       <c r="K65" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L65" s="5" t="inlineStr"/>
       <c r="M65" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N65" s="5" t="inlineStr"/>
-      <c r="O65" s="5" t="inlineStr"/>
-      <c r="P65" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O65" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P65" s="5" t="inlineStr"/>
       <c r="Q65" s="5" t="inlineStr"/>
       <c r="R65" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S65" s="5" t="inlineStr"/>
       <c r="T65" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U65" s="5" t="inlineStr"/>
+      <c r="V65" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W65" s="5" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
@@ -8890,43 +9484,45 @@
       <c r="F66" s="5" t="inlineStr"/>
       <c r="G66" s="5" t="inlineStr"/>
       <c r="H66" s="5" t="inlineStr"/>
-      <c r="I66" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I66" s="5" t="inlineStr"/>
       <c r="J66" s="5" t="inlineStr"/>
       <c r="K66" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L66" s="5" t="inlineStr"/>
       <c r="M66" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N66" s="5" t="inlineStr"/>
-      <c r="O66" s="5" t="inlineStr"/>
-      <c r="P66" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O66" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P66" s="5" t="inlineStr"/>
       <c r="Q66" s="5" t="inlineStr"/>
       <c r="R66" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S66" s="5" t="inlineStr"/>
       <c r="T66" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U66" s="5" t="inlineStr"/>
+      <c r="V66" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W66" s="5" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
@@ -8951,43 +9547,45 @@
       <c r="F67" s="5" t="inlineStr"/>
       <c r="G67" s="5" t="inlineStr"/>
       <c r="H67" s="5" t="inlineStr"/>
-      <c r="I67" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I67" s="5" t="inlineStr"/>
       <c r="J67" s="5" t="inlineStr"/>
       <c r="K67" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L67" s="5" t="inlineStr"/>
       <c r="M67" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N67" s="5" t="inlineStr"/>
-      <c r="O67" s="5" t="inlineStr"/>
-      <c r="P67" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O67" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P67" s="5" t="inlineStr"/>
       <c r="Q67" s="5" t="inlineStr"/>
       <c r="R67" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S67" s="5" t="inlineStr"/>
       <c r="T67" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U67" s="5" t="inlineStr"/>
+      <c r="V67" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W67" s="5" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
@@ -9009,46 +9607,52 @@
       <c r="E68" s="5" t="n">
         <v>0.9562</v>
       </c>
-      <c r="F68" s="5" t="inlineStr"/>
-      <c r="G68" s="5" t="inlineStr"/>
+      <c r="F68" s="5" t="n">
+        <v>0.1520359556040282</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>0.1684419945136396</v>
+      </c>
       <c r="H68" s="5" t="inlineStr"/>
-      <c r="I68" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I68" s="5" t="inlineStr"/>
       <c r="J68" s="5" t="inlineStr"/>
       <c r="K68" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L68" s="5" t="inlineStr"/>
       <c r="M68" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N68" s="5" t="inlineStr"/>
-      <c r="O68" s="5" t="inlineStr"/>
-      <c r="P68" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O68" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P68" s="5" t="inlineStr"/>
       <c r="Q68" s="5" t="inlineStr"/>
       <c r="R68" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S68" s="5" t="inlineStr"/>
       <c r="T68" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U68" s="5" t="inlineStr"/>
+      <c r="V68" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W68" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C68">
@@ -9279,6 +9883,30 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="V2:V68">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W2:W68">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/VIC_curtailment.xlsx
+++ b/outputs/VIC_curtailment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -67,7 +67,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -82,9 +82,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -456,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X68"/>
+  <dimension ref="A1:P67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -475,14 +472,6 @@
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="12" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -566,46 +555,6 @@
           <t>FY26-27 (Draft)</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Curt FY1</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Curt FY2</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Curt FY3</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Curt Avg</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Offl FY1</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Offl FY2</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Offl FY3</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Offl Avg</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -650,10 +599,10 @@
         <v>66</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>0.3710560565867671</v>
+        <v>0.3236</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>0.2719808764553837</v>
+        <v>0.2465</v>
       </c>
       <c r="L2" s="5" t="n">
         <v>0.833539620209753</v>
@@ -669,30 +618,6 @@
       </c>
       <c r="P2" s="5" t="n">
         <v>0.9114</v>
-      </c>
-      <c r="Q2" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="S2" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" s="6" t="n">
-        <v>0.02666666666666667</v>
-      </c>
-      <c r="U2" s="6" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="V2" s="6" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="W2" s="6" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="X2" s="6" t="n">
-        <v>0.12</v>
       </c>
     </row>
     <row r="3">
@@ -742,14 +667,6 @@
       <c r="P3" s="5" t="n">
         <v>0.9012</v>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
-      <c r="V3" s="6" t="inlineStr"/>
-      <c r="W3" s="6" t="inlineStr"/>
-      <c r="X3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -788,17 +705,13 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>31</v>
+        <v>31.16</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="J4" s="5" t="n">
-        <v>0.1600293147297279</v>
-      </c>
-      <c r="K4" s="5" t="n">
-        <v>0.2827710603192121</v>
-      </c>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
       <c r="L4" s="5" t="n">
         <v>0.547516873654646</v>
       </c>
@@ -814,30 +727,6 @@
       <c r="P4" s="5" t="n">
         <v>0.9307</v>
       </c>
-      <c r="Q4" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="S4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" s="6" t="n">
-        <v>0.02666666666666667</v>
-      </c>
-      <c r="U4" s="6" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="V4" s="6" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="W4" s="6" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="X4" s="6" t="n">
-        <v>0.12</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -882,10 +771,10 @@
         <v>66</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>0.05215670207613177</v>
+        <v>0.0499</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>0.05460168559670209</v>
+        <v>0.054</v>
       </c>
       <c r="L5" s="5" t="n">
         <v>0.547516873654646</v>
@@ -902,30 +791,6 @@
       <c r="P5" s="5" t="n">
         <v>0.9307</v>
       </c>
-      <c r="Q5" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="S5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" s="6" t="n">
-        <v>0.02666666666666667</v>
-      </c>
-      <c r="U5" s="6" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="V5" s="6" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="W5" s="6" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="X5" s="6" t="n">
-        <v>0.12</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -964,14 +829,14 @@
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>93.31</v>
+        <v>93.48</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>66</v>
       </c>
       <c r="J6" s="5" t="inlineStr"/>
       <c r="K6" s="5" t="n">
-        <v>0.2650311526126716</v>
+        <v>0.2374</v>
       </c>
       <c r="L6" s="5" t="n">
         <v>0.389503957787889</v>
@@ -988,30 +853,6 @@
       <c r="P6" s="5" t="n">
         <v>0.9223</v>
       </c>
-      <c r="Q6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" s="6" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="V6" s="6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="W6" s="6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="X6" s="6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1055,11 +896,9 @@
       <c r="I7" s="2" t="n">
         <v>220</v>
       </c>
-      <c r="J7" s="5" t="n">
-        <v>0.1954445746044534</v>
-      </c>
+      <c r="J7" s="5" t="inlineStr"/>
       <c r="K7" s="5" t="n">
-        <v>0.07798287623836642</v>
+        <v>0.0688</v>
       </c>
       <c r="L7" s="5" t="n">
         <v>0.390717855103594</v>
@@ -1076,30 +915,6 @@
       <c r="P7" s="5" t="n">
         <v>0.9292</v>
       </c>
-      <c r="Q7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="6" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="V7" s="6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="W7" s="6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="X7" s="6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1138,10 +953,10 @@
       </c>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="5" t="n">
-        <v>0.1990273759688161</v>
+        <v>0.1836</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>0.2408960878187453</v>
+        <v>0.2057</v>
       </c>
       <c r="L8" s="5" t="inlineStr"/>
       <c r="M8" s="5" t="inlineStr"/>
@@ -1154,14 +969,6 @@
       <c r="P8" s="5" t="n">
         <v>0.922</v>
       </c>
-      <c r="Q8" s="6" t="inlineStr"/>
-      <c r="R8" s="6" t="inlineStr"/>
-      <c r="S8" s="6" t="inlineStr"/>
-      <c r="T8" s="6" t="inlineStr"/>
-      <c r="U8" s="6" t="inlineStr"/>
-      <c r="V8" s="6" t="inlineStr"/>
-      <c r="W8" s="6" t="inlineStr"/>
-      <c r="X8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1210,14 +1017,6 @@
       <c r="P9" s="5" t="n">
         <v>0.9262</v>
       </c>
-      <c r="Q9" s="6" t="inlineStr"/>
-      <c r="R9" s="6" t="inlineStr"/>
-      <c r="S9" s="6" t="inlineStr"/>
-      <c r="T9" s="6" t="inlineStr"/>
-      <c r="U9" s="6" t="inlineStr"/>
-      <c r="V9" s="6" t="inlineStr"/>
-      <c r="W9" s="6" t="inlineStr"/>
-      <c r="X9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1256,16 +1055,16 @@
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>104</v>
+        <v>104.5</v>
       </c>
       <c r="I10" s="2" t="n">
         <v>66</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>0.3169574937730341</v>
+        <v>0.2761</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>0.1686799728674456</v>
+        <v>0.159</v>
       </c>
       <c r="L10" s="5" t="n">
         <v>0.8554020168196</v>
@@ -1282,30 +1081,6 @@
       <c r="P10" s="5" t="n">
         <v>0.9088000000000001</v>
       </c>
-      <c r="Q10" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="S10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" s="6" t="n">
-        <v>0.02666666666666667</v>
-      </c>
-      <c r="U10" s="6" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="V10" s="6" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="W10" s="6" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="X10" s="6" t="n">
-        <v>0.12</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1344,9 +1119,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="n">
-        <v>0.04898598021985823</v>
-      </c>
+      <c r="K11" s="5" t="inlineStr"/>
       <c r="L11" s="5" t="inlineStr"/>
       <c r="M11" s="5" t="inlineStr"/>
       <c r="N11" s="5" t="n">
@@ -1358,14 +1131,6 @@
       <c r="P11" s="5" t="n">
         <v>0.9330000000000001</v>
       </c>
-      <c r="Q11" s="6" t="inlineStr"/>
-      <c r="R11" s="6" t="inlineStr"/>
-      <c r="S11" s="6" t="inlineStr"/>
-      <c r="T11" s="6" t="inlineStr"/>
-      <c r="U11" s="6" t="inlineStr"/>
-      <c r="V11" s="6" t="inlineStr"/>
-      <c r="W11" s="6" t="inlineStr"/>
-      <c r="X11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1404,16 +1169,16 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>239</v>
+        <v>199.95</v>
       </c>
       <c r="I12" s="2" t="n">
         <v>220</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0.1091648532990047</v>
+        <v>0.106</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>0.1136272868211855</v>
+        <v>0.1081</v>
       </c>
       <c r="L12" s="5" t="n">
         <v>0.827440107601162</v>
@@ -1429,30 +1194,6 @@
       </c>
       <c r="P12" s="5" t="n">
         <v>0.878</v>
-      </c>
-      <c r="Q12" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="S12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" s="6" t="n">
-        <v>0.02666666666666667</v>
-      </c>
-      <c r="U12" s="6" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="V12" s="6" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="W12" s="6" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="X12" s="6" t="n">
-        <v>0.12</v>
       </c>
     </row>
     <row r="13">
@@ -1500,14 +1241,6 @@
         <v>0.9441000000000001</v>
       </c>
       <c r="P13" s="5" t="inlineStr"/>
-      <c r="Q13" s="6" t="inlineStr"/>
-      <c r="R13" s="6" t="inlineStr"/>
-      <c r="S13" s="6" t="inlineStr"/>
-      <c r="T13" s="6" t="inlineStr"/>
-      <c r="U13" s="6" t="inlineStr"/>
-      <c r="V13" s="6" t="inlineStr"/>
-      <c r="W13" s="6" t="inlineStr"/>
-      <c r="X13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1546,9 +1279,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="5" t="inlineStr"/>
-      <c r="K14" s="5" t="n">
-        <v>0.1074948342034868</v>
-      </c>
+      <c r="K14" s="5" t="inlineStr"/>
       <c r="L14" s="5" t="inlineStr"/>
       <c r="M14" s="5" t="inlineStr"/>
       <c r="N14" s="5" t="n">
@@ -1560,14 +1291,6 @@
       <c r="P14" s="5" t="n">
         <v>0.9248</v>
       </c>
-      <c r="Q14" s="6" t="inlineStr"/>
-      <c r="R14" s="6" t="inlineStr"/>
-      <c r="S14" s="6" t="inlineStr"/>
-      <c r="T14" s="6" t="inlineStr"/>
-      <c r="U14" s="6" t="inlineStr"/>
-      <c r="V14" s="6" t="inlineStr"/>
-      <c r="W14" s="6" t="inlineStr"/>
-      <c r="X14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1606,16 +1329,16 @@
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>112</v>
+        <v>101.08</v>
       </c>
       <c r="I15" s="2" t="n">
         <v>66</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>0.3437740975604878</v>
+        <v>0.2971</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>0.1415139558510223</v>
+        <v>0.1275</v>
       </c>
       <c r="L15" s="5" t="n">
         <v>0.389503957787889</v>
@@ -1631,30 +1354,6 @@
       </c>
       <c r="P15" s="5" t="n">
         <v>0.9223</v>
-      </c>
-      <c r="Q15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" s="6" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="V15" s="6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="W15" s="6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="X15" s="6" t="n">
-        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1706,14 +1405,6 @@
       <c r="P16" s="5" t="n">
         <v>0.928</v>
       </c>
-      <c r="Q16" s="6" t="inlineStr"/>
-      <c r="R16" s="6" t="inlineStr"/>
-      <c r="S16" s="6" t="inlineStr"/>
-      <c r="T16" s="6" t="inlineStr"/>
-      <c r="U16" s="6" t="inlineStr"/>
-      <c r="V16" s="6" t="inlineStr"/>
-      <c r="W16" s="6" t="inlineStr"/>
-      <c r="X16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1758,10 +1449,10 @@
         <v>66</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>0.3584538984210027</v>
+        <v>0.3065</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>0.2739101642738966</v>
+        <v>0.2491</v>
       </c>
       <c r="L17" s="5" t="n">
         <v>0.833539620209753</v>
@@ -1778,30 +1469,6 @@
       <c r="P17" s="5" t="n">
         <v>0.9114</v>
       </c>
-      <c r="Q17" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="S17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" s="6" t="n">
-        <v>0.02666666666666667</v>
-      </c>
-      <c r="U17" s="6" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="V17" s="6" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="W17" s="6" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="X17" s="6" t="n">
-        <v>0.12</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1840,17 +1507,15 @@
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="I18" s="2" t="n">
         <v>66</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>0.2487248512923422</v>
-      </c>
-      <c r="K18" s="5" t="n">
-        <v>0.1094894731574723</v>
-      </c>
+        <v>0.2227</v>
+      </c>
+      <c r="K18" s="5" t="inlineStr"/>
       <c r="L18" s="5" t="n">
         <v>0.390717855103594</v>
       </c>
@@ -1866,30 +1531,6 @@
       <c r="P18" s="5" t="n">
         <v>0.922</v>
       </c>
-      <c r="Q18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" s="6" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="V18" s="6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="W18" s="6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="X18" s="6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1934,9 +1575,7 @@
         <v>66</v>
       </c>
       <c r="J19" s="5" t="inlineStr"/>
-      <c r="K19" s="5" t="n">
-        <v>0.1428920071912686</v>
-      </c>
+      <c r="K19" s="5" t="inlineStr"/>
       <c r="L19" s="5" t="n">
         <v>0.389503957787889</v>
       </c>
@@ -1952,14 +1591,6 @@
       <c r="P19" s="5" t="n">
         <v>0.9223</v>
       </c>
-      <c r="Q19" s="6" t="inlineStr"/>
-      <c r="R19" s="6" t="inlineStr"/>
-      <c r="S19" s="6" t="inlineStr"/>
-      <c r="T19" s="6" t="inlineStr"/>
-      <c r="U19" s="6" t="inlineStr"/>
-      <c r="V19" s="6" t="inlineStr"/>
-      <c r="W19" s="6" t="inlineStr"/>
-      <c r="X19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1998,16 +1629,16 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="I20" s="2" t="n">
         <v>66</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>0.3372382246917938</v>
+        <v>0.2786</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>0.2486746048568231</v>
+        <v>0.2351</v>
       </c>
       <c r="L20" s="5" t="n">
         <v>0.8554020168196</v>
@@ -2024,30 +1655,6 @@
       <c r="P20" s="5" t="n">
         <v>0.9088000000000001</v>
       </c>
-      <c r="Q20" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="S20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" s="6" t="n">
-        <v>0.02666666666666667</v>
-      </c>
-      <c r="U20" s="6" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="V20" s="6" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="W20" s="6" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="X20" s="6" t="n">
-        <v>0.12</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -2086,10 +1693,10 @@
       </c>
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="5" t="n">
-        <v>0.07896687551826564</v>
+        <v>0.0756</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>0.04879956378773898</v>
+        <v>0.0482</v>
       </c>
       <c r="L21" s="5" t="inlineStr"/>
       <c r="M21" s="5" t="inlineStr"/>
@@ -2102,14 +1709,6 @@
       <c r="P21" s="5" t="n">
         <v>0.8999</v>
       </c>
-      <c r="Q21" s="6" t="inlineStr"/>
-      <c r="R21" s="6" t="inlineStr"/>
-      <c r="S21" s="6" t="inlineStr"/>
-      <c r="T21" s="6" t="inlineStr"/>
-      <c r="U21" s="6" t="inlineStr"/>
-      <c r="V21" s="6" t="inlineStr"/>
-      <c r="W21" s="6" t="inlineStr"/>
-      <c r="X21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2148,10 +1747,10 @@
       </c>
       <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="5" t="n">
-        <v>0.007890464523191421</v>
+        <v>0.0078</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>0.005078393583182961</v>
+        <v>0.0051</v>
       </c>
       <c r="L22" s="5" t="inlineStr"/>
       <c r="M22" s="5" t="inlineStr"/>
@@ -2164,14 +1763,6 @@
       <c r="P22" s="5" t="n">
         <v>0.9913999999999999</v>
       </c>
-      <c r="Q22" s="6" t="inlineStr"/>
-      <c r="R22" s="6" t="inlineStr"/>
-      <c r="S22" s="6" t="inlineStr"/>
-      <c r="T22" s="6" t="inlineStr"/>
-      <c r="U22" s="6" t="inlineStr"/>
-      <c r="V22" s="6" t="inlineStr"/>
-      <c r="W22" s="6" t="inlineStr"/>
-      <c r="X22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2210,10 +1801,10 @@
       </c>
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="5" t="n">
-        <v>0.228198922467751</v>
+        <v>0.2041</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>0.2029431742155934</v>
+        <v>0.1906</v>
       </c>
       <c r="L23" s="5" t="inlineStr"/>
       <c r="M23" s="5" t="inlineStr"/>
@@ -2226,14 +1817,6 @@
       <c r="P23" s="5" t="n">
         <v>0.945</v>
       </c>
-      <c r="Q23" s="6" t="inlineStr"/>
-      <c r="R23" s="6" t="inlineStr"/>
-      <c r="S23" s="6" t="inlineStr"/>
-      <c r="T23" s="6" t="inlineStr"/>
-      <c r="U23" s="6" t="inlineStr"/>
-      <c r="V23" s="6" t="inlineStr"/>
-      <c r="W23" s="6" t="inlineStr"/>
-      <c r="X23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2272,10 +1855,10 @@
       </c>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="5" t="n">
-        <v>0.04586386696325562</v>
+        <v>0.045</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>0.03247885424318653</v>
+        <v>0.0316</v>
       </c>
       <c r="L24" s="5" t="inlineStr"/>
       <c r="M24" s="5" t="inlineStr"/>
@@ -2288,14 +1871,6 @@
       <c r="P24" s="5" t="n">
         <v>0.945</v>
       </c>
-      <c r="Q24" s="6" t="inlineStr"/>
-      <c r="R24" s="6" t="inlineStr"/>
-      <c r="S24" s="6" t="inlineStr"/>
-      <c r="T24" s="6" t="inlineStr"/>
-      <c r="U24" s="6" t="inlineStr"/>
-      <c r="V24" s="6" t="inlineStr"/>
-      <c r="W24" s="6" t="inlineStr"/>
-      <c r="X24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2334,10 +1909,10 @@
       </c>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="5" t="n">
-        <v>0.03468796155479126</v>
+        <v>0.0347</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>0.02811506234350913</v>
+        <v>0.0284</v>
       </c>
       <c r="L25" s="5" t="inlineStr"/>
       <c r="M25" s="5" t="inlineStr"/>
@@ -2350,14 +1925,6 @@
       <c r="P25" s="5" t="n">
         <v>0.89</v>
       </c>
-      <c r="Q25" s="6" t="inlineStr"/>
-      <c r="R25" s="6" t="inlineStr"/>
-      <c r="S25" s="6" t="inlineStr"/>
-      <c r="T25" s="6" t="inlineStr"/>
-      <c r="U25" s="6" t="inlineStr"/>
-      <c r="V25" s="6" t="inlineStr"/>
-      <c r="W25" s="6" t="inlineStr"/>
-      <c r="X25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2408,14 +1975,6 @@
       <c r="P26" s="5" t="n">
         <v>0.9801</v>
       </c>
-      <c r="Q26" s="6" t="inlineStr"/>
-      <c r="R26" s="6" t="inlineStr"/>
-      <c r="S26" s="6" t="inlineStr"/>
-      <c r="T26" s="6" t="inlineStr"/>
-      <c r="U26" s="6" t="inlineStr"/>
-      <c r="V26" s="6" t="inlineStr"/>
-      <c r="W26" s="6" t="inlineStr"/>
-      <c r="X26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2464,14 +2023,6 @@
         <v>0.9825</v>
       </c>
       <c r="P27" s="5" t="inlineStr"/>
-      <c r="Q27" s="6" t="inlineStr"/>
-      <c r="R27" s="6" t="inlineStr"/>
-      <c r="S27" s="6" t="inlineStr"/>
-      <c r="T27" s="6" t="inlineStr"/>
-      <c r="U27" s="6" t="inlineStr"/>
-      <c r="V27" s="6" t="inlineStr"/>
-      <c r="W27" s="6" t="inlineStr"/>
-      <c r="X27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2510,10 +2061,10 @@
       </c>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="5" t="n">
-        <v>0.06000630720703115</v>
+        <v>0.0578</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>0.0990364762086815</v>
+        <v>0.0958</v>
       </c>
       <c r="L28" s="5" t="inlineStr"/>
       <c r="M28" s="5" t="inlineStr"/>
@@ -2526,14 +2077,6 @@
       <c r="P28" s="5" t="n">
         <v>0.9978</v>
       </c>
-      <c r="Q28" s="6" t="inlineStr"/>
-      <c r="R28" s="6" t="inlineStr"/>
-      <c r="S28" s="6" t="inlineStr"/>
-      <c r="T28" s="6" t="inlineStr"/>
-      <c r="U28" s="6" t="inlineStr"/>
-      <c r="V28" s="6" t="inlineStr"/>
-      <c r="W28" s="6" t="inlineStr"/>
-      <c r="X28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2584,14 +2127,6 @@
       <c r="P29" s="5" t="n">
         <v>0.9952</v>
       </c>
-      <c r="Q29" s="6" t="inlineStr"/>
-      <c r="R29" s="6" t="inlineStr"/>
-      <c r="S29" s="6" t="inlineStr"/>
-      <c r="T29" s="6" t="inlineStr"/>
-      <c r="U29" s="6" t="inlineStr"/>
-      <c r="V29" s="6" t="inlineStr"/>
-      <c r="W29" s="6" t="inlineStr"/>
-      <c r="X29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2642,14 +2177,6 @@
       <c r="P30" s="5" t="n">
         <v>1.0065</v>
       </c>
-      <c r="Q30" s="6" t="inlineStr"/>
-      <c r="R30" s="6" t="inlineStr"/>
-      <c r="S30" s="6" t="inlineStr"/>
-      <c r="T30" s="6" t="inlineStr"/>
-      <c r="U30" s="6" t="inlineStr"/>
-      <c r="V30" s="6" t="inlineStr"/>
-      <c r="W30" s="6" t="inlineStr"/>
-      <c r="X30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2688,10 +2215,10 @@
       </c>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="5" t="n">
-        <v>0.05765254706148304</v>
+        <v>0.0553</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>0.07617724801951264</v>
+        <v>0.0678</v>
       </c>
       <c r="L31" s="5" t="inlineStr"/>
       <c r="M31" s="5" t="inlineStr"/>
@@ -2704,14 +2231,6 @@
       <c r="P31" s="5" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q31" s="6" t="inlineStr"/>
-      <c r="R31" s="6" t="inlineStr"/>
-      <c r="S31" s="6" t="inlineStr"/>
-      <c r="T31" s="6" t="inlineStr"/>
-      <c r="U31" s="6" t="inlineStr"/>
-      <c r="V31" s="6" t="inlineStr"/>
-      <c r="W31" s="6" t="inlineStr"/>
-      <c r="X31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2762,14 +2281,6 @@
       <c r="P32" s="5" t="n">
         <v>0.901</v>
       </c>
-      <c r="Q32" s="6" t="inlineStr"/>
-      <c r="R32" s="6" t="inlineStr"/>
-      <c r="S32" s="6" t="inlineStr"/>
-      <c r="T32" s="6" t="inlineStr"/>
-      <c r="U32" s="6" t="inlineStr"/>
-      <c r="V32" s="6" t="inlineStr"/>
-      <c r="W32" s="6" t="inlineStr"/>
-      <c r="X32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2808,10 +2319,10 @@
       </c>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="5" t="n">
-        <v>0.1090852472782988</v>
+        <v>0.1012</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>0.1329011055420474</v>
+        <v>0.125</v>
       </c>
       <c r="L33" s="5" t="inlineStr"/>
       <c r="M33" s="5" t="inlineStr"/>
@@ -2824,14 +2335,6 @@
       <c r="P33" s="5" t="n">
         <v>0.9833</v>
       </c>
-      <c r="Q33" s="6" t="inlineStr"/>
-      <c r="R33" s="6" t="inlineStr"/>
-      <c r="S33" s="6" t="inlineStr"/>
-      <c r="T33" s="6" t="inlineStr"/>
-      <c r="U33" s="6" t="inlineStr"/>
-      <c r="V33" s="6" t="inlineStr"/>
-      <c r="W33" s="6" t="inlineStr"/>
-      <c r="X33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2870,10 +2373,10 @@
       </c>
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="5" t="n">
-        <v>0.07673420102808481</v>
+        <v>0.0735</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>0.04879482272464053</v>
+        <v>0.0467</v>
       </c>
       <c r="L34" s="5" t="inlineStr"/>
       <c r="M34" s="5" t="inlineStr"/>
@@ -2886,14 +2389,6 @@
       <c r="P34" s="5" t="n">
         <v>0.9833</v>
       </c>
-      <c r="Q34" s="6" t="inlineStr"/>
-      <c r="R34" s="6" t="inlineStr"/>
-      <c r="S34" s="6" t="inlineStr"/>
-      <c r="T34" s="6" t="inlineStr"/>
-      <c r="U34" s="6" t="inlineStr"/>
-      <c r="V34" s="6" t="inlineStr"/>
-      <c r="W34" s="6" t="inlineStr"/>
-      <c r="X34" s="6" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2932,10 +2427,10 @@
       </c>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="5" t="n">
-        <v>0.08376688909880559</v>
+        <v>0.0794</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>0.03441493291566089</v>
+        <v>0.0331</v>
       </c>
       <c r="L35" s="5" t="inlineStr"/>
       <c r="M35" s="5" t="inlineStr"/>
@@ -2948,14 +2443,6 @@
       <c r="P35" s="5" t="n">
         <v>0.9833</v>
       </c>
-      <c r="Q35" s="6" t="inlineStr"/>
-      <c r="R35" s="6" t="inlineStr"/>
-      <c r="S35" s="6" t="inlineStr"/>
-      <c r="T35" s="6" t="inlineStr"/>
-      <c r="U35" s="6" t="inlineStr"/>
-      <c r="V35" s="6" t="inlineStr"/>
-      <c r="W35" s="6" t="inlineStr"/>
-      <c r="X35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2994,11 +2481,9 @@
       </c>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="5" t="n">
-        <v>0.165261756131016</v>
-      </c>
-      <c r="K36" s="5" t="n">
-        <v>0.1792215413644107</v>
-      </c>
+        <v>0.1555</v>
+      </c>
+      <c r="K36" s="5" t="inlineStr"/>
       <c r="L36" s="5" t="inlineStr"/>
       <c r="M36" s="5" t="inlineStr"/>
       <c r="N36" s="5" t="n">
@@ -3010,14 +2495,6 @@
       <c r="P36" s="5" t="n">
         <v>0.9569</v>
       </c>
-      <c r="Q36" s="6" t="inlineStr"/>
-      <c r="R36" s="6" t="inlineStr"/>
-      <c r="S36" s="6" t="inlineStr"/>
-      <c r="T36" s="6" t="inlineStr"/>
-      <c r="U36" s="6" t="inlineStr"/>
-      <c r="V36" s="6" t="inlineStr"/>
-      <c r="W36" s="6" t="inlineStr"/>
-      <c r="X36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -3064,14 +2541,6 @@
       </c>
       <c r="O37" s="5" t="inlineStr"/>
       <c r="P37" s="5" t="inlineStr"/>
-      <c r="Q37" s="6" t="inlineStr"/>
-      <c r="R37" s="6" t="inlineStr"/>
-      <c r="S37" s="6" t="inlineStr"/>
-      <c r="T37" s="6" t="inlineStr"/>
-      <c r="U37" s="6" t="inlineStr"/>
-      <c r="V37" s="6" t="inlineStr"/>
-      <c r="W37" s="6" t="inlineStr"/>
-      <c r="X37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -3122,14 +2591,6 @@
       <c r="P38" s="5" t="n">
         <v>0.9952</v>
       </c>
-      <c r="Q38" s="6" t="inlineStr"/>
-      <c r="R38" s="6" t="inlineStr"/>
-      <c r="S38" s="6" t="inlineStr"/>
-      <c r="T38" s="6" t="inlineStr"/>
-      <c r="U38" s="6" t="inlineStr"/>
-      <c r="V38" s="6" t="inlineStr"/>
-      <c r="W38" s="6" t="inlineStr"/>
-      <c r="X38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3168,9 +2629,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="5" t="inlineStr"/>
-      <c r="K39" s="5" t="n">
-        <v>0.08800887843952154</v>
-      </c>
+      <c r="K39" s="5" t="inlineStr"/>
       <c r="L39" s="5" t="inlineStr"/>
       <c r="M39" s="5" t="inlineStr"/>
       <c r="N39" s="5" t="n">
@@ -3182,14 +2641,6 @@
       <c r="P39" s="5" t="n">
         <v>0.9819</v>
       </c>
-      <c r="Q39" s="6" t="inlineStr"/>
-      <c r="R39" s="6" t="inlineStr"/>
-      <c r="S39" s="6" t="inlineStr"/>
-      <c r="T39" s="6" t="inlineStr"/>
-      <c r="U39" s="6" t="inlineStr"/>
-      <c r="V39" s="6" t="inlineStr"/>
-      <c r="W39" s="6" t="inlineStr"/>
-      <c r="X39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3228,9 +2679,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="5" t="inlineStr"/>
-      <c r="K40" s="5" t="n">
-        <v>0.1119293945604837</v>
-      </c>
+      <c r="K40" s="5" t="inlineStr"/>
       <c r="L40" s="5" t="inlineStr"/>
       <c r="M40" s="5" t="inlineStr"/>
       <c r="N40" s="5" t="n">
@@ -3242,14 +2691,6 @@
       <c r="P40" s="5" t="n">
         <v>0.9819</v>
       </c>
-      <c r="Q40" s="6" t="inlineStr"/>
-      <c r="R40" s="6" t="inlineStr"/>
-      <c r="S40" s="6" t="inlineStr"/>
-      <c r="T40" s="6" t="inlineStr"/>
-      <c r="U40" s="6" t="inlineStr"/>
-      <c r="V40" s="6" t="inlineStr"/>
-      <c r="W40" s="6" t="inlineStr"/>
-      <c r="X40" s="6" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -3288,9 +2729,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="5" t="inlineStr"/>
-      <c r="K41" s="5" t="n">
-        <v>0.0123018750239543</v>
-      </c>
+      <c r="K41" s="5" t="inlineStr"/>
       <c r="L41" s="5" t="inlineStr"/>
       <c r="M41" s="5" t="inlineStr"/>
       <c r="N41" s="5" t="n">
@@ -3302,14 +2741,6 @@
       <c r="P41" s="5" t="n">
         <v>0.9819</v>
       </c>
-      <c r="Q41" s="6" t="inlineStr"/>
-      <c r="R41" s="6" t="inlineStr"/>
-      <c r="S41" s="6" t="inlineStr"/>
-      <c r="T41" s="6" t="inlineStr"/>
-      <c r="U41" s="6" t="inlineStr"/>
-      <c r="V41" s="6" t="inlineStr"/>
-      <c r="W41" s="6" t="inlineStr"/>
-      <c r="X41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -3358,14 +2789,6 @@
       <c r="P42" s="5" t="n">
         <v>0.9824000000000001</v>
       </c>
-      <c r="Q42" s="6" t="inlineStr"/>
-      <c r="R42" s="6" t="inlineStr"/>
-      <c r="S42" s="6" t="inlineStr"/>
-      <c r="T42" s="6" t="inlineStr"/>
-      <c r="U42" s="6" t="inlineStr"/>
-      <c r="V42" s="6" t="inlineStr"/>
-      <c r="W42" s="6" t="inlineStr"/>
-      <c r="X42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3414,14 +2837,6 @@
       <c r="P43" s="5" t="n">
         <v>0.9824000000000001</v>
       </c>
-      <c r="Q43" s="6" t="inlineStr"/>
-      <c r="R43" s="6" t="inlineStr"/>
-      <c r="S43" s="6" t="inlineStr"/>
-      <c r="T43" s="6" t="inlineStr"/>
-      <c r="U43" s="6" t="inlineStr"/>
-      <c r="V43" s="6" t="inlineStr"/>
-      <c r="W43" s="6" t="inlineStr"/>
-      <c r="X43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3459,11 +2874,9 @@
         <v>96.59999999999999</v>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="5" t="n">
-        <v>0.006730440322401998</v>
-      </c>
+      <c r="J44" s="5" t="inlineStr"/>
       <c r="K44" s="5" t="n">
-        <v>0.1828368307734174</v>
+        <v>0.1766</v>
       </c>
       <c r="L44" s="5" t="inlineStr"/>
       <c r="M44" s="5" t="inlineStr"/>
@@ -3476,14 +2889,6 @@
       <c r="P44" s="5" t="n">
         <v>0.9829</v>
       </c>
-      <c r="Q44" s="6" t="inlineStr"/>
-      <c r="R44" s="6" t="inlineStr"/>
-      <c r="S44" s="6" t="inlineStr"/>
-      <c r="T44" s="6" t="inlineStr"/>
-      <c r="U44" s="6" t="inlineStr"/>
-      <c r="V44" s="6" t="inlineStr"/>
-      <c r="W44" s="6" t="inlineStr"/>
-      <c r="X44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3534,14 +2939,6 @@
       <c r="P45" s="5" t="n">
         <v>0.9801</v>
       </c>
-      <c r="Q45" s="6" t="inlineStr"/>
-      <c r="R45" s="6" t="inlineStr"/>
-      <c r="S45" s="6" t="inlineStr"/>
-      <c r="T45" s="6" t="inlineStr"/>
-      <c r="U45" s="6" t="inlineStr"/>
-      <c r="V45" s="6" t="inlineStr"/>
-      <c r="W45" s="6" t="inlineStr"/>
-      <c r="X45" s="6" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3580,10 +2977,10 @@
       </c>
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="5" t="n">
-        <v>0.1118721818565486</v>
+        <v>0.1062</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>0.178900785388332</v>
+        <v>0.173</v>
       </c>
       <c r="L46" s="5" t="inlineStr"/>
       <c r="M46" s="5" t="inlineStr"/>
@@ -3596,14 +2993,6 @@
       <c r="P46" s="5" t="n">
         <v>0.901</v>
       </c>
-      <c r="Q46" s="6" t="inlineStr"/>
-      <c r="R46" s="6" t="inlineStr"/>
-      <c r="S46" s="6" t="inlineStr"/>
-      <c r="T46" s="6" t="inlineStr"/>
-      <c r="U46" s="6" t="inlineStr"/>
-      <c r="V46" s="6" t="inlineStr"/>
-      <c r="W46" s="6" t="inlineStr"/>
-      <c r="X46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3642,10 +3031,10 @@
       </c>
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="5" t="n">
-        <v>0.07862362779385146</v>
+        <v>0.074</v>
       </c>
       <c r="K47" s="5" t="n">
-        <v>0.1393456838590317</v>
+        <v>0.1339</v>
       </c>
       <c r="L47" s="5" t="inlineStr"/>
       <c r="M47" s="5" t="inlineStr"/>
@@ -3658,14 +3047,6 @@
       <c r="P47" s="5" t="n">
         <v>0.983</v>
       </c>
-      <c r="Q47" s="6" t="inlineStr"/>
-      <c r="R47" s="6" t="inlineStr"/>
-      <c r="S47" s="6" t="inlineStr"/>
-      <c r="T47" s="6" t="inlineStr"/>
-      <c r="U47" s="6" t="inlineStr"/>
-      <c r="V47" s="6" t="inlineStr"/>
-      <c r="W47" s="6" t="inlineStr"/>
-      <c r="X47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3716,14 +3097,6 @@
       <c r="P48" s="5" t="n">
         <v>0.9801</v>
       </c>
-      <c r="Q48" s="6" t="inlineStr"/>
-      <c r="R48" s="6" t="inlineStr"/>
-      <c r="S48" s="6" t="inlineStr"/>
-      <c r="T48" s="6" t="inlineStr"/>
-      <c r="U48" s="6" t="inlineStr"/>
-      <c r="V48" s="6" t="inlineStr"/>
-      <c r="W48" s="6" t="inlineStr"/>
-      <c r="X48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -3762,10 +3135,10 @@
       </c>
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="5" t="n">
-        <v>0.09237139852010201</v>
+        <v>0.0878</v>
       </c>
       <c r="K49" s="5" t="n">
-        <v>0.09029336657571219</v>
+        <v>0.0847</v>
       </c>
       <c r="L49" s="5" t="inlineStr"/>
       <c r="M49" s="5" t="inlineStr"/>
@@ -3778,14 +3151,6 @@
       <c r="P49" s="5" t="n">
         <v>0.9569</v>
       </c>
-      <c r="Q49" s="6" t="inlineStr"/>
-      <c r="R49" s="6" t="inlineStr"/>
-      <c r="S49" s="6" t="inlineStr"/>
-      <c r="T49" s="6" t="inlineStr"/>
-      <c r="U49" s="6" t="inlineStr"/>
-      <c r="V49" s="6" t="inlineStr"/>
-      <c r="W49" s="6" t="inlineStr"/>
-      <c r="X49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3824,10 +3189,10 @@
       </c>
       <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="5" t="n">
-        <v>0.1347524443952343</v>
+        <v>0.1264</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>0.1060249296605559</v>
+        <v>0.09810000000000001</v>
       </c>
       <c r="L50" s="5" t="inlineStr"/>
       <c r="M50" s="5" t="inlineStr"/>
@@ -3840,14 +3205,6 @@
       <c r="P50" s="5" t="n">
         <v>0.9519</v>
       </c>
-      <c r="Q50" s="6" t="inlineStr"/>
-      <c r="R50" s="6" t="inlineStr"/>
-      <c r="S50" s="6" t="inlineStr"/>
-      <c r="T50" s="6" t="inlineStr"/>
-      <c r="U50" s="6" t="inlineStr"/>
-      <c r="V50" s="6" t="inlineStr"/>
-      <c r="W50" s="6" t="inlineStr"/>
-      <c r="X50" s="6" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3898,14 +3255,6 @@
       <c r="P51" s="5" t="n">
         <v>0.9952</v>
       </c>
-      <c r="Q51" s="6" t="inlineStr"/>
-      <c r="R51" s="6" t="inlineStr"/>
-      <c r="S51" s="6" t="inlineStr"/>
-      <c r="T51" s="6" t="inlineStr"/>
-      <c r="U51" s="6" t="inlineStr"/>
-      <c r="V51" s="6" t="inlineStr"/>
-      <c r="W51" s="6" t="inlineStr"/>
-      <c r="X51" s="6" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3944,10 +3293,10 @@
       </c>
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="5" t="n">
-        <v>0.05030984963358887</v>
+        <v>0.05</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>0.0523074239242165</v>
+        <v>0.0498</v>
       </c>
       <c r="L52" s="5" t="inlineStr"/>
       <c r="M52" s="5" t="inlineStr"/>
@@ -3960,14 +3309,6 @@
       <c r="P52" s="5" t="n">
         <v>0.9893999999999999</v>
       </c>
-      <c r="Q52" s="6" t="inlineStr"/>
-      <c r="R52" s="6" t="inlineStr"/>
-      <c r="S52" s="6" t="inlineStr"/>
-      <c r="T52" s="6" t="inlineStr"/>
-      <c r="U52" s="6" t="inlineStr"/>
-      <c r="V52" s="6" t="inlineStr"/>
-      <c r="W52" s="6" t="inlineStr"/>
-      <c r="X52" s="6" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -4006,10 +3347,10 @@
       </c>
       <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="5" t="n">
-        <v>0.1905628760534537</v>
+        <v>0.1784</v>
       </c>
       <c r="K53" s="5" t="n">
-        <v>0.2791924245645767</v>
+        <v>0.2533</v>
       </c>
       <c r="L53" s="5" t="inlineStr"/>
       <c r="M53" s="5" t="inlineStr"/>
@@ -4022,14 +3363,6 @@
       <c r="P53" s="5" t="n">
         <v>0.9569</v>
       </c>
-      <c r="Q53" s="6" t="inlineStr"/>
-      <c r="R53" s="6" t="inlineStr"/>
-      <c r="S53" s="6" t="inlineStr"/>
-      <c r="T53" s="6" t="inlineStr"/>
-      <c r="U53" s="6" t="inlineStr"/>
-      <c r="V53" s="6" t="inlineStr"/>
-      <c r="W53" s="6" t="inlineStr"/>
-      <c r="X53" s="6" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -4068,10 +3401,10 @@
       </c>
       <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="5" t="n">
-        <v>0.1929403130048908</v>
+        <v>0.1857</v>
       </c>
       <c r="K54" s="5" t="n">
-        <v>0.2955409110236449</v>
+        <v>0.2838</v>
       </c>
       <c r="L54" s="5" t="inlineStr"/>
       <c r="M54" s="5" t="inlineStr"/>
@@ -4084,14 +3417,6 @@
       <c r="P54" s="5" t="n">
         <v>0.8881</v>
       </c>
-      <c r="Q54" s="6" t="inlineStr"/>
-      <c r="R54" s="6" t="inlineStr"/>
-      <c r="S54" s="6" t="inlineStr"/>
-      <c r="T54" s="6" t="inlineStr"/>
-      <c r="U54" s="6" t="inlineStr"/>
-      <c r="V54" s="6" t="inlineStr"/>
-      <c r="W54" s="6" t="inlineStr"/>
-      <c r="X54" s="6" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -4130,10 +3455,10 @@
       </c>
       <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="5" t="n">
-        <v>0.1820130053159992</v>
+        <v>0.1619</v>
       </c>
       <c r="K55" s="5" t="n">
-        <v>0.2502015276870414</v>
+        <v>0.2355</v>
       </c>
       <c r="L55" s="5" t="inlineStr"/>
       <c r="M55" s="5" t="inlineStr"/>
@@ -4146,14 +3471,6 @@
       <c r="P55" s="5" t="n">
         <v>0.8881</v>
       </c>
-      <c r="Q55" s="6" t="inlineStr"/>
-      <c r="R55" s="6" t="inlineStr"/>
-      <c r="S55" s="6" t="inlineStr"/>
-      <c r="T55" s="6" t="inlineStr"/>
-      <c r="U55" s="6" t="inlineStr"/>
-      <c r="V55" s="6" t="inlineStr"/>
-      <c r="W55" s="6" t="inlineStr"/>
-      <c r="X55" s="6" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -4192,10 +3509,10 @@
       </c>
       <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="5" t="n">
-        <v>0.06059805759477788</v>
+        <v>0.0583</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>0.0793430622023733</v>
+        <v>0.077</v>
       </c>
       <c r="L56" s="5" t="inlineStr"/>
       <c r="M56" s="5" t="inlineStr"/>
@@ -4208,24 +3525,16 @@
       <c r="P56" s="5" t="n">
         <v>0.9952</v>
       </c>
-      <c r="Q56" s="6" t="inlineStr"/>
-      <c r="R56" s="6" t="inlineStr"/>
-      <c r="S56" s="6" t="inlineStr"/>
-      <c r="T56" s="6" t="inlineStr"/>
-      <c r="U56" s="6" t="inlineStr"/>
-      <c r="V56" s="6" t="inlineStr"/>
-      <c r="W56" s="6" t="inlineStr"/>
-      <c r="X56" s="6" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>RYANCWF1</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Portland Wind Farm</t>
+          <t>Ryan Corner Wind Farm</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4250,34 +3559,34 @@
         </is>
       </c>
       <c r="H57" s="4" t="n">
-        <v>148</v>
+        <v>218.4</v>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="5" t="inlineStr"/>
-      <c r="K57" s="5" t="inlineStr"/>
+      <c r="K57" s="5" t="n">
+        <v>0.0931</v>
+      </c>
       <c r="L57" s="5" t="inlineStr"/>
       <c r="M57" s="5" t="inlineStr"/>
-      <c r="N57" s="5" t="inlineStr"/>
-      <c r="O57" s="5" t="inlineStr"/>
-      <c r="P57" s="5" t="inlineStr"/>
-      <c r="Q57" s="6" t="inlineStr"/>
-      <c r="R57" s="6" t="inlineStr"/>
-      <c r="S57" s="6" t="inlineStr"/>
-      <c r="T57" s="6" t="inlineStr"/>
-      <c r="U57" s="6" t="inlineStr"/>
-      <c r="V57" s="6" t="inlineStr"/>
-      <c r="W57" s="6" t="inlineStr"/>
-      <c r="X57" s="6" t="inlineStr"/>
+      <c r="N57" s="5" t="n">
+        <v>0.9787</v>
+      </c>
+      <c r="O57" s="5" t="n">
+        <v>0.9875</v>
+      </c>
+      <c r="P57" s="5" t="n">
+        <v>0.9837</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>RYANCWF1</t>
+          <t>SALTCRK1</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Ryan Corner Wind Farm</t>
+          <t>Salt Creek Wind Farm</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4302,42 +3611,36 @@
         </is>
       </c>
       <c r="H58" s="4" t="n">
-        <v>218.4</v>
+        <v>54</v>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="5" t="inlineStr"/>
+      <c r="J58" s="5" t="n">
+        <v>0.1607</v>
+      </c>
       <c r="K58" s="5" t="n">
-        <v>0.1030626282962745</v>
+        <v>0.2295</v>
       </c>
       <c r="L58" s="5" t="inlineStr"/>
       <c r="M58" s="5" t="inlineStr"/>
       <c r="N58" s="5" t="n">
-        <v>0.9787</v>
+        <v>0.9388</v>
       </c>
       <c r="O58" s="5" t="n">
-        <v>0.9875</v>
+        <v>0.9519</v>
       </c>
       <c r="P58" s="5" t="n">
-        <v>0.9837</v>
-      </c>
-      <c r="Q58" s="6" t="inlineStr"/>
-      <c r="R58" s="6" t="inlineStr"/>
-      <c r="S58" s="6" t="inlineStr"/>
-      <c r="T58" s="6" t="inlineStr"/>
-      <c r="U58" s="6" t="inlineStr"/>
-      <c r="V58" s="6" t="inlineStr"/>
-      <c r="W58" s="6" t="inlineStr"/>
-      <c r="X58" s="6" t="inlineStr"/>
+        <v>0.951</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>SALTCRK1</t>
+          <t>STOCKYD1</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Salt Creek Wind Farm</t>
+          <t>Stockyard Hill Wind Farm</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4362,44 +3665,36 @@
         </is>
       </c>
       <c r="H59" s="4" t="n">
-        <v>54</v>
+        <v>531</v>
       </c>
       <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="5" t="n">
-        <v>0.1701534557235311</v>
+        <v>0.0653</v>
       </c>
       <c r="K59" s="5" t="n">
-        <v>0.2438491711773283</v>
+        <v>0.0216</v>
       </c>
       <c r="L59" s="5" t="inlineStr"/>
       <c r="M59" s="5" t="inlineStr"/>
       <c r="N59" s="5" t="n">
-        <v>0.9388</v>
+        <v>0.9812</v>
       </c>
       <c r="O59" s="5" t="n">
-        <v>0.9519</v>
+        <v>0.9845</v>
       </c>
       <c r="P59" s="5" t="n">
-        <v>0.951</v>
-      </c>
-      <c r="Q59" s="6" t="inlineStr"/>
-      <c r="R59" s="6" t="inlineStr"/>
-      <c r="S59" s="6" t="inlineStr"/>
-      <c r="T59" s="6" t="inlineStr"/>
-      <c r="U59" s="6" t="inlineStr"/>
-      <c r="V59" s="6" t="inlineStr"/>
-      <c r="W59" s="6" t="inlineStr"/>
-      <c r="X59" s="6" t="inlineStr"/>
+        <v>0.9832</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>STOCKYD1</t>
+          <t>TIMWEST</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Stockyard Hill Wind Farm</t>
+          <t>Timboon West Wind Farm</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4424,44 +3719,32 @@
         </is>
       </c>
       <c r="H60" s="4" t="n">
-        <v>531</v>
+        <v>7.2</v>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="5" t="n">
-        <v>0.0683590128113456</v>
-      </c>
-      <c r="K60" s="5" t="n">
-        <v>0.02031868173035667</v>
-      </c>
+      <c r="J60" s="5" t="inlineStr"/>
+      <c r="K60" s="5" t="inlineStr"/>
       <c r="L60" s="5" t="inlineStr"/>
       <c r="M60" s="5" t="inlineStr"/>
       <c r="N60" s="5" t="n">
-        <v>0.9812</v>
+        <v>0.9993</v>
       </c>
       <c r="O60" s="5" t="n">
-        <v>0.9845</v>
+        <v>1.0018</v>
       </c>
       <c r="P60" s="5" t="n">
-        <v>0.9832</v>
-      </c>
-      <c r="Q60" s="6" t="inlineStr"/>
-      <c r="R60" s="6" t="inlineStr"/>
-      <c r="S60" s="6" t="inlineStr"/>
-      <c r="T60" s="6" t="inlineStr"/>
-      <c r="U60" s="6" t="inlineStr"/>
-      <c r="V60" s="6" t="inlineStr"/>
-      <c r="W60" s="6" t="inlineStr"/>
-      <c r="X60" s="6" t="inlineStr"/>
+        <v>0.9952</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>TIMWEST</t>
+          <t>TOORAWF</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Timboon West Wind Farm</t>
+          <t>Toora Wind Farm</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4486,7 +3769,7 @@
         </is>
       </c>
       <c r="H61" s="4" t="n">
-        <v>7.2</v>
+        <v>21</v>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
       <c r="J61" s="5" t="inlineStr"/>
@@ -4494,32 +3777,24 @@
       <c r="L61" s="5" t="inlineStr"/>
       <c r="M61" s="5" t="inlineStr"/>
       <c r="N61" s="5" t="n">
-        <v>0.9993</v>
+        <v>0.9848</v>
       </c>
       <c r="O61" s="5" t="n">
-        <v>1.0018</v>
+        <v>0.9862</v>
       </c>
       <c r="P61" s="5" t="n">
-        <v>0.9952</v>
-      </c>
-      <c r="Q61" s="6" t="inlineStr"/>
-      <c r="R61" s="6" t="inlineStr"/>
-      <c r="S61" s="6" t="inlineStr"/>
-      <c r="T61" s="6" t="inlineStr"/>
-      <c r="U61" s="6" t="inlineStr"/>
-      <c r="V61" s="6" t="inlineStr"/>
-      <c r="W61" s="6" t="inlineStr"/>
-      <c r="X61" s="6" t="inlineStr"/>
+        <v>0.9913999999999999</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>TOORAWF</t>
+          <t>WAUBRAWF</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Toora Wind Farm</t>
+          <t>Waubra Wind Farm</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4544,7 +3819,7 @@
         </is>
       </c>
       <c r="H62" s="4" t="n">
-        <v>21</v>
+        <v>192</v>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="5" t="inlineStr"/>
@@ -4552,32 +3827,24 @@
       <c r="L62" s="5" t="inlineStr"/>
       <c r="M62" s="5" t="inlineStr"/>
       <c r="N62" s="5" t="n">
-        <v>0.9848</v>
+        <v>0.9149</v>
       </c>
       <c r="O62" s="5" t="n">
-        <v>0.9862</v>
+        <v>0.9329</v>
       </c>
       <c r="P62" s="5" t="n">
-        <v>0.9913999999999999</v>
-      </c>
-      <c r="Q62" s="6" t="inlineStr"/>
-      <c r="R62" s="6" t="inlineStr"/>
-      <c r="S62" s="6" t="inlineStr"/>
-      <c r="T62" s="6" t="inlineStr"/>
-      <c r="U62" s="6" t="inlineStr"/>
-      <c r="V62" s="6" t="inlineStr"/>
-      <c r="W62" s="6" t="inlineStr"/>
-      <c r="X62" s="6" t="inlineStr"/>
+        <v>0.9317</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>WAUBRAWF</t>
+          <t>WONWP</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Waubra Wind Farm</t>
+          <t>Wonthaggi Wind Farm</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -4602,7 +3869,7 @@
         </is>
       </c>
       <c r="H63" s="4" t="n">
-        <v>192</v>
+        <v>12</v>
       </c>
       <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="5" t="inlineStr"/>
@@ -4610,32 +3877,24 @@
       <c r="L63" s="5" t="inlineStr"/>
       <c r="M63" s="5" t="inlineStr"/>
       <c r="N63" s="5" t="n">
-        <v>0.9149</v>
+        <v>0.9848</v>
       </c>
       <c r="O63" s="5" t="n">
-        <v>0.9329</v>
+        <v>0.9862</v>
       </c>
       <c r="P63" s="5" t="n">
-        <v>0.9317</v>
-      </c>
-      <c r="Q63" s="6" t="inlineStr"/>
-      <c r="R63" s="6" t="inlineStr"/>
-      <c r="S63" s="6" t="inlineStr"/>
-      <c r="T63" s="6" t="inlineStr"/>
-      <c r="U63" s="6" t="inlineStr"/>
-      <c r="V63" s="6" t="inlineStr"/>
-      <c r="W63" s="6" t="inlineStr"/>
-      <c r="X63" s="6" t="inlineStr"/>
+        <v>0.9913999999999999</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>WONWP</t>
+          <t>YSWF1</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Wonthaggi Wind Farm</t>
+          <t>Yaloak South Wind Farm</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -4660,7 +3919,7 @@
         </is>
       </c>
       <c r="H64" s="4" t="n">
-        <v>12</v>
+        <v>28.7</v>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="5" t="inlineStr"/>
@@ -4668,32 +3927,24 @@
       <c r="L64" s="5" t="inlineStr"/>
       <c r="M64" s="5" t="inlineStr"/>
       <c r="N64" s="5" t="n">
-        <v>0.9848</v>
+        <v>0.9718</v>
       </c>
       <c r="O64" s="5" t="n">
-        <v>0.9862</v>
+        <v>0.9825</v>
       </c>
       <c r="P64" s="5" t="n">
-        <v>0.9913999999999999</v>
-      </c>
-      <c r="Q64" s="6" t="inlineStr"/>
-      <c r="R64" s="6" t="inlineStr"/>
-      <c r="S64" s="6" t="inlineStr"/>
-      <c r="T64" s="6" t="inlineStr"/>
-      <c r="U64" s="6" t="inlineStr"/>
-      <c r="V64" s="6" t="inlineStr"/>
-      <c r="W64" s="6" t="inlineStr"/>
-      <c r="X64" s="6" t="inlineStr"/>
+        <v>0.9801</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>YSWF1</t>
+          <t>YAMBUKWF</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Yaloak South Wind Farm</t>
+          <t>Yambuk Wind Farm</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -4718,7 +3969,7 @@
         </is>
       </c>
       <c r="H65" s="4" t="n">
-        <v>28.7</v>
+        <v>30</v>
       </c>
       <c r="I65" s="2" t="inlineStr"/>
       <c r="J65" s="5" t="inlineStr"/>
@@ -4726,32 +3977,24 @@
       <c r="L65" s="5" t="inlineStr"/>
       <c r="M65" s="5" t="inlineStr"/>
       <c r="N65" s="5" t="n">
-        <v>0.9718</v>
+        <v>0.9993</v>
       </c>
       <c r="O65" s="5" t="n">
-        <v>0.9825</v>
+        <v>1.0018</v>
       </c>
       <c r="P65" s="5" t="n">
-        <v>0.9801</v>
-      </c>
-      <c r="Q65" s="6" t="inlineStr"/>
-      <c r="R65" s="6" t="inlineStr"/>
-      <c r="S65" s="6" t="inlineStr"/>
-      <c r="T65" s="6" t="inlineStr"/>
-      <c r="U65" s="6" t="inlineStr"/>
-      <c r="V65" s="6" t="inlineStr"/>
-      <c r="W65" s="6" t="inlineStr"/>
-      <c r="X65" s="6" t="inlineStr"/>
+        <v>0.9952</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>YAMBUKWF</t>
+          <t>YAWWF1</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Yambuk Wind Farm</t>
+          <t>Yawong Wind Farm</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -4776,7 +4019,7 @@
         </is>
       </c>
       <c r="H66" s="4" t="n">
-        <v>30</v>
+        <v>7.2</v>
       </c>
       <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="5" t="inlineStr"/>
@@ -4784,32 +4027,24 @@
       <c r="L66" s="5" t="inlineStr"/>
       <c r="M66" s="5" t="inlineStr"/>
       <c r="N66" s="5" t="n">
-        <v>0.9993</v>
+        <v>1.0072</v>
       </c>
       <c r="O66" s="5" t="n">
-        <v>1.0018</v>
+        <v>1.0166</v>
       </c>
       <c r="P66" s="5" t="n">
-        <v>0.9952</v>
-      </c>
-      <c r="Q66" s="6" t="inlineStr"/>
-      <c r="R66" s="6" t="inlineStr"/>
-      <c r="S66" s="6" t="inlineStr"/>
-      <c r="T66" s="6" t="inlineStr"/>
-      <c r="U66" s="6" t="inlineStr"/>
-      <c r="V66" s="6" t="inlineStr"/>
-      <c r="W66" s="6" t="inlineStr"/>
-      <c r="X66" s="6" t="inlineStr"/>
+        <v>1.0065</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>YAWWF1</t>
+          <t>YENDWF1</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Yawong Wind Farm</t>
+          <t>Yendon Wind Farm</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -4834,92 +4069,26 @@
         </is>
       </c>
       <c r="H67" s="4" t="n">
-        <v>7.2</v>
+        <v>144.4</v>
       </c>
       <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="5" t="inlineStr"/>
-      <c r="K67" s="5" t="inlineStr"/>
+      <c r="J67" s="5" t="n">
+        <v>0.1421</v>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>0.1581</v>
+      </c>
       <c r="L67" s="5" t="inlineStr"/>
       <c r="M67" s="5" t="inlineStr"/>
       <c r="N67" s="5" t="n">
-        <v>1.0072</v>
+        <v>0.9425</v>
       </c>
       <c r="O67" s="5" t="n">
-        <v>1.0166</v>
+        <v>0.9537</v>
       </c>
       <c r="P67" s="5" t="n">
-        <v>1.0065</v>
-      </c>
-      <c r="Q67" s="6" t="inlineStr"/>
-      <c r="R67" s="6" t="inlineStr"/>
-      <c r="S67" s="6" t="inlineStr"/>
-      <c r="T67" s="6" t="inlineStr"/>
-      <c r="U67" s="6" t="inlineStr"/>
-      <c r="V67" s="6" t="inlineStr"/>
-      <c r="W67" s="6" t="inlineStr"/>
-      <c r="X67" s="6" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>YENDWF1</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>Yendon Wind Farm</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Wind</t>
-        </is>
-      </c>
-      <c r="D68" s="3" t="inlineStr"/>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F68" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>VIC</t>
-        </is>
-      </c>
-      <c r="H68" s="4" t="n">
-        <v>144.4</v>
-      </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="5" t="n">
-        <v>0.1520359556040282</v>
-      </c>
-      <c r="K68" s="5" t="n">
-        <v>0.1684419945136396</v>
-      </c>
-      <c r="L68" s="5" t="inlineStr"/>
-      <c r="M68" s="5" t="inlineStr"/>
-      <c r="N68" s="5" t="n">
-        <v>0.9425</v>
-      </c>
-      <c r="O68" s="5" t="n">
-        <v>0.9537</v>
-      </c>
-      <c r="P68" s="5" t="n">
         <v>0.9562</v>
       </c>
-      <c r="Q68" s="6" t="inlineStr"/>
-      <c r="R68" s="6" t="inlineStr"/>
-      <c r="S68" s="6" t="inlineStr"/>
-      <c r="T68" s="6" t="inlineStr"/>
-      <c r="U68" s="6" t="inlineStr"/>
-      <c r="V68" s="6" t="inlineStr"/>
-      <c r="W68" s="6" t="inlineStr"/>
-      <c r="X68" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4932,7 +4101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W68"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4944,146 +4113,62 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>DUID</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Fuel</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>MLF_FY24-25</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>MLF_FY25-26</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>MLF_FY26-27 (Draft)</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>CURTAILMENT_ACTUAL_FY23-24</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>CURTAILMENT_ACTUAL_FY24-25</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>ELI_CURTAILMENT_NEAR</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>ELI_CURTAILMENT_MED</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_FY1</t>
-        </is>
-      </c>
-      <c r="K1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_FY1_LABEL</t>
-        </is>
-      </c>
-      <c r="L1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_FY2</t>
-        </is>
-      </c>
-      <c r="M1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_FY2_LABEL</t>
-        </is>
-      </c>
-      <c r="N1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_FY3</t>
-        </is>
-      </c>
-      <c r="O1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_FY3_LABEL</t>
-        </is>
-      </c>
-      <c r="P1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_AVG</t>
-        </is>
-      </c>
-      <c r="Q1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_FY1</t>
-        </is>
-      </c>
-      <c r="R1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_FY1_LABEL</t>
-        </is>
-      </c>
-      <c r="S1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_FY2</t>
-        </is>
-      </c>
-      <c r="T1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_FY2_LABEL</t>
-        </is>
-      </c>
-      <c r="U1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_FY3</t>
-        </is>
-      </c>
-      <c r="V1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_FY3_LABEL</t>
-        </is>
-      </c>
-      <c r="W1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_AVG</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>BANN1</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5098,10 +4183,10 @@
         <v>0.9114</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>0.3710560565867671</v>
+        <v>0.3236</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.2719808764553837</v>
+        <v>0.2465</v>
       </c>
       <c r="H2" s="5" t="n">
         <v>0.833539620209753</v>
@@ -5109,68 +4194,14 @@
       <c r="I2" s="5" t="n">
         <v>0.164192244302687</v>
       </c>
-      <c r="J2" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L2" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="M2" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P2" s="5" t="n">
-        <v>0.02666666666666667</v>
-      </c>
-      <c r="Q2" s="5" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="R2" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S2" s="5" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="T2" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U2" s="5" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="V2" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W2" s="5" t="n">
-        <v>0.12</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>CRWARP1</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5186,52 +4217,14 @@
       <c r="G3" s="5" t="inlineStr"/>
       <c r="H3" s="5" t="inlineStr"/>
       <c r="I3" s="5" t="inlineStr"/>
-      <c r="J3" s="5" t="inlineStr"/>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="inlineStr"/>
-      <c r="M3" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N3" s="5" t="inlineStr"/>
-      <c r="O3" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P3" s="5" t="inlineStr"/>
-      <c r="Q3" s="5" t="inlineStr"/>
-      <c r="R3" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S3" s="5" t="inlineStr"/>
-      <c r="T3" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U3" s="5" t="inlineStr"/>
-      <c r="V3" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>COHUNSF1</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5245,80 +4238,22 @@
       <c r="E4" s="5" t="n">
         <v>0.9307</v>
       </c>
-      <c r="F4" s="5" t="n">
-        <v>0.1600293147297279</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>0.2827710603192121</v>
-      </c>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
       <c r="H4" s="5" t="n">
         <v>0.547516873654646</v>
       </c>
       <c r="I4" s="5" t="n">
         <v>0.122422882740379</v>
       </c>
-      <c r="J4" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="M4" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P4" s="5" t="n">
-        <v>0.02666666666666667</v>
-      </c>
-      <c r="Q4" s="5" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="R4" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S4" s="5" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="T4" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U4" s="5" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="V4" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W4" s="5" t="n">
-        <v>0.12</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>GANNSF1</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5333,10 +4268,10 @@
         <v>0.9307</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.05215670207613177</v>
+        <v>0.0499</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.05460168559670209</v>
+        <v>0.054</v>
       </c>
       <c r="H5" s="5" t="n">
         <v>0.547516873654646</v>
@@ -5344,68 +4279,14 @@
       <c r="I5" s="5" t="n">
         <v>0.122422882740379</v>
       </c>
-      <c r="J5" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="M5" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P5" s="5" t="n">
-        <v>0.02666666666666667</v>
-      </c>
-      <c r="Q5" s="5" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="R5" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S5" s="5" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="T5" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U5" s="5" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="V5" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W5" s="5" t="n">
-        <v>0.12</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>GIRGSF</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5421,7 +4302,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr"/>
       <c r="G6" s="5" t="n">
-        <v>0.2650311526126716</v>
+        <v>0.2374</v>
       </c>
       <c r="H6" s="5" t="n">
         <v>0.389503957787889</v>
@@ -5429,68 +4310,14 @@
       <c r="I6" s="5" t="n">
         <v>0.08205629867681941</v>
       </c>
-      <c r="J6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="5" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="R6" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S6" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="T6" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U6" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="V6" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W6" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>GLENSF1</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5504,11 +4331,9 @@
       <c r="E7" s="5" t="n">
         <v>0.9292</v>
       </c>
-      <c r="F7" s="5" t="n">
-        <v>0.1954445746044534</v>
-      </c>
+      <c r="F7" s="5" t="inlineStr"/>
       <c r="G7" s="5" t="n">
-        <v>0.07798287623836642</v>
+        <v>0.0688</v>
       </c>
       <c r="H7" s="5" t="n">
         <v>0.390717855103594</v>
@@ -5516,68 +4341,14 @@
       <c r="I7" s="5" t="n">
         <v>0.08997768712489811</v>
       </c>
-      <c r="J7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="5" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="R7" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S7" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="T7" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U7" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="V7" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W7" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>GLRWNSF1</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5592,59 +4363,21 @@
         <v>0.922</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.1990273759688161</v>
+        <v>0.1836</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.2408960878187453</v>
+        <v>0.2057</v>
       </c>
       <c r="H8" s="5" t="inlineStr"/>
       <c r="I8" s="5" t="inlineStr"/>
-      <c r="J8" s="5" t="inlineStr"/>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="inlineStr"/>
-      <c r="M8" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N8" s="5" t="inlineStr"/>
-      <c r="O8" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P8" s="5" t="inlineStr"/>
-      <c r="Q8" s="5" t="inlineStr"/>
-      <c r="R8" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S8" s="5" t="inlineStr"/>
-      <c r="T8" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U8" s="5" t="inlineStr"/>
-      <c r="V8" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>GOESF1</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5660,52 +4393,14 @@
       <c r="G9" s="5" t="inlineStr"/>
       <c r="H9" s="5" t="inlineStr"/>
       <c r="I9" s="5" t="inlineStr"/>
-      <c r="J9" s="5" t="inlineStr"/>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr"/>
-      <c r="M9" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N9" s="5" t="inlineStr"/>
-      <c r="O9" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P9" s="5" t="inlineStr"/>
-      <c r="Q9" s="5" t="inlineStr"/>
-      <c r="R9" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S9" s="5" t="inlineStr"/>
-      <c r="T9" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U9" s="5" t="inlineStr"/>
-      <c r="V9" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>KARSF1</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5720,10 +4415,10 @@
         <v>0.9088000000000001</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.3169574937730341</v>
+        <v>0.2761</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.1686799728674456</v>
+        <v>0.159</v>
       </c>
       <c r="H10" s="5" t="n">
         <v>0.8554020168196</v>
@@ -5731,68 +4426,14 @@
       <c r="I10" s="5" t="n">
         <v>0.072415601225557</v>
       </c>
-      <c r="J10" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="M10" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P10" s="5" t="n">
-        <v>0.02666666666666667</v>
-      </c>
-      <c r="Q10" s="5" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="R10" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S10" s="5" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="T10" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U10" s="5" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="V10" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W10" s="5" t="n">
-        <v>0.12</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>KERNGSP1</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5807,57 +4448,17 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="n">
-        <v>0.04898598021985823</v>
-      </c>
+      <c r="G11" s="5" t="inlineStr"/>
       <c r="H11" s="5" t="inlineStr"/>
       <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="inlineStr"/>
-      <c r="M11" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N11" s="5" t="inlineStr"/>
-      <c r="O11" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P11" s="5" t="inlineStr"/>
-      <c r="Q11" s="5" t="inlineStr"/>
-      <c r="R11" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S11" s="5" t="inlineStr"/>
-      <c r="T11" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U11" s="5" t="inlineStr"/>
-      <c r="V11" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>KIAMSF1</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5872,10 +4473,10 @@
         <v>0.878</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.1091648532990047</v>
+        <v>0.106</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.1136272868211855</v>
+        <v>0.1081</v>
       </c>
       <c r="H12" s="5" t="n">
         <v>0.827440107601162</v>
@@ -5883,68 +4484,14 @@
       <c r="I12" s="5" t="n">
         <v>0.0878331516592939</v>
       </c>
-      <c r="J12" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L12" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="M12" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P12" s="5" t="n">
-        <v>0.02666666666666667</v>
-      </c>
-      <c r="Q12" s="5" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="R12" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S12" s="5" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="T12" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U12" s="5" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="V12" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W12" s="5" t="n">
-        <v>0.12</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>LANCSF1</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5958,52 +4505,14 @@
       <c r="G13" s="5" t="inlineStr"/>
       <c r="H13" s="5" t="inlineStr"/>
       <c r="I13" s="5" t="inlineStr"/>
-      <c r="J13" s="5" t="inlineStr"/>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L13" s="5" t="inlineStr"/>
-      <c r="M13" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N13" s="5" t="inlineStr"/>
-      <c r="O13" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P13" s="5" t="inlineStr"/>
-      <c r="Q13" s="5" t="inlineStr"/>
-      <c r="R13" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S13" s="5" t="inlineStr"/>
-      <c r="T13" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U13" s="5" t="inlineStr"/>
-      <c r="V13" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>MOKOSF1</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6018,57 +4527,17 @@
         <v>0.9248</v>
       </c>
       <c r="F14" s="5" t="inlineStr"/>
-      <c r="G14" s="5" t="n">
-        <v>0.1074948342034868</v>
-      </c>
+      <c r="G14" s="5" t="inlineStr"/>
       <c r="H14" s="5" t="inlineStr"/>
       <c r="I14" s="5" t="inlineStr"/>
-      <c r="J14" s="5" t="inlineStr"/>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L14" s="5" t="inlineStr"/>
-      <c r="M14" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N14" s="5" t="inlineStr"/>
-      <c r="O14" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P14" s="5" t="inlineStr"/>
-      <c r="Q14" s="5" t="inlineStr"/>
-      <c r="R14" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S14" s="5" t="inlineStr"/>
-      <c r="T14" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U14" s="5" t="inlineStr"/>
-      <c r="V14" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>NUMURSF1</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6083,10 +4552,10 @@
         <v>0.9223</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.3437740975604878</v>
+        <v>0.2971</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.1415139558510223</v>
+        <v>0.1275</v>
       </c>
       <c r="H15" s="5" t="n">
         <v>0.389503957787889</v>
@@ -6094,68 +4563,14 @@
       <c r="I15" s="5" t="n">
         <v>0.08205629867681941</v>
       </c>
-      <c r="J15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="5" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="R15" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S15" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="T15" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U15" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="V15" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W15" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>WNSF1</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6173,52 +4588,14 @@
       <c r="G16" s="5" t="inlineStr"/>
       <c r="H16" s="5" t="inlineStr"/>
       <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L16" s="5" t="inlineStr"/>
-      <c r="M16" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N16" s="5" t="inlineStr"/>
-      <c r="O16" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P16" s="5" t="inlineStr"/>
-      <c r="Q16" s="5" t="inlineStr"/>
-      <c r="R16" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S16" s="5" t="inlineStr"/>
-      <c r="T16" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U16" s="5" t="inlineStr"/>
-      <c r="V16" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>WEMENSF1</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6233,10 +4610,10 @@
         <v>0.9114</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.3584538984210027</v>
+        <v>0.3065</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.2739101642738966</v>
+        <v>0.2491</v>
       </c>
       <c r="H17" s="5" t="n">
         <v>0.833539620209753</v>
@@ -6244,68 +4621,14 @@
       <c r="I17" s="5" t="n">
         <v>0.164192244302687</v>
       </c>
-      <c r="J17" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L17" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="M17" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P17" s="5" t="n">
-        <v>0.02666666666666667</v>
-      </c>
-      <c r="Q17" s="5" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="R17" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S17" s="5" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="T17" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U17" s="5" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="V17" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W17" s="5" t="n">
-        <v>0.12</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>WINTSF1</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6320,79 +4643,23 @@
         <v>0.922</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.2487248512923422</v>
-      </c>
-      <c r="G18" s="5" t="n">
-        <v>0.1094894731574723</v>
-      </c>
+        <v>0.2227</v>
+      </c>
+      <c r="G18" s="5" t="inlineStr"/>
       <c r="H18" s="5" t="n">
         <v>0.390717855103594</v>
       </c>
       <c r="I18" s="5" t="n">
         <v>0.08997768712489811</v>
       </c>
-      <c r="J18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="5" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="R18" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S18" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="T18" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U18" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="V18" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W18" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>WUNUSF1</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6407,61 +4674,21 @@
         <v>0.9223</v>
       </c>
       <c r="F19" s="5" t="inlineStr"/>
-      <c r="G19" s="5" t="n">
-        <v>0.1428920071912686</v>
-      </c>
+      <c r="G19" s="5" t="inlineStr"/>
       <c r="H19" s="5" t="n">
         <v>0.389503957787889</v>
       </c>
       <c r="I19" s="5" t="n">
         <v>0.08205629867681941</v>
       </c>
-      <c r="J19" s="5" t="inlineStr"/>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L19" s="5" t="inlineStr"/>
-      <c r="M19" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N19" s="5" t="inlineStr"/>
-      <c r="O19" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P19" s="5" t="inlineStr"/>
-      <c r="Q19" s="5" t="inlineStr"/>
-      <c r="R19" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S19" s="5" t="inlineStr"/>
-      <c r="T19" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U19" s="5" t="inlineStr"/>
-      <c r="V19" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>YATSF1</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6476,10 +4703,10 @@
         <v>0.9088000000000001</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.3372382246917938</v>
+        <v>0.2786</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.2486746048568231</v>
+        <v>0.2351</v>
       </c>
       <c r="H20" s="5" t="n">
         <v>0.8554020168196</v>
@@ -6487,68 +4714,14 @@
       <c r="I20" s="5" t="n">
         <v>0.072415601225557</v>
       </c>
-      <c r="J20" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L20" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="M20" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P20" s="5" t="n">
-        <v>0.02666666666666667</v>
-      </c>
-      <c r="Q20" s="5" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="R20" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S20" s="5" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="T20" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U20" s="5" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="V20" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W20" s="5" t="n">
-        <v>0.12</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>ARWF1</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6563,59 +4736,21 @@
         <v>0.8999</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.07896687551826564</v>
+        <v>0.0756</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.04879956378773898</v>
+        <v>0.0482</v>
       </c>
       <c r="H21" s="5" t="inlineStr"/>
       <c r="I21" s="5" t="inlineStr"/>
-      <c r="J21" s="5" t="inlineStr"/>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="inlineStr"/>
-      <c r="M21" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N21" s="5" t="inlineStr"/>
-      <c r="O21" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P21" s="5" t="inlineStr"/>
-      <c r="Q21" s="5" t="inlineStr"/>
-      <c r="R21" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S21" s="5" t="inlineStr"/>
-      <c r="T21" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U21" s="5" t="inlineStr"/>
-      <c r="V21" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>BALDHWF1</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6630,59 +4765,21 @@
         <v>0.9913999999999999</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.007890464523191421</v>
+        <v>0.0078</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.005078393583182961</v>
+        <v>0.0051</v>
       </c>
       <c r="H22" s="5" t="inlineStr"/>
       <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L22" s="5" t="inlineStr"/>
-      <c r="M22" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N22" s="5" t="inlineStr"/>
-      <c r="O22" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P22" s="5" t="inlineStr"/>
-      <c r="Q22" s="5" t="inlineStr"/>
-      <c r="R22" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S22" s="5" t="inlineStr"/>
-      <c r="T22" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U22" s="5" t="inlineStr"/>
-      <c r="V22" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>BRYB2WF2</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6697,59 +4794,21 @@
         <v>0.945</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.228198922467751</v>
+        <v>0.2041</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.2029431742155934</v>
+        <v>0.1906</v>
       </c>
       <c r="H23" s="5" t="inlineStr"/>
       <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr"/>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N23" s="5" t="inlineStr"/>
-      <c r="O23" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P23" s="5" t="inlineStr"/>
-      <c r="Q23" s="5" t="inlineStr"/>
-      <c r="R23" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S23" s="5" t="inlineStr"/>
-      <c r="T23" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U23" s="5" t="inlineStr"/>
-      <c r="V23" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>BRYB1WF1</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6764,59 +4823,21 @@
         <v>0.945</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.04586386696325562</v>
+        <v>0.045</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.03247885424318653</v>
+        <v>0.0316</v>
       </c>
       <c r="H24" s="5" t="inlineStr"/>
       <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L24" s="5" t="inlineStr"/>
-      <c r="M24" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N24" s="5" t="inlineStr"/>
-      <c r="O24" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P24" s="5" t="inlineStr"/>
-      <c r="Q24" s="5" t="inlineStr"/>
-      <c r="R24" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S24" s="5" t="inlineStr"/>
-      <c r="T24" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U24" s="5" t="inlineStr"/>
-      <c r="V24" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>BULGANA1</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6831,59 +4852,21 @@
         <v>0.89</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>0.03468796155479126</v>
+        <v>0.0347</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.02811506234350913</v>
+        <v>0.0284</v>
       </c>
       <c r="H25" s="5" t="inlineStr"/>
       <c r="I25" s="5" t="inlineStr"/>
-      <c r="J25" s="5" t="inlineStr"/>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr"/>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N25" s="5" t="inlineStr"/>
-      <c r="O25" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P25" s="5" t="inlineStr"/>
-      <c r="Q25" s="5" t="inlineStr"/>
-      <c r="R25" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S25" s="5" t="inlineStr"/>
-      <c r="T25" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U25" s="5" t="inlineStr"/>
-      <c r="V25" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>CHALLHWF</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6901,52 +4884,14 @@
       <c r="G26" s="5" t="inlineStr"/>
       <c r="H26" s="5" t="inlineStr"/>
       <c r="I26" s="5" t="inlineStr"/>
-      <c r="J26" s="5" t="inlineStr"/>
-      <c r="K26" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L26" s="5" t="inlineStr"/>
-      <c r="M26" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N26" s="5" t="inlineStr"/>
-      <c r="O26" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P26" s="5" t="inlineStr"/>
-      <c r="Q26" s="5" t="inlineStr"/>
-      <c r="R26" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S26" s="5" t="inlineStr"/>
-      <c r="T26" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U26" s="5" t="inlineStr"/>
-      <c r="V26" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>CHPSTWF1</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6962,52 +4907,14 @@
       <c r="G27" s="5" t="inlineStr"/>
       <c r="H27" s="5" t="inlineStr"/>
       <c r="I27" s="5" t="inlineStr"/>
-      <c r="J27" s="5" t="inlineStr"/>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="inlineStr"/>
-      <c r="M27" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N27" s="5" t="inlineStr"/>
-      <c r="O27" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P27" s="5" t="inlineStr"/>
-      <c r="Q27" s="5" t="inlineStr"/>
-      <c r="R27" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S27" s="5" t="inlineStr"/>
-      <c r="T27" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U27" s="5" t="inlineStr"/>
-      <c r="V27" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>CHYTWF1</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -7022,59 +4929,21 @@
         <v>0.9978</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.06000630720703115</v>
+        <v>0.0578</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0990364762086815</v>
+        <v>0.0958</v>
       </c>
       <c r="H28" s="5" t="inlineStr"/>
       <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L28" s="5" t="inlineStr"/>
-      <c r="M28" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N28" s="5" t="inlineStr"/>
-      <c r="O28" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P28" s="5" t="inlineStr"/>
-      <c r="Q28" s="5" t="inlineStr"/>
-      <c r="R28" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S28" s="5" t="inlineStr"/>
-      <c r="T28" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U28" s="5" t="inlineStr"/>
-      <c r="V28" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>CODRNGTON</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -7092,52 +4961,14 @@
       <c r="G29" s="5" t="inlineStr"/>
       <c r="H29" s="5" t="inlineStr"/>
       <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L29" s="5" t="inlineStr"/>
-      <c r="M29" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N29" s="5" t="inlineStr"/>
-      <c r="O29" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P29" s="5" t="inlineStr"/>
-      <c r="Q29" s="5" t="inlineStr"/>
-      <c r="R29" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S29" s="5" t="inlineStr"/>
-      <c r="T29" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U29" s="5" t="inlineStr"/>
-      <c r="V29" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>CBWF1</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -7155,52 +4986,14 @@
       <c r="G30" s="5" t="inlineStr"/>
       <c r="H30" s="5" t="inlineStr"/>
       <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L30" s="5" t="inlineStr"/>
-      <c r="M30" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N30" s="5" t="inlineStr"/>
-      <c r="O30" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P30" s="5" t="inlineStr"/>
-      <c r="Q30" s="5" t="inlineStr"/>
-      <c r="R30" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S30" s="5" t="inlineStr"/>
-      <c r="T30" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U30" s="5" t="inlineStr"/>
-      <c r="V30" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>CROWLWF1</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -7215,59 +5008,21 @@
         <v>0.9</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>0.05765254706148304</v>
+        <v>0.0553</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.07617724801951264</v>
+        <v>0.0678</v>
       </c>
       <c r="H31" s="5" t="inlineStr"/>
       <c r="I31" s="5" t="inlineStr"/>
-      <c r="J31" s="5" t="inlineStr"/>
-      <c r="K31" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L31" s="5" t="inlineStr"/>
-      <c r="M31" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N31" s="5" t="inlineStr"/>
-      <c r="O31" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P31" s="5" t="inlineStr"/>
-      <c r="Q31" s="5" t="inlineStr"/>
-      <c r="R31" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S31" s="5" t="inlineStr"/>
-      <c r="T31" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U31" s="5" t="inlineStr"/>
-      <c r="V31" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>DIAPURWF1</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -7285,52 +5040,14 @@
       <c r="G32" s="5" t="inlineStr"/>
       <c r="H32" s="5" t="inlineStr"/>
       <c r="I32" s="5" t="inlineStr"/>
-      <c r="J32" s="5" t="inlineStr"/>
-      <c r="K32" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L32" s="5" t="inlineStr"/>
-      <c r="M32" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N32" s="5" t="inlineStr"/>
-      <c r="O32" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P32" s="5" t="inlineStr"/>
-      <c r="Q32" s="5" t="inlineStr"/>
-      <c r="R32" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S32" s="5" t="inlineStr"/>
-      <c r="T32" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U32" s="5" t="inlineStr"/>
-      <c r="V32" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>DUNDWF1</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -7345,59 +5062,21 @@
         <v>0.9833</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>0.1090852472782988</v>
+        <v>0.1012</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.1329011055420474</v>
+        <v>0.125</v>
       </c>
       <c r="H33" s="5" t="inlineStr"/>
       <c r="I33" s="5" t="inlineStr"/>
-      <c r="J33" s="5" t="inlineStr"/>
-      <c r="K33" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L33" s="5" t="inlineStr"/>
-      <c r="M33" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N33" s="5" t="inlineStr"/>
-      <c r="O33" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P33" s="5" t="inlineStr"/>
-      <c r="Q33" s="5" t="inlineStr"/>
-      <c r="R33" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S33" s="5" t="inlineStr"/>
-      <c r="T33" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U33" s="5" t="inlineStr"/>
-      <c r="V33" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>DUNDWF2</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -7412,59 +5091,21 @@
         <v>0.9833</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.07673420102808481</v>
+        <v>0.0735</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.04879482272464053</v>
+        <v>0.0467</v>
       </c>
       <c r="H34" s="5" t="inlineStr"/>
       <c r="I34" s="5" t="inlineStr"/>
-      <c r="J34" s="5" t="inlineStr"/>
-      <c r="K34" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L34" s="5" t="inlineStr"/>
-      <c r="M34" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N34" s="5" t="inlineStr"/>
-      <c r="O34" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P34" s="5" t="inlineStr"/>
-      <c r="Q34" s="5" t="inlineStr"/>
-      <c r="R34" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S34" s="5" t="inlineStr"/>
-      <c r="T34" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U34" s="5" t="inlineStr"/>
-      <c r="V34" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>DUNDWF3</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -7479,59 +5120,21 @@
         <v>0.9833</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>0.08376688909880559</v>
+        <v>0.0794</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.03441493291566089</v>
+        <v>0.0331</v>
       </c>
       <c r="H35" s="5" t="inlineStr"/>
       <c r="I35" s="5" t="inlineStr"/>
-      <c r="J35" s="5" t="inlineStr"/>
-      <c r="K35" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L35" s="5" t="inlineStr"/>
-      <c r="M35" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N35" s="5" t="inlineStr"/>
-      <c r="O35" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P35" s="5" t="inlineStr"/>
-      <c r="Q35" s="5" t="inlineStr"/>
-      <c r="R35" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S35" s="5" t="inlineStr"/>
-      <c r="T35" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U35" s="5" t="inlineStr"/>
-      <c r="V35" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W35" s="5" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>ELAINWF1</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -7546,59 +5149,19 @@
         <v>0.9569</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>0.165261756131016</v>
-      </c>
-      <c r="G36" s="5" t="n">
-        <v>0.1792215413644107</v>
-      </c>
+        <v>0.1555</v>
+      </c>
+      <c r="G36" s="5" t="inlineStr"/>
       <c r="H36" s="5" t="inlineStr"/>
       <c r="I36" s="5" t="inlineStr"/>
-      <c r="J36" s="5" t="inlineStr"/>
-      <c r="K36" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L36" s="5" t="inlineStr"/>
-      <c r="M36" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N36" s="5" t="inlineStr"/>
-      <c r="O36" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P36" s="5" t="inlineStr"/>
-      <c r="Q36" s="5" t="inlineStr"/>
-      <c r="R36" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S36" s="5" t="inlineStr"/>
-      <c r="T36" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U36" s="5" t="inlineStr"/>
-      <c r="V36" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>FNWF1</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -7612,52 +5175,14 @@
       <c r="G37" s="5" t="inlineStr"/>
       <c r="H37" s="5" t="inlineStr"/>
       <c r="I37" s="5" t="inlineStr"/>
-      <c r="J37" s="5" t="inlineStr"/>
-      <c r="K37" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L37" s="5" t="inlineStr"/>
-      <c r="M37" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N37" s="5" t="inlineStr"/>
-      <c r="O37" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P37" s="5" t="inlineStr"/>
-      <c r="Q37" s="5" t="inlineStr"/>
-      <c r="R37" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S37" s="5" t="inlineStr"/>
-      <c r="T37" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U37" s="5" t="inlineStr"/>
-      <c r="V37" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>FSWF1</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -7675,52 +5200,14 @@
       <c r="G38" s="5" t="inlineStr"/>
       <c r="H38" s="5" t="inlineStr"/>
       <c r="I38" s="5" t="inlineStr"/>
-      <c r="J38" s="5" t="inlineStr"/>
-      <c r="K38" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L38" s="5" t="inlineStr"/>
-      <c r="M38" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N38" s="5" t="inlineStr"/>
-      <c r="O38" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P38" s="5" t="inlineStr"/>
-      <c r="Q38" s="5" t="inlineStr"/>
-      <c r="R38" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S38" s="5" t="inlineStr"/>
-      <c r="T38" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U38" s="5" t="inlineStr"/>
-      <c r="V38" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>GPWFEST1</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -7735,57 +5222,17 @@
         <v>0.9819</v>
       </c>
       <c r="F39" s="5" t="inlineStr"/>
-      <c r="G39" s="5" t="n">
-        <v>0.08800887843952154</v>
-      </c>
+      <c r="G39" s="5" t="inlineStr"/>
       <c r="H39" s="5" t="inlineStr"/>
       <c r="I39" s="5" t="inlineStr"/>
-      <c r="J39" s="5" t="inlineStr"/>
-      <c r="K39" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L39" s="5" t="inlineStr"/>
-      <c r="M39" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N39" s="5" t="inlineStr"/>
-      <c r="O39" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P39" s="5" t="inlineStr"/>
-      <c r="Q39" s="5" t="inlineStr"/>
-      <c r="R39" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S39" s="5" t="inlineStr"/>
-      <c r="T39" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U39" s="5" t="inlineStr"/>
-      <c r="V39" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="8" t="inlineStr">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>GPWFEST2</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -7800,57 +5247,17 @@
         <v>0.9819</v>
       </c>
       <c r="F40" s="5" t="inlineStr"/>
-      <c r="G40" s="5" t="n">
-        <v>0.1119293945604837</v>
-      </c>
+      <c r="G40" s="5" t="inlineStr"/>
       <c r="H40" s="5" t="inlineStr"/>
       <c r="I40" s="5" t="inlineStr"/>
-      <c r="J40" s="5" t="inlineStr"/>
-      <c r="K40" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L40" s="5" t="inlineStr"/>
-      <c r="M40" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N40" s="5" t="inlineStr"/>
-      <c r="O40" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P40" s="5" t="inlineStr"/>
-      <c r="Q40" s="5" t="inlineStr"/>
-      <c r="R40" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S40" s="5" t="inlineStr"/>
-      <c r="T40" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U40" s="5" t="inlineStr"/>
-      <c r="V40" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>GPWFEST3</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -7865,57 +5272,17 @@
         <v>0.9819</v>
       </c>
       <c r="F41" s="5" t="inlineStr"/>
-      <c r="G41" s="5" t="n">
-        <v>0.0123018750239543</v>
-      </c>
+      <c r="G41" s="5" t="inlineStr"/>
       <c r="H41" s="5" t="inlineStr"/>
       <c r="I41" s="5" t="inlineStr"/>
-      <c r="J41" s="5" t="inlineStr"/>
-      <c r="K41" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L41" s="5" t="inlineStr"/>
-      <c r="M41" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N41" s="5" t="inlineStr"/>
-      <c r="O41" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P41" s="5" t="inlineStr"/>
-      <c r="Q41" s="5" t="inlineStr"/>
-      <c r="R41" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S41" s="5" t="inlineStr"/>
-      <c r="T41" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U41" s="5" t="inlineStr"/>
-      <c r="V41" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W41" s="5" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="inlineStr">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>GPWFWST1</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -7931,52 +5298,14 @@
       <c r="G42" s="5" t="inlineStr"/>
       <c r="H42" s="5" t="inlineStr"/>
       <c r="I42" s="5" t="inlineStr"/>
-      <c r="J42" s="5" t="inlineStr"/>
-      <c r="K42" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L42" s="5" t="inlineStr"/>
-      <c r="M42" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N42" s="5" t="inlineStr"/>
-      <c r="O42" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P42" s="5" t="inlineStr"/>
-      <c r="Q42" s="5" t="inlineStr"/>
-      <c r="R42" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S42" s="5" t="inlineStr"/>
-      <c r="T42" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U42" s="5" t="inlineStr"/>
-      <c r="V42" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>GPWFWST2</t>
         </is>
       </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -7992,52 +5321,14 @@
       <c r="G43" s="5" t="inlineStr"/>
       <c r="H43" s="5" t="inlineStr"/>
       <c r="I43" s="5" t="inlineStr"/>
-      <c r="J43" s="5" t="inlineStr"/>
-      <c r="K43" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L43" s="5" t="inlineStr"/>
-      <c r="M43" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N43" s="5" t="inlineStr"/>
-      <c r="O43" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P43" s="5" t="inlineStr"/>
-      <c r="Q43" s="5" t="inlineStr"/>
-      <c r="R43" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S43" s="5" t="inlineStr"/>
-      <c r="T43" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U43" s="5" t="inlineStr"/>
-      <c r="V43" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="8" t="inlineStr">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>HD1WF1</t>
         </is>
       </c>
-      <c r="B44" s="8" t="inlineStr">
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -8051,60 +5342,20 @@
       <c r="E44" s="5" t="n">
         <v>0.9829</v>
       </c>
-      <c r="F44" s="5" t="n">
-        <v>0.006730440322401998</v>
-      </c>
+      <c r="F44" s="5" t="inlineStr"/>
       <c r="G44" s="5" t="n">
-        <v>0.1828368307734174</v>
+        <v>0.1766</v>
       </c>
       <c r="H44" s="5" t="inlineStr"/>
       <c r="I44" s="5" t="inlineStr"/>
-      <c r="J44" s="5" t="inlineStr"/>
-      <c r="K44" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L44" s="5" t="inlineStr"/>
-      <c r="M44" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N44" s="5" t="inlineStr"/>
-      <c r="O44" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P44" s="5" t="inlineStr"/>
-      <c r="Q44" s="5" t="inlineStr"/>
-      <c r="R44" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S44" s="5" t="inlineStr"/>
-      <c r="T44" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U44" s="5" t="inlineStr"/>
-      <c r="V44" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W44" s="5" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="8" t="inlineStr">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>HEPWIND1</t>
         </is>
       </c>
-      <c r="B45" s="8" t="inlineStr">
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -8122,52 +5373,14 @@
       <c r="G45" s="5" t="inlineStr"/>
       <c r="H45" s="5" t="inlineStr"/>
       <c r="I45" s="5" t="inlineStr"/>
-      <c r="J45" s="5" t="inlineStr"/>
-      <c r="K45" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L45" s="5" t="inlineStr"/>
-      <c r="M45" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N45" s="5" t="inlineStr"/>
-      <c r="O45" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P45" s="5" t="inlineStr"/>
-      <c r="Q45" s="5" t="inlineStr"/>
-      <c r="R45" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S45" s="5" t="inlineStr"/>
-      <c r="T45" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U45" s="5" t="inlineStr"/>
-      <c r="V45" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W45" s="5" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="8" t="inlineStr">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>KIATAWF1</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr">
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -8182,59 +5395,21 @@
         <v>0.901</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0.1118721818565486</v>
+        <v>0.1062</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.178900785388332</v>
+        <v>0.173</v>
       </c>
       <c r="H46" s="5" t="inlineStr"/>
       <c r="I46" s="5" t="inlineStr"/>
-      <c r="J46" s="5" t="inlineStr"/>
-      <c r="K46" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L46" s="5" t="inlineStr"/>
-      <c r="M46" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N46" s="5" t="inlineStr"/>
-      <c r="O46" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P46" s="5" t="inlineStr"/>
-      <c r="Q46" s="5" t="inlineStr"/>
-      <c r="R46" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S46" s="5" t="inlineStr"/>
-      <c r="T46" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U46" s="5" t="inlineStr"/>
-      <c r="V46" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="8" t="inlineStr">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>MACARTH1</t>
         </is>
       </c>
-      <c r="B47" s="8" t="inlineStr">
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -8249,59 +5424,21 @@
         <v>0.983</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>0.07862362779385146</v>
+        <v>0.074</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.1393456838590317</v>
+        <v>0.1339</v>
       </c>
       <c r="H47" s="5" t="inlineStr"/>
       <c r="I47" s="5" t="inlineStr"/>
-      <c r="J47" s="5" t="inlineStr"/>
-      <c r="K47" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L47" s="5" t="inlineStr"/>
-      <c r="M47" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N47" s="5" t="inlineStr"/>
-      <c r="O47" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P47" s="5" t="inlineStr"/>
-      <c r="Q47" s="5" t="inlineStr"/>
-      <c r="R47" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S47" s="5" t="inlineStr"/>
-      <c r="T47" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U47" s="5" t="inlineStr"/>
-      <c r="V47" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W47" s="5" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="8" t="inlineStr">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>MAROOWF1</t>
         </is>
       </c>
-      <c r="B48" s="8" t="inlineStr">
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -8319,52 +5456,14 @@
       <c r="G48" s="5" t="inlineStr"/>
       <c r="H48" s="5" t="inlineStr"/>
       <c r="I48" s="5" t="inlineStr"/>
-      <c r="J48" s="5" t="inlineStr"/>
-      <c r="K48" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L48" s="5" t="inlineStr"/>
-      <c r="M48" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N48" s="5" t="inlineStr"/>
-      <c r="O48" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P48" s="5" t="inlineStr"/>
-      <c r="Q48" s="5" t="inlineStr"/>
-      <c r="R48" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S48" s="5" t="inlineStr"/>
-      <c r="T48" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U48" s="5" t="inlineStr"/>
-      <c r="V48" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W48" s="5" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="inlineStr">
+      <c r="A49" s="7" t="inlineStr">
         <is>
           <t>MOORAWF1</t>
         </is>
       </c>
-      <c r="B49" s="8" t="inlineStr">
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -8379,59 +5478,21 @@
         <v>0.9569</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>0.09237139852010201</v>
+        <v>0.0878</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.09029336657571219</v>
+        <v>0.0847</v>
       </c>
       <c r="H49" s="5" t="inlineStr"/>
       <c r="I49" s="5" t="inlineStr"/>
-      <c r="J49" s="5" t="inlineStr"/>
-      <c r="K49" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L49" s="5" t="inlineStr"/>
-      <c r="M49" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N49" s="5" t="inlineStr"/>
-      <c r="O49" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P49" s="5" t="inlineStr"/>
-      <c r="Q49" s="5" t="inlineStr"/>
-      <c r="R49" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S49" s="5" t="inlineStr"/>
-      <c r="T49" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U49" s="5" t="inlineStr"/>
-      <c r="V49" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="8" t="inlineStr">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t>MRTLSWF1</t>
         </is>
       </c>
-      <c r="B50" s="8" t="inlineStr">
+      <c r="B50" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -8446,59 +5507,21 @@
         <v>0.9519</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>0.1347524443952343</v>
+        <v>0.1264</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.1060249296605559</v>
+        <v>0.09810000000000001</v>
       </c>
       <c r="H50" s="5" t="inlineStr"/>
       <c r="I50" s="5" t="inlineStr"/>
-      <c r="J50" s="5" t="inlineStr"/>
-      <c r="K50" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L50" s="5" t="inlineStr"/>
-      <c r="M50" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N50" s="5" t="inlineStr"/>
-      <c r="O50" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P50" s="5" t="inlineStr"/>
-      <c r="Q50" s="5" t="inlineStr"/>
-      <c r="R50" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S50" s="5" t="inlineStr"/>
-      <c r="T50" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U50" s="5" t="inlineStr"/>
-      <c r="V50" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W50" s="5" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="8" t="inlineStr">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>MLWF1</t>
         </is>
       </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -8516,52 +5539,14 @@
       <c r="G51" s="5" t="inlineStr"/>
       <c r="H51" s="5" t="inlineStr"/>
       <c r="I51" s="5" t="inlineStr"/>
-      <c r="J51" s="5" t="inlineStr"/>
-      <c r="K51" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L51" s="5" t="inlineStr"/>
-      <c r="M51" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N51" s="5" t="inlineStr"/>
-      <c r="O51" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P51" s="5" t="inlineStr"/>
-      <c r="Q51" s="5" t="inlineStr"/>
-      <c r="R51" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S51" s="5" t="inlineStr"/>
-      <c r="T51" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U51" s="5" t="inlineStr"/>
-      <c r="V51" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W51" s="5" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="8" t="inlineStr">
+      <c r="A52" s="7" t="inlineStr">
         <is>
           <t>MTGELWF1</t>
         </is>
       </c>
-      <c r="B52" s="8" t="inlineStr">
+      <c r="B52" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -8576,59 +5561,21 @@
         <v>0.9893999999999999</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>0.05030984963358887</v>
+        <v>0.05</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0523074239242165</v>
+        <v>0.0498</v>
       </c>
       <c r="H52" s="5" t="inlineStr"/>
       <c r="I52" s="5" t="inlineStr"/>
-      <c r="J52" s="5" t="inlineStr"/>
-      <c r="K52" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L52" s="5" t="inlineStr"/>
-      <c r="M52" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N52" s="5" t="inlineStr"/>
-      <c r="O52" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P52" s="5" t="inlineStr"/>
-      <c r="Q52" s="5" t="inlineStr"/>
-      <c r="R52" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S52" s="5" t="inlineStr"/>
-      <c r="T52" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U52" s="5" t="inlineStr"/>
-      <c r="V52" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W52" s="5" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="8" t="inlineStr">
+      <c r="A53" s="7" t="inlineStr">
         <is>
           <t>MERCER01</t>
         </is>
       </c>
-      <c r="B53" s="8" t="inlineStr">
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -8643,59 +5590,21 @@
         <v>0.9569</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>0.1905628760534537</v>
+        <v>0.1784</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.2791924245645767</v>
+        <v>0.2533</v>
       </c>
       <c r="H53" s="5" t="inlineStr"/>
       <c r="I53" s="5" t="inlineStr"/>
-      <c r="J53" s="5" t="inlineStr"/>
-      <c r="K53" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L53" s="5" t="inlineStr"/>
-      <c r="M53" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N53" s="5" t="inlineStr"/>
-      <c r="O53" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P53" s="5" t="inlineStr"/>
-      <c r="Q53" s="5" t="inlineStr"/>
-      <c r="R53" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S53" s="5" t="inlineStr"/>
-      <c r="T53" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U53" s="5" t="inlineStr"/>
-      <c r="V53" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W53" s="5" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="8" t="inlineStr">
+      <c r="A54" s="7" t="inlineStr">
         <is>
           <t>MUWAWF1</t>
         </is>
       </c>
-      <c r="B54" s="8" t="inlineStr">
+      <c r="B54" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -8710,59 +5619,21 @@
         <v>0.8881</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>0.1929403130048908</v>
+        <v>0.1857</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.2955409110236449</v>
+        <v>0.2838</v>
       </c>
       <c r="H54" s="5" t="inlineStr"/>
       <c r="I54" s="5" t="inlineStr"/>
-      <c r="J54" s="5" t="inlineStr"/>
-      <c r="K54" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L54" s="5" t="inlineStr"/>
-      <c r="M54" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N54" s="5" t="inlineStr"/>
-      <c r="O54" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P54" s="5" t="inlineStr"/>
-      <c r="Q54" s="5" t="inlineStr"/>
-      <c r="R54" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S54" s="5" t="inlineStr"/>
-      <c r="T54" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U54" s="5" t="inlineStr"/>
-      <c r="V54" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W54" s="5" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="8" t="inlineStr">
+      <c r="A55" s="7" t="inlineStr">
         <is>
           <t>MUWAWF2</t>
         </is>
       </c>
-      <c r="B55" s="8" t="inlineStr">
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -8777,59 +5648,21 @@
         <v>0.8881</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>0.1820130053159992</v>
+        <v>0.1619</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.2502015276870414</v>
+        <v>0.2355</v>
       </c>
       <c r="H55" s="5" t="inlineStr"/>
       <c r="I55" s="5" t="inlineStr"/>
-      <c r="J55" s="5" t="inlineStr"/>
-      <c r="K55" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L55" s="5" t="inlineStr"/>
-      <c r="M55" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N55" s="5" t="inlineStr"/>
-      <c r="O55" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P55" s="5" t="inlineStr"/>
-      <c r="Q55" s="5" t="inlineStr"/>
-      <c r="R55" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S55" s="5" t="inlineStr"/>
-      <c r="T55" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U55" s="5" t="inlineStr"/>
-      <c r="V55" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W55" s="5" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="8" t="inlineStr">
+      <c r="A56" s="7" t="inlineStr">
         <is>
           <t>OAKLAND1</t>
         </is>
       </c>
-      <c r="B56" s="8" t="inlineStr">
+      <c r="B56" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -8844,818 +5677,305 @@
         <v>0.9952</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>0.06059805759477788</v>
+        <v>0.0583</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0793430622023733</v>
+        <v>0.077</v>
       </c>
       <c r="H56" s="5" t="inlineStr"/>
       <c r="I56" s="5" t="inlineStr"/>
-      <c r="J56" s="5" t="inlineStr"/>
-      <c r="K56" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L56" s="5" t="inlineStr"/>
-      <c r="M56" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N56" s="5" t="inlineStr"/>
-      <c r="O56" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P56" s="5" t="inlineStr"/>
-      <c r="Q56" s="5" t="inlineStr"/>
-      <c r="R56" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S56" s="5" t="inlineStr"/>
-      <c r="T56" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U56" s="5" t="inlineStr"/>
-      <c r="V56" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W56" s="5" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B57" s="8" t="inlineStr">
-        <is>
-          <t>Wind</t>
-        </is>
-      </c>
-      <c r="C57" s="5" t="inlineStr"/>
-      <c r="D57" s="5" t="inlineStr"/>
-      <c r="E57" s="5" t="inlineStr"/>
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>RYANCWF1</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>0.9787</v>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>0.9875</v>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>0.9837</v>
+      </c>
       <c r="F57" s="5" t="inlineStr"/>
-      <c r="G57" s="5" t="inlineStr"/>
+      <c r="G57" s="5" t="n">
+        <v>0.0931</v>
+      </c>
       <c r="H57" s="5" t="inlineStr"/>
       <c r="I57" s="5" t="inlineStr"/>
-      <c r="J57" s="5" t="inlineStr"/>
-      <c r="K57" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L57" s="5" t="inlineStr"/>
-      <c r="M57" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N57" s="5" t="inlineStr"/>
-      <c r="O57" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P57" s="5" t="inlineStr"/>
-      <c r="Q57" s="5" t="inlineStr"/>
-      <c r="R57" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S57" s="5" t="inlineStr"/>
-      <c r="T57" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U57" s="5" t="inlineStr"/>
-      <c r="V57" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W57" s="5" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="8" t="inlineStr">
-        <is>
-          <t>RYANCWF1</t>
-        </is>
-      </c>
-      <c r="B58" s="8" t="inlineStr">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>SALTCRK1</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
       </c>
       <c r="C58" s="5" t="n">
-        <v>0.9787</v>
+        <v>0.9388</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>0.9875</v>
+        <v>0.9519</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>0.9837</v>
-      </c>
-      <c r="F58" s="5" t="inlineStr"/>
+        <v>0.951</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>0.1607</v>
+      </c>
       <c r="G58" s="5" t="n">
-        <v>0.1030626282962745</v>
+        <v>0.2295</v>
       </c>
       <c r="H58" s="5" t="inlineStr"/>
       <c r="I58" s="5" t="inlineStr"/>
-      <c r="J58" s="5" t="inlineStr"/>
-      <c r="K58" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L58" s="5" t="inlineStr"/>
-      <c r="M58" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N58" s="5" t="inlineStr"/>
-      <c r="O58" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P58" s="5" t="inlineStr"/>
-      <c r="Q58" s="5" t="inlineStr"/>
-      <c r="R58" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S58" s="5" t="inlineStr"/>
-      <c r="T58" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U58" s="5" t="inlineStr"/>
-      <c r="V58" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W58" s="5" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="8" t="inlineStr">
-        <is>
-          <t>SALTCRK1</t>
-        </is>
-      </c>
-      <c r="B59" s="8" t="inlineStr">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>STOCKYD1</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>0.9388</v>
+        <v>0.9812</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>0.9519</v>
+        <v>0.9845</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>0.951</v>
+        <v>0.9832</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>0.1701534557235311</v>
+        <v>0.0653</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.2438491711773283</v>
+        <v>0.0216</v>
       </c>
       <c r="H59" s="5" t="inlineStr"/>
       <c r="I59" s="5" t="inlineStr"/>
-      <c r="J59" s="5" t="inlineStr"/>
-      <c r="K59" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L59" s="5" t="inlineStr"/>
-      <c r="M59" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N59" s="5" t="inlineStr"/>
-      <c r="O59" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P59" s="5" t="inlineStr"/>
-      <c r="Q59" s="5" t="inlineStr"/>
-      <c r="R59" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S59" s="5" t="inlineStr"/>
-      <c r="T59" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U59" s="5" t="inlineStr"/>
-      <c r="V59" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W59" s="5" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="8" t="inlineStr">
-        <is>
-          <t>STOCKYD1</t>
-        </is>
-      </c>
-      <c r="B60" s="8" t="inlineStr">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>TIMWEST</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
       </c>
       <c r="C60" s="5" t="n">
-        <v>0.9812</v>
+        <v>0.9993</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>0.9845</v>
+        <v>1.0018</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>0.9832</v>
-      </c>
-      <c r="F60" s="5" t="n">
-        <v>0.0683590128113456</v>
-      </c>
-      <c r="G60" s="5" t="n">
-        <v>0.02031868173035667</v>
-      </c>
+        <v>0.9952</v>
+      </c>
+      <c r="F60" s="5" t="inlineStr"/>
+      <c r="G60" s="5" t="inlineStr"/>
       <c r="H60" s="5" t="inlineStr"/>
       <c r="I60" s="5" t="inlineStr"/>
-      <c r="J60" s="5" t="inlineStr"/>
-      <c r="K60" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L60" s="5" t="inlineStr"/>
-      <c r="M60" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N60" s="5" t="inlineStr"/>
-      <c r="O60" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P60" s="5" t="inlineStr"/>
-      <c r="Q60" s="5" t="inlineStr"/>
-      <c r="R60" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S60" s="5" t="inlineStr"/>
-      <c r="T60" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U60" s="5" t="inlineStr"/>
-      <c r="V60" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W60" s="5" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="8" t="inlineStr">
-        <is>
-          <t>TIMWEST</t>
-        </is>
-      </c>
-      <c r="B61" s="8" t="inlineStr">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>TOORAWF</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>0.9993</v>
+        <v>0.9848</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>1.0018</v>
+        <v>0.9862</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>0.9952</v>
+        <v>0.9913999999999999</v>
       </c>
       <c r="F61" s="5" t="inlineStr"/>
       <c r="G61" s="5" t="inlineStr"/>
       <c r="H61" s="5" t="inlineStr"/>
       <c r="I61" s="5" t="inlineStr"/>
-      <c r="J61" s="5" t="inlineStr"/>
-      <c r="K61" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L61" s="5" t="inlineStr"/>
-      <c r="M61" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N61" s="5" t="inlineStr"/>
-      <c r="O61" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P61" s="5" t="inlineStr"/>
-      <c r="Q61" s="5" t="inlineStr"/>
-      <c r="R61" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S61" s="5" t="inlineStr"/>
-      <c r="T61" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U61" s="5" t="inlineStr"/>
-      <c r="V61" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W61" s="5" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="8" t="inlineStr">
-        <is>
-          <t>TOORAWF</t>
-        </is>
-      </c>
-      <c r="B62" s="8" t="inlineStr">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>WAUBRAWF</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
       </c>
       <c r="C62" s="5" t="n">
-        <v>0.9848</v>
+        <v>0.9149</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>0.9862</v>
+        <v>0.9329</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>0.9913999999999999</v>
+        <v>0.9317</v>
       </c>
       <c r="F62" s="5" t="inlineStr"/>
       <c r="G62" s="5" t="inlineStr"/>
       <c r="H62" s="5" t="inlineStr"/>
       <c r="I62" s="5" t="inlineStr"/>
-      <c r="J62" s="5" t="inlineStr"/>
-      <c r="K62" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L62" s="5" t="inlineStr"/>
-      <c r="M62" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N62" s="5" t="inlineStr"/>
-      <c r="O62" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P62" s="5" t="inlineStr"/>
-      <c r="Q62" s="5" t="inlineStr"/>
-      <c r="R62" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S62" s="5" t="inlineStr"/>
-      <c r="T62" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U62" s="5" t="inlineStr"/>
-      <c r="V62" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W62" s="5" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="8" t="inlineStr">
-        <is>
-          <t>WAUBRAWF</t>
-        </is>
-      </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>WONWP</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>0.9149</v>
+        <v>0.9848</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>0.9329</v>
+        <v>0.9862</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>0.9317</v>
+        <v>0.9913999999999999</v>
       </c>
       <c r="F63" s="5" t="inlineStr"/>
       <c r="G63" s="5" t="inlineStr"/>
       <c r="H63" s="5" t="inlineStr"/>
       <c r="I63" s="5" t="inlineStr"/>
-      <c r="J63" s="5" t="inlineStr"/>
-      <c r="K63" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L63" s="5" t="inlineStr"/>
-      <c r="M63" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N63" s="5" t="inlineStr"/>
-      <c r="O63" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P63" s="5" t="inlineStr"/>
-      <c r="Q63" s="5" t="inlineStr"/>
-      <c r="R63" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S63" s="5" t="inlineStr"/>
-      <c r="T63" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U63" s="5" t="inlineStr"/>
-      <c r="V63" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W63" s="5" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="8" t="inlineStr">
-        <is>
-          <t>WONWP</t>
-        </is>
-      </c>
-      <c r="B64" s="8" t="inlineStr">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>YSWF1</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
       </c>
       <c r="C64" s="5" t="n">
-        <v>0.9848</v>
+        <v>0.9718</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>0.9862</v>
+        <v>0.9825</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>0.9913999999999999</v>
+        <v>0.9801</v>
       </c>
       <c r="F64" s="5" t="inlineStr"/>
       <c r="G64" s="5" t="inlineStr"/>
       <c r="H64" s="5" t="inlineStr"/>
       <c r="I64" s="5" t="inlineStr"/>
-      <c r="J64" s="5" t="inlineStr"/>
-      <c r="K64" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L64" s="5" t="inlineStr"/>
-      <c r="M64" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N64" s="5" t="inlineStr"/>
-      <c r="O64" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P64" s="5" t="inlineStr"/>
-      <c r="Q64" s="5" t="inlineStr"/>
-      <c r="R64" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S64" s="5" t="inlineStr"/>
-      <c r="T64" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U64" s="5" t="inlineStr"/>
-      <c r="V64" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W64" s="5" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="8" t="inlineStr">
-        <is>
-          <t>YSWF1</t>
-        </is>
-      </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>YAMBUKWF</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>0.9718</v>
+        <v>0.9993</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>0.9825</v>
+        <v>1.0018</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>0.9801</v>
+        <v>0.9952</v>
       </c>
       <c r="F65" s="5" t="inlineStr"/>
       <c r="G65" s="5" t="inlineStr"/>
       <c r="H65" s="5" t="inlineStr"/>
       <c r="I65" s="5" t="inlineStr"/>
-      <c r="J65" s="5" t="inlineStr"/>
-      <c r="K65" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L65" s="5" t="inlineStr"/>
-      <c r="M65" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N65" s="5" t="inlineStr"/>
-      <c r="O65" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P65" s="5" t="inlineStr"/>
-      <c r="Q65" s="5" t="inlineStr"/>
-      <c r="R65" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S65" s="5" t="inlineStr"/>
-      <c r="T65" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U65" s="5" t="inlineStr"/>
-      <c r="V65" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W65" s="5" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="8" t="inlineStr">
-        <is>
-          <t>YAMBUKWF</t>
-        </is>
-      </c>
-      <c r="B66" s="8" t="inlineStr">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>YAWWF1</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
       </c>
       <c r="C66" s="5" t="n">
-        <v>0.9993</v>
+        <v>1.0072</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>1.0018</v>
+        <v>1.0166</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>0.9952</v>
+        <v>1.0065</v>
       </c>
       <c r="F66" s="5" t="inlineStr"/>
       <c r="G66" s="5" t="inlineStr"/>
       <c r="H66" s="5" t="inlineStr"/>
       <c r="I66" s="5" t="inlineStr"/>
-      <c r="J66" s="5" t="inlineStr"/>
-      <c r="K66" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L66" s="5" t="inlineStr"/>
-      <c r="M66" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N66" s="5" t="inlineStr"/>
-      <c r="O66" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P66" s="5" t="inlineStr"/>
-      <c r="Q66" s="5" t="inlineStr"/>
-      <c r="R66" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S66" s="5" t="inlineStr"/>
-      <c r="T66" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U66" s="5" t="inlineStr"/>
-      <c r="V66" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W66" s="5" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="8" t="inlineStr">
-        <is>
-          <t>YAWWF1</t>
-        </is>
-      </c>
-      <c r="B67" s="8" t="inlineStr">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>YENDWF1</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>1.0072</v>
+        <v>0.9425</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>1.0166</v>
+        <v>0.9537</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>1.0065</v>
-      </c>
-      <c r="F67" s="5" t="inlineStr"/>
-      <c r="G67" s="5" t="inlineStr"/>
+        <v>0.9562</v>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>0.1421</v>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>0.1581</v>
+      </c>
       <c r="H67" s="5" t="inlineStr"/>
       <c r="I67" s="5" t="inlineStr"/>
-      <c r="J67" s="5" t="inlineStr"/>
-      <c r="K67" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L67" s="5" t="inlineStr"/>
-      <c r="M67" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N67" s="5" t="inlineStr"/>
-      <c r="O67" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P67" s="5" t="inlineStr"/>
-      <c r="Q67" s="5" t="inlineStr"/>
-      <c r="R67" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S67" s="5" t="inlineStr"/>
-      <c r="T67" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U67" s="5" t="inlineStr"/>
-      <c r="V67" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W67" s="5" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="8" t="inlineStr">
-        <is>
-          <t>YENDWF1</t>
-        </is>
-      </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>Wind</t>
-        </is>
-      </c>
-      <c r="C68" s="5" t="n">
-        <v>0.9425</v>
-      </c>
-      <c r="D68" s="5" t="n">
-        <v>0.9537</v>
-      </c>
-      <c r="E68" s="5" t="n">
-        <v>0.9562</v>
-      </c>
-      <c r="F68" s="5" t="n">
-        <v>0.1520359556040282</v>
-      </c>
-      <c r="G68" s="5" t="n">
-        <v>0.1684419945136396</v>
-      </c>
-      <c r="H68" s="5" t="inlineStr"/>
-      <c r="I68" s="5" t="inlineStr"/>
-      <c r="J68" s="5" t="inlineStr"/>
-      <c r="K68" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L68" s="5" t="inlineStr"/>
-      <c r="M68" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N68" s="5" t="inlineStr"/>
-      <c r="O68" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P68" s="5" t="inlineStr"/>
-      <c r="Q68" s="5" t="inlineStr"/>
-      <c r="R68" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S68" s="5" t="inlineStr"/>
-      <c r="T68" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U68" s="5" t="inlineStr"/>
-      <c r="V68" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W68" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C68">
+  <conditionalFormatting sqref="C2:C67">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -9667,7 +5987,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D68">
+  <conditionalFormatting sqref="D2:D67">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -9679,7 +5999,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E68">
+  <conditionalFormatting sqref="E2:E67">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -9691,7 +6011,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F68">
+  <conditionalFormatting sqref="F2:F67">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -9703,7 +6023,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G68">
+  <conditionalFormatting sqref="G2:G67">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -9715,7 +6035,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H68">
+  <conditionalFormatting sqref="H2:H67">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -9727,176 +6047,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I68">
+  <conditionalFormatting sqref="I2:I67">
     <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J68">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K68">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L68">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M68">
-    <cfRule type="colorScale" priority="11">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N68">
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O68">
-    <cfRule type="colorScale" priority="13">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P68">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q68">
-    <cfRule type="colorScale" priority="15">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R68">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S68">
-    <cfRule type="colorScale" priority="17">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T68">
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U68">
-    <cfRule type="colorScale" priority="19">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V68">
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="W2:W68">
-    <cfRule type="colorScale" priority="21">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/outputs/VIC_curtailment.xlsx
+++ b/outputs/VIC_curtailment.xlsx
@@ -67,7 +67,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -82,6 +82,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -453,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P67"/>
+  <dimension ref="A1:X67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -472,6 +475,14 @@
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -555,6 +566,46 @@
           <t>FY26-27 (Draft)</t>
         </is>
       </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Curt FY1</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Curt FY2</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Curt FY3</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Curt Avg</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Offl FY1</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Offl FY2</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Offl FY3</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Offl Avg</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -618,6 +669,30 @@
       </c>
       <c r="P2" s="5" t="n">
         <v>0.9114</v>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="S2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" s="6" t="n">
+        <v>0.02666666666666667</v>
+      </c>
+      <c r="U2" s="6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="V2" s="6" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="W2" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="X2" s="6" t="n">
+        <v>0.12</v>
       </c>
     </row>
     <row r="3">
@@ -667,6 +742,14 @@
       <c r="P3" s="5" t="n">
         <v>0.9012</v>
       </c>
+      <c r="Q3" s="6" t="inlineStr"/>
+      <c r="R3" s="6" t="inlineStr"/>
+      <c r="S3" s="6" t="inlineStr"/>
+      <c r="T3" s="6" t="inlineStr"/>
+      <c r="U3" s="6" t="inlineStr"/>
+      <c r="V3" s="6" t="inlineStr"/>
+      <c r="W3" s="6" t="inlineStr"/>
+      <c r="X3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -727,6 +810,30 @@
       <c r="P4" s="5" t="n">
         <v>0.9307</v>
       </c>
+      <c r="Q4" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="S4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="6" t="n">
+        <v>0.02666666666666667</v>
+      </c>
+      <c r="U4" s="6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="V4" s="6" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="W4" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="X4" s="6" t="n">
+        <v>0.12</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -790,6 +897,30 @@
       </c>
       <c r="P5" s="5" t="n">
         <v>0.9307</v>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="S5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="6" t="n">
+        <v>0.02666666666666667</v>
+      </c>
+      <c r="U5" s="6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="V5" s="6" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="W5" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="X5" s="6" t="n">
+        <v>0.12</v>
       </c>
     </row>
     <row r="6">
@@ -853,6 +984,30 @@
       <c r="P6" s="5" t="n">
         <v>0.9223</v>
       </c>
+      <c r="Q6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="V6" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="W6" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X6" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -914,6 +1069,30 @@
       </c>
       <c r="P7" s="5" t="n">
         <v>0.9292</v>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="V7" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="W7" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X7" s="6" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -969,6 +1148,14 @@
       <c r="P8" s="5" t="n">
         <v>0.922</v>
       </c>
+      <c r="Q8" s="6" t="inlineStr"/>
+      <c r="R8" s="6" t="inlineStr"/>
+      <c r="S8" s="6" t="inlineStr"/>
+      <c r="T8" s="6" t="inlineStr"/>
+      <c r="U8" s="6" t="inlineStr"/>
+      <c r="V8" s="6" t="inlineStr"/>
+      <c r="W8" s="6" t="inlineStr"/>
+      <c r="X8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1017,6 +1204,14 @@
       <c r="P9" s="5" t="n">
         <v>0.9262</v>
       </c>
+      <c r="Q9" s="6" t="inlineStr"/>
+      <c r="R9" s="6" t="inlineStr"/>
+      <c r="S9" s="6" t="inlineStr"/>
+      <c r="T9" s="6" t="inlineStr"/>
+      <c r="U9" s="6" t="inlineStr"/>
+      <c r="V9" s="6" t="inlineStr"/>
+      <c r="W9" s="6" t="inlineStr"/>
+      <c r="X9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1080,6 +1275,30 @@
       </c>
       <c r="P10" s="5" t="n">
         <v>0.9088000000000001</v>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="S10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="6" t="n">
+        <v>0.02666666666666667</v>
+      </c>
+      <c r="U10" s="6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="V10" s="6" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="W10" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="X10" s="6" t="n">
+        <v>0.12</v>
       </c>
     </row>
     <row r="11">
@@ -1131,6 +1350,14 @@
       <c r="P11" s="5" t="n">
         <v>0.9330000000000001</v>
       </c>
+      <c r="Q11" s="6" t="inlineStr"/>
+      <c r="R11" s="6" t="inlineStr"/>
+      <c r="S11" s="6" t="inlineStr"/>
+      <c r="T11" s="6" t="inlineStr"/>
+      <c r="U11" s="6" t="inlineStr"/>
+      <c r="V11" s="6" t="inlineStr"/>
+      <c r="W11" s="6" t="inlineStr"/>
+      <c r="X11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1194,6 +1421,30 @@
       </c>
       <c r="P12" s="5" t="n">
         <v>0.878</v>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="S12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="6" t="n">
+        <v>0.02666666666666667</v>
+      </c>
+      <c r="U12" s="6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="V12" s="6" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="W12" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="X12" s="6" t="n">
+        <v>0.12</v>
       </c>
     </row>
     <row r="13">
@@ -1241,6 +1492,14 @@
         <v>0.9441000000000001</v>
       </c>
       <c r="P13" s="5" t="inlineStr"/>
+      <c r="Q13" s="6" t="inlineStr"/>
+      <c r="R13" s="6" t="inlineStr"/>
+      <c r="S13" s="6" t="inlineStr"/>
+      <c r="T13" s="6" t="inlineStr"/>
+      <c r="U13" s="6" t="inlineStr"/>
+      <c r="V13" s="6" t="inlineStr"/>
+      <c r="W13" s="6" t="inlineStr"/>
+      <c r="X13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1291,6 +1550,14 @@
       <c r="P14" s="5" t="n">
         <v>0.9248</v>
       </c>
+      <c r="Q14" s="6" t="inlineStr"/>
+      <c r="R14" s="6" t="inlineStr"/>
+      <c r="S14" s="6" t="inlineStr"/>
+      <c r="T14" s="6" t="inlineStr"/>
+      <c r="U14" s="6" t="inlineStr"/>
+      <c r="V14" s="6" t="inlineStr"/>
+      <c r="W14" s="6" t="inlineStr"/>
+      <c r="X14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1354,6 +1621,30 @@
       </c>
       <c r="P15" s="5" t="n">
         <v>0.9223</v>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="V15" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="W15" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X15" s="6" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1405,6 +1696,14 @@
       <c r="P16" s="5" t="n">
         <v>0.928</v>
       </c>
+      <c r="Q16" s="6" t="inlineStr"/>
+      <c r="R16" s="6" t="inlineStr"/>
+      <c r="S16" s="6" t="inlineStr"/>
+      <c r="T16" s="6" t="inlineStr"/>
+      <c r="U16" s="6" t="inlineStr"/>
+      <c r="V16" s="6" t="inlineStr"/>
+      <c r="W16" s="6" t="inlineStr"/>
+      <c r="X16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1468,6 +1767,30 @@
       </c>
       <c r="P17" s="5" t="n">
         <v>0.9114</v>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="S17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="6" t="n">
+        <v>0.02666666666666667</v>
+      </c>
+      <c r="U17" s="6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="V17" s="6" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="W17" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="X17" s="6" t="n">
+        <v>0.12</v>
       </c>
     </row>
     <row r="18">
@@ -1530,6 +1853,30 @@
       </c>
       <c r="P18" s="5" t="n">
         <v>0.922</v>
+      </c>
+      <c r="Q18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="V18" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="W18" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X18" s="6" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -1591,6 +1938,14 @@
       <c r="P19" s="5" t="n">
         <v>0.9223</v>
       </c>
+      <c r="Q19" s="6" t="inlineStr"/>
+      <c r="R19" s="6" t="inlineStr"/>
+      <c r="S19" s="6" t="inlineStr"/>
+      <c r="T19" s="6" t="inlineStr"/>
+      <c r="U19" s="6" t="inlineStr"/>
+      <c r="V19" s="6" t="inlineStr"/>
+      <c r="W19" s="6" t="inlineStr"/>
+      <c r="X19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1654,6 +2009,30 @@
       </c>
       <c r="P20" s="5" t="n">
         <v>0.9088000000000001</v>
+      </c>
+      <c r="Q20" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="S20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="6" t="n">
+        <v>0.02666666666666667</v>
+      </c>
+      <c r="U20" s="6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="V20" s="6" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="W20" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="X20" s="6" t="n">
+        <v>0.12</v>
       </c>
     </row>
     <row r="21">
@@ -1709,6 +2088,14 @@
       <c r="P21" s="5" t="n">
         <v>0.8999</v>
       </c>
+      <c r="Q21" s="6" t="inlineStr"/>
+      <c r="R21" s="6" t="inlineStr"/>
+      <c r="S21" s="6" t="inlineStr"/>
+      <c r="T21" s="6" t="inlineStr"/>
+      <c r="U21" s="6" t="inlineStr"/>
+      <c r="V21" s="6" t="inlineStr"/>
+      <c r="W21" s="6" t="inlineStr"/>
+      <c r="X21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1763,6 +2150,14 @@
       <c r="P22" s="5" t="n">
         <v>0.9913999999999999</v>
       </c>
+      <c r="Q22" s="6" t="inlineStr"/>
+      <c r="R22" s="6" t="inlineStr"/>
+      <c r="S22" s="6" t="inlineStr"/>
+      <c r="T22" s="6" t="inlineStr"/>
+      <c r="U22" s="6" t="inlineStr"/>
+      <c r="V22" s="6" t="inlineStr"/>
+      <c r="W22" s="6" t="inlineStr"/>
+      <c r="X22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1817,6 +2212,14 @@
       <c r="P23" s="5" t="n">
         <v>0.945</v>
       </c>
+      <c r="Q23" s="6" t="inlineStr"/>
+      <c r="R23" s="6" t="inlineStr"/>
+      <c r="S23" s="6" t="inlineStr"/>
+      <c r="T23" s="6" t="inlineStr"/>
+      <c r="U23" s="6" t="inlineStr"/>
+      <c r="V23" s="6" t="inlineStr"/>
+      <c r="W23" s="6" t="inlineStr"/>
+      <c r="X23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1871,6 +2274,14 @@
       <c r="P24" s="5" t="n">
         <v>0.945</v>
       </c>
+      <c r="Q24" s="6" t="inlineStr"/>
+      <c r="R24" s="6" t="inlineStr"/>
+      <c r="S24" s="6" t="inlineStr"/>
+      <c r="T24" s="6" t="inlineStr"/>
+      <c r="U24" s="6" t="inlineStr"/>
+      <c r="V24" s="6" t="inlineStr"/>
+      <c r="W24" s="6" t="inlineStr"/>
+      <c r="X24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1925,6 +2336,14 @@
       <c r="P25" s="5" t="n">
         <v>0.89</v>
       </c>
+      <c r="Q25" s="6" t="inlineStr"/>
+      <c r="R25" s="6" t="inlineStr"/>
+      <c r="S25" s="6" t="inlineStr"/>
+      <c r="T25" s="6" t="inlineStr"/>
+      <c r="U25" s="6" t="inlineStr"/>
+      <c r="V25" s="6" t="inlineStr"/>
+      <c r="W25" s="6" t="inlineStr"/>
+      <c r="X25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1975,6 +2394,14 @@
       <c r="P26" s="5" t="n">
         <v>0.9801</v>
       </c>
+      <c r="Q26" s="6" t="inlineStr"/>
+      <c r="R26" s="6" t="inlineStr"/>
+      <c r="S26" s="6" t="inlineStr"/>
+      <c r="T26" s="6" t="inlineStr"/>
+      <c r="U26" s="6" t="inlineStr"/>
+      <c r="V26" s="6" t="inlineStr"/>
+      <c r="W26" s="6" t="inlineStr"/>
+      <c r="X26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2023,6 +2450,14 @@
         <v>0.9825</v>
       </c>
       <c r="P27" s="5" t="inlineStr"/>
+      <c r="Q27" s="6" t="inlineStr"/>
+      <c r="R27" s="6" t="inlineStr"/>
+      <c r="S27" s="6" t="inlineStr"/>
+      <c r="T27" s="6" t="inlineStr"/>
+      <c r="U27" s="6" t="inlineStr"/>
+      <c r="V27" s="6" t="inlineStr"/>
+      <c r="W27" s="6" t="inlineStr"/>
+      <c r="X27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2077,6 +2512,14 @@
       <c r="P28" s="5" t="n">
         <v>0.9978</v>
       </c>
+      <c r="Q28" s="6" t="inlineStr"/>
+      <c r="R28" s="6" t="inlineStr"/>
+      <c r="S28" s="6" t="inlineStr"/>
+      <c r="T28" s="6" t="inlineStr"/>
+      <c r="U28" s="6" t="inlineStr"/>
+      <c r="V28" s="6" t="inlineStr"/>
+      <c r="W28" s="6" t="inlineStr"/>
+      <c r="X28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2127,6 +2570,14 @@
       <c r="P29" s="5" t="n">
         <v>0.9952</v>
       </c>
+      <c r="Q29" s="6" t="inlineStr"/>
+      <c r="R29" s="6" t="inlineStr"/>
+      <c r="S29" s="6" t="inlineStr"/>
+      <c r="T29" s="6" t="inlineStr"/>
+      <c r="U29" s="6" t="inlineStr"/>
+      <c r="V29" s="6" t="inlineStr"/>
+      <c r="W29" s="6" t="inlineStr"/>
+      <c r="X29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2177,6 +2628,14 @@
       <c r="P30" s="5" t="n">
         <v>1.0065</v>
       </c>
+      <c r="Q30" s="6" t="inlineStr"/>
+      <c r="R30" s="6" t="inlineStr"/>
+      <c r="S30" s="6" t="inlineStr"/>
+      <c r="T30" s="6" t="inlineStr"/>
+      <c r="U30" s="6" t="inlineStr"/>
+      <c r="V30" s="6" t="inlineStr"/>
+      <c r="W30" s="6" t="inlineStr"/>
+      <c r="X30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2231,6 +2690,14 @@
       <c r="P31" s="5" t="n">
         <v>0.9</v>
       </c>
+      <c r="Q31" s="6" t="inlineStr"/>
+      <c r="R31" s="6" t="inlineStr"/>
+      <c r="S31" s="6" t="inlineStr"/>
+      <c r="T31" s="6" t="inlineStr"/>
+      <c r="U31" s="6" t="inlineStr"/>
+      <c r="V31" s="6" t="inlineStr"/>
+      <c r="W31" s="6" t="inlineStr"/>
+      <c r="X31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2281,6 +2748,14 @@
       <c r="P32" s="5" t="n">
         <v>0.901</v>
       </c>
+      <c r="Q32" s="6" t="inlineStr"/>
+      <c r="R32" s="6" t="inlineStr"/>
+      <c r="S32" s="6" t="inlineStr"/>
+      <c r="T32" s="6" t="inlineStr"/>
+      <c r="U32" s="6" t="inlineStr"/>
+      <c r="V32" s="6" t="inlineStr"/>
+      <c r="W32" s="6" t="inlineStr"/>
+      <c r="X32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2335,6 +2810,14 @@
       <c r="P33" s="5" t="n">
         <v>0.9833</v>
       </c>
+      <c r="Q33" s="6" t="inlineStr"/>
+      <c r="R33" s="6" t="inlineStr"/>
+      <c r="S33" s="6" t="inlineStr"/>
+      <c r="T33" s="6" t="inlineStr"/>
+      <c r="U33" s="6" t="inlineStr"/>
+      <c r="V33" s="6" t="inlineStr"/>
+      <c r="W33" s="6" t="inlineStr"/>
+      <c r="X33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2389,6 +2872,14 @@
       <c r="P34" s="5" t="n">
         <v>0.9833</v>
       </c>
+      <c r="Q34" s="6" t="inlineStr"/>
+      <c r="R34" s="6" t="inlineStr"/>
+      <c r="S34" s="6" t="inlineStr"/>
+      <c r="T34" s="6" t="inlineStr"/>
+      <c r="U34" s="6" t="inlineStr"/>
+      <c r="V34" s="6" t="inlineStr"/>
+      <c r="W34" s="6" t="inlineStr"/>
+      <c r="X34" s="6" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2443,6 +2934,14 @@
       <c r="P35" s="5" t="n">
         <v>0.9833</v>
       </c>
+      <c r="Q35" s="6" t="inlineStr"/>
+      <c r="R35" s="6" t="inlineStr"/>
+      <c r="S35" s="6" t="inlineStr"/>
+      <c r="T35" s="6" t="inlineStr"/>
+      <c r="U35" s="6" t="inlineStr"/>
+      <c r="V35" s="6" t="inlineStr"/>
+      <c r="W35" s="6" t="inlineStr"/>
+      <c r="X35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2495,6 +2994,14 @@
       <c r="P36" s="5" t="n">
         <v>0.9569</v>
       </c>
+      <c r="Q36" s="6" t="inlineStr"/>
+      <c r="R36" s="6" t="inlineStr"/>
+      <c r="S36" s="6" t="inlineStr"/>
+      <c r="T36" s="6" t="inlineStr"/>
+      <c r="U36" s="6" t="inlineStr"/>
+      <c r="V36" s="6" t="inlineStr"/>
+      <c r="W36" s="6" t="inlineStr"/>
+      <c r="X36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2541,6 +3048,14 @@
       </c>
       <c r="O37" s="5" t="inlineStr"/>
       <c r="P37" s="5" t="inlineStr"/>
+      <c r="Q37" s="6" t="inlineStr"/>
+      <c r="R37" s="6" t="inlineStr"/>
+      <c r="S37" s="6" t="inlineStr"/>
+      <c r="T37" s="6" t="inlineStr"/>
+      <c r="U37" s="6" t="inlineStr"/>
+      <c r="V37" s="6" t="inlineStr"/>
+      <c r="W37" s="6" t="inlineStr"/>
+      <c r="X37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2591,6 +3106,14 @@
       <c r="P38" s="5" t="n">
         <v>0.9952</v>
       </c>
+      <c r="Q38" s="6" t="inlineStr"/>
+      <c r="R38" s="6" t="inlineStr"/>
+      <c r="S38" s="6" t="inlineStr"/>
+      <c r="T38" s="6" t="inlineStr"/>
+      <c r="U38" s="6" t="inlineStr"/>
+      <c r="V38" s="6" t="inlineStr"/>
+      <c r="W38" s="6" t="inlineStr"/>
+      <c r="X38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2641,6 +3164,14 @@
       <c r="P39" s="5" t="n">
         <v>0.9819</v>
       </c>
+      <c r="Q39" s="6" t="inlineStr"/>
+      <c r="R39" s="6" t="inlineStr"/>
+      <c r="S39" s="6" t="inlineStr"/>
+      <c r="T39" s="6" t="inlineStr"/>
+      <c r="U39" s="6" t="inlineStr"/>
+      <c r="V39" s="6" t="inlineStr"/>
+      <c r="W39" s="6" t="inlineStr"/>
+      <c r="X39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2691,6 +3222,14 @@
       <c r="P40" s="5" t="n">
         <v>0.9819</v>
       </c>
+      <c r="Q40" s="6" t="inlineStr"/>
+      <c r="R40" s="6" t="inlineStr"/>
+      <c r="S40" s="6" t="inlineStr"/>
+      <c r="T40" s="6" t="inlineStr"/>
+      <c r="U40" s="6" t="inlineStr"/>
+      <c r="V40" s="6" t="inlineStr"/>
+      <c r="W40" s="6" t="inlineStr"/>
+      <c r="X40" s="6" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2741,6 +3280,14 @@
       <c r="P41" s="5" t="n">
         <v>0.9819</v>
       </c>
+      <c r="Q41" s="6" t="inlineStr"/>
+      <c r="R41" s="6" t="inlineStr"/>
+      <c r="S41" s="6" t="inlineStr"/>
+      <c r="T41" s="6" t="inlineStr"/>
+      <c r="U41" s="6" t="inlineStr"/>
+      <c r="V41" s="6" t="inlineStr"/>
+      <c r="W41" s="6" t="inlineStr"/>
+      <c r="X41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2789,6 +3336,14 @@
       <c r="P42" s="5" t="n">
         <v>0.9824000000000001</v>
       </c>
+      <c r="Q42" s="6" t="inlineStr"/>
+      <c r="R42" s="6" t="inlineStr"/>
+      <c r="S42" s="6" t="inlineStr"/>
+      <c r="T42" s="6" t="inlineStr"/>
+      <c r="U42" s="6" t="inlineStr"/>
+      <c r="V42" s="6" t="inlineStr"/>
+      <c r="W42" s="6" t="inlineStr"/>
+      <c r="X42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2837,6 +3392,14 @@
       <c r="P43" s="5" t="n">
         <v>0.9824000000000001</v>
       </c>
+      <c r="Q43" s="6" t="inlineStr"/>
+      <c r="R43" s="6" t="inlineStr"/>
+      <c r="S43" s="6" t="inlineStr"/>
+      <c r="T43" s="6" t="inlineStr"/>
+      <c r="U43" s="6" t="inlineStr"/>
+      <c r="V43" s="6" t="inlineStr"/>
+      <c r="W43" s="6" t="inlineStr"/>
+      <c r="X43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2889,6 +3452,14 @@
       <c r="P44" s="5" t="n">
         <v>0.9829</v>
       </c>
+      <c r="Q44" s="6" t="inlineStr"/>
+      <c r="R44" s="6" t="inlineStr"/>
+      <c r="S44" s="6" t="inlineStr"/>
+      <c r="T44" s="6" t="inlineStr"/>
+      <c r="U44" s="6" t="inlineStr"/>
+      <c r="V44" s="6" t="inlineStr"/>
+      <c r="W44" s="6" t="inlineStr"/>
+      <c r="X44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -2939,6 +3510,14 @@
       <c r="P45" s="5" t="n">
         <v>0.9801</v>
       </c>
+      <c r="Q45" s="6" t="inlineStr"/>
+      <c r="R45" s="6" t="inlineStr"/>
+      <c r="S45" s="6" t="inlineStr"/>
+      <c r="T45" s="6" t="inlineStr"/>
+      <c r="U45" s="6" t="inlineStr"/>
+      <c r="V45" s="6" t="inlineStr"/>
+      <c r="W45" s="6" t="inlineStr"/>
+      <c r="X45" s="6" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2993,6 +3572,14 @@
       <c r="P46" s="5" t="n">
         <v>0.901</v>
       </c>
+      <c r="Q46" s="6" t="inlineStr"/>
+      <c r="R46" s="6" t="inlineStr"/>
+      <c r="S46" s="6" t="inlineStr"/>
+      <c r="T46" s="6" t="inlineStr"/>
+      <c r="U46" s="6" t="inlineStr"/>
+      <c r="V46" s="6" t="inlineStr"/>
+      <c r="W46" s="6" t="inlineStr"/>
+      <c r="X46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3047,6 +3634,14 @@
       <c r="P47" s="5" t="n">
         <v>0.983</v>
       </c>
+      <c r="Q47" s="6" t="inlineStr"/>
+      <c r="R47" s="6" t="inlineStr"/>
+      <c r="S47" s="6" t="inlineStr"/>
+      <c r="T47" s="6" t="inlineStr"/>
+      <c r="U47" s="6" t="inlineStr"/>
+      <c r="V47" s="6" t="inlineStr"/>
+      <c r="W47" s="6" t="inlineStr"/>
+      <c r="X47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3097,6 +3692,14 @@
       <c r="P48" s="5" t="n">
         <v>0.9801</v>
       </c>
+      <c r="Q48" s="6" t="inlineStr"/>
+      <c r="R48" s="6" t="inlineStr"/>
+      <c r="S48" s="6" t="inlineStr"/>
+      <c r="T48" s="6" t="inlineStr"/>
+      <c r="U48" s="6" t="inlineStr"/>
+      <c r="V48" s="6" t="inlineStr"/>
+      <c r="W48" s="6" t="inlineStr"/>
+      <c r="X48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -3151,6 +3754,14 @@
       <c r="P49" s="5" t="n">
         <v>0.9569</v>
       </c>
+      <c r="Q49" s="6" t="inlineStr"/>
+      <c r="R49" s="6" t="inlineStr"/>
+      <c r="S49" s="6" t="inlineStr"/>
+      <c r="T49" s="6" t="inlineStr"/>
+      <c r="U49" s="6" t="inlineStr"/>
+      <c r="V49" s="6" t="inlineStr"/>
+      <c r="W49" s="6" t="inlineStr"/>
+      <c r="X49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3205,6 +3816,14 @@
       <c r="P50" s="5" t="n">
         <v>0.9519</v>
       </c>
+      <c r="Q50" s="6" t="inlineStr"/>
+      <c r="R50" s="6" t="inlineStr"/>
+      <c r="S50" s="6" t="inlineStr"/>
+      <c r="T50" s="6" t="inlineStr"/>
+      <c r="U50" s="6" t="inlineStr"/>
+      <c r="V50" s="6" t="inlineStr"/>
+      <c r="W50" s="6" t="inlineStr"/>
+      <c r="X50" s="6" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3255,6 +3874,14 @@
       <c r="P51" s="5" t="n">
         <v>0.9952</v>
       </c>
+      <c r="Q51" s="6" t="inlineStr"/>
+      <c r="R51" s="6" t="inlineStr"/>
+      <c r="S51" s="6" t="inlineStr"/>
+      <c r="T51" s="6" t="inlineStr"/>
+      <c r="U51" s="6" t="inlineStr"/>
+      <c r="V51" s="6" t="inlineStr"/>
+      <c r="W51" s="6" t="inlineStr"/>
+      <c r="X51" s="6" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3309,6 +3936,14 @@
       <c r="P52" s="5" t="n">
         <v>0.9893999999999999</v>
       </c>
+      <c r="Q52" s="6" t="inlineStr"/>
+      <c r="R52" s="6" t="inlineStr"/>
+      <c r="S52" s="6" t="inlineStr"/>
+      <c r="T52" s="6" t="inlineStr"/>
+      <c r="U52" s="6" t="inlineStr"/>
+      <c r="V52" s="6" t="inlineStr"/>
+      <c r="W52" s="6" t="inlineStr"/>
+      <c r="X52" s="6" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -3363,6 +3998,14 @@
       <c r="P53" s="5" t="n">
         <v>0.9569</v>
       </c>
+      <c r="Q53" s="6" t="inlineStr"/>
+      <c r="R53" s="6" t="inlineStr"/>
+      <c r="S53" s="6" t="inlineStr"/>
+      <c r="T53" s="6" t="inlineStr"/>
+      <c r="U53" s="6" t="inlineStr"/>
+      <c r="V53" s="6" t="inlineStr"/>
+      <c r="W53" s="6" t="inlineStr"/>
+      <c r="X53" s="6" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -3417,6 +4060,14 @@
       <c r="P54" s="5" t="n">
         <v>0.8881</v>
       </c>
+      <c r="Q54" s="6" t="inlineStr"/>
+      <c r="R54" s="6" t="inlineStr"/>
+      <c r="S54" s="6" t="inlineStr"/>
+      <c r="T54" s="6" t="inlineStr"/>
+      <c r="U54" s="6" t="inlineStr"/>
+      <c r="V54" s="6" t="inlineStr"/>
+      <c r="W54" s="6" t="inlineStr"/>
+      <c r="X54" s="6" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3471,6 +4122,14 @@
       <c r="P55" s="5" t="n">
         <v>0.8881</v>
       </c>
+      <c r="Q55" s="6" t="inlineStr"/>
+      <c r="R55" s="6" t="inlineStr"/>
+      <c r="S55" s="6" t="inlineStr"/>
+      <c r="T55" s="6" t="inlineStr"/>
+      <c r="U55" s="6" t="inlineStr"/>
+      <c r="V55" s="6" t="inlineStr"/>
+      <c r="W55" s="6" t="inlineStr"/>
+      <c r="X55" s="6" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3525,6 +4184,14 @@
       <c r="P56" s="5" t="n">
         <v>0.9952</v>
       </c>
+      <c r="Q56" s="6" t="inlineStr"/>
+      <c r="R56" s="6" t="inlineStr"/>
+      <c r="S56" s="6" t="inlineStr"/>
+      <c r="T56" s="6" t="inlineStr"/>
+      <c r="U56" s="6" t="inlineStr"/>
+      <c r="V56" s="6" t="inlineStr"/>
+      <c r="W56" s="6" t="inlineStr"/>
+      <c r="X56" s="6" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -3577,6 +4244,14 @@
       <c r="P57" s="5" t="n">
         <v>0.9837</v>
       </c>
+      <c r="Q57" s="6" t="inlineStr"/>
+      <c r="R57" s="6" t="inlineStr"/>
+      <c r="S57" s="6" t="inlineStr"/>
+      <c r="T57" s="6" t="inlineStr"/>
+      <c r="U57" s="6" t="inlineStr"/>
+      <c r="V57" s="6" t="inlineStr"/>
+      <c r="W57" s="6" t="inlineStr"/>
+      <c r="X57" s="6" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -3631,6 +4306,14 @@
       <c r="P58" s="5" t="n">
         <v>0.951</v>
       </c>
+      <c r="Q58" s="6" t="inlineStr"/>
+      <c r="R58" s="6" t="inlineStr"/>
+      <c r="S58" s="6" t="inlineStr"/>
+      <c r="T58" s="6" t="inlineStr"/>
+      <c r="U58" s="6" t="inlineStr"/>
+      <c r="V58" s="6" t="inlineStr"/>
+      <c r="W58" s="6" t="inlineStr"/>
+      <c r="X58" s="6" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -3685,6 +4368,14 @@
       <c r="P59" s="5" t="n">
         <v>0.9832</v>
       </c>
+      <c r="Q59" s="6" t="inlineStr"/>
+      <c r="R59" s="6" t="inlineStr"/>
+      <c r="S59" s="6" t="inlineStr"/>
+      <c r="T59" s="6" t="inlineStr"/>
+      <c r="U59" s="6" t="inlineStr"/>
+      <c r="V59" s="6" t="inlineStr"/>
+      <c r="W59" s="6" t="inlineStr"/>
+      <c r="X59" s="6" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -3735,6 +4426,14 @@
       <c r="P60" s="5" t="n">
         <v>0.9952</v>
       </c>
+      <c r="Q60" s="6" t="inlineStr"/>
+      <c r="R60" s="6" t="inlineStr"/>
+      <c r="S60" s="6" t="inlineStr"/>
+      <c r="T60" s="6" t="inlineStr"/>
+      <c r="U60" s="6" t="inlineStr"/>
+      <c r="V60" s="6" t="inlineStr"/>
+      <c r="W60" s="6" t="inlineStr"/>
+      <c r="X60" s="6" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -3785,6 +4484,14 @@
       <c r="P61" s="5" t="n">
         <v>0.9913999999999999</v>
       </c>
+      <c r="Q61" s="6" t="inlineStr"/>
+      <c r="R61" s="6" t="inlineStr"/>
+      <c r="S61" s="6" t="inlineStr"/>
+      <c r="T61" s="6" t="inlineStr"/>
+      <c r="U61" s="6" t="inlineStr"/>
+      <c r="V61" s="6" t="inlineStr"/>
+      <c r="W61" s="6" t="inlineStr"/>
+      <c r="X61" s="6" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -3835,6 +4542,14 @@
       <c r="P62" s="5" t="n">
         <v>0.9317</v>
       </c>
+      <c r="Q62" s="6" t="inlineStr"/>
+      <c r="R62" s="6" t="inlineStr"/>
+      <c r="S62" s="6" t="inlineStr"/>
+      <c r="T62" s="6" t="inlineStr"/>
+      <c r="U62" s="6" t="inlineStr"/>
+      <c r="V62" s="6" t="inlineStr"/>
+      <c r="W62" s="6" t="inlineStr"/>
+      <c r="X62" s="6" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -3885,6 +4600,14 @@
       <c r="P63" s="5" t="n">
         <v>0.9913999999999999</v>
       </c>
+      <c r="Q63" s="6" t="inlineStr"/>
+      <c r="R63" s="6" t="inlineStr"/>
+      <c r="S63" s="6" t="inlineStr"/>
+      <c r="T63" s="6" t="inlineStr"/>
+      <c r="U63" s="6" t="inlineStr"/>
+      <c r="V63" s="6" t="inlineStr"/>
+      <c r="W63" s="6" t="inlineStr"/>
+      <c r="X63" s="6" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -3935,6 +4658,14 @@
       <c r="P64" s="5" t="n">
         <v>0.9801</v>
       </c>
+      <c r="Q64" s="6" t="inlineStr"/>
+      <c r="R64" s="6" t="inlineStr"/>
+      <c r="S64" s="6" t="inlineStr"/>
+      <c r="T64" s="6" t="inlineStr"/>
+      <c r="U64" s="6" t="inlineStr"/>
+      <c r="V64" s="6" t="inlineStr"/>
+      <c r="W64" s="6" t="inlineStr"/>
+      <c r="X64" s="6" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -3985,6 +4716,14 @@
       <c r="P65" s="5" t="n">
         <v>0.9952</v>
       </c>
+      <c r="Q65" s="6" t="inlineStr"/>
+      <c r="R65" s="6" t="inlineStr"/>
+      <c r="S65" s="6" t="inlineStr"/>
+      <c r="T65" s="6" t="inlineStr"/>
+      <c r="U65" s="6" t="inlineStr"/>
+      <c r="V65" s="6" t="inlineStr"/>
+      <c r="W65" s="6" t="inlineStr"/>
+      <c r="X65" s="6" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -4035,6 +4774,14 @@
       <c r="P66" s="5" t="n">
         <v>1.0065</v>
       </c>
+      <c r="Q66" s="6" t="inlineStr"/>
+      <c r="R66" s="6" t="inlineStr"/>
+      <c r="S66" s="6" t="inlineStr"/>
+      <c r="T66" s="6" t="inlineStr"/>
+      <c r="U66" s="6" t="inlineStr"/>
+      <c r="V66" s="6" t="inlineStr"/>
+      <c r="W66" s="6" t="inlineStr"/>
+      <c r="X66" s="6" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -4089,6 +4836,14 @@
       <c r="P67" s="5" t="n">
         <v>0.9562</v>
       </c>
+      <c r="Q67" s="6" t="inlineStr"/>
+      <c r="R67" s="6" t="inlineStr"/>
+      <c r="S67" s="6" t="inlineStr"/>
+      <c r="T67" s="6" t="inlineStr"/>
+      <c r="U67" s="6" t="inlineStr"/>
+      <c r="V67" s="6" t="inlineStr"/>
+      <c r="W67" s="6" t="inlineStr"/>
+      <c r="X67" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4101,7 +4856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:W67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4113,62 +4868,146 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>DUID</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>Fuel</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>MLF_FY24-25</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>MLF_FY25-26</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>MLF_FY26-27 (Draft)</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>CURTAILMENT_ACTUAL_FY23-24</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>CURTAILMENT_ACTUAL_FY24-25</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>ELI_CURTAILMENT_NEAR</t>
         </is>
       </c>
-      <c r="I1" s="6" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>ELI_CURTAILMENT_MED</t>
         </is>
       </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_FY1</t>
+        </is>
+      </c>
+      <c r="K1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_FY1_LABEL</t>
+        </is>
+      </c>
+      <c r="L1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_FY2</t>
+        </is>
+      </c>
+      <c r="M1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_FY2_LABEL</t>
+        </is>
+      </c>
+      <c r="N1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_FY3</t>
+        </is>
+      </c>
+      <c r="O1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_FY3_LABEL</t>
+        </is>
+      </c>
+      <c r="P1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_AVG</t>
+        </is>
+      </c>
+      <c r="Q1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_FY1</t>
+        </is>
+      </c>
+      <c r="R1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_FY1_LABEL</t>
+        </is>
+      </c>
+      <c r="S1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_FY2</t>
+        </is>
+      </c>
+      <c r="T1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_FY2_LABEL</t>
+        </is>
+      </c>
+      <c r="U1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_FY3</t>
+        </is>
+      </c>
+      <c r="V1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_FY3_LABEL</t>
+        </is>
+      </c>
+      <c r="W1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_AVG</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>BANN1</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4194,14 +5033,68 @@
       <c r="I2" s="5" t="n">
         <v>0.164192244302687</v>
       </c>
+      <c r="J2" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="n">
+        <v>0.02666666666666667</v>
+      </c>
+      <c r="Q2" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="n">
+        <v>0.12</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>CRWARP1</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4217,14 +5110,52 @@
       <c r="G3" s="5" t="inlineStr"/>
       <c r="H3" s="5" t="inlineStr"/>
       <c r="I3" s="5" t="inlineStr"/>
+      <c r="J3" s="5" t="inlineStr"/>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr"/>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr"/>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr"/>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="inlineStr"/>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>COHUNSF1</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4246,14 +5177,68 @@
       <c r="I4" s="5" t="n">
         <v>0.122422882740379</v>
       </c>
+      <c r="J4" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="n">
+        <v>0.02666666666666667</v>
+      </c>
+      <c r="Q4" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="R4" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S4" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="T4" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U4" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="V4" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="n">
+        <v>0.12</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>GANNSF1</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4279,14 +5264,68 @@
       <c r="I5" s="5" t="n">
         <v>0.122422882740379</v>
       </c>
+      <c r="J5" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P5" s="5" t="n">
+        <v>0.02666666666666667</v>
+      </c>
+      <c r="Q5" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S5" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="T5" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U5" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="V5" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W5" s="5" t="n">
+        <v>0.12</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>GIRGSF</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4310,14 +5349,68 @@
       <c r="I6" s="5" t="n">
         <v>0.08205629867681941</v>
       </c>
+      <c r="J6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="R6" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S6" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="T6" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U6" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="V6" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W6" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>GLENSF1</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4341,14 +5434,68 @@
       <c r="I7" s="5" t="n">
         <v>0.08997768712489811</v>
       </c>
+      <c r="J7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="R7" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S7" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="T7" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U7" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="V7" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W7" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>GLRWNSF1</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4370,14 +5517,52 @@
       </c>
       <c r="H8" s="5" t="inlineStr"/>
       <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr"/>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P8" s="5" t="inlineStr"/>
+      <c r="Q8" s="5" t="inlineStr"/>
+      <c r="R8" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S8" s="5" t="inlineStr"/>
+      <c r="T8" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U8" s="5" t="inlineStr"/>
+      <c r="V8" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>GOESF1</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4393,14 +5578,52 @@
       <c r="G9" s="5" t="inlineStr"/>
       <c r="H9" s="5" t="inlineStr"/>
       <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P9" s="5" t="inlineStr"/>
+      <c r="Q9" s="5" t="inlineStr"/>
+      <c r="R9" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S9" s="5" t="inlineStr"/>
+      <c r="T9" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U9" s="5" t="inlineStr"/>
+      <c r="V9" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>KARSF1</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4426,14 +5649,68 @@
       <c r="I10" s="5" t="n">
         <v>0.072415601225557</v>
       </c>
+      <c r="J10" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P10" s="5" t="n">
+        <v>0.02666666666666667</v>
+      </c>
+      <c r="Q10" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="R10" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S10" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="T10" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U10" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="V10" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W10" s="5" t="n">
+        <v>0.12</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>KERNGSP1</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4451,14 +5728,52 @@
       <c r="G11" s="5" t="inlineStr"/>
       <c r="H11" s="5" t="inlineStr"/>
       <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P11" s="5" t="inlineStr"/>
+      <c r="Q11" s="5" t="inlineStr"/>
+      <c r="R11" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S11" s="5" t="inlineStr"/>
+      <c r="T11" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U11" s="5" t="inlineStr"/>
+      <c r="V11" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>KIAMSF1</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4484,14 +5799,68 @@
       <c r="I12" s="5" t="n">
         <v>0.0878331516592939</v>
       </c>
+      <c r="J12" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P12" s="5" t="n">
+        <v>0.02666666666666667</v>
+      </c>
+      <c r="Q12" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="R12" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S12" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="T12" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U12" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="V12" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W12" s="5" t="n">
+        <v>0.12</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>LANCSF1</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4505,14 +5874,52 @@
       <c r="G13" s="5" t="inlineStr"/>
       <c r="H13" s="5" t="inlineStr"/>
       <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr"/>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P13" s="5" t="inlineStr"/>
+      <c r="Q13" s="5" t="inlineStr"/>
+      <c r="R13" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S13" s="5" t="inlineStr"/>
+      <c r="T13" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U13" s="5" t="inlineStr"/>
+      <c r="V13" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>MOKOSF1</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4530,14 +5937,52 @@
       <c r="G14" s="5" t="inlineStr"/>
       <c r="H14" s="5" t="inlineStr"/>
       <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr"/>
+      <c r="M14" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P14" s="5" t="inlineStr"/>
+      <c r="Q14" s="5" t="inlineStr"/>
+      <c r="R14" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S14" s="5" t="inlineStr"/>
+      <c r="T14" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U14" s="5" t="inlineStr"/>
+      <c r="V14" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>NUMURSF1</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4563,14 +6008,68 @@
       <c r="I15" s="5" t="n">
         <v>0.08205629867681941</v>
       </c>
+      <c r="J15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="R15" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S15" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="T15" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U15" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="V15" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W15" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>WNSF1</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4588,14 +6087,52 @@
       <c r="G16" s="5" t="inlineStr"/>
       <c r="H16" s="5" t="inlineStr"/>
       <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N16" s="5" t="inlineStr"/>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P16" s="5" t="inlineStr"/>
+      <c r="Q16" s="5" t="inlineStr"/>
+      <c r="R16" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S16" s="5" t="inlineStr"/>
+      <c r="T16" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U16" s="5" t="inlineStr"/>
+      <c r="V16" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>WEMENSF1</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4621,14 +6158,68 @@
       <c r="I17" s="5" t="n">
         <v>0.164192244302687</v>
       </c>
+      <c r="J17" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M17" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P17" s="5" t="n">
+        <v>0.02666666666666667</v>
+      </c>
+      <c r="Q17" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="R17" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S17" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="T17" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U17" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="V17" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W17" s="5" t="n">
+        <v>0.12</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>WINTSF1</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4652,14 +6243,68 @@
       <c r="I18" s="5" t="n">
         <v>0.08997768712489811</v>
       </c>
+      <c r="J18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="R18" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S18" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="T18" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U18" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="V18" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W18" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>WUNUSF1</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4681,14 +6326,52 @@
       <c r="I19" s="5" t="n">
         <v>0.08205629867681941</v>
       </c>
+      <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr"/>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N19" s="5" t="inlineStr"/>
+      <c r="O19" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P19" s="5" t="inlineStr"/>
+      <c r="Q19" s="5" t="inlineStr"/>
+      <c r="R19" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S19" s="5" t="inlineStr"/>
+      <c r="T19" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U19" s="5" t="inlineStr"/>
+      <c r="V19" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>YATSF1</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4714,14 +6397,68 @@
       <c r="I20" s="5" t="n">
         <v>0.072415601225557</v>
       </c>
+      <c r="J20" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P20" s="5" t="n">
+        <v>0.02666666666666667</v>
+      </c>
+      <c r="Q20" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="R20" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S20" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="T20" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U20" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="V20" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W20" s="5" t="n">
+        <v>0.12</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>ARWF1</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4743,14 +6480,52 @@
       </c>
       <c r="H21" s="5" t="inlineStr"/>
       <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr"/>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N21" s="5" t="inlineStr"/>
+      <c r="O21" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P21" s="5" t="inlineStr"/>
+      <c r="Q21" s="5" t="inlineStr"/>
+      <c r="R21" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S21" s="5" t="inlineStr"/>
+      <c r="T21" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U21" s="5" t="inlineStr"/>
+      <c r="V21" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>BALDHWF1</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4772,14 +6547,52 @@
       </c>
       <c r="H22" s="5" t="inlineStr"/>
       <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr"/>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N22" s="5" t="inlineStr"/>
+      <c r="O22" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P22" s="5" t="inlineStr"/>
+      <c r="Q22" s="5" t="inlineStr"/>
+      <c r="R22" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S22" s="5" t="inlineStr"/>
+      <c r="T22" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U22" s="5" t="inlineStr"/>
+      <c r="V22" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>BRYB2WF2</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4801,14 +6614,52 @@
       </c>
       <c r="H23" s="5" t="inlineStr"/>
       <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr"/>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr"/>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N23" s="5" t="inlineStr"/>
+      <c r="O23" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P23" s="5" t="inlineStr"/>
+      <c r="Q23" s="5" t="inlineStr"/>
+      <c r="R23" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S23" s="5" t="inlineStr"/>
+      <c r="T23" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U23" s="5" t="inlineStr"/>
+      <c r="V23" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>BRYB1WF1</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4830,14 +6681,52 @@
       </c>
       <c r="H24" s="5" t="inlineStr"/>
       <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr"/>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N24" s="5" t="inlineStr"/>
+      <c r="O24" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P24" s="5" t="inlineStr"/>
+      <c r="Q24" s="5" t="inlineStr"/>
+      <c r="R24" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S24" s="5" t="inlineStr"/>
+      <c r="T24" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U24" s="5" t="inlineStr"/>
+      <c r="V24" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>BULGANA1</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4859,14 +6748,52 @@
       </c>
       <c r="H25" s="5" t="inlineStr"/>
       <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr"/>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N25" s="5" t="inlineStr"/>
+      <c r="O25" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P25" s="5" t="inlineStr"/>
+      <c r="Q25" s="5" t="inlineStr"/>
+      <c r="R25" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S25" s="5" t="inlineStr"/>
+      <c r="T25" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U25" s="5" t="inlineStr"/>
+      <c r="V25" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>CHALLHWF</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4884,14 +6811,52 @@
       <c r="G26" s="5" t="inlineStr"/>
       <c r="H26" s="5" t="inlineStr"/>
       <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr"/>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N26" s="5" t="inlineStr"/>
+      <c r="O26" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P26" s="5" t="inlineStr"/>
+      <c r="Q26" s="5" t="inlineStr"/>
+      <c r="R26" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S26" s="5" t="inlineStr"/>
+      <c r="T26" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U26" s="5" t="inlineStr"/>
+      <c r="V26" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>CHPSTWF1</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4907,14 +6872,52 @@
       <c r="G27" s="5" t="inlineStr"/>
       <c r="H27" s="5" t="inlineStr"/>
       <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N27" s="5" t="inlineStr"/>
+      <c r="O27" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P27" s="5" t="inlineStr"/>
+      <c r="Q27" s="5" t="inlineStr"/>
+      <c r="R27" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S27" s="5" t="inlineStr"/>
+      <c r="T27" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U27" s="5" t="inlineStr"/>
+      <c r="V27" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>CHYTWF1</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4936,14 +6939,52 @@
       </c>
       <c r="H28" s="5" t="inlineStr"/>
       <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="inlineStr"/>
+      <c r="M28" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N28" s="5" t="inlineStr"/>
+      <c r="O28" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P28" s="5" t="inlineStr"/>
+      <c r="Q28" s="5" t="inlineStr"/>
+      <c r="R28" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S28" s="5" t="inlineStr"/>
+      <c r="T28" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U28" s="5" t="inlineStr"/>
+      <c r="V28" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>CODRNGTON</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4961,14 +7002,52 @@
       <c r="G29" s="5" t="inlineStr"/>
       <c r="H29" s="5" t="inlineStr"/>
       <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr"/>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr"/>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N29" s="5" t="inlineStr"/>
+      <c r="O29" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P29" s="5" t="inlineStr"/>
+      <c r="Q29" s="5" t="inlineStr"/>
+      <c r="R29" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S29" s="5" t="inlineStr"/>
+      <c r="T29" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U29" s="5" t="inlineStr"/>
+      <c r="V29" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>CBWF1</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4986,14 +7065,52 @@
       <c r="G30" s="5" t="inlineStr"/>
       <c r="H30" s="5" t="inlineStr"/>
       <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="inlineStr"/>
+      <c r="M30" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N30" s="5" t="inlineStr"/>
+      <c r="O30" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P30" s="5" t="inlineStr"/>
+      <c r="Q30" s="5" t="inlineStr"/>
+      <c r="R30" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S30" s="5" t="inlineStr"/>
+      <c r="T30" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U30" s="5" t="inlineStr"/>
+      <c r="V30" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>CROWLWF1</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5015,14 +7132,52 @@
       </c>
       <c r="H31" s="5" t="inlineStr"/>
       <c r="I31" s="5" t="inlineStr"/>
+      <c r="J31" s="5" t="inlineStr"/>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr"/>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N31" s="5" t="inlineStr"/>
+      <c r="O31" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P31" s="5" t="inlineStr"/>
+      <c r="Q31" s="5" t="inlineStr"/>
+      <c r="R31" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S31" s="5" t="inlineStr"/>
+      <c r="T31" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U31" s="5" t="inlineStr"/>
+      <c r="V31" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>DIAPURWF1</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5040,14 +7195,52 @@
       <c r="G32" s="5" t="inlineStr"/>
       <c r="H32" s="5" t="inlineStr"/>
       <c r="I32" s="5" t="inlineStr"/>
+      <c r="J32" s="5" t="inlineStr"/>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr"/>
+      <c r="M32" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N32" s="5" t="inlineStr"/>
+      <c r="O32" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P32" s="5" t="inlineStr"/>
+      <c r="Q32" s="5" t="inlineStr"/>
+      <c r="R32" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S32" s="5" t="inlineStr"/>
+      <c r="T32" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U32" s="5" t="inlineStr"/>
+      <c r="V32" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>DUNDWF1</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5069,14 +7262,52 @@
       </c>
       <c r="H33" s="5" t="inlineStr"/>
       <c r="I33" s="5" t="inlineStr"/>
+      <c r="J33" s="5" t="inlineStr"/>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr"/>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N33" s="5" t="inlineStr"/>
+      <c r="O33" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P33" s="5" t="inlineStr"/>
+      <c r="Q33" s="5" t="inlineStr"/>
+      <c r="R33" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S33" s="5" t="inlineStr"/>
+      <c r="T33" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U33" s="5" t="inlineStr"/>
+      <c r="V33" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>DUNDWF2</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5098,14 +7329,52 @@
       </c>
       <c r="H34" s="5" t="inlineStr"/>
       <c r="I34" s="5" t="inlineStr"/>
+      <c r="J34" s="5" t="inlineStr"/>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="inlineStr"/>
+      <c r="M34" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N34" s="5" t="inlineStr"/>
+      <c r="O34" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P34" s="5" t="inlineStr"/>
+      <c r="Q34" s="5" t="inlineStr"/>
+      <c r="R34" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S34" s="5" t="inlineStr"/>
+      <c r="T34" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U34" s="5" t="inlineStr"/>
+      <c r="V34" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="inlineStr">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>DUNDWF3</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5127,14 +7396,52 @@
       </c>
       <c r="H35" s="5" t="inlineStr"/>
       <c r="I35" s="5" t="inlineStr"/>
+      <c r="J35" s="5" t="inlineStr"/>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr"/>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N35" s="5" t="inlineStr"/>
+      <c r="O35" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P35" s="5" t="inlineStr"/>
+      <c r="Q35" s="5" t="inlineStr"/>
+      <c r="R35" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S35" s="5" t="inlineStr"/>
+      <c r="T35" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U35" s="5" t="inlineStr"/>
+      <c r="V35" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W35" s="5" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>ELAINWF1</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5154,14 +7461,52 @@
       <c r="G36" s="5" t="inlineStr"/>
       <c r="H36" s="5" t="inlineStr"/>
       <c r="I36" s="5" t="inlineStr"/>
+      <c r="J36" s="5" t="inlineStr"/>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="inlineStr"/>
+      <c r="M36" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N36" s="5" t="inlineStr"/>
+      <c r="O36" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P36" s="5" t="inlineStr"/>
+      <c r="Q36" s="5" t="inlineStr"/>
+      <c r="R36" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S36" s="5" t="inlineStr"/>
+      <c r="T36" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U36" s="5" t="inlineStr"/>
+      <c r="V36" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="inlineStr">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>FNWF1</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5175,14 +7520,52 @@
       <c r="G37" s="5" t="inlineStr"/>
       <c r="H37" s="5" t="inlineStr"/>
       <c r="I37" s="5" t="inlineStr"/>
+      <c r="J37" s="5" t="inlineStr"/>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr"/>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N37" s="5" t="inlineStr"/>
+      <c r="O37" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P37" s="5" t="inlineStr"/>
+      <c r="Q37" s="5" t="inlineStr"/>
+      <c r="R37" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S37" s="5" t="inlineStr"/>
+      <c r="T37" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U37" s="5" t="inlineStr"/>
+      <c r="V37" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="7" t="inlineStr">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>FSWF1</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5200,14 +7583,52 @@
       <c r="G38" s="5" t="inlineStr"/>
       <c r="H38" s="5" t="inlineStr"/>
       <c r="I38" s="5" t="inlineStr"/>
+      <c r="J38" s="5" t="inlineStr"/>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L38" s="5" t="inlineStr"/>
+      <c r="M38" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N38" s="5" t="inlineStr"/>
+      <c r="O38" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P38" s="5" t="inlineStr"/>
+      <c r="Q38" s="5" t="inlineStr"/>
+      <c r="R38" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S38" s="5" t="inlineStr"/>
+      <c r="T38" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U38" s="5" t="inlineStr"/>
+      <c r="V38" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="7" t="inlineStr">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>GPWFEST1</t>
         </is>
       </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5225,14 +7646,52 @@
       <c r="G39" s="5" t="inlineStr"/>
       <c r="H39" s="5" t="inlineStr"/>
       <c r="I39" s="5" t="inlineStr"/>
+      <c r="J39" s="5" t="inlineStr"/>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr"/>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N39" s="5" t="inlineStr"/>
+      <c r="O39" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P39" s="5" t="inlineStr"/>
+      <c r="Q39" s="5" t="inlineStr"/>
+      <c r="R39" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S39" s="5" t="inlineStr"/>
+      <c r="T39" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U39" s="5" t="inlineStr"/>
+      <c r="V39" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="7" t="inlineStr">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>GPWFEST2</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B40" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5250,14 +7709,52 @@
       <c r="G40" s="5" t="inlineStr"/>
       <c r="H40" s="5" t="inlineStr"/>
       <c r="I40" s="5" t="inlineStr"/>
+      <c r="J40" s="5" t="inlineStr"/>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L40" s="5" t="inlineStr"/>
+      <c r="M40" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N40" s="5" t="inlineStr"/>
+      <c r="O40" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P40" s="5" t="inlineStr"/>
+      <c r="Q40" s="5" t="inlineStr"/>
+      <c r="R40" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S40" s="5" t="inlineStr"/>
+      <c r="T40" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U40" s="5" t="inlineStr"/>
+      <c r="V40" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="7" t="inlineStr">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>GPWFEST3</t>
         </is>
       </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="B41" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5275,14 +7772,52 @@
       <c r="G41" s="5" t="inlineStr"/>
       <c r="H41" s="5" t="inlineStr"/>
       <c r="I41" s="5" t="inlineStr"/>
+      <c r="J41" s="5" t="inlineStr"/>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr"/>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N41" s="5" t="inlineStr"/>
+      <c r="O41" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P41" s="5" t="inlineStr"/>
+      <c r="Q41" s="5" t="inlineStr"/>
+      <c r="R41" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S41" s="5" t="inlineStr"/>
+      <c r="T41" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U41" s="5" t="inlineStr"/>
+      <c r="V41" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W41" s="5" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>GPWFWST1</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B42" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5298,14 +7833,52 @@
       <c r="G42" s="5" t="inlineStr"/>
       <c r="H42" s="5" t="inlineStr"/>
       <c r="I42" s="5" t="inlineStr"/>
+      <c r="J42" s="5" t="inlineStr"/>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L42" s="5" t="inlineStr"/>
+      <c r="M42" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N42" s="5" t="inlineStr"/>
+      <c r="O42" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P42" s="5" t="inlineStr"/>
+      <c r="Q42" s="5" t="inlineStr"/>
+      <c r="R42" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S42" s="5" t="inlineStr"/>
+      <c r="T42" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U42" s="5" t="inlineStr"/>
+      <c r="V42" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="7" t="inlineStr">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>GPWFWST2</t>
         </is>
       </c>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="B43" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5321,14 +7894,52 @@
       <c r="G43" s="5" t="inlineStr"/>
       <c r="H43" s="5" t="inlineStr"/>
       <c r="I43" s="5" t="inlineStr"/>
+      <c r="J43" s="5" t="inlineStr"/>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr"/>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N43" s="5" t="inlineStr"/>
+      <c r="O43" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P43" s="5" t="inlineStr"/>
+      <c r="Q43" s="5" t="inlineStr"/>
+      <c r="R43" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S43" s="5" t="inlineStr"/>
+      <c r="T43" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U43" s="5" t="inlineStr"/>
+      <c r="V43" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="7" t="inlineStr">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>HD1WF1</t>
         </is>
       </c>
-      <c r="B44" s="7" t="inlineStr">
+      <c r="B44" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5348,14 +7959,52 @@
       </c>
       <c r="H44" s="5" t="inlineStr"/>
       <c r="I44" s="5" t="inlineStr"/>
+      <c r="J44" s="5" t="inlineStr"/>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="inlineStr"/>
+      <c r="M44" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N44" s="5" t="inlineStr"/>
+      <c r="O44" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P44" s="5" t="inlineStr"/>
+      <c r="Q44" s="5" t="inlineStr"/>
+      <c r="R44" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S44" s="5" t="inlineStr"/>
+      <c r="T44" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U44" s="5" t="inlineStr"/>
+      <c r="V44" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W44" s="5" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="7" t="inlineStr">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>HEPWIND1</t>
         </is>
       </c>
-      <c r="B45" s="7" t="inlineStr">
+      <c r="B45" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5373,14 +8022,52 @@
       <c r="G45" s="5" t="inlineStr"/>
       <c r="H45" s="5" t="inlineStr"/>
       <c r="I45" s="5" t="inlineStr"/>
+      <c r="J45" s="5" t="inlineStr"/>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr"/>
+      <c r="M45" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N45" s="5" t="inlineStr"/>
+      <c r="O45" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P45" s="5" t="inlineStr"/>
+      <c r="Q45" s="5" t="inlineStr"/>
+      <c r="R45" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S45" s="5" t="inlineStr"/>
+      <c r="T45" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U45" s="5" t="inlineStr"/>
+      <c r="V45" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W45" s="5" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="7" t="inlineStr">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>KIATAWF1</t>
         </is>
       </c>
-      <c r="B46" s="7" t="inlineStr">
+      <c r="B46" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5402,14 +8089,52 @@
       </c>
       <c r="H46" s="5" t="inlineStr"/>
       <c r="I46" s="5" t="inlineStr"/>
+      <c r="J46" s="5" t="inlineStr"/>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L46" s="5" t="inlineStr"/>
+      <c r="M46" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N46" s="5" t="inlineStr"/>
+      <c r="O46" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P46" s="5" t="inlineStr"/>
+      <c r="Q46" s="5" t="inlineStr"/>
+      <c r="R46" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S46" s="5" t="inlineStr"/>
+      <c r="T46" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U46" s="5" t="inlineStr"/>
+      <c r="V46" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="7" t="inlineStr">
+      <c r="A47" s="8" t="inlineStr">
         <is>
           <t>MACARTH1</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="B47" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5431,14 +8156,52 @@
       </c>
       <c r="H47" s="5" t="inlineStr"/>
       <c r="I47" s="5" t="inlineStr"/>
+      <c r="J47" s="5" t="inlineStr"/>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr"/>
+      <c r="M47" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N47" s="5" t="inlineStr"/>
+      <c r="O47" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P47" s="5" t="inlineStr"/>
+      <c r="Q47" s="5" t="inlineStr"/>
+      <c r="R47" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S47" s="5" t="inlineStr"/>
+      <c r="T47" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U47" s="5" t="inlineStr"/>
+      <c r="V47" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W47" s="5" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="7" t="inlineStr">
+      <c r="A48" s="8" t="inlineStr">
         <is>
           <t>MAROOWF1</t>
         </is>
       </c>
-      <c r="B48" s="7" t="inlineStr">
+      <c r="B48" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5456,14 +8219,52 @@
       <c r="G48" s="5" t="inlineStr"/>
       <c r="H48" s="5" t="inlineStr"/>
       <c r="I48" s="5" t="inlineStr"/>
+      <c r="J48" s="5" t="inlineStr"/>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L48" s="5" t="inlineStr"/>
+      <c r="M48" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N48" s="5" t="inlineStr"/>
+      <c r="O48" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P48" s="5" t="inlineStr"/>
+      <c r="Q48" s="5" t="inlineStr"/>
+      <c r="R48" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S48" s="5" t="inlineStr"/>
+      <c r="T48" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U48" s="5" t="inlineStr"/>
+      <c r="V48" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W48" s="5" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="7" t="inlineStr">
+      <c r="A49" s="8" t="inlineStr">
         <is>
           <t>MOORAWF1</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
+      <c r="B49" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5485,14 +8286,52 @@
       </c>
       <c r="H49" s="5" t="inlineStr"/>
       <c r="I49" s="5" t="inlineStr"/>
+      <c r="J49" s="5" t="inlineStr"/>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr"/>
+      <c r="M49" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N49" s="5" t="inlineStr"/>
+      <c r="O49" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P49" s="5" t="inlineStr"/>
+      <c r="Q49" s="5" t="inlineStr"/>
+      <c r="R49" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S49" s="5" t="inlineStr"/>
+      <c r="T49" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U49" s="5" t="inlineStr"/>
+      <c r="V49" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="7" t="inlineStr">
+      <c r="A50" s="8" t="inlineStr">
         <is>
           <t>MRTLSWF1</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="B50" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5514,14 +8353,52 @@
       </c>
       <c r="H50" s="5" t="inlineStr"/>
       <c r="I50" s="5" t="inlineStr"/>
+      <c r="J50" s="5" t="inlineStr"/>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L50" s="5" t="inlineStr"/>
+      <c r="M50" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N50" s="5" t="inlineStr"/>
+      <c r="O50" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P50" s="5" t="inlineStr"/>
+      <c r="Q50" s="5" t="inlineStr"/>
+      <c r="R50" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S50" s="5" t="inlineStr"/>
+      <c r="T50" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U50" s="5" t="inlineStr"/>
+      <c r="V50" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W50" s="5" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="7" t="inlineStr">
+      <c r="A51" s="8" t="inlineStr">
         <is>
           <t>MLWF1</t>
         </is>
       </c>
-      <c r="B51" s="7" t="inlineStr">
+      <c r="B51" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5539,14 +8416,52 @@
       <c r="G51" s="5" t="inlineStr"/>
       <c r="H51" s="5" t="inlineStr"/>
       <c r="I51" s="5" t="inlineStr"/>
+      <c r="J51" s="5" t="inlineStr"/>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr"/>
+      <c r="M51" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N51" s="5" t="inlineStr"/>
+      <c r="O51" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P51" s="5" t="inlineStr"/>
+      <c r="Q51" s="5" t="inlineStr"/>
+      <c r="R51" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S51" s="5" t="inlineStr"/>
+      <c r="T51" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U51" s="5" t="inlineStr"/>
+      <c r="V51" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W51" s="5" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="7" t="inlineStr">
+      <c r="A52" s="8" t="inlineStr">
         <is>
           <t>MTGELWF1</t>
         </is>
       </c>
-      <c r="B52" s="7" t="inlineStr">
+      <c r="B52" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5568,14 +8483,52 @@
       </c>
       <c r="H52" s="5" t="inlineStr"/>
       <c r="I52" s="5" t="inlineStr"/>
+      <c r="J52" s="5" t="inlineStr"/>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L52" s="5" t="inlineStr"/>
+      <c r="M52" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N52" s="5" t="inlineStr"/>
+      <c r="O52" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P52" s="5" t="inlineStr"/>
+      <c r="Q52" s="5" t="inlineStr"/>
+      <c r="R52" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S52" s="5" t="inlineStr"/>
+      <c r="T52" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U52" s="5" t="inlineStr"/>
+      <c r="V52" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W52" s="5" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="7" t="inlineStr">
+      <c r="A53" s="8" t="inlineStr">
         <is>
           <t>MERCER01</t>
         </is>
       </c>
-      <c r="B53" s="7" t="inlineStr">
+      <c r="B53" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5597,14 +8550,52 @@
       </c>
       <c r="H53" s="5" t="inlineStr"/>
       <c r="I53" s="5" t="inlineStr"/>
+      <c r="J53" s="5" t="inlineStr"/>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr"/>
+      <c r="M53" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N53" s="5" t="inlineStr"/>
+      <c r="O53" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P53" s="5" t="inlineStr"/>
+      <c r="Q53" s="5" t="inlineStr"/>
+      <c r="R53" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S53" s="5" t="inlineStr"/>
+      <c r="T53" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U53" s="5" t="inlineStr"/>
+      <c r="V53" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W53" s="5" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="7" t="inlineStr">
+      <c r="A54" s="8" t="inlineStr">
         <is>
           <t>MUWAWF1</t>
         </is>
       </c>
-      <c r="B54" s="7" t="inlineStr">
+      <c r="B54" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5626,14 +8617,52 @@
       </c>
       <c r="H54" s="5" t="inlineStr"/>
       <c r="I54" s="5" t="inlineStr"/>
+      <c r="J54" s="5" t="inlineStr"/>
+      <c r="K54" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L54" s="5" t="inlineStr"/>
+      <c r="M54" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N54" s="5" t="inlineStr"/>
+      <c r="O54" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P54" s="5" t="inlineStr"/>
+      <c r="Q54" s="5" t="inlineStr"/>
+      <c r="R54" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S54" s="5" t="inlineStr"/>
+      <c r="T54" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U54" s="5" t="inlineStr"/>
+      <c r="V54" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W54" s="5" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="7" t="inlineStr">
+      <c r="A55" s="8" t="inlineStr">
         <is>
           <t>MUWAWF2</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
+      <c r="B55" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5655,14 +8684,52 @@
       </c>
       <c r="H55" s="5" t="inlineStr"/>
       <c r="I55" s="5" t="inlineStr"/>
+      <c r="J55" s="5" t="inlineStr"/>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="inlineStr"/>
+      <c r="M55" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N55" s="5" t="inlineStr"/>
+      <c r="O55" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P55" s="5" t="inlineStr"/>
+      <c r="Q55" s="5" t="inlineStr"/>
+      <c r="R55" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S55" s="5" t="inlineStr"/>
+      <c r="T55" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U55" s="5" t="inlineStr"/>
+      <c r="V55" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W55" s="5" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="7" t="inlineStr">
+      <c r="A56" s="8" t="inlineStr">
         <is>
           <t>OAKLAND1</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
+      <c r="B56" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5684,14 +8751,52 @@
       </c>
       <c r="H56" s="5" t="inlineStr"/>
       <c r="I56" s="5" t="inlineStr"/>
+      <c r="J56" s="5" t="inlineStr"/>
+      <c r="K56" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L56" s="5" t="inlineStr"/>
+      <c r="M56" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N56" s="5" t="inlineStr"/>
+      <c r="O56" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P56" s="5" t="inlineStr"/>
+      <c r="Q56" s="5" t="inlineStr"/>
+      <c r="R56" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S56" s="5" t="inlineStr"/>
+      <c r="T56" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U56" s="5" t="inlineStr"/>
+      <c r="V56" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W56" s="5" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="7" t="inlineStr">
+      <c r="A57" s="8" t="inlineStr">
         <is>
           <t>RYANCWF1</t>
         </is>
       </c>
-      <c r="B57" s="7" t="inlineStr">
+      <c r="B57" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5711,14 +8816,52 @@
       </c>
       <c r="H57" s="5" t="inlineStr"/>
       <c r="I57" s="5" t="inlineStr"/>
+      <c r="J57" s="5" t="inlineStr"/>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L57" s="5" t="inlineStr"/>
+      <c r="M57" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N57" s="5" t="inlineStr"/>
+      <c r="O57" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P57" s="5" t="inlineStr"/>
+      <c r="Q57" s="5" t="inlineStr"/>
+      <c r="R57" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S57" s="5" t="inlineStr"/>
+      <c r="T57" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U57" s="5" t="inlineStr"/>
+      <c r="V57" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W57" s="5" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="7" t="inlineStr">
+      <c r="A58" s="8" t="inlineStr">
         <is>
           <t>SALTCRK1</t>
         </is>
       </c>
-      <c r="B58" s="7" t="inlineStr">
+      <c r="B58" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5740,14 +8883,52 @@
       </c>
       <c r="H58" s="5" t="inlineStr"/>
       <c r="I58" s="5" t="inlineStr"/>
+      <c r="J58" s="5" t="inlineStr"/>
+      <c r="K58" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L58" s="5" t="inlineStr"/>
+      <c r="M58" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N58" s="5" t="inlineStr"/>
+      <c r="O58" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P58" s="5" t="inlineStr"/>
+      <c r="Q58" s="5" t="inlineStr"/>
+      <c r="R58" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S58" s="5" t="inlineStr"/>
+      <c r="T58" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U58" s="5" t="inlineStr"/>
+      <c r="V58" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W58" s="5" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="7" t="inlineStr">
+      <c r="A59" s="8" t="inlineStr">
         <is>
           <t>STOCKYD1</t>
         </is>
       </c>
-      <c r="B59" s="7" t="inlineStr">
+      <c r="B59" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5769,14 +8950,52 @@
       </c>
       <c r="H59" s="5" t="inlineStr"/>
       <c r="I59" s="5" t="inlineStr"/>
+      <c r="J59" s="5" t="inlineStr"/>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L59" s="5" t="inlineStr"/>
+      <c r="M59" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N59" s="5" t="inlineStr"/>
+      <c r="O59" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P59" s="5" t="inlineStr"/>
+      <c r="Q59" s="5" t="inlineStr"/>
+      <c r="R59" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S59" s="5" t="inlineStr"/>
+      <c r="T59" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U59" s="5" t="inlineStr"/>
+      <c r="V59" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W59" s="5" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="7" t="inlineStr">
+      <c r="A60" s="8" t="inlineStr">
         <is>
           <t>TIMWEST</t>
         </is>
       </c>
-      <c r="B60" s="7" t="inlineStr">
+      <c r="B60" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5794,14 +9013,52 @@
       <c r="G60" s="5" t="inlineStr"/>
       <c r="H60" s="5" t="inlineStr"/>
       <c r="I60" s="5" t="inlineStr"/>
+      <c r="J60" s="5" t="inlineStr"/>
+      <c r="K60" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L60" s="5" t="inlineStr"/>
+      <c r="M60" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N60" s="5" t="inlineStr"/>
+      <c r="O60" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P60" s="5" t="inlineStr"/>
+      <c r="Q60" s="5" t="inlineStr"/>
+      <c r="R60" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S60" s="5" t="inlineStr"/>
+      <c r="T60" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U60" s="5" t="inlineStr"/>
+      <c r="V60" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W60" s="5" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="7" t="inlineStr">
+      <c r="A61" s="8" t="inlineStr">
         <is>
           <t>TOORAWF</t>
         </is>
       </c>
-      <c r="B61" s="7" t="inlineStr">
+      <c r="B61" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5819,14 +9076,52 @@
       <c r="G61" s="5" t="inlineStr"/>
       <c r="H61" s="5" t="inlineStr"/>
       <c r="I61" s="5" t="inlineStr"/>
+      <c r="J61" s="5" t="inlineStr"/>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L61" s="5" t="inlineStr"/>
+      <c r="M61" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N61" s="5" t="inlineStr"/>
+      <c r="O61" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P61" s="5" t="inlineStr"/>
+      <c r="Q61" s="5" t="inlineStr"/>
+      <c r="R61" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S61" s="5" t="inlineStr"/>
+      <c r="T61" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U61" s="5" t="inlineStr"/>
+      <c r="V61" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W61" s="5" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="7" t="inlineStr">
+      <c r="A62" s="8" t="inlineStr">
         <is>
           <t>WAUBRAWF</t>
         </is>
       </c>
-      <c r="B62" s="7" t="inlineStr">
+      <c r="B62" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5844,14 +9139,52 @@
       <c r="G62" s="5" t="inlineStr"/>
       <c r="H62" s="5" t="inlineStr"/>
       <c r="I62" s="5" t="inlineStr"/>
+      <c r="J62" s="5" t="inlineStr"/>
+      <c r="K62" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L62" s="5" t="inlineStr"/>
+      <c r="M62" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N62" s="5" t="inlineStr"/>
+      <c r="O62" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P62" s="5" t="inlineStr"/>
+      <c r="Q62" s="5" t="inlineStr"/>
+      <c r="R62" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S62" s="5" t="inlineStr"/>
+      <c r="T62" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U62" s="5" t="inlineStr"/>
+      <c r="V62" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W62" s="5" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="7" t="inlineStr">
+      <c r="A63" s="8" t="inlineStr">
         <is>
           <t>WONWP</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr">
+      <c r="B63" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5869,14 +9202,52 @@
       <c r="G63" s="5" t="inlineStr"/>
       <c r="H63" s="5" t="inlineStr"/>
       <c r="I63" s="5" t="inlineStr"/>
+      <c r="J63" s="5" t="inlineStr"/>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="inlineStr"/>
+      <c r="M63" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N63" s="5" t="inlineStr"/>
+      <c r="O63" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P63" s="5" t="inlineStr"/>
+      <c r="Q63" s="5" t="inlineStr"/>
+      <c r="R63" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S63" s="5" t="inlineStr"/>
+      <c r="T63" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U63" s="5" t="inlineStr"/>
+      <c r="V63" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W63" s="5" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="7" t="inlineStr">
+      <c r="A64" s="8" t="inlineStr">
         <is>
           <t>YSWF1</t>
         </is>
       </c>
-      <c r="B64" s="7" t="inlineStr">
+      <c r="B64" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5894,14 +9265,52 @@
       <c r="G64" s="5" t="inlineStr"/>
       <c r="H64" s="5" t="inlineStr"/>
       <c r="I64" s="5" t="inlineStr"/>
+      <c r="J64" s="5" t="inlineStr"/>
+      <c r="K64" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L64" s="5" t="inlineStr"/>
+      <c r="M64" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N64" s="5" t="inlineStr"/>
+      <c r="O64" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P64" s="5" t="inlineStr"/>
+      <c r="Q64" s="5" t="inlineStr"/>
+      <c r="R64" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S64" s="5" t="inlineStr"/>
+      <c r="T64" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U64" s="5" t="inlineStr"/>
+      <c r="V64" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W64" s="5" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="7" t="inlineStr">
+      <c r="A65" s="8" t="inlineStr">
         <is>
           <t>YAMBUKWF</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
+      <c r="B65" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5919,14 +9328,52 @@
       <c r="G65" s="5" t="inlineStr"/>
       <c r="H65" s="5" t="inlineStr"/>
       <c r="I65" s="5" t="inlineStr"/>
+      <c r="J65" s="5" t="inlineStr"/>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L65" s="5" t="inlineStr"/>
+      <c r="M65" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N65" s="5" t="inlineStr"/>
+      <c r="O65" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P65" s="5" t="inlineStr"/>
+      <c r="Q65" s="5" t="inlineStr"/>
+      <c r="R65" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S65" s="5" t="inlineStr"/>
+      <c r="T65" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U65" s="5" t="inlineStr"/>
+      <c r="V65" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W65" s="5" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="7" t="inlineStr">
+      <c r="A66" s="8" t="inlineStr">
         <is>
           <t>YAWWF1</t>
         </is>
       </c>
-      <c r="B66" s="7" t="inlineStr">
+      <c r="B66" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5944,14 +9391,52 @@
       <c r="G66" s="5" t="inlineStr"/>
       <c r="H66" s="5" t="inlineStr"/>
       <c r="I66" s="5" t="inlineStr"/>
+      <c r="J66" s="5" t="inlineStr"/>
+      <c r="K66" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L66" s="5" t="inlineStr"/>
+      <c r="M66" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N66" s="5" t="inlineStr"/>
+      <c r="O66" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P66" s="5" t="inlineStr"/>
+      <c r="Q66" s="5" t="inlineStr"/>
+      <c r="R66" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S66" s="5" t="inlineStr"/>
+      <c r="T66" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U66" s="5" t="inlineStr"/>
+      <c r="V66" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W66" s="5" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="7" t="inlineStr">
+      <c r="A67" s="8" t="inlineStr">
         <is>
           <t>YENDWF1</t>
         </is>
       </c>
-      <c r="B67" s="7" t="inlineStr">
+      <c r="B67" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5973,6 +9458,44 @@
       </c>
       <c r="H67" s="5" t="inlineStr"/>
       <c r="I67" s="5" t="inlineStr"/>
+      <c r="J67" s="5" t="inlineStr"/>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L67" s="5" t="inlineStr"/>
+      <c r="M67" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N67" s="5" t="inlineStr"/>
+      <c r="O67" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P67" s="5" t="inlineStr"/>
+      <c r="Q67" s="5" t="inlineStr"/>
+      <c r="R67" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S67" s="5" t="inlineStr"/>
+      <c r="T67" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U67" s="5" t="inlineStr"/>
+      <c r="V67" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W67" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C67">
@@ -6059,6 +9582,174 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J67">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K67">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L67">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M67">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N2:N67">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O2:O67">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P2:P67">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q2:Q67">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R2:R67">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S2:S67">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T2:T67">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U2:U67">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V2:V67">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W2:W67">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/VIC_curtailment.xlsx
+++ b/outputs/VIC_curtailment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/outputs/VIC_curtailment.xlsx
+++ b/outputs/VIC_curtailment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/outputs/VIC_curtailment.xlsx
+++ b/outputs/VIC_curtailment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X67"/>
+  <dimension ref="A1:W67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -482,7 +482,6 @@
     <col width="12" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="12" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -553,55 +552,50 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>FY24-25</t>
+          <t>FY25-26</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>FY25-26</t>
+          <t>FY26-27</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>FY26-27 (Draft)</t>
+          <t>Curt FY1</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Curt FY1</t>
+          <t>Curt FY2</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Curt FY2</t>
+          <t>Curt FY3</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Curt FY3</t>
+          <t>Curt Avg</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Curt Avg</t>
+          <t>Offl FY1</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Offl FY1</t>
+          <t>Offl FY2</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Offl FY2</t>
+          <t>Offl FY3</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Offl FY3</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Offl Avg</t>
         </is>
@@ -662,36 +656,33 @@
         <v>0.164192244302687</v>
       </c>
       <c r="N2" s="5" t="n">
-        <v>0.8584000000000001</v>
+        <v>0.8986</v>
       </c>
       <c r="O2" s="5" t="n">
-        <v>0.8986</v>
-      </c>
-      <c r="P2" s="5" t="n">
-        <v>0.9114</v>
+        <v>0.9092</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v>0.02</v>
       </c>
       <c r="Q2" s="6" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="R2" s="6" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="S2" s="6" t="n">
-        <v>0</v>
+        <v>0.02666666666666667</v>
       </c>
       <c r="T2" s="6" t="n">
-        <v>0.02666666666666667</v>
+        <v>0.11</v>
       </c>
       <c r="U2" s="6" t="n">
-        <v>0.11</v>
+        <v>0.17</v>
       </c>
       <c r="V2" s="6" t="n">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="W2" s="6" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="X2" s="6" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -735,13 +726,13 @@
       <c r="K3" s="5" t="inlineStr"/>
       <c r="L3" s="5" t="inlineStr"/>
       <c r="M3" s="5" t="inlineStr"/>
-      <c r="N3" s="5" t="inlineStr"/>
+      <c r="N3" s="5" t="n">
+        <v>0.8883</v>
+      </c>
       <c r="O3" s="5" t="n">
-        <v>0.8883</v>
-      </c>
-      <c r="P3" s="5" t="n">
-        <v>0.9012</v>
-      </c>
+        <v>0.8963</v>
+      </c>
+      <c r="P3" s="6" t="inlineStr"/>
       <c r="Q3" s="6" t="inlineStr"/>
       <c r="R3" s="6" t="inlineStr"/>
       <c r="S3" s="6" t="inlineStr"/>
@@ -749,7 +740,6 @@
       <c r="U3" s="6" t="inlineStr"/>
       <c r="V3" s="6" t="inlineStr"/>
       <c r="W3" s="6" t="inlineStr"/>
-      <c r="X3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -802,36 +792,33 @@
         <v>0.122422882740379</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>0.8962</v>
+        <v>0.9305</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>0.9305</v>
-      </c>
-      <c r="P4" s="5" t="n">
-        <v>0.9307</v>
+        <v>0.929</v>
+      </c>
+      <c r="P4" s="6" t="n">
+        <v>0.02</v>
       </c>
       <c r="Q4" s="6" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="R4" s="6" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="S4" s="6" t="n">
-        <v>0</v>
+        <v>0.02666666666666667</v>
       </c>
       <c r="T4" s="6" t="n">
-        <v>0.02666666666666667</v>
+        <v>0.11</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.11</v>
+        <v>0.17</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="X4" s="6" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -890,36 +877,33 @@
         <v>0.122422882740379</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>0.8962</v>
+        <v>0.9305</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>0.9305</v>
-      </c>
-      <c r="P5" s="5" t="n">
-        <v>0.9307</v>
+        <v>0.929</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v>0.02</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>0</v>
+        <v>0.02666666666666667</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>0.02666666666666667</v>
+        <v>0.11</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.11</v>
+        <v>0.17</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="X5" s="6" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -976,13 +960,13 @@
         <v>0.08205629867681941</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>0.9477</v>
+        <v>0.9463</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>0.9463</v>
-      </c>
-      <c r="P6" s="5" t="n">
-        <v>0.9223</v>
+        <v>0.921</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>0</v>
@@ -994,18 +978,15 @@
         <v>0</v>
       </c>
       <c r="T6" s="6" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="U6" s="6" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V6" s="6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="W6" s="6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="X6" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -1062,13 +1043,13 @@
         <v>0.08997768712489811</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>0.9626</v>
+        <v>0.949</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>0.949</v>
-      </c>
-      <c r="P7" s="5" t="n">
-        <v>0.9292</v>
+        <v>0.9294</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1080,18 +1061,15 @@
         <v>0</v>
       </c>
       <c r="T7" s="6" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="X7" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -1140,14 +1118,12 @@
       <c r="L8" s="5" t="inlineStr"/>
       <c r="M8" s="5" t="inlineStr"/>
       <c r="N8" s="5" t="n">
-        <v>0.9455</v>
+        <v>0.9402</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>0.9402</v>
-      </c>
-      <c r="P8" s="5" t="n">
-        <v>0.922</v>
-      </c>
+        <v>0.9211</v>
+      </c>
+      <c r="P8" s="6" t="inlineStr"/>
       <c r="Q8" s="6" t="inlineStr"/>
       <c r="R8" s="6" t="inlineStr"/>
       <c r="S8" s="6" t="inlineStr"/>
@@ -1155,7 +1131,6 @@
       <c r="U8" s="6" t="inlineStr"/>
       <c r="V8" s="6" t="inlineStr"/>
       <c r="W8" s="6" t="inlineStr"/>
-      <c r="X8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1197,13 +1172,13 @@
       <c r="K9" s="5" t="inlineStr"/>
       <c r="L9" s="5" t="inlineStr"/>
       <c r="M9" s="5" t="inlineStr"/>
-      <c r="N9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="n">
+        <v>0.9328</v>
+      </c>
       <c r="O9" s="5" t="n">
-        <v>0.9328</v>
-      </c>
-      <c r="P9" s="5" t="n">
-        <v>0.9262</v>
-      </c>
+        <v>0.9261</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr"/>
       <c r="Q9" s="6" t="inlineStr"/>
       <c r="R9" s="6" t="inlineStr"/>
       <c r="S9" s="6" t="inlineStr"/>
@@ -1211,7 +1186,6 @@
       <c r="U9" s="6" t="inlineStr"/>
       <c r="V9" s="6" t="inlineStr"/>
       <c r="W9" s="6" t="inlineStr"/>
-      <c r="X9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1268,36 +1242,33 @@
         <v>0.072415601225557</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>0.8506</v>
+        <v>0.8895</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>0.8895</v>
-      </c>
-      <c r="P10" s="5" t="n">
-        <v>0.9088000000000001</v>
+        <v>0.9051</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v>0.02</v>
       </c>
       <c r="Q10" s="6" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="R10" s="6" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="S10" s="6" t="n">
-        <v>0</v>
+        <v>0.02666666666666667</v>
       </c>
       <c r="T10" s="6" t="n">
-        <v>0.02666666666666667</v>
+        <v>0.11</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.11</v>
+        <v>0.17</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="X10" s="6" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -1342,14 +1313,12 @@
       <c r="L11" s="5" t="inlineStr"/>
       <c r="M11" s="5" t="inlineStr"/>
       <c r="N11" s="5" t="n">
-        <v>0.8964</v>
+        <v>0.9329</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>0.9329</v>
-      </c>
-      <c r="P11" s="5" t="n">
-        <v>0.9330000000000001</v>
-      </c>
+        <v>0.9311</v>
+      </c>
+      <c r="P11" s="6" t="inlineStr"/>
       <c r="Q11" s="6" t="inlineStr"/>
       <c r="R11" s="6" t="inlineStr"/>
       <c r="S11" s="6" t="inlineStr"/>
@@ -1357,7 +1326,6 @@
       <c r="U11" s="6" t="inlineStr"/>
       <c r="V11" s="6" t="inlineStr"/>
       <c r="W11" s="6" t="inlineStr"/>
-      <c r="X11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1414,36 +1382,33 @@
         <v>0.0878331516592939</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>0.8363</v>
+        <v>0.8784999999999999</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>0.8784999999999999</v>
-      </c>
-      <c r="P12" s="5" t="n">
-        <v>0.878</v>
+        <v>0.8738</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v>0.02</v>
       </c>
       <c r="Q12" s="6" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="R12" s="6" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="S12" s="6" t="n">
-        <v>0</v>
+        <v>0.02666666666666667</v>
       </c>
       <c r="T12" s="6" t="n">
-        <v>0.02666666666666667</v>
+        <v>0.11</v>
       </c>
       <c r="U12" s="6" t="n">
-        <v>0.11</v>
+        <v>0.17</v>
       </c>
       <c r="V12" s="6" t="n">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="W12" s="6" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="X12" s="6" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -1487,11 +1452,13 @@
       <c r="K13" s="5" t="inlineStr"/>
       <c r="L13" s="5" t="inlineStr"/>
       <c r="M13" s="5" t="inlineStr"/>
-      <c r="N13" s="5" t="inlineStr"/>
+      <c r="N13" s="5" t="n">
+        <v>0.9441000000000001</v>
+      </c>
       <c r="O13" s="5" t="n">
-        <v>0.9441000000000001</v>
-      </c>
-      <c r="P13" s="5" t="inlineStr"/>
+        <v>0.921</v>
+      </c>
+      <c r="P13" s="6" t="inlineStr"/>
       <c r="Q13" s="6" t="inlineStr"/>
       <c r="R13" s="6" t="inlineStr"/>
       <c r="S13" s="6" t="inlineStr"/>
@@ -1499,7 +1466,6 @@
       <c r="U13" s="6" t="inlineStr"/>
       <c r="V13" s="6" t="inlineStr"/>
       <c r="W13" s="6" t="inlineStr"/>
-      <c r="X13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1542,14 +1508,12 @@
       <c r="L14" s="5" t="inlineStr"/>
       <c r="M14" s="5" t="inlineStr"/>
       <c r="N14" s="5" t="n">
-        <v>0.9484</v>
+        <v>0.9415</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>0.9415</v>
-      </c>
-      <c r="P14" s="5" t="n">
-        <v>0.9248</v>
-      </c>
+        <v>0.9257</v>
+      </c>
+      <c r="P14" s="6" t="inlineStr"/>
       <c r="Q14" s="6" t="inlineStr"/>
       <c r="R14" s="6" t="inlineStr"/>
       <c r="S14" s="6" t="inlineStr"/>
@@ -1557,7 +1521,6 @@
       <c r="U14" s="6" t="inlineStr"/>
       <c r="V14" s="6" t="inlineStr"/>
       <c r="W14" s="6" t="inlineStr"/>
-      <c r="X14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1614,13 +1577,13 @@
         <v>0.08205629867681941</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>0.9477</v>
+        <v>0.9463</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>0.9463</v>
-      </c>
-      <c r="P15" s="5" t="n">
-        <v>0.9223</v>
+        <v>0.921</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="Q15" s="6" t="n">
         <v>0</v>
@@ -1632,18 +1595,15 @@
         <v>0</v>
       </c>
       <c r="T15" s="6" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="U15" s="6" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V15" s="6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="W15" s="6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="X15" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -1688,14 +1648,12 @@
       <c r="L16" s="5" t="inlineStr"/>
       <c r="M16" s="5" t="inlineStr"/>
       <c r="N16" s="5" t="n">
-        <v>1.0015</v>
+        <v>0.9519</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>0.9519</v>
-      </c>
-      <c r="P16" s="5" t="n">
-        <v>0.928</v>
-      </c>
+        <v>0.9282</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr"/>
       <c r="Q16" s="6" t="inlineStr"/>
       <c r="R16" s="6" t="inlineStr"/>
       <c r="S16" s="6" t="inlineStr"/>
@@ -1703,7 +1661,6 @@
       <c r="U16" s="6" t="inlineStr"/>
       <c r="V16" s="6" t="inlineStr"/>
       <c r="W16" s="6" t="inlineStr"/>
-      <c r="X16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1760,36 +1717,33 @@
         <v>0.164192244302687</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>0.8584000000000001</v>
+        <v>0.8986</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>0.8986</v>
-      </c>
-      <c r="P17" s="5" t="n">
-        <v>0.9114</v>
+        <v>0.9092</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v>0.02</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="R17" s="6" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="S17" s="6" t="n">
-        <v>0</v>
+        <v>0.02666666666666667</v>
       </c>
       <c r="T17" s="6" t="n">
-        <v>0.02666666666666667</v>
+        <v>0.11</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.11</v>
+        <v>0.17</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="X17" s="6" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -1846,13 +1800,13 @@
         <v>0.08997768712489811</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>0.9455</v>
+        <v>0.9402</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>0.9402</v>
-      </c>
-      <c r="P18" s="5" t="n">
-        <v>0.922</v>
+        <v>0.9211</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
@@ -1864,18 +1818,15 @@
         <v>0</v>
       </c>
       <c r="T18" s="6" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="W18" s="6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="X18" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -1930,14 +1881,12 @@
         <v>0.08205629867681941</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>0.9477</v>
+        <v>0.9463</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>0.9463</v>
-      </c>
-      <c r="P19" s="5" t="n">
-        <v>0.9223</v>
-      </c>
+        <v>0.921</v>
+      </c>
+      <c r="P19" s="6" t="inlineStr"/>
       <c r="Q19" s="6" t="inlineStr"/>
       <c r="R19" s="6" t="inlineStr"/>
       <c r="S19" s="6" t="inlineStr"/>
@@ -1945,7 +1894,6 @@
       <c r="U19" s="6" t="inlineStr"/>
       <c r="V19" s="6" t="inlineStr"/>
       <c r="W19" s="6" t="inlineStr"/>
-      <c r="X19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -2002,36 +1950,33 @@
         <v>0.072415601225557</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>0.8506</v>
+        <v>0.8895</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>0.8895</v>
-      </c>
-      <c r="P20" s="5" t="n">
-        <v>0.9088000000000001</v>
+        <v>0.9051</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v>0.02</v>
       </c>
       <c r="Q20" s="6" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="R20" s="6" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="S20" s="6" t="n">
-        <v>0</v>
+        <v>0.02666666666666667</v>
       </c>
       <c r="T20" s="6" t="n">
-        <v>0.02666666666666667</v>
+        <v>0.11</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>0.11</v>
+        <v>0.17</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="X20" s="6" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -2080,14 +2025,12 @@
       <c r="L21" s="5" t="inlineStr"/>
       <c r="M21" s="5" t="inlineStr"/>
       <c r="N21" s="5" t="n">
-        <v>0.8856000000000001</v>
+        <v>0.9031</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>0.9031</v>
-      </c>
-      <c r="P21" s="5" t="n">
-        <v>0.8999</v>
-      </c>
+        <v>0.898</v>
+      </c>
+      <c r="P21" s="6" t="inlineStr"/>
       <c r="Q21" s="6" t="inlineStr"/>
       <c r="R21" s="6" t="inlineStr"/>
       <c r="S21" s="6" t="inlineStr"/>
@@ -2095,7 +2038,6 @@
       <c r="U21" s="6" t="inlineStr"/>
       <c r="V21" s="6" t="inlineStr"/>
       <c r="W21" s="6" t="inlineStr"/>
-      <c r="X21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2142,14 +2084,12 @@
       <c r="L22" s="5" t="inlineStr"/>
       <c r="M22" s="5" t="inlineStr"/>
       <c r="N22" s="5" t="n">
-        <v>0.9848</v>
+        <v>0.9862</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>0.9862</v>
-      </c>
-      <c r="P22" s="5" t="n">
-        <v>0.9913999999999999</v>
-      </c>
+        <v>0.992</v>
+      </c>
+      <c r="P22" s="6" t="inlineStr"/>
       <c r="Q22" s="6" t="inlineStr"/>
       <c r="R22" s="6" t="inlineStr"/>
       <c r="S22" s="6" t="inlineStr"/>
@@ -2157,7 +2097,6 @@
       <c r="U22" s="6" t="inlineStr"/>
       <c r="V22" s="6" t="inlineStr"/>
       <c r="W22" s="6" t="inlineStr"/>
-      <c r="X22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2204,14 +2143,12 @@
       <c r="L23" s="5" t="inlineStr"/>
       <c r="M23" s="5" t="inlineStr"/>
       <c r="N23" s="5" t="n">
-        <v>0.9315</v>
+        <v>0.9465</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>0.9465</v>
-      </c>
-      <c r="P23" s="5" t="n">
-        <v>0.945</v>
-      </c>
+        <v>0.9436</v>
+      </c>
+      <c r="P23" s="6" t="inlineStr"/>
       <c r="Q23" s="6" t="inlineStr"/>
       <c r="R23" s="6" t="inlineStr"/>
       <c r="S23" s="6" t="inlineStr"/>
@@ -2219,7 +2156,6 @@
       <c r="U23" s="6" t="inlineStr"/>
       <c r="V23" s="6" t="inlineStr"/>
       <c r="W23" s="6" t="inlineStr"/>
-      <c r="X23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2266,14 +2202,12 @@
       <c r="L24" s="5" t="inlineStr"/>
       <c r="M24" s="5" t="inlineStr"/>
       <c r="N24" s="5" t="n">
-        <v>0.9315</v>
+        <v>0.9465</v>
       </c>
       <c r="O24" s="5" t="n">
-        <v>0.9465</v>
-      </c>
-      <c r="P24" s="5" t="n">
-        <v>0.945</v>
-      </c>
+        <v>0.9436</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr"/>
       <c r="Q24" s="6" t="inlineStr"/>
       <c r="R24" s="6" t="inlineStr"/>
       <c r="S24" s="6" t="inlineStr"/>
@@ -2281,7 +2215,6 @@
       <c r="U24" s="6" t="inlineStr"/>
       <c r="V24" s="6" t="inlineStr"/>
       <c r="W24" s="6" t="inlineStr"/>
-      <c r="X24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2328,14 +2261,12 @@
       <c r="L25" s="5" t="inlineStr"/>
       <c r="M25" s="5" t="inlineStr"/>
       <c r="N25" s="5" t="n">
-        <v>0.8733</v>
+        <v>0.8907</v>
       </c>
       <c r="O25" s="5" t="n">
-        <v>0.8907</v>
-      </c>
-      <c r="P25" s="5" t="n">
-        <v>0.89</v>
-      </c>
+        <v>0.8868</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr"/>
       <c r="Q25" s="6" t="inlineStr"/>
       <c r="R25" s="6" t="inlineStr"/>
       <c r="S25" s="6" t="inlineStr"/>
@@ -2343,7 +2274,6 @@
       <c r="U25" s="6" t="inlineStr"/>
       <c r="V25" s="6" t="inlineStr"/>
       <c r="W25" s="6" t="inlineStr"/>
-      <c r="X25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2386,14 +2316,12 @@
       <c r="L26" s="5" t="inlineStr"/>
       <c r="M26" s="5" t="inlineStr"/>
       <c r="N26" s="5" t="n">
-        <v>0.9718</v>
+        <v>0.9825</v>
       </c>
       <c r="O26" s="5" t="n">
-        <v>0.9825</v>
-      </c>
-      <c r="P26" s="5" t="n">
-        <v>0.9801</v>
-      </c>
+        <v>0.9791</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr"/>
       <c r="Q26" s="6" t="inlineStr"/>
       <c r="R26" s="6" t="inlineStr"/>
       <c r="S26" s="6" t="inlineStr"/>
@@ -2401,7 +2329,6 @@
       <c r="U26" s="6" t="inlineStr"/>
       <c r="V26" s="6" t="inlineStr"/>
       <c r="W26" s="6" t="inlineStr"/>
-      <c r="X26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2444,12 +2371,10 @@
       <c r="L27" s="5" t="inlineStr"/>
       <c r="M27" s="5" t="inlineStr"/>
       <c r="N27" s="5" t="n">
-        <v>0.9718</v>
-      </c>
-      <c r="O27" s="5" t="n">
         <v>0.9825</v>
       </c>
-      <c r="P27" s="5" t="inlineStr"/>
+      <c r="O27" s="5" t="inlineStr"/>
+      <c r="P27" s="6" t="inlineStr"/>
       <c r="Q27" s="6" t="inlineStr"/>
       <c r="R27" s="6" t="inlineStr"/>
       <c r="S27" s="6" t="inlineStr"/>
@@ -2457,7 +2382,6 @@
       <c r="U27" s="6" t="inlineStr"/>
       <c r="V27" s="6" t="inlineStr"/>
       <c r="W27" s="6" t="inlineStr"/>
-      <c r="X27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2504,14 +2428,12 @@
       <c r="L28" s="5" t="inlineStr"/>
       <c r="M28" s="5" t="inlineStr"/>
       <c r="N28" s="5" t="n">
-        <v>0.9976</v>
+        <v>0.998</v>
       </c>
       <c r="O28" s="5" t="n">
-        <v>0.998</v>
-      </c>
-      <c r="P28" s="5" t="n">
-        <v>0.9978</v>
-      </c>
+        <v>0.9977</v>
+      </c>
+      <c r="P28" s="6" t="inlineStr"/>
       <c r="Q28" s="6" t="inlineStr"/>
       <c r="R28" s="6" t="inlineStr"/>
       <c r="S28" s="6" t="inlineStr"/>
@@ -2519,7 +2441,6 @@
       <c r="U28" s="6" t="inlineStr"/>
       <c r="V28" s="6" t="inlineStr"/>
       <c r="W28" s="6" t="inlineStr"/>
-      <c r="X28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2562,14 +2483,12 @@
       <c r="L29" s="5" t="inlineStr"/>
       <c r="M29" s="5" t="inlineStr"/>
       <c r="N29" s="5" t="n">
-        <v>0.9993</v>
+        <v>1.0018</v>
       </c>
       <c r="O29" s="5" t="n">
-        <v>1.0018</v>
-      </c>
-      <c r="P29" s="5" t="n">
-        <v>0.9952</v>
-      </c>
+        <v>0.9949</v>
+      </c>
+      <c r="P29" s="6" t="inlineStr"/>
       <c r="Q29" s="6" t="inlineStr"/>
       <c r="R29" s="6" t="inlineStr"/>
       <c r="S29" s="6" t="inlineStr"/>
@@ -2577,7 +2496,6 @@
       <c r="U29" s="6" t="inlineStr"/>
       <c r="V29" s="6" t="inlineStr"/>
       <c r="W29" s="6" t="inlineStr"/>
-      <c r="X29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2620,14 +2538,12 @@
       <c r="L30" s="5" t="inlineStr"/>
       <c r="M30" s="5" t="inlineStr"/>
       <c r="N30" s="5" t="n">
-        <v>1.0072</v>
+        <v>1.0166</v>
       </c>
       <c r="O30" s="5" t="n">
-        <v>1.0166</v>
-      </c>
-      <c r="P30" s="5" t="n">
-        <v>1.0065</v>
-      </c>
+        <v>1.0031</v>
+      </c>
+      <c r="P30" s="6" t="inlineStr"/>
       <c r="Q30" s="6" t="inlineStr"/>
       <c r="R30" s="6" t="inlineStr"/>
       <c r="S30" s="6" t="inlineStr"/>
@@ -2635,7 +2551,6 @@
       <c r="U30" s="6" t="inlineStr"/>
       <c r="V30" s="6" t="inlineStr"/>
       <c r="W30" s="6" t="inlineStr"/>
-      <c r="X30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2682,14 +2597,12 @@
       <c r="L31" s="5" t="inlineStr"/>
       <c r="M31" s="5" t="inlineStr"/>
       <c r="N31" s="5" t="n">
-        <v>0.8833</v>
+        <v>0.9004</v>
       </c>
       <c r="O31" s="5" t="n">
-        <v>0.9004</v>
-      </c>
-      <c r="P31" s="5" t="n">
-        <v>0.9</v>
-      </c>
+        <v>0.8966</v>
+      </c>
+      <c r="P31" s="6" t="inlineStr"/>
       <c r="Q31" s="6" t="inlineStr"/>
       <c r="R31" s="6" t="inlineStr"/>
       <c r="S31" s="6" t="inlineStr"/>
@@ -2697,7 +2610,6 @@
       <c r="U31" s="6" t="inlineStr"/>
       <c r="V31" s="6" t="inlineStr"/>
       <c r="W31" s="6" t="inlineStr"/>
-      <c r="X31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2740,14 +2652,12 @@
       <c r="L32" s="5" t="inlineStr"/>
       <c r="M32" s="5" t="inlineStr"/>
       <c r="N32" s="5" t="n">
-        <v>0.8733</v>
+        <v>0.8959</v>
       </c>
       <c r="O32" s="5" t="n">
-        <v>0.8959</v>
-      </c>
-      <c r="P32" s="5" t="n">
-        <v>0.901</v>
-      </c>
+        <v>0.8954</v>
+      </c>
+      <c r="P32" s="6" t="inlineStr"/>
       <c r="Q32" s="6" t="inlineStr"/>
       <c r="R32" s="6" t="inlineStr"/>
       <c r="S32" s="6" t="inlineStr"/>
@@ -2755,7 +2665,6 @@
       <c r="U32" s="6" t="inlineStr"/>
       <c r="V32" s="6" t="inlineStr"/>
       <c r="W32" s="6" t="inlineStr"/>
-      <c r="X32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2802,14 +2711,12 @@
       <c r="L33" s="5" t="inlineStr"/>
       <c r="M33" s="5" t="inlineStr"/>
       <c r="N33" s="5" t="n">
-        <v>0.981</v>
+        <v>0.9845</v>
       </c>
       <c r="O33" s="5" t="n">
-        <v>0.9845</v>
-      </c>
-      <c r="P33" s="5" t="n">
-        <v>0.9833</v>
-      </c>
+        <v>0.9827</v>
+      </c>
+      <c r="P33" s="6" t="inlineStr"/>
       <c r="Q33" s="6" t="inlineStr"/>
       <c r="R33" s="6" t="inlineStr"/>
       <c r="S33" s="6" t="inlineStr"/>
@@ -2817,7 +2724,6 @@
       <c r="U33" s="6" t="inlineStr"/>
       <c r="V33" s="6" t="inlineStr"/>
       <c r="W33" s="6" t="inlineStr"/>
-      <c r="X33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2864,14 +2770,12 @@
       <c r="L34" s="5" t="inlineStr"/>
       <c r="M34" s="5" t="inlineStr"/>
       <c r="N34" s="5" t="n">
-        <v>0.981</v>
+        <v>0.9845</v>
       </c>
       <c r="O34" s="5" t="n">
-        <v>0.9845</v>
-      </c>
-      <c r="P34" s="5" t="n">
-        <v>0.9833</v>
-      </c>
+        <v>0.9827</v>
+      </c>
+      <c r="P34" s="6" t="inlineStr"/>
       <c r="Q34" s="6" t="inlineStr"/>
       <c r="R34" s="6" t="inlineStr"/>
       <c r="S34" s="6" t="inlineStr"/>
@@ -2879,7 +2783,6 @@
       <c r="U34" s="6" t="inlineStr"/>
       <c r="V34" s="6" t="inlineStr"/>
       <c r="W34" s="6" t="inlineStr"/>
-      <c r="X34" s="6" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2926,14 +2829,12 @@
       <c r="L35" s="5" t="inlineStr"/>
       <c r="M35" s="5" t="inlineStr"/>
       <c r="N35" s="5" t="n">
-        <v>0.981</v>
+        <v>0.9845</v>
       </c>
       <c r="O35" s="5" t="n">
-        <v>0.9845</v>
-      </c>
-      <c r="P35" s="5" t="n">
-        <v>0.9833</v>
-      </c>
+        <v>0.9827</v>
+      </c>
+      <c r="P35" s="6" t="inlineStr"/>
       <c r="Q35" s="6" t="inlineStr"/>
       <c r="R35" s="6" t="inlineStr"/>
       <c r="S35" s="6" t="inlineStr"/>
@@ -2941,7 +2842,6 @@
       <c r="U35" s="6" t="inlineStr"/>
       <c r="V35" s="6" t="inlineStr"/>
       <c r="W35" s="6" t="inlineStr"/>
-      <c r="X35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2986,14 +2886,12 @@
       <c r="L36" s="5" t="inlineStr"/>
       <c r="M36" s="5" t="inlineStr"/>
       <c r="N36" s="5" t="n">
-        <v>0.9475</v>
+        <v>0.9569</v>
       </c>
       <c r="O36" s="5" t="n">
-        <v>0.9569</v>
-      </c>
-      <c r="P36" s="5" t="n">
-        <v>0.9569</v>
-      </c>
+        <v>0.9556</v>
+      </c>
+      <c r="P36" s="6" t="inlineStr"/>
       <c r="Q36" s="6" t="inlineStr"/>
       <c r="R36" s="6" t="inlineStr"/>
       <c r="S36" s="6" t="inlineStr"/>
@@ -3001,7 +2899,6 @@
       <c r="U36" s="6" t="inlineStr"/>
       <c r="V36" s="6" t="inlineStr"/>
       <c r="W36" s="6" t="inlineStr"/>
-      <c r="X36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -3043,11 +2940,9 @@
       <c r="K37" s="5" t="inlineStr"/>
       <c r="L37" s="5" t="inlineStr"/>
       <c r="M37" s="5" t="inlineStr"/>
-      <c r="N37" s="5" t="n">
-        <v>0.9993</v>
-      </c>
+      <c r="N37" s="5" t="inlineStr"/>
       <c r="O37" s="5" t="inlineStr"/>
-      <c r="P37" s="5" t="inlineStr"/>
+      <c r="P37" s="6" t="inlineStr"/>
       <c r="Q37" s="6" t="inlineStr"/>
       <c r="R37" s="6" t="inlineStr"/>
       <c r="S37" s="6" t="inlineStr"/>
@@ -3055,7 +2950,6 @@
       <c r="U37" s="6" t="inlineStr"/>
       <c r="V37" s="6" t="inlineStr"/>
       <c r="W37" s="6" t="inlineStr"/>
-      <c r="X37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -3098,14 +2992,12 @@
       <c r="L38" s="5" t="inlineStr"/>
       <c r="M38" s="5" t="inlineStr"/>
       <c r="N38" s="5" t="n">
-        <v>0.9993</v>
+        <v>1.0018</v>
       </c>
       <c r="O38" s="5" t="n">
-        <v>1.0018</v>
-      </c>
-      <c r="P38" s="5" t="n">
-        <v>0.9952</v>
-      </c>
+        <v>0.9949</v>
+      </c>
+      <c r="P38" s="6" t="inlineStr"/>
       <c r="Q38" s="6" t="inlineStr"/>
       <c r="R38" s="6" t="inlineStr"/>
       <c r="S38" s="6" t="inlineStr"/>
@@ -3113,7 +3005,6 @@
       <c r="U38" s="6" t="inlineStr"/>
       <c r="V38" s="6" t="inlineStr"/>
       <c r="W38" s="6" t="inlineStr"/>
-      <c r="X38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3156,14 +3047,12 @@
       <c r="L39" s="5" t="inlineStr"/>
       <c r="M39" s="5" t="inlineStr"/>
       <c r="N39" s="5" t="n">
-        <v>0.9808</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="O39" s="5" t="n">
-        <v>0.9834000000000001</v>
-      </c>
-      <c r="P39" s="5" t="n">
-        <v>0.9819</v>
-      </c>
+        <v>0.9815</v>
+      </c>
+      <c r="P39" s="6" t="inlineStr"/>
       <c r="Q39" s="6" t="inlineStr"/>
       <c r="R39" s="6" t="inlineStr"/>
       <c r="S39" s="6" t="inlineStr"/>
@@ -3171,7 +3060,6 @@
       <c r="U39" s="6" t="inlineStr"/>
       <c r="V39" s="6" t="inlineStr"/>
       <c r="W39" s="6" t="inlineStr"/>
-      <c r="X39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3214,14 +3102,12 @@
       <c r="L40" s="5" t="inlineStr"/>
       <c r="M40" s="5" t="inlineStr"/>
       <c r="N40" s="5" t="n">
-        <v>0.9808</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="O40" s="5" t="n">
-        <v>0.9834000000000001</v>
-      </c>
-      <c r="P40" s="5" t="n">
-        <v>0.9819</v>
-      </c>
+        <v>0.9815</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr"/>
       <c r="Q40" s="6" t="inlineStr"/>
       <c r="R40" s="6" t="inlineStr"/>
       <c r="S40" s="6" t="inlineStr"/>
@@ -3229,7 +3115,6 @@
       <c r="U40" s="6" t="inlineStr"/>
       <c r="V40" s="6" t="inlineStr"/>
       <c r="W40" s="6" t="inlineStr"/>
-      <c r="X40" s="6" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -3272,14 +3157,12 @@
       <c r="L41" s="5" t="inlineStr"/>
       <c r="M41" s="5" t="inlineStr"/>
       <c r="N41" s="5" t="n">
-        <v>0.9808</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="O41" s="5" t="n">
-        <v>0.9834000000000001</v>
-      </c>
-      <c r="P41" s="5" t="n">
-        <v>0.9819</v>
-      </c>
+        <v>0.9815</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr"/>
       <c r="Q41" s="6" t="inlineStr"/>
       <c r="R41" s="6" t="inlineStr"/>
       <c r="S41" s="6" t="inlineStr"/>
@@ -3287,7 +3170,6 @@
       <c r="U41" s="6" t="inlineStr"/>
       <c r="V41" s="6" t="inlineStr"/>
       <c r="W41" s="6" t="inlineStr"/>
-      <c r="X41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -3329,13 +3211,13 @@
       <c r="K42" s="5" t="inlineStr"/>
       <c r="L42" s="5" t="inlineStr"/>
       <c r="M42" s="5" t="inlineStr"/>
-      <c r="N42" s="5" t="inlineStr"/>
+      <c r="N42" s="5" t="n">
+        <v>0.9837</v>
+      </c>
       <c r="O42" s="5" t="n">
-        <v>0.9837</v>
-      </c>
-      <c r="P42" s="5" t="n">
-        <v>0.9824000000000001</v>
-      </c>
+        <v>0.9823</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr"/>
       <c r="Q42" s="6" t="inlineStr"/>
       <c r="R42" s="6" t="inlineStr"/>
       <c r="S42" s="6" t="inlineStr"/>
@@ -3343,7 +3225,6 @@
       <c r="U42" s="6" t="inlineStr"/>
       <c r="V42" s="6" t="inlineStr"/>
       <c r="W42" s="6" t="inlineStr"/>
-      <c r="X42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3385,13 +3266,13 @@
       <c r="K43" s="5" t="inlineStr"/>
       <c r="L43" s="5" t="inlineStr"/>
       <c r="M43" s="5" t="inlineStr"/>
-      <c r="N43" s="5" t="inlineStr"/>
+      <c r="N43" s="5" t="n">
+        <v>0.9837</v>
+      </c>
       <c r="O43" s="5" t="n">
-        <v>0.9837</v>
-      </c>
-      <c r="P43" s="5" t="n">
-        <v>0.9824000000000001</v>
-      </c>
+        <v>0.9823</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr"/>
       <c r="Q43" s="6" t="inlineStr"/>
       <c r="R43" s="6" t="inlineStr"/>
       <c r="S43" s="6" t="inlineStr"/>
@@ -3399,7 +3280,6 @@
       <c r="U43" s="6" t="inlineStr"/>
       <c r="V43" s="6" t="inlineStr"/>
       <c r="W43" s="6" t="inlineStr"/>
-      <c r="X43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3444,14 +3324,12 @@
       <c r="L44" s="5" t="inlineStr"/>
       <c r="M44" s="5" t="inlineStr"/>
       <c r="N44" s="5" t="n">
-        <v>0.9809</v>
+        <v>0.9865</v>
       </c>
       <c r="O44" s="5" t="n">
-        <v>0.9865</v>
-      </c>
-      <c r="P44" s="5" t="n">
-        <v>0.9829</v>
-      </c>
+        <v>0.9822</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr"/>
       <c r="Q44" s="6" t="inlineStr"/>
       <c r="R44" s="6" t="inlineStr"/>
       <c r="S44" s="6" t="inlineStr"/>
@@ -3459,7 +3337,6 @@
       <c r="U44" s="6" t="inlineStr"/>
       <c r="V44" s="6" t="inlineStr"/>
       <c r="W44" s="6" t="inlineStr"/>
-      <c r="X44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3502,14 +3379,12 @@
       <c r="L45" s="5" t="inlineStr"/>
       <c r="M45" s="5" t="inlineStr"/>
       <c r="N45" s="5" t="n">
-        <v>0.9718</v>
+        <v>0.9825</v>
       </c>
       <c r="O45" s="5" t="n">
-        <v>0.9825</v>
-      </c>
-      <c r="P45" s="5" t="n">
-        <v>0.9801</v>
-      </c>
+        <v>0.9791</v>
+      </c>
+      <c r="P45" s="6" t="inlineStr"/>
       <c r="Q45" s="6" t="inlineStr"/>
       <c r="R45" s="6" t="inlineStr"/>
       <c r="S45" s="6" t="inlineStr"/>
@@ -3517,7 +3392,6 @@
       <c r="U45" s="6" t="inlineStr"/>
       <c r="V45" s="6" t="inlineStr"/>
       <c r="W45" s="6" t="inlineStr"/>
-      <c r="X45" s="6" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3564,14 +3438,12 @@
       <c r="L46" s="5" t="inlineStr"/>
       <c r="M46" s="5" t="inlineStr"/>
       <c r="N46" s="5" t="n">
-        <v>0.8733</v>
+        <v>0.8959</v>
       </c>
       <c r="O46" s="5" t="n">
-        <v>0.8959</v>
-      </c>
-      <c r="P46" s="5" t="n">
-        <v>0.901</v>
-      </c>
+        <v>0.8954</v>
+      </c>
+      <c r="P46" s="6" t="inlineStr"/>
       <c r="Q46" s="6" t="inlineStr"/>
       <c r="R46" s="6" t="inlineStr"/>
       <c r="S46" s="6" t="inlineStr"/>
@@ -3579,7 +3451,6 @@
       <c r="U46" s="6" t="inlineStr"/>
       <c r="V46" s="6" t="inlineStr"/>
       <c r="W46" s="6" t="inlineStr"/>
-      <c r="X46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3626,14 +3497,12 @@
       <c r="L47" s="5" t="inlineStr"/>
       <c r="M47" s="5" t="inlineStr"/>
       <c r="N47" s="5" t="n">
-        <v>0.9781</v>
+        <v>0.9829</v>
       </c>
       <c r="O47" s="5" t="n">
-        <v>0.9829</v>
-      </c>
-      <c r="P47" s="5" t="n">
-        <v>0.983</v>
-      </c>
+        <v>0.9824000000000001</v>
+      </c>
+      <c r="P47" s="6" t="inlineStr"/>
       <c r="Q47" s="6" t="inlineStr"/>
       <c r="R47" s="6" t="inlineStr"/>
       <c r="S47" s="6" t="inlineStr"/>
@@ -3641,7 +3510,6 @@
       <c r="U47" s="6" t="inlineStr"/>
       <c r="V47" s="6" t="inlineStr"/>
       <c r="W47" s="6" t="inlineStr"/>
-      <c r="X47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3684,14 +3552,12 @@
       <c r="L48" s="5" t="inlineStr"/>
       <c r="M48" s="5" t="inlineStr"/>
       <c r="N48" s="5" t="n">
-        <v>0.9718</v>
+        <v>0.9825</v>
       </c>
       <c r="O48" s="5" t="n">
-        <v>0.9825</v>
-      </c>
-      <c r="P48" s="5" t="n">
-        <v>0.9801</v>
-      </c>
+        <v>0.9791</v>
+      </c>
+      <c r="P48" s="6" t="inlineStr"/>
       <c r="Q48" s="6" t="inlineStr"/>
       <c r="R48" s="6" t="inlineStr"/>
       <c r="S48" s="6" t="inlineStr"/>
@@ -3699,7 +3565,6 @@
       <c r="U48" s="6" t="inlineStr"/>
       <c r="V48" s="6" t="inlineStr"/>
       <c r="W48" s="6" t="inlineStr"/>
-      <c r="X48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -3746,14 +3611,12 @@
       <c r="L49" s="5" t="inlineStr"/>
       <c r="M49" s="5" t="inlineStr"/>
       <c r="N49" s="5" t="n">
-        <v>0.9475</v>
+        <v>0.9569</v>
       </c>
       <c r="O49" s="5" t="n">
-        <v>0.9569</v>
-      </c>
-      <c r="P49" s="5" t="n">
-        <v>0.9569</v>
-      </c>
+        <v>0.9556</v>
+      </c>
+      <c r="P49" s="6" t="inlineStr"/>
       <c r="Q49" s="6" t="inlineStr"/>
       <c r="R49" s="6" t="inlineStr"/>
       <c r="S49" s="6" t="inlineStr"/>
@@ -3761,7 +3624,6 @@
       <c r="U49" s="6" t="inlineStr"/>
       <c r="V49" s="6" t="inlineStr"/>
       <c r="W49" s="6" t="inlineStr"/>
-      <c r="X49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3808,14 +3670,12 @@
       <c r="L50" s="5" t="inlineStr"/>
       <c r="M50" s="5" t="inlineStr"/>
       <c r="N50" s="5" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.9525</v>
       </c>
       <c r="O50" s="5" t="n">
-        <v>0.9525</v>
-      </c>
-      <c r="P50" s="5" t="n">
-        <v>0.9519</v>
-      </c>
+        <v>0.9507</v>
+      </c>
+      <c r="P50" s="6" t="inlineStr"/>
       <c r="Q50" s="6" t="inlineStr"/>
       <c r="R50" s="6" t="inlineStr"/>
       <c r="S50" s="6" t="inlineStr"/>
@@ -3823,7 +3683,6 @@
       <c r="U50" s="6" t="inlineStr"/>
       <c r="V50" s="6" t="inlineStr"/>
       <c r="W50" s="6" t="inlineStr"/>
-      <c r="X50" s="6" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3866,14 +3725,12 @@
       <c r="L51" s="5" t="inlineStr"/>
       <c r="M51" s="5" t="inlineStr"/>
       <c r="N51" s="5" t="n">
-        <v>0.9993</v>
+        <v>1.0018</v>
       </c>
       <c r="O51" s="5" t="n">
-        <v>1.0018</v>
-      </c>
-      <c r="P51" s="5" t="n">
-        <v>0.9952</v>
-      </c>
+        <v>0.9949</v>
+      </c>
+      <c r="P51" s="6" t="inlineStr"/>
       <c r="Q51" s="6" t="inlineStr"/>
       <c r="R51" s="6" t="inlineStr"/>
       <c r="S51" s="6" t="inlineStr"/>
@@ -3881,7 +3738,6 @@
       <c r="U51" s="6" t="inlineStr"/>
       <c r="V51" s="6" t="inlineStr"/>
       <c r="W51" s="6" t="inlineStr"/>
-      <c r="X51" s="6" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3928,14 +3784,12 @@
       <c r="L52" s="5" t="inlineStr"/>
       <c r="M52" s="5" t="inlineStr"/>
       <c r="N52" s="5" t="n">
-        <v>0.9855</v>
+        <v>0.9879</v>
       </c>
       <c r="O52" s="5" t="n">
-        <v>0.9879</v>
-      </c>
-      <c r="P52" s="5" t="n">
-        <v>0.9893999999999999</v>
-      </c>
+        <v>0.989</v>
+      </c>
+      <c r="P52" s="6" t="inlineStr"/>
       <c r="Q52" s="6" t="inlineStr"/>
       <c r="R52" s="6" t="inlineStr"/>
       <c r="S52" s="6" t="inlineStr"/>
@@ -3943,7 +3797,6 @@
       <c r="U52" s="6" t="inlineStr"/>
       <c r="V52" s="6" t="inlineStr"/>
       <c r="W52" s="6" t="inlineStr"/>
-      <c r="X52" s="6" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -3990,14 +3843,12 @@
       <c r="L53" s="5" t="inlineStr"/>
       <c r="M53" s="5" t="inlineStr"/>
       <c r="N53" s="5" t="n">
-        <v>0.9475</v>
+        <v>0.9569</v>
       </c>
       <c r="O53" s="5" t="n">
-        <v>0.9569</v>
-      </c>
-      <c r="P53" s="5" t="n">
-        <v>0.9569</v>
-      </c>
+        <v>0.9556</v>
+      </c>
+      <c r="P53" s="6" t="inlineStr"/>
       <c r="Q53" s="6" t="inlineStr"/>
       <c r="R53" s="6" t="inlineStr"/>
       <c r="S53" s="6" t="inlineStr"/>
@@ -4005,7 +3856,6 @@
       <c r="U53" s="6" t="inlineStr"/>
       <c r="V53" s="6" t="inlineStr"/>
       <c r="W53" s="6" t="inlineStr"/>
-      <c r="X53" s="6" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -4052,14 +3902,12 @@
       <c r="L54" s="5" t="inlineStr"/>
       <c r="M54" s="5" t="inlineStr"/>
       <c r="N54" s="5" t="n">
-        <v>0.8619</v>
+        <v>0.8817</v>
       </c>
       <c r="O54" s="5" t="n">
-        <v>0.8817</v>
-      </c>
-      <c r="P54" s="5" t="n">
-        <v>0.8881</v>
-      </c>
+        <v>0.8824</v>
+      </c>
+      <c r="P54" s="6" t="inlineStr"/>
       <c r="Q54" s="6" t="inlineStr"/>
       <c r="R54" s="6" t="inlineStr"/>
       <c r="S54" s="6" t="inlineStr"/>
@@ -4067,7 +3915,6 @@
       <c r="U54" s="6" t="inlineStr"/>
       <c r="V54" s="6" t="inlineStr"/>
       <c r="W54" s="6" t="inlineStr"/>
-      <c r="X54" s="6" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -4114,14 +3961,12 @@
       <c r="L55" s="5" t="inlineStr"/>
       <c r="M55" s="5" t="inlineStr"/>
       <c r="N55" s="5" t="n">
-        <v>0.8619</v>
+        <v>0.8817</v>
       </c>
       <c r="O55" s="5" t="n">
-        <v>0.8817</v>
-      </c>
-      <c r="P55" s="5" t="n">
-        <v>0.8881</v>
-      </c>
+        <v>0.8824</v>
+      </c>
+      <c r="P55" s="6" t="inlineStr"/>
       <c r="Q55" s="6" t="inlineStr"/>
       <c r="R55" s="6" t="inlineStr"/>
       <c r="S55" s="6" t="inlineStr"/>
@@ -4129,7 +3974,6 @@
       <c r="U55" s="6" t="inlineStr"/>
       <c r="V55" s="6" t="inlineStr"/>
       <c r="W55" s="6" t="inlineStr"/>
-      <c r="X55" s="6" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -4176,14 +4020,12 @@
       <c r="L56" s="5" t="inlineStr"/>
       <c r="M56" s="5" t="inlineStr"/>
       <c r="N56" s="5" t="n">
-        <v>0.9993</v>
+        <v>1.0018</v>
       </c>
       <c r="O56" s="5" t="n">
-        <v>1.0018</v>
-      </c>
-      <c r="P56" s="5" t="n">
-        <v>0.9952</v>
-      </c>
+        <v>0.9949</v>
+      </c>
+      <c r="P56" s="6" t="inlineStr"/>
       <c r="Q56" s="6" t="inlineStr"/>
       <c r="R56" s="6" t="inlineStr"/>
       <c r="S56" s="6" t="inlineStr"/>
@@ -4191,7 +4033,6 @@
       <c r="U56" s="6" t="inlineStr"/>
       <c r="V56" s="6" t="inlineStr"/>
       <c r="W56" s="6" t="inlineStr"/>
-      <c r="X56" s="6" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -4236,14 +4077,12 @@
       <c r="L57" s="5" t="inlineStr"/>
       <c r="M57" s="5" t="inlineStr"/>
       <c r="N57" s="5" t="n">
-        <v>0.9787</v>
+        <v>0.9875</v>
       </c>
       <c r="O57" s="5" t="n">
-        <v>0.9875</v>
-      </c>
-      <c r="P57" s="5" t="n">
-        <v>0.9837</v>
-      </c>
+        <v>0.983</v>
+      </c>
+      <c r="P57" s="6" t="inlineStr"/>
       <c r="Q57" s="6" t="inlineStr"/>
       <c r="R57" s="6" t="inlineStr"/>
       <c r="S57" s="6" t="inlineStr"/>
@@ -4251,7 +4090,6 @@
       <c r="U57" s="6" t="inlineStr"/>
       <c r="V57" s="6" t="inlineStr"/>
       <c r="W57" s="6" t="inlineStr"/>
-      <c r="X57" s="6" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -4298,14 +4136,12 @@
       <c r="L58" s="5" t="inlineStr"/>
       <c r="M58" s="5" t="inlineStr"/>
       <c r="N58" s="5" t="n">
-        <v>0.9388</v>
+        <v>0.9519</v>
       </c>
       <c r="O58" s="5" t="n">
-        <v>0.9519</v>
-      </c>
-      <c r="P58" s="5" t="n">
-        <v>0.951</v>
-      </c>
+        <v>0.9499</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr"/>
       <c r="Q58" s="6" t="inlineStr"/>
       <c r="R58" s="6" t="inlineStr"/>
       <c r="S58" s="6" t="inlineStr"/>
@@ -4313,7 +4149,6 @@
       <c r="U58" s="6" t="inlineStr"/>
       <c r="V58" s="6" t="inlineStr"/>
       <c r="W58" s="6" t="inlineStr"/>
-      <c r="X58" s="6" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -4360,14 +4195,12 @@
       <c r="L59" s="5" t="inlineStr"/>
       <c r="M59" s="5" t="inlineStr"/>
       <c r="N59" s="5" t="n">
-        <v>0.9812</v>
+        <v>0.9845</v>
       </c>
       <c r="O59" s="5" t="n">
-        <v>0.9845</v>
-      </c>
-      <c r="P59" s="5" t="n">
-        <v>0.9832</v>
-      </c>
+        <v>0.9827</v>
+      </c>
+      <c r="P59" s="6" t="inlineStr"/>
       <c r="Q59" s="6" t="inlineStr"/>
       <c r="R59" s="6" t="inlineStr"/>
       <c r="S59" s="6" t="inlineStr"/>
@@ -4375,7 +4208,6 @@
       <c r="U59" s="6" t="inlineStr"/>
       <c r="V59" s="6" t="inlineStr"/>
       <c r="W59" s="6" t="inlineStr"/>
-      <c r="X59" s="6" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -4418,14 +4250,12 @@
       <c r="L60" s="5" t="inlineStr"/>
       <c r="M60" s="5" t="inlineStr"/>
       <c r="N60" s="5" t="n">
-        <v>0.9993</v>
+        <v>1.0018</v>
       </c>
       <c r="O60" s="5" t="n">
-        <v>1.0018</v>
-      </c>
-      <c r="P60" s="5" t="n">
-        <v>0.9952</v>
-      </c>
+        <v>0.9949</v>
+      </c>
+      <c r="P60" s="6" t="inlineStr"/>
       <c r="Q60" s="6" t="inlineStr"/>
       <c r="R60" s="6" t="inlineStr"/>
       <c r="S60" s="6" t="inlineStr"/>
@@ -4433,7 +4263,6 @@
       <c r="U60" s="6" t="inlineStr"/>
       <c r="V60" s="6" t="inlineStr"/>
       <c r="W60" s="6" t="inlineStr"/>
-      <c r="X60" s="6" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -4476,14 +4305,12 @@
       <c r="L61" s="5" t="inlineStr"/>
       <c r="M61" s="5" t="inlineStr"/>
       <c r="N61" s="5" t="n">
-        <v>0.9848</v>
+        <v>0.9862</v>
       </c>
       <c r="O61" s="5" t="n">
-        <v>0.9862</v>
-      </c>
-      <c r="P61" s="5" t="n">
-        <v>0.9913999999999999</v>
-      </c>
+        <v>0.992</v>
+      </c>
+      <c r="P61" s="6" t="inlineStr"/>
       <c r="Q61" s="6" t="inlineStr"/>
       <c r="R61" s="6" t="inlineStr"/>
       <c r="S61" s="6" t="inlineStr"/>
@@ -4491,7 +4318,6 @@
       <c r="U61" s="6" t="inlineStr"/>
       <c r="V61" s="6" t="inlineStr"/>
       <c r="W61" s="6" t="inlineStr"/>
-      <c r="X61" s="6" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -4534,14 +4360,12 @@
       <c r="L62" s="5" t="inlineStr"/>
       <c r="M62" s="5" t="inlineStr"/>
       <c r="N62" s="5" t="n">
-        <v>0.9149</v>
+        <v>0.9329</v>
       </c>
       <c r="O62" s="5" t="n">
-        <v>0.9329</v>
-      </c>
-      <c r="P62" s="5" t="n">
-        <v>0.9317</v>
-      </c>
+        <v>0.9298999999999999</v>
+      </c>
+      <c r="P62" s="6" t="inlineStr"/>
       <c r="Q62" s="6" t="inlineStr"/>
       <c r="R62" s="6" t="inlineStr"/>
       <c r="S62" s="6" t="inlineStr"/>
@@ -4549,7 +4373,6 @@
       <c r="U62" s="6" t="inlineStr"/>
       <c r="V62" s="6" t="inlineStr"/>
       <c r="W62" s="6" t="inlineStr"/>
-      <c r="X62" s="6" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -4592,14 +4415,12 @@
       <c r="L63" s="5" t="inlineStr"/>
       <c r="M63" s="5" t="inlineStr"/>
       <c r="N63" s="5" t="n">
-        <v>0.9848</v>
+        <v>0.9862</v>
       </c>
       <c r="O63" s="5" t="n">
-        <v>0.9862</v>
-      </c>
-      <c r="P63" s="5" t="n">
-        <v>0.9913999999999999</v>
-      </c>
+        <v>0.992</v>
+      </c>
+      <c r="P63" s="6" t="inlineStr"/>
       <c r="Q63" s="6" t="inlineStr"/>
       <c r="R63" s="6" t="inlineStr"/>
       <c r="S63" s="6" t="inlineStr"/>
@@ -4607,7 +4428,6 @@
       <c r="U63" s="6" t="inlineStr"/>
       <c r="V63" s="6" t="inlineStr"/>
       <c r="W63" s="6" t="inlineStr"/>
-      <c r="X63" s="6" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -4650,14 +4470,12 @@
       <c r="L64" s="5" t="inlineStr"/>
       <c r="M64" s="5" t="inlineStr"/>
       <c r="N64" s="5" t="n">
-        <v>0.9718</v>
+        <v>0.9825</v>
       </c>
       <c r="O64" s="5" t="n">
-        <v>0.9825</v>
-      </c>
-      <c r="P64" s="5" t="n">
-        <v>0.9801</v>
-      </c>
+        <v>0.9791</v>
+      </c>
+      <c r="P64" s="6" t="inlineStr"/>
       <c r="Q64" s="6" t="inlineStr"/>
       <c r="R64" s="6" t="inlineStr"/>
       <c r="S64" s="6" t="inlineStr"/>
@@ -4665,7 +4483,6 @@
       <c r="U64" s="6" t="inlineStr"/>
       <c r="V64" s="6" t="inlineStr"/>
       <c r="W64" s="6" t="inlineStr"/>
-      <c r="X64" s="6" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -4708,14 +4525,12 @@
       <c r="L65" s="5" t="inlineStr"/>
       <c r="M65" s="5" t="inlineStr"/>
       <c r="N65" s="5" t="n">
-        <v>0.9993</v>
+        <v>1.0018</v>
       </c>
       <c r="O65" s="5" t="n">
-        <v>1.0018</v>
-      </c>
-      <c r="P65" s="5" t="n">
-        <v>0.9952</v>
-      </c>
+        <v>0.9949</v>
+      </c>
+      <c r="P65" s="6" t="inlineStr"/>
       <c r="Q65" s="6" t="inlineStr"/>
       <c r="R65" s="6" t="inlineStr"/>
       <c r="S65" s="6" t="inlineStr"/>
@@ -4723,7 +4538,6 @@
       <c r="U65" s="6" t="inlineStr"/>
       <c r="V65" s="6" t="inlineStr"/>
       <c r="W65" s="6" t="inlineStr"/>
-      <c r="X65" s="6" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -4766,14 +4580,12 @@
       <c r="L66" s="5" t="inlineStr"/>
       <c r="M66" s="5" t="inlineStr"/>
       <c r="N66" s="5" t="n">
-        <v>1.0072</v>
+        <v>1.0166</v>
       </c>
       <c r="O66" s="5" t="n">
-        <v>1.0166</v>
-      </c>
-      <c r="P66" s="5" t="n">
-        <v>1.0065</v>
-      </c>
+        <v>1.0031</v>
+      </c>
+      <c r="P66" s="6" t="inlineStr"/>
       <c r="Q66" s="6" t="inlineStr"/>
       <c r="R66" s="6" t="inlineStr"/>
       <c r="S66" s="6" t="inlineStr"/>
@@ -4781,7 +4593,6 @@
       <c r="U66" s="6" t="inlineStr"/>
       <c r="V66" s="6" t="inlineStr"/>
       <c r="W66" s="6" t="inlineStr"/>
-      <c r="X66" s="6" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -4828,14 +4639,12 @@
       <c r="L67" s="5" t="inlineStr"/>
       <c r="M67" s="5" t="inlineStr"/>
       <c r="N67" s="5" t="n">
-        <v>0.9425</v>
+        <v>0.9537</v>
       </c>
       <c r="O67" s="5" t="n">
-        <v>0.9537</v>
-      </c>
-      <c r="P67" s="5" t="n">
-        <v>0.9562</v>
-      </c>
+        <v>0.9547</v>
+      </c>
+      <c r="P67" s="6" t="inlineStr"/>
       <c r="Q67" s="6" t="inlineStr"/>
       <c r="R67" s="6" t="inlineStr"/>
       <c r="S67" s="6" t="inlineStr"/>
@@ -4843,7 +4652,6 @@
       <c r="U67" s="6" t="inlineStr"/>
       <c r="V67" s="6" t="inlineStr"/>
       <c r="W67" s="6" t="inlineStr"/>
-      <c r="X67" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4856,7 +4664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W67"/>
+  <dimension ref="A1:V67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4881,7 +4689,6 @@
     <col width="14" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4897,105 +4704,100 @@
       </c>
       <c r="C1" s="7" t="inlineStr">
         <is>
-          <t>MLF_FY24-25</t>
+          <t>MLF_FY25-26</t>
         </is>
       </c>
       <c r="D1" s="7" t="inlineStr">
         <is>
-          <t>MLF_FY25-26</t>
+          <t>MLF_FY26-27</t>
         </is>
       </c>
       <c r="E1" s="7" t="inlineStr">
         <is>
-          <t>MLF_FY26-27 (Draft)</t>
+          <t>CURTAILMENT_ACTUAL_FY23-24</t>
         </is>
       </c>
       <c r="F1" s="7" t="inlineStr">
         <is>
-          <t>CURTAILMENT_ACTUAL_FY23-24</t>
+          <t>CURTAILMENT_ACTUAL_FY24-25</t>
         </is>
       </c>
       <c r="G1" s="7" t="inlineStr">
         <is>
-          <t>CURTAILMENT_ACTUAL_FY24-25</t>
+          <t>ELI_CURTAILMENT_NEAR</t>
         </is>
       </c>
       <c r="H1" s="7" t="inlineStr">
         <is>
-          <t>ELI_CURTAILMENT_NEAR</t>
+          <t>ELI_CURTAILMENT_MED</t>
         </is>
       </c>
       <c r="I1" s="7" t="inlineStr">
         <is>
-          <t>ELI_CURTAILMENT_MED</t>
+          <t>ISP_CURTAILMENT_FY1</t>
         </is>
       </c>
       <c r="J1" s="7" t="inlineStr">
         <is>
-          <t>ISP_CURTAILMENT_FY1</t>
+          <t>ISP_CURTAILMENT_FY1_LABEL</t>
         </is>
       </c>
       <c r="K1" s="7" t="inlineStr">
         <is>
-          <t>ISP_CURTAILMENT_FY1_LABEL</t>
+          <t>ISP_CURTAILMENT_FY2</t>
         </is>
       </c>
       <c r="L1" s="7" t="inlineStr">
         <is>
-          <t>ISP_CURTAILMENT_FY2</t>
+          <t>ISP_CURTAILMENT_FY2_LABEL</t>
         </is>
       </c>
       <c r="M1" s="7" t="inlineStr">
         <is>
-          <t>ISP_CURTAILMENT_FY2_LABEL</t>
+          <t>ISP_CURTAILMENT_FY3</t>
         </is>
       </c>
       <c r="N1" s="7" t="inlineStr">
         <is>
-          <t>ISP_CURTAILMENT_FY3</t>
+          <t>ISP_CURTAILMENT_FY3_LABEL</t>
         </is>
       </c>
       <c r="O1" s="7" t="inlineStr">
         <is>
-          <t>ISP_CURTAILMENT_FY3_LABEL</t>
+          <t>ISP_CURTAILMENT_AVG</t>
         </is>
       </c>
       <c r="P1" s="7" t="inlineStr">
         <is>
-          <t>ISP_CURTAILMENT_AVG</t>
+          <t>ISP_OFFLOADING_FY1</t>
         </is>
       </c>
       <c r="Q1" s="7" t="inlineStr">
         <is>
-          <t>ISP_OFFLOADING_FY1</t>
+          <t>ISP_OFFLOADING_FY1_LABEL</t>
         </is>
       </c>
       <c r="R1" s="7" t="inlineStr">
         <is>
-          <t>ISP_OFFLOADING_FY1_LABEL</t>
+          <t>ISP_OFFLOADING_FY2</t>
         </is>
       </c>
       <c r="S1" s="7" t="inlineStr">
         <is>
-          <t>ISP_OFFLOADING_FY2</t>
+          <t>ISP_OFFLOADING_FY2_LABEL</t>
         </is>
       </c>
       <c r="T1" s="7" t="inlineStr">
         <is>
-          <t>ISP_OFFLOADING_FY2_LABEL</t>
+          <t>ISP_OFFLOADING_FY3</t>
         </is>
       </c>
       <c r="U1" s="7" t="inlineStr">
         <is>
-          <t>ISP_OFFLOADING_FY3</t>
+          <t>ISP_OFFLOADING_FY3_LABEL</t>
         </is>
       </c>
       <c r="V1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_FY3_LABEL</t>
-        </is>
-      </c>
-      <c r="W1" s="7" t="inlineStr">
         <is>
           <t>ISP_OFFLOADING_AVG</t>
         </is>
@@ -5013,78 +4815,75 @@
         </is>
       </c>
       <c r="C2" s="5" t="n">
-        <v>0.8584000000000001</v>
+        <v>0.8986</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>0.8986</v>
+        <v>0.9092</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.9114</v>
+        <v>0.3236</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>0.3236</v>
+        <v>0.2465</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.2465</v>
+        <v>0.833539620209753</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>0.833539620209753</v>
+        <v>0.164192244302687</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>0.164192244302687</v>
-      </c>
-      <c r="J2" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L2" s="5" t="n">
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="M2" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N2" s="5" t="n">
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O2" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="n">
+        <v>0.02666666666666667</v>
       </c>
       <c r="P2" s="5" t="n">
-        <v>0.02666666666666667</v>
-      </c>
-      <c r="Q2" s="5" t="n">
         <v>0.11</v>
       </c>
-      <c r="R2" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S2" s="5" t="n">
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="n">
         <v>0.17</v>
       </c>
-      <c r="T2" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U2" s="5" t="n">
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="n">
         <v>0.08</v>
       </c>
-      <c r="V2" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W2" s="5" t="n">
+      <c r="U2" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V2" s="5" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -5099,55 +4898,54 @@
           <t>Solar</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr"/>
+      <c r="C3" s="5" t="n">
+        <v>0.8883</v>
+      </c>
       <c r="D3" s="5" t="n">
-        <v>0.8883</v>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>0.9012</v>
-      </c>
+        <v>0.8963</v>
+      </c>
+      <c r="E3" s="5" t="inlineStr"/>
       <c r="F3" s="5" t="inlineStr"/>
       <c r="G3" s="5" t="inlineStr"/>
       <c r="H3" s="5" t="inlineStr"/>
       <c r="I3" s="5" t="inlineStr"/>
-      <c r="J3" s="5" t="inlineStr"/>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="inlineStr"/>
-      <c r="M3" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N3" s="5" t="inlineStr"/>
-      <c r="O3" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr"/>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr"/>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr"/>
       <c r="P3" s="5" t="inlineStr"/>
-      <c r="Q3" s="5" t="inlineStr"/>
-      <c r="R3" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S3" s="5" t="inlineStr"/>
-      <c r="T3" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U3" s="5" t="inlineStr"/>
-      <c r="V3" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr"/>
+      <c r="U3" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
@@ -5161,74 +4959,71 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>0.8962</v>
+        <v>0.9305</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>0.9305</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>0.9307</v>
-      </c>
+        <v>0.929</v>
+      </c>
+      <c r="E4" s="5" t="inlineStr"/>
       <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="n">
+        <v>0.547516873654646</v>
+      </c>
       <c r="H4" s="5" t="n">
-        <v>0.547516873654646</v>
+        <v>0.122422882740379</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>0.122422882740379</v>
-      </c>
-      <c r="J4" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="n">
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="M4" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N4" s="5" t="n">
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O4" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="n">
+        <v>0.02666666666666667</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>0.02666666666666667</v>
-      </c>
-      <c r="Q4" s="5" t="n">
         <v>0.11</v>
       </c>
-      <c r="R4" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S4" s="5" t="n">
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="n">
         <v>0.17</v>
       </c>
-      <c r="T4" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U4" s="5" t="n">
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="n">
         <v>0.08</v>
       </c>
-      <c r="V4" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W4" s="5" t="n">
+      <c r="U4" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V4" s="5" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -5244,78 +5039,75 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>0.8962</v>
+        <v>0.9305</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0.9305</v>
+        <v>0.929</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.9307</v>
+        <v>0.0499</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.0499</v>
+        <v>0.054</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.054</v>
+        <v>0.547516873654646</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>0.547516873654646</v>
+        <v>0.122422882740379</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>0.122422882740379</v>
-      </c>
-      <c r="J5" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L5" s="5" t="n">
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="M5" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N5" s="5" t="n">
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O5" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O5" s="5" t="n">
+        <v>0.02666666666666667</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>0.02666666666666667</v>
-      </c>
-      <c r="Q5" s="5" t="n">
         <v>0.11</v>
       </c>
-      <c r="R5" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S5" s="5" t="n">
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R5" s="5" t="n">
         <v>0.17</v>
       </c>
-      <c r="T5" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U5" s="5" t="n">
+      <c r="S5" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T5" s="5" t="n">
         <v>0.08</v>
       </c>
-      <c r="V5" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W5" s="5" t="n">
+      <c r="U5" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V5" s="5" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -5331,76 +5123,73 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0.9477</v>
+        <v>0.9463</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0.9463</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>0.9223</v>
-      </c>
-      <c r="F6" s="5" t="inlineStr"/>
+        <v>0.921</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="n">
+        <v>0.2374</v>
+      </c>
       <c r="G6" s="5" t="n">
-        <v>0.2374</v>
+        <v>0.389503957787889</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>0.389503957787889</v>
+        <v>0.08205629867681941</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0.08205629867681941</v>
-      </c>
-      <c r="J6" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L6" s="5" t="n">
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M6" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N6" s="5" t="n">
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O6" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="5" t="n">
         <v>0.04</v>
       </c>
-      <c r="R6" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S6" s="5" t="n">
+      <c r="Q6" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R6" s="5" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="T6" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U6" s="5" t="n">
+      <c r="S6" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T6" s="5" t="n">
         <v>0.1</v>
       </c>
-      <c r="V6" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W6" s="5" t="n">
+      <c r="U6" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V6" s="5" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -5416,76 +5205,73 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.9626</v>
+        <v>0.949</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0.949</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>0.9292</v>
-      </c>
-      <c r="F7" s="5" t="inlineStr"/>
+        <v>0.9294</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="n">
+        <v>0.0688</v>
+      </c>
       <c r="G7" s="5" t="n">
-        <v>0.0688</v>
+        <v>0.390717855103594</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>0.390717855103594</v>
+        <v>0.08997768712489811</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>0.08997768712489811</v>
-      </c>
-      <c r="J7" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L7" s="5" t="n">
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N7" s="5" t="n">
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O7" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O7" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="5" t="n">
         <v>0.04</v>
       </c>
-      <c r="R7" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S7" s="5" t="n">
+      <c r="Q7" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R7" s="5" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="T7" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U7" s="5" t="n">
+      <c r="S7" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T7" s="5" t="n">
         <v>0.1</v>
       </c>
-      <c r="V7" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W7" s="5" t="n">
+      <c r="U7" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V7" s="5" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -5501,60 +5287,57 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>0.9455</v>
+        <v>0.9402</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0.9402</v>
+        <v>0.9211</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.922</v>
+        <v>0.1836</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.1836</v>
-      </c>
-      <c r="G8" s="5" t="n">
         <v>0.2057</v>
       </c>
+      <c r="G8" s="5" t="inlineStr"/>
       <c r="H8" s="5" t="inlineStr"/>
       <c r="I8" s="5" t="inlineStr"/>
-      <c r="J8" s="5" t="inlineStr"/>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="inlineStr"/>
-      <c r="M8" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N8" s="5" t="inlineStr"/>
-      <c r="O8" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr"/>
+      <c r="N8" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O8" s="5" t="inlineStr"/>
       <c r="P8" s="5" t="inlineStr"/>
-      <c r="Q8" s="5" t="inlineStr"/>
-      <c r="R8" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S8" s="5" t="inlineStr"/>
-      <c r="T8" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U8" s="5" t="inlineStr"/>
-      <c r="V8" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W8" s="5" t="inlineStr"/>
+      <c r="Q8" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R8" s="5" t="inlineStr"/>
+      <c r="S8" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T8" s="5" t="inlineStr"/>
+      <c r="U8" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
@@ -5567,55 +5350,54 @@
           <t>Solar</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="n">
+        <v>0.9328</v>
+      </c>
       <c r="D9" s="5" t="n">
-        <v>0.9328</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>0.9262</v>
-      </c>
+        <v>0.9261</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr"/>
       <c r="F9" s="5" t="inlineStr"/>
       <c r="G9" s="5" t="inlineStr"/>
       <c r="H9" s="5" t="inlineStr"/>
       <c r="I9" s="5" t="inlineStr"/>
-      <c r="J9" s="5" t="inlineStr"/>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr"/>
-      <c r="M9" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N9" s="5" t="inlineStr"/>
-      <c r="O9" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O9" s="5" t="inlineStr"/>
       <c r="P9" s="5" t="inlineStr"/>
-      <c r="Q9" s="5" t="inlineStr"/>
-      <c r="R9" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S9" s="5" t="inlineStr"/>
-      <c r="T9" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U9" s="5" t="inlineStr"/>
-      <c r="V9" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W9" s="5" t="inlineStr"/>
+      <c r="Q9" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R9" s="5" t="inlineStr"/>
+      <c r="S9" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T9" s="5" t="inlineStr"/>
+      <c r="U9" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -5629,78 +5411,75 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0.8506</v>
+        <v>0.8895</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>0.8895</v>
+        <v>0.9051</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.9088000000000001</v>
+        <v>0.2761</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.2761</v>
+        <v>0.159</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.159</v>
+        <v>0.8554020168196</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>0.8554020168196</v>
+        <v>0.072415601225557</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0.072415601225557</v>
-      </c>
-      <c r="J10" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="n">
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="M10" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N10" s="5" t="n">
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O10" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+      <c r="N10" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O10" s="5" t="n">
+        <v>0.02666666666666667</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>0.02666666666666667</v>
-      </c>
-      <c r="Q10" s="5" t="n">
         <v>0.11</v>
       </c>
-      <c r="R10" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S10" s="5" t="n">
+      <c r="Q10" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R10" s="5" t="n">
         <v>0.17</v>
       </c>
-      <c r="T10" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U10" s="5" t="n">
+      <c r="S10" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T10" s="5" t="n">
         <v>0.08</v>
       </c>
-      <c r="V10" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W10" s="5" t="n">
+      <c r="U10" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V10" s="5" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -5716,56 +5495,53 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0.8964</v>
+        <v>0.9329</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>0.9329</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>0.9330000000000001</v>
-      </c>
+        <v>0.9311</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr"/>
       <c r="F11" s="5" t="inlineStr"/>
       <c r="G11" s="5" t="inlineStr"/>
       <c r="H11" s="5" t="inlineStr"/>
       <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="inlineStr"/>
-      <c r="M11" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N11" s="5" t="inlineStr"/>
-      <c r="O11" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O11" s="5" t="inlineStr"/>
       <c r="P11" s="5" t="inlineStr"/>
-      <c r="Q11" s="5" t="inlineStr"/>
-      <c r="R11" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S11" s="5" t="inlineStr"/>
-      <c r="T11" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U11" s="5" t="inlineStr"/>
-      <c r="V11" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W11" s="5" t="inlineStr"/>
+      <c r="Q11" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R11" s="5" t="inlineStr"/>
+      <c r="S11" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T11" s="5" t="inlineStr"/>
+      <c r="U11" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
@@ -5779,78 +5555,75 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0.8363</v>
+        <v>0.8784999999999999</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>0.8784999999999999</v>
+        <v>0.8738</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.878</v>
+        <v>0.106</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.106</v>
+        <v>0.1081</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.1081</v>
+        <v>0.827440107601162</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0.827440107601162</v>
+        <v>0.0878331516592939</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.0878331516592939</v>
-      </c>
-      <c r="J12" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L12" s="5" t="n">
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="M12" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N12" s="5" t="n">
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O12" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+      <c r="N12" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O12" s="5" t="n">
+        <v>0.02666666666666667</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>0.02666666666666667</v>
-      </c>
-      <c r="Q12" s="5" t="n">
         <v>0.11</v>
       </c>
-      <c r="R12" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S12" s="5" t="n">
+      <c r="Q12" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R12" s="5" t="n">
         <v>0.17</v>
       </c>
-      <c r="T12" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U12" s="5" t="n">
+      <c r="S12" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T12" s="5" t="n">
         <v>0.08</v>
       </c>
-      <c r="V12" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W12" s="5" t="n">
+      <c r="U12" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V12" s="5" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -5865,53 +5638,54 @@
           <t>Solar</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="n">
+        <v>0.9441000000000001</v>
+      </c>
       <c r="D13" s="5" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.921</v>
       </c>
       <c r="E13" s="5" t="inlineStr"/>
       <c r="F13" s="5" t="inlineStr"/>
       <c r="G13" s="5" t="inlineStr"/>
       <c r="H13" s="5" t="inlineStr"/>
       <c r="I13" s="5" t="inlineStr"/>
-      <c r="J13" s="5" t="inlineStr"/>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L13" s="5" t="inlineStr"/>
-      <c r="M13" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N13" s="5" t="inlineStr"/>
-      <c r="O13" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O13" s="5" t="inlineStr"/>
       <c r="P13" s="5" t="inlineStr"/>
-      <c r="Q13" s="5" t="inlineStr"/>
-      <c r="R13" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S13" s="5" t="inlineStr"/>
-      <c r="T13" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U13" s="5" t="inlineStr"/>
-      <c r="V13" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W13" s="5" t="inlineStr"/>
+      <c r="Q13" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R13" s="5" t="inlineStr"/>
+      <c r="S13" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T13" s="5" t="inlineStr"/>
+      <c r="U13" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
@@ -5925,56 +5699,53 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>0.9484</v>
+        <v>0.9415</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>0.9415</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>0.9248</v>
-      </c>
+        <v>0.9257</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr"/>
       <c r="F14" s="5" t="inlineStr"/>
       <c r="G14" s="5" t="inlineStr"/>
       <c r="H14" s="5" t="inlineStr"/>
       <c r="I14" s="5" t="inlineStr"/>
-      <c r="J14" s="5" t="inlineStr"/>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L14" s="5" t="inlineStr"/>
-      <c r="M14" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N14" s="5" t="inlineStr"/>
-      <c r="O14" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="inlineStr"/>
+      <c r="N14" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O14" s="5" t="inlineStr"/>
       <c r="P14" s="5" t="inlineStr"/>
-      <c r="Q14" s="5" t="inlineStr"/>
-      <c r="R14" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S14" s="5" t="inlineStr"/>
-      <c r="T14" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U14" s="5" t="inlineStr"/>
-      <c r="V14" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W14" s="5" t="inlineStr"/>
+      <c r="Q14" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R14" s="5" t="inlineStr"/>
+      <c r="S14" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T14" s="5" t="inlineStr"/>
+      <c r="U14" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
@@ -5988,78 +5759,75 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>0.9477</v>
+        <v>0.9463</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>0.9463</v>
+        <v>0.921</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.9223</v>
+        <v>0.2971</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.2971</v>
+        <v>0.1275</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.1275</v>
+        <v>0.389503957787889</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>0.389503957787889</v>
+        <v>0.08205629867681941</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>0.08205629867681941</v>
-      </c>
-      <c r="J15" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L15" s="5" t="n">
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M15" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N15" s="5" t="n">
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O15" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+      <c r="N15" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O15" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="5" t="n">
         <v>0.04</v>
       </c>
-      <c r="R15" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S15" s="5" t="n">
+      <c r="Q15" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R15" s="5" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="T15" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U15" s="5" t="n">
+      <c r="S15" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T15" s="5" t="n">
         <v>0.1</v>
       </c>
-      <c r="V15" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W15" s="5" t="n">
+      <c r="U15" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V15" s="5" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -6075,56 +5843,53 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>1.0015</v>
+        <v>0.9519</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>0.9519</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>0.928</v>
-      </c>
+        <v>0.9282</v>
+      </c>
+      <c r="E16" s="5" t="inlineStr"/>
       <c r="F16" s="5" t="inlineStr"/>
       <c r="G16" s="5" t="inlineStr"/>
       <c r="H16" s="5" t="inlineStr"/>
       <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L16" s="5" t="inlineStr"/>
-      <c r="M16" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N16" s="5" t="inlineStr"/>
-      <c r="O16" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr"/>
+      <c r="N16" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O16" s="5" t="inlineStr"/>
       <c r="P16" s="5" t="inlineStr"/>
-      <c r="Q16" s="5" t="inlineStr"/>
-      <c r="R16" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S16" s="5" t="inlineStr"/>
-      <c r="T16" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U16" s="5" t="inlineStr"/>
-      <c r="V16" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W16" s="5" t="inlineStr"/>
+      <c r="Q16" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R16" s="5" t="inlineStr"/>
+      <c r="S16" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T16" s="5" t="inlineStr"/>
+      <c r="U16" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -6138,78 +5903,75 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>0.8584000000000001</v>
+        <v>0.8986</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>0.8986</v>
+        <v>0.9092</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0.9114</v>
+        <v>0.3065</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.3065</v>
+        <v>0.2491</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.2491</v>
+        <v>0.833539620209753</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>0.833539620209753</v>
+        <v>0.164192244302687</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>0.164192244302687</v>
-      </c>
-      <c r="J17" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L17" s="5" t="n">
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="M17" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N17" s="5" t="n">
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O17" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O17" s="5" t="n">
+        <v>0.02666666666666667</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>0.02666666666666667</v>
-      </c>
-      <c r="Q17" s="5" t="n">
         <v>0.11</v>
       </c>
-      <c r="R17" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S17" s="5" t="n">
+      <c r="Q17" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R17" s="5" t="n">
         <v>0.17</v>
       </c>
-      <c r="T17" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U17" s="5" t="n">
+      <c r="S17" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T17" s="5" t="n">
         <v>0.08</v>
       </c>
-      <c r="V17" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W17" s="5" t="n">
+      <c r="U17" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V17" s="5" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -6225,76 +5987,73 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>0.9455</v>
+        <v>0.9402</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>0.9402</v>
+        <v>0.9211</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.922</v>
-      </c>
-      <c r="F18" s="5" t="n">
         <v>0.2227</v>
       </c>
-      <c r="G18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="n">
+        <v>0.390717855103594</v>
+      </c>
       <c r="H18" s="5" t="n">
-        <v>0.390717855103594</v>
+        <v>0.08997768712489811</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>0.08997768712489811</v>
-      </c>
-      <c r="J18" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L18" s="5" t="n">
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M18" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N18" s="5" t="n">
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O18" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+      <c r="N18" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O18" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="5" t="n">
         <v>0.04</v>
       </c>
-      <c r="R18" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S18" s="5" t="n">
+      <c r="Q18" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R18" s="5" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="T18" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U18" s="5" t="n">
+      <c r="S18" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T18" s="5" t="n">
         <v>0.1</v>
       </c>
-      <c r="V18" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W18" s="5" t="n">
+      <c r="U18" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V18" s="5" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -6310,60 +6069,57 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>0.9477</v>
+        <v>0.9463</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>0.9463</v>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>0.9223</v>
-      </c>
+        <v>0.921</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr"/>
       <c r="F19" s="5" t="inlineStr"/>
-      <c r="G19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="n">
+        <v>0.389503957787889</v>
+      </c>
       <c r="H19" s="5" t="n">
-        <v>0.389503957787889</v>
-      </c>
-      <c r="I19" s="5" t="n">
         <v>0.08205629867681941</v>
       </c>
-      <c r="J19" s="5" t="inlineStr"/>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L19" s="5" t="inlineStr"/>
-      <c r="M19" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N19" s="5" t="inlineStr"/>
-      <c r="O19" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O19" s="5" t="inlineStr"/>
       <c r="P19" s="5" t="inlineStr"/>
-      <c r="Q19" s="5" t="inlineStr"/>
-      <c r="R19" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S19" s="5" t="inlineStr"/>
-      <c r="T19" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U19" s="5" t="inlineStr"/>
-      <c r="V19" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W19" s="5" t="inlineStr"/>
+      <c r="Q19" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R19" s="5" t="inlineStr"/>
+      <c r="S19" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T19" s="5" t="inlineStr"/>
+      <c r="U19" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -6377,78 +6133,75 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>0.8506</v>
+        <v>0.8895</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>0.8895</v>
+        <v>0.9051</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0.9088000000000001</v>
+        <v>0.2786</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.2786</v>
+        <v>0.2351</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.2351</v>
+        <v>0.8554020168196</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>0.8554020168196</v>
+        <v>0.072415601225557</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>0.072415601225557</v>
-      </c>
-      <c r="J20" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L20" s="5" t="n">
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="M20" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N20" s="5" t="n">
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O20" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+      <c r="N20" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O20" s="5" t="n">
+        <v>0.02666666666666667</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>0.02666666666666667</v>
-      </c>
-      <c r="Q20" s="5" t="n">
         <v>0.11</v>
       </c>
-      <c r="R20" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S20" s="5" t="n">
+      <c r="Q20" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R20" s="5" t="n">
         <v>0.17</v>
       </c>
-      <c r="T20" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U20" s="5" t="n">
+      <c r="S20" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T20" s="5" t="n">
         <v>0.08</v>
       </c>
-      <c r="V20" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W20" s="5" t="n">
+      <c r="U20" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V20" s="5" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -6464,60 +6217,57 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>0.8856000000000001</v>
+        <v>0.9031</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>0.9031</v>
+        <v>0.898</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0.8999</v>
+        <v>0.0756</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.0756</v>
-      </c>
-      <c r="G21" s="5" t="n">
         <v>0.0482</v>
       </c>
+      <c r="G21" s="5" t="inlineStr"/>
       <c r="H21" s="5" t="inlineStr"/>
       <c r="I21" s="5" t="inlineStr"/>
-      <c r="J21" s="5" t="inlineStr"/>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="inlineStr"/>
-      <c r="M21" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N21" s="5" t="inlineStr"/>
-      <c r="O21" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O21" s="5" t="inlineStr"/>
       <c r="P21" s="5" t="inlineStr"/>
-      <c r="Q21" s="5" t="inlineStr"/>
-      <c r="R21" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S21" s="5" t="inlineStr"/>
-      <c r="T21" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U21" s="5" t="inlineStr"/>
-      <c r="V21" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W21" s="5" t="inlineStr"/>
+      <c r="Q21" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R21" s="5" t="inlineStr"/>
+      <c r="S21" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T21" s="5" t="inlineStr"/>
+      <c r="U21" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
@@ -6531,60 +6281,57 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>0.9848</v>
+        <v>0.9862</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>0.9862</v>
+        <v>0.992</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0.9913999999999999</v>
+        <v>0.0078</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.0078</v>
-      </c>
-      <c r="G22" s="5" t="n">
         <v>0.0051</v>
       </c>
+      <c r="G22" s="5" t="inlineStr"/>
       <c r="H22" s="5" t="inlineStr"/>
       <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L22" s="5" t="inlineStr"/>
-      <c r="M22" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N22" s="5" t="inlineStr"/>
-      <c r="O22" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr"/>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr"/>
+      <c r="N22" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O22" s="5" t="inlineStr"/>
       <c r="P22" s="5" t="inlineStr"/>
-      <c r="Q22" s="5" t="inlineStr"/>
-      <c r="R22" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S22" s="5" t="inlineStr"/>
-      <c r="T22" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U22" s="5" t="inlineStr"/>
-      <c r="V22" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W22" s="5" t="inlineStr"/>
+      <c r="Q22" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R22" s="5" t="inlineStr"/>
+      <c r="S22" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T22" s="5" t="inlineStr"/>
+      <c r="U22" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
@@ -6598,60 +6345,57 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>0.9315</v>
+        <v>0.9465</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>0.9465</v>
+        <v>0.9436</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0.945</v>
+        <v>0.2041</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.2041</v>
-      </c>
-      <c r="G23" s="5" t="n">
         <v>0.1906</v>
       </c>
+      <c r="G23" s="5" t="inlineStr"/>
       <c r="H23" s="5" t="inlineStr"/>
       <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr"/>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N23" s="5" t="inlineStr"/>
-      <c r="O23" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr"/>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O23" s="5" t="inlineStr"/>
       <c r="P23" s="5" t="inlineStr"/>
-      <c r="Q23" s="5" t="inlineStr"/>
-      <c r="R23" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S23" s="5" t="inlineStr"/>
-      <c r="T23" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U23" s="5" t="inlineStr"/>
-      <c r="V23" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W23" s="5" t="inlineStr"/>
+      <c r="Q23" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R23" s="5" t="inlineStr"/>
+      <c r="S23" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T23" s="5" t="inlineStr"/>
+      <c r="U23" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
@@ -6665,60 +6409,57 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>0.9315</v>
+        <v>0.9465</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>0.9465</v>
+        <v>0.9436</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0.945</v>
+        <v>0.045</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="G24" s="5" t="n">
         <v>0.0316</v>
       </c>
+      <c r="G24" s="5" t="inlineStr"/>
       <c r="H24" s="5" t="inlineStr"/>
       <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L24" s="5" t="inlineStr"/>
-      <c r="M24" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N24" s="5" t="inlineStr"/>
-      <c r="O24" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr"/>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="inlineStr"/>
+      <c r="N24" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O24" s="5" t="inlineStr"/>
       <c r="P24" s="5" t="inlineStr"/>
-      <c r="Q24" s="5" t="inlineStr"/>
-      <c r="R24" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S24" s="5" t="inlineStr"/>
-      <c r="T24" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U24" s="5" t="inlineStr"/>
-      <c r="V24" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W24" s="5" t="inlineStr"/>
+      <c r="Q24" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R24" s="5" t="inlineStr"/>
+      <c r="S24" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T24" s="5" t="inlineStr"/>
+      <c r="U24" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
@@ -6732,60 +6473,57 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>0.8733</v>
+        <v>0.8907</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>0.8907</v>
+        <v>0.8868</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>0.89</v>
+        <v>0.0347</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>0.0347</v>
-      </c>
-      <c r="G25" s="5" t="n">
         <v>0.0284</v>
       </c>
+      <c r="G25" s="5" t="inlineStr"/>
       <c r="H25" s="5" t="inlineStr"/>
       <c r="I25" s="5" t="inlineStr"/>
-      <c r="J25" s="5" t="inlineStr"/>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr"/>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N25" s="5" t="inlineStr"/>
-      <c r="O25" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr"/>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O25" s="5" t="inlineStr"/>
       <c r="P25" s="5" t="inlineStr"/>
-      <c r="Q25" s="5" t="inlineStr"/>
-      <c r="R25" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S25" s="5" t="inlineStr"/>
-      <c r="T25" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U25" s="5" t="inlineStr"/>
-      <c r="V25" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W25" s="5" t="inlineStr"/>
+      <c r="Q25" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R25" s="5" t="inlineStr"/>
+      <c r="S25" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T25" s="5" t="inlineStr"/>
+      <c r="U25" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
@@ -6799,56 +6537,53 @@
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>0.9718</v>
+        <v>0.9825</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>0.9825</v>
-      </c>
-      <c r="E26" s="5" t="n">
-        <v>0.9801</v>
-      </c>
+        <v>0.9791</v>
+      </c>
+      <c r="E26" s="5" t="inlineStr"/>
       <c r="F26" s="5" t="inlineStr"/>
       <c r="G26" s="5" t="inlineStr"/>
       <c r="H26" s="5" t="inlineStr"/>
       <c r="I26" s="5" t="inlineStr"/>
-      <c r="J26" s="5" t="inlineStr"/>
-      <c r="K26" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L26" s="5" t="inlineStr"/>
-      <c r="M26" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N26" s="5" t="inlineStr"/>
-      <c r="O26" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr"/>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M26" s="5" t="inlineStr"/>
+      <c r="N26" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O26" s="5" t="inlineStr"/>
       <c r="P26" s="5" t="inlineStr"/>
-      <c r="Q26" s="5" t="inlineStr"/>
-      <c r="R26" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S26" s="5" t="inlineStr"/>
-      <c r="T26" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U26" s="5" t="inlineStr"/>
-      <c r="V26" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W26" s="5" t="inlineStr"/>
+      <c r="Q26" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R26" s="5" t="inlineStr"/>
+      <c r="S26" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T26" s="5" t="inlineStr"/>
+      <c r="U26" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
@@ -6862,54 +6597,51 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>0.9718</v>
-      </c>
-      <c r="D27" s="5" t="n">
         <v>0.9825</v>
       </c>
+      <c r="D27" s="5" t="inlineStr"/>
       <c r="E27" s="5" t="inlineStr"/>
       <c r="F27" s="5" t="inlineStr"/>
       <c r="G27" s="5" t="inlineStr"/>
       <c r="H27" s="5" t="inlineStr"/>
       <c r="I27" s="5" t="inlineStr"/>
-      <c r="J27" s="5" t="inlineStr"/>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="inlineStr"/>
-      <c r="M27" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N27" s="5" t="inlineStr"/>
-      <c r="O27" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O27" s="5" t="inlineStr"/>
       <c r="P27" s="5" t="inlineStr"/>
-      <c r="Q27" s="5" t="inlineStr"/>
-      <c r="R27" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S27" s="5" t="inlineStr"/>
-      <c r="T27" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U27" s="5" t="inlineStr"/>
-      <c r="V27" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W27" s="5" t="inlineStr"/>
+      <c r="Q27" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R27" s="5" t="inlineStr"/>
+      <c r="S27" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T27" s="5" t="inlineStr"/>
+      <c r="U27" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
@@ -6923,60 +6655,57 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>0.9976</v>
+        <v>0.998</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>0.998</v>
+        <v>0.9977</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0.9978</v>
+        <v>0.0578</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.0578</v>
-      </c>
-      <c r="G28" s="5" t="n">
         <v>0.0958</v>
       </c>
+      <c r="G28" s="5" t="inlineStr"/>
       <c r="H28" s="5" t="inlineStr"/>
       <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L28" s="5" t="inlineStr"/>
-      <c r="M28" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N28" s="5" t="inlineStr"/>
-      <c r="O28" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr"/>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M28" s="5" t="inlineStr"/>
+      <c r="N28" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O28" s="5" t="inlineStr"/>
       <c r="P28" s="5" t="inlineStr"/>
-      <c r="Q28" s="5" t="inlineStr"/>
-      <c r="R28" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S28" s="5" t="inlineStr"/>
-      <c r="T28" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U28" s="5" t="inlineStr"/>
-      <c r="V28" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W28" s="5" t="inlineStr"/>
+      <c r="Q28" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R28" s="5" t="inlineStr"/>
+      <c r="S28" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T28" s="5" t="inlineStr"/>
+      <c r="U28" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
@@ -6990,56 +6719,53 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>0.9993</v>
+        <v>1.0018</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>1.0018</v>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>0.9952</v>
-      </c>
+        <v>0.9949</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr"/>
       <c r="F29" s="5" t="inlineStr"/>
       <c r="G29" s="5" t="inlineStr"/>
       <c r="H29" s="5" t="inlineStr"/>
       <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L29" s="5" t="inlineStr"/>
-      <c r="M29" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N29" s="5" t="inlineStr"/>
-      <c r="O29" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr"/>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O29" s="5" t="inlineStr"/>
       <c r="P29" s="5" t="inlineStr"/>
-      <c r="Q29" s="5" t="inlineStr"/>
-      <c r="R29" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S29" s="5" t="inlineStr"/>
-      <c r="T29" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U29" s="5" t="inlineStr"/>
-      <c r="V29" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W29" s="5" t="inlineStr"/>
+      <c r="Q29" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R29" s="5" t="inlineStr"/>
+      <c r="S29" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T29" s="5" t="inlineStr"/>
+      <c r="U29" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
@@ -7053,56 +6779,53 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>1.0072</v>
+        <v>1.0166</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>1.0166</v>
-      </c>
-      <c r="E30" s="5" t="n">
-        <v>1.0065</v>
-      </c>
+        <v>1.0031</v>
+      </c>
+      <c r="E30" s="5" t="inlineStr"/>
       <c r="F30" s="5" t="inlineStr"/>
       <c r="G30" s="5" t="inlineStr"/>
       <c r="H30" s="5" t="inlineStr"/>
       <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L30" s="5" t="inlineStr"/>
-      <c r="M30" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N30" s="5" t="inlineStr"/>
-      <c r="O30" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr"/>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M30" s="5" t="inlineStr"/>
+      <c r="N30" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O30" s="5" t="inlineStr"/>
       <c r="P30" s="5" t="inlineStr"/>
-      <c r="Q30" s="5" t="inlineStr"/>
-      <c r="R30" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S30" s="5" t="inlineStr"/>
-      <c r="T30" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U30" s="5" t="inlineStr"/>
-      <c r="V30" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W30" s="5" t="inlineStr"/>
+      <c r="Q30" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R30" s="5" t="inlineStr"/>
+      <c r="S30" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T30" s="5" t="inlineStr"/>
+      <c r="U30" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
@@ -7116,60 +6839,57 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>0.8833</v>
+        <v>0.9004</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>0.9004</v>
+        <v>0.8966</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>0.9</v>
+        <v>0.0553</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>0.0553</v>
-      </c>
-      <c r="G31" s="5" t="n">
         <v>0.0678</v>
       </c>
+      <c r="G31" s="5" t="inlineStr"/>
       <c r="H31" s="5" t="inlineStr"/>
       <c r="I31" s="5" t="inlineStr"/>
-      <c r="J31" s="5" t="inlineStr"/>
-      <c r="K31" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L31" s="5" t="inlineStr"/>
-      <c r="M31" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N31" s="5" t="inlineStr"/>
-      <c r="O31" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr"/>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr"/>
+      <c r="N31" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O31" s="5" t="inlineStr"/>
       <c r="P31" s="5" t="inlineStr"/>
-      <c r="Q31" s="5" t="inlineStr"/>
-      <c r="R31" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S31" s="5" t="inlineStr"/>
-      <c r="T31" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U31" s="5" t="inlineStr"/>
-      <c r="V31" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W31" s="5" t="inlineStr"/>
+      <c r="Q31" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R31" s="5" t="inlineStr"/>
+      <c r="S31" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T31" s="5" t="inlineStr"/>
+      <c r="U31" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
@@ -7183,56 +6903,53 @@
         </is>
       </c>
       <c r="C32" s="5" t="n">
-        <v>0.8733</v>
+        <v>0.8959</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>0.8959</v>
-      </c>
-      <c r="E32" s="5" t="n">
-        <v>0.901</v>
-      </c>
+        <v>0.8954</v>
+      </c>
+      <c r="E32" s="5" t="inlineStr"/>
       <c r="F32" s="5" t="inlineStr"/>
       <c r="G32" s="5" t="inlineStr"/>
       <c r="H32" s="5" t="inlineStr"/>
       <c r="I32" s="5" t="inlineStr"/>
-      <c r="J32" s="5" t="inlineStr"/>
-      <c r="K32" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L32" s="5" t="inlineStr"/>
-      <c r="M32" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N32" s="5" t="inlineStr"/>
-      <c r="O32" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr"/>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="inlineStr"/>
+      <c r="N32" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O32" s="5" t="inlineStr"/>
       <c r="P32" s="5" t="inlineStr"/>
-      <c r="Q32" s="5" t="inlineStr"/>
-      <c r="R32" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S32" s="5" t="inlineStr"/>
-      <c r="T32" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U32" s="5" t="inlineStr"/>
-      <c r="V32" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W32" s="5" t="inlineStr"/>
+      <c r="Q32" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R32" s="5" t="inlineStr"/>
+      <c r="S32" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T32" s="5" t="inlineStr"/>
+      <c r="U32" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
@@ -7246,60 +6963,57 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>0.981</v>
+        <v>0.9845</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>0.9845</v>
+        <v>0.9827</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0.9833</v>
+        <v>0.1012</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>0.1012</v>
-      </c>
-      <c r="G33" s="5" t="n">
         <v>0.125</v>
       </c>
+      <c r="G33" s="5" t="inlineStr"/>
       <c r="H33" s="5" t="inlineStr"/>
       <c r="I33" s="5" t="inlineStr"/>
-      <c r="J33" s="5" t="inlineStr"/>
-      <c r="K33" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L33" s="5" t="inlineStr"/>
-      <c r="M33" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N33" s="5" t="inlineStr"/>
-      <c r="O33" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr"/>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr"/>
+      <c r="N33" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O33" s="5" t="inlineStr"/>
       <c r="P33" s="5" t="inlineStr"/>
-      <c r="Q33" s="5" t="inlineStr"/>
-      <c r="R33" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S33" s="5" t="inlineStr"/>
-      <c r="T33" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U33" s="5" t="inlineStr"/>
-      <c r="V33" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W33" s="5" t="inlineStr"/>
+      <c r="Q33" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R33" s="5" t="inlineStr"/>
+      <c r="S33" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T33" s="5" t="inlineStr"/>
+      <c r="U33" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
@@ -7313,60 +7027,57 @@
         </is>
       </c>
       <c r="C34" s="5" t="n">
-        <v>0.981</v>
+        <v>0.9845</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>0.9845</v>
+        <v>0.9827</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0.9833</v>
+        <v>0.0735</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.0735</v>
-      </c>
-      <c r="G34" s="5" t="n">
         <v>0.0467</v>
       </c>
+      <c r="G34" s="5" t="inlineStr"/>
       <c r="H34" s="5" t="inlineStr"/>
       <c r="I34" s="5" t="inlineStr"/>
-      <c r="J34" s="5" t="inlineStr"/>
-      <c r="K34" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L34" s="5" t="inlineStr"/>
-      <c r="M34" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N34" s="5" t="inlineStr"/>
-      <c r="O34" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr"/>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M34" s="5" t="inlineStr"/>
+      <c r="N34" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O34" s="5" t="inlineStr"/>
       <c r="P34" s="5" t="inlineStr"/>
-      <c r="Q34" s="5" t="inlineStr"/>
-      <c r="R34" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S34" s="5" t="inlineStr"/>
-      <c r="T34" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U34" s="5" t="inlineStr"/>
-      <c r="V34" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W34" s="5" t="inlineStr"/>
+      <c r="Q34" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R34" s="5" t="inlineStr"/>
+      <c r="S34" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T34" s="5" t="inlineStr"/>
+      <c r="U34" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
@@ -7380,60 +7091,57 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>0.981</v>
+        <v>0.9845</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>0.9845</v>
+        <v>0.9827</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>0.9833</v>
+        <v>0.0794</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>0.0794</v>
-      </c>
-      <c r="G35" s="5" t="n">
         <v>0.0331</v>
       </c>
+      <c r="G35" s="5" t="inlineStr"/>
       <c r="H35" s="5" t="inlineStr"/>
       <c r="I35" s="5" t="inlineStr"/>
-      <c r="J35" s="5" t="inlineStr"/>
-      <c r="K35" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L35" s="5" t="inlineStr"/>
-      <c r="M35" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N35" s="5" t="inlineStr"/>
-      <c r="O35" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr"/>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr"/>
+      <c r="N35" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O35" s="5" t="inlineStr"/>
       <c r="P35" s="5" t="inlineStr"/>
-      <c r="Q35" s="5" t="inlineStr"/>
-      <c r="R35" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S35" s="5" t="inlineStr"/>
-      <c r="T35" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U35" s="5" t="inlineStr"/>
-      <c r="V35" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W35" s="5" t="inlineStr"/>
+      <c r="Q35" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R35" s="5" t="inlineStr"/>
+      <c r="S35" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T35" s="5" t="inlineStr"/>
+      <c r="U35" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V35" s="5" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
@@ -7447,58 +7155,55 @@
         </is>
       </c>
       <c r="C36" s="5" t="n">
-        <v>0.9475</v>
+        <v>0.9569</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>0.9569</v>
+        <v>0.9556</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>0.9569</v>
-      </c>
-      <c r="F36" s="5" t="n">
         <v>0.1555</v>
       </c>
+      <c r="F36" s="5" t="inlineStr"/>
       <c r="G36" s="5" t="inlineStr"/>
       <c r="H36" s="5" t="inlineStr"/>
       <c r="I36" s="5" t="inlineStr"/>
-      <c r="J36" s="5" t="inlineStr"/>
-      <c r="K36" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L36" s="5" t="inlineStr"/>
-      <c r="M36" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N36" s="5" t="inlineStr"/>
-      <c r="O36" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr"/>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M36" s="5" t="inlineStr"/>
+      <c r="N36" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O36" s="5" t="inlineStr"/>
       <c r="P36" s="5" t="inlineStr"/>
-      <c r="Q36" s="5" t="inlineStr"/>
-      <c r="R36" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S36" s="5" t="inlineStr"/>
-      <c r="T36" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U36" s="5" t="inlineStr"/>
-      <c r="V36" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W36" s="5" t="inlineStr"/>
+      <c r="Q36" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R36" s="5" t="inlineStr"/>
+      <c r="S36" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T36" s="5" t="inlineStr"/>
+      <c r="U36" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
@@ -7511,53 +7216,50 @@
           <t>Wind</t>
         </is>
       </c>
-      <c r="C37" s="5" t="n">
-        <v>0.9993</v>
-      </c>
+      <c r="C37" s="5" t="inlineStr"/>
       <c r="D37" s="5" t="inlineStr"/>
       <c r="E37" s="5" t="inlineStr"/>
       <c r="F37" s="5" t="inlineStr"/>
       <c r="G37" s="5" t="inlineStr"/>
       <c r="H37" s="5" t="inlineStr"/>
       <c r="I37" s="5" t="inlineStr"/>
-      <c r="J37" s="5" t="inlineStr"/>
-      <c r="K37" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L37" s="5" t="inlineStr"/>
-      <c r="M37" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N37" s="5" t="inlineStr"/>
-      <c r="O37" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr"/>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr"/>
+      <c r="N37" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O37" s="5" t="inlineStr"/>
       <c r="P37" s="5" t="inlineStr"/>
-      <c r="Q37" s="5" t="inlineStr"/>
-      <c r="R37" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S37" s="5" t="inlineStr"/>
-      <c r="T37" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U37" s="5" t="inlineStr"/>
-      <c r="V37" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W37" s="5" t="inlineStr"/>
+      <c r="Q37" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R37" s="5" t="inlineStr"/>
+      <c r="S37" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T37" s="5" t="inlineStr"/>
+      <c r="U37" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
@@ -7571,56 +7273,53 @@
         </is>
       </c>
       <c r="C38" s="5" t="n">
-        <v>0.9993</v>
+        <v>1.0018</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>1.0018</v>
-      </c>
-      <c r="E38" s="5" t="n">
-        <v>0.9952</v>
-      </c>
+        <v>0.9949</v>
+      </c>
+      <c r="E38" s="5" t="inlineStr"/>
       <c r="F38" s="5" t="inlineStr"/>
       <c r="G38" s="5" t="inlineStr"/>
       <c r="H38" s="5" t="inlineStr"/>
       <c r="I38" s="5" t="inlineStr"/>
-      <c r="J38" s="5" t="inlineStr"/>
-      <c r="K38" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L38" s="5" t="inlineStr"/>
-      <c r="M38" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N38" s="5" t="inlineStr"/>
-      <c r="O38" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr"/>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M38" s="5" t="inlineStr"/>
+      <c r="N38" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O38" s="5" t="inlineStr"/>
       <c r="P38" s="5" t="inlineStr"/>
-      <c r="Q38" s="5" t="inlineStr"/>
-      <c r="R38" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S38" s="5" t="inlineStr"/>
-      <c r="T38" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U38" s="5" t="inlineStr"/>
-      <c r="V38" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W38" s="5" t="inlineStr"/>
+      <c r="Q38" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R38" s="5" t="inlineStr"/>
+      <c r="S38" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T38" s="5" t="inlineStr"/>
+      <c r="U38" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
@@ -7634,56 +7333,53 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>0.9808</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>0.9834000000000001</v>
-      </c>
-      <c r="E39" s="5" t="n">
-        <v>0.9819</v>
-      </c>
+        <v>0.9815</v>
+      </c>
+      <c r="E39" s="5" t="inlineStr"/>
       <c r="F39" s="5" t="inlineStr"/>
       <c r="G39" s="5" t="inlineStr"/>
       <c r="H39" s="5" t="inlineStr"/>
       <c r="I39" s="5" t="inlineStr"/>
-      <c r="J39" s="5" t="inlineStr"/>
-      <c r="K39" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L39" s="5" t="inlineStr"/>
-      <c r="M39" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N39" s="5" t="inlineStr"/>
-      <c r="O39" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr"/>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr"/>
+      <c r="N39" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O39" s="5" t="inlineStr"/>
       <c r="P39" s="5" t="inlineStr"/>
-      <c r="Q39" s="5" t="inlineStr"/>
-      <c r="R39" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S39" s="5" t="inlineStr"/>
-      <c r="T39" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U39" s="5" t="inlineStr"/>
-      <c r="V39" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W39" s="5" t="inlineStr"/>
+      <c r="Q39" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R39" s="5" t="inlineStr"/>
+      <c r="S39" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T39" s="5" t="inlineStr"/>
+      <c r="U39" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
@@ -7697,56 +7393,53 @@
         </is>
       </c>
       <c r="C40" s="5" t="n">
-        <v>0.9808</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>0.9834000000000001</v>
-      </c>
-      <c r="E40" s="5" t="n">
-        <v>0.9819</v>
-      </c>
+        <v>0.9815</v>
+      </c>
+      <c r="E40" s="5" t="inlineStr"/>
       <c r="F40" s="5" t="inlineStr"/>
       <c r="G40" s="5" t="inlineStr"/>
       <c r="H40" s="5" t="inlineStr"/>
       <c r="I40" s="5" t="inlineStr"/>
-      <c r="J40" s="5" t="inlineStr"/>
-      <c r="K40" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L40" s="5" t="inlineStr"/>
-      <c r="M40" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N40" s="5" t="inlineStr"/>
-      <c r="O40" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="inlineStr"/>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M40" s="5" t="inlineStr"/>
+      <c r="N40" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O40" s="5" t="inlineStr"/>
       <c r="P40" s="5" t="inlineStr"/>
-      <c r="Q40" s="5" t="inlineStr"/>
-      <c r="R40" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S40" s="5" t="inlineStr"/>
-      <c r="T40" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U40" s="5" t="inlineStr"/>
-      <c r="V40" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W40" s="5" t="inlineStr"/>
+      <c r="Q40" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R40" s="5" t="inlineStr"/>
+      <c r="S40" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T40" s="5" t="inlineStr"/>
+      <c r="U40" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
@@ -7760,56 +7453,53 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>0.9808</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>0.9834000000000001</v>
-      </c>
-      <c r="E41" s="5" t="n">
-        <v>0.9819</v>
-      </c>
+        <v>0.9815</v>
+      </c>
+      <c r="E41" s="5" t="inlineStr"/>
       <c r="F41" s="5" t="inlineStr"/>
       <c r="G41" s="5" t="inlineStr"/>
       <c r="H41" s="5" t="inlineStr"/>
       <c r="I41" s="5" t="inlineStr"/>
-      <c r="J41" s="5" t="inlineStr"/>
-      <c r="K41" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L41" s="5" t="inlineStr"/>
-      <c r="M41" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N41" s="5" t="inlineStr"/>
-      <c r="O41" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr"/>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr"/>
+      <c r="N41" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O41" s="5" t="inlineStr"/>
       <c r="P41" s="5" t="inlineStr"/>
-      <c r="Q41" s="5" t="inlineStr"/>
-      <c r="R41" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S41" s="5" t="inlineStr"/>
-      <c r="T41" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U41" s="5" t="inlineStr"/>
-      <c r="V41" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W41" s="5" t="inlineStr"/>
+      <c r="Q41" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R41" s="5" t="inlineStr"/>
+      <c r="S41" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T41" s="5" t="inlineStr"/>
+      <c r="U41" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V41" s="5" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
@@ -7822,55 +7512,54 @@
           <t>Wind</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr"/>
+      <c r="C42" s="5" t="n">
+        <v>0.9837</v>
+      </c>
       <c r="D42" s="5" t="n">
-        <v>0.9837</v>
-      </c>
-      <c r="E42" s="5" t="n">
-        <v>0.9824000000000001</v>
-      </c>
+        <v>0.9823</v>
+      </c>
+      <c r="E42" s="5" t="inlineStr"/>
       <c r="F42" s="5" t="inlineStr"/>
       <c r="G42" s="5" t="inlineStr"/>
       <c r="H42" s="5" t="inlineStr"/>
       <c r="I42" s="5" t="inlineStr"/>
-      <c r="J42" s="5" t="inlineStr"/>
-      <c r="K42" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L42" s="5" t="inlineStr"/>
-      <c r="M42" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N42" s="5" t="inlineStr"/>
-      <c r="O42" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="inlineStr"/>
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M42" s="5" t="inlineStr"/>
+      <c r="N42" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O42" s="5" t="inlineStr"/>
       <c r="P42" s="5" t="inlineStr"/>
-      <c r="Q42" s="5" t="inlineStr"/>
-      <c r="R42" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S42" s="5" t="inlineStr"/>
-      <c r="T42" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U42" s="5" t="inlineStr"/>
-      <c r="V42" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W42" s="5" t="inlineStr"/>
+      <c r="Q42" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R42" s="5" t="inlineStr"/>
+      <c r="S42" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T42" s="5" t="inlineStr"/>
+      <c r="U42" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
@@ -7883,55 +7572,54 @@
           <t>Wind</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr"/>
+      <c r="C43" s="5" t="n">
+        <v>0.9837</v>
+      </c>
       <c r="D43" s="5" t="n">
-        <v>0.9837</v>
-      </c>
-      <c r="E43" s="5" t="n">
-        <v>0.9824000000000001</v>
-      </c>
+        <v>0.9823</v>
+      </c>
+      <c r="E43" s="5" t="inlineStr"/>
       <c r="F43" s="5" t="inlineStr"/>
       <c r="G43" s="5" t="inlineStr"/>
       <c r="H43" s="5" t="inlineStr"/>
       <c r="I43" s="5" t="inlineStr"/>
-      <c r="J43" s="5" t="inlineStr"/>
-      <c r="K43" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L43" s="5" t="inlineStr"/>
-      <c r="M43" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N43" s="5" t="inlineStr"/>
-      <c r="O43" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr"/>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr"/>
+      <c r="N43" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O43" s="5" t="inlineStr"/>
       <c r="P43" s="5" t="inlineStr"/>
-      <c r="Q43" s="5" t="inlineStr"/>
-      <c r="R43" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S43" s="5" t="inlineStr"/>
-      <c r="T43" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U43" s="5" t="inlineStr"/>
-      <c r="V43" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W43" s="5" t="inlineStr"/>
+      <c r="Q43" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R43" s="5" t="inlineStr"/>
+      <c r="S43" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T43" s="5" t="inlineStr"/>
+      <c r="U43" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
@@ -7945,58 +7633,55 @@
         </is>
       </c>
       <c r="C44" s="5" t="n">
-        <v>0.9809</v>
+        <v>0.9865</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>0.9865</v>
-      </c>
-      <c r="E44" s="5" t="n">
-        <v>0.9829</v>
-      </c>
-      <c r="F44" s="5" t="inlineStr"/>
-      <c r="G44" s="5" t="n">
+        <v>0.9822</v>
+      </c>
+      <c r="E44" s="5" t="inlineStr"/>
+      <c r="F44" s="5" t="n">
         <v>0.1766</v>
       </c>
+      <c r="G44" s="5" t="inlineStr"/>
       <c r="H44" s="5" t="inlineStr"/>
       <c r="I44" s="5" t="inlineStr"/>
-      <c r="J44" s="5" t="inlineStr"/>
-      <c r="K44" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L44" s="5" t="inlineStr"/>
-      <c r="M44" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N44" s="5" t="inlineStr"/>
-      <c r="O44" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="inlineStr"/>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M44" s="5" t="inlineStr"/>
+      <c r="N44" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O44" s="5" t="inlineStr"/>
       <c r="P44" s="5" t="inlineStr"/>
-      <c r="Q44" s="5" t="inlineStr"/>
-      <c r="R44" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S44" s="5" t="inlineStr"/>
-      <c r="T44" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U44" s="5" t="inlineStr"/>
-      <c r="V44" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W44" s="5" t="inlineStr"/>
+      <c r="Q44" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R44" s="5" t="inlineStr"/>
+      <c r="S44" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T44" s="5" t="inlineStr"/>
+      <c r="U44" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V44" s="5" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
@@ -8010,56 +7695,53 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>0.9718</v>
+        <v>0.9825</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>0.9825</v>
-      </c>
-      <c r="E45" s="5" t="n">
-        <v>0.9801</v>
-      </c>
+        <v>0.9791</v>
+      </c>
+      <c r="E45" s="5" t="inlineStr"/>
       <c r="F45" s="5" t="inlineStr"/>
       <c r="G45" s="5" t="inlineStr"/>
       <c r="H45" s="5" t="inlineStr"/>
       <c r="I45" s="5" t="inlineStr"/>
-      <c r="J45" s="5" t="inlineStr"/>
-      <c r="K45" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L45" s="5" t="inlineStr"/>
-      <c r="M45" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N45" s="5" t="inlineStr"/>
-      <c r="O45" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr"/>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M45" s="5" t="inlineStr"/>
+      <c r="N45" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O45" s="5" t="inlineStr"/>
       <c r="P45" s="5" t="inlineStr"/>
-      <c r="Q45" s="5" t="inlineStr"/>
-      <c r="R45" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S45" s="5" t="inlineStr"/>
-      <c r="T45" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U45" s="5" t="inlineStr"/>
-      <c r="V45" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W45" s="5" t="inlineStr"/>
+      <c r="Q45" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R45" s="5" t="inlineStr"/>
+      <c r="S45" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T45" s="5" t="inlineStr"/>
+      <c r="U45" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V45" s="5" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
@@ -8073,60 +7755,57 @@
         </is>
       </c>
       <c r="C46" s="5" t="n">
-        <v>0.8733</v>
+        <v>0.8959</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>0.8959</v>
+        <v>0.8954</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>0.901</v>
+        <v>0.1062</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0.1062</v>
-      </c>
-      <c r="G46" s="5" t="n">
         <v>0.173</v>
       </c>
+      <c r="G46" s="5" t="inlineStr"/>
       <c r="H46" s="5" t="inlineStr"/>
       <c r="I46" s="5" t="inlineStr"/>
-      <c r="J46" s="5" t="inlineStr"/>
-      <c r="K46" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L46" s="5" t="inlineStr"/>
-      <c r="M46" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N46" s="5" t="inlineStr"/>
-      <c r="O46" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="inlineStr"/>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M46" s="5" t="inlineStr"/>
+      <c r="N46" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O46" s="5" t="inlineStr"/>
       <c r="P46" s="5" t="inlineStr"/>
-      <c r="Q46" s="5" t="inlineStr"/>
-      <c r="R46" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S46" s="5" t="inlineStr"/>
-      <c r="T46" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U46" s="5" t="inlineStr"/>
-      <c r="V46" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W46" s="5" t="inlineStr"/>
+      <c r="Q46" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R46" s="5" t="inlineStr"/>
+      <c r="S46" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T46" s="5" t="inlineStr"/>
+      <c r="U46" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
@@ -8140,60 +7819,57 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>0.9781</v>
+        <v>0.9829</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>0.9829</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0.983</v>
+        <v>0.074</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>0.074</v>
-      </c>
-      <c r="G47" s="5" t="n">
         <v>0.1339</v>
       </c>
+      <c r="G47" s="5" t="inlineStr"/>
       <c r="H47" s="5" t="inlineStr"/>
       <c r="I47" s="5" t="inlineStr"/>
-      <c r="J47" s="5" t="inlineStr"/>
-      <c r="K47" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L47" s="5" t="inlineStr"/>
-      <c r="M47" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N47" s="5" t="inlineStr"/>
-      <c r="O47" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr"/>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M47" s="5" t="inlineStr"/>
+      <c r="N47" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O47" s="5" t="inlineStr"/>
       <c r="P47" s="5" t="inlineStr"/>
-      <c r="Q47" s="5" t="inlineStr"/>
-      <c r="R47" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S47" s="5" t="inlineStr"/>
-      <c r="T47" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U47" s="5" t="inlineStr"/>
-      <c r="V47" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W47" s="5" t="inlineStr"/>
+      <c r="Q47" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R47" s="5" t="inlineStr"/>
+      <c r="S47" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T47" s="5" t="inlineStr"/>
+      <c r="U47" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V47" s="5" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
@@ -8207,56 +7883,53 @@
         </is>
       </c>
       <c r="C48" s="5" t="n">
-        <v>0.9718</v>
+        <v>0.9825</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>0.9825</v>
-      </c>
-      <c r="E48" s="5" t="n">
-        <v>0.9801</v>
-      </c>
+        <v>0.9791</v>
+      </c>
+      <c r="E48" s="5" t="inlineStr"/>
       <c r="F48" s="5" t="inlineStr"/>
       <c r="G48" s="5" t="inlineStr"/>
       <c r="H48" s="5" t="inlineStr"/>
       <c r="I48" s="5" t="inlineStr"/>
-      <c r="J48" s="5" t="inlineStr"/>
-      <c r="K48" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L48" s="5" t="inlineStr"/>
-      <c r="M48" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N48" s="5" t="inlineStr"/>
-      <c r="O48" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="inlineStr"/>
+      <c r="L48" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M48" s="5" t="inlineStr"/>
+      <c r="N48" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O48" s="5" t="inlineStr"/>
       <c r="P48" s="5" t="inlineStr"/>
-      <c r="Q48" s="5" t="inlineStr"/>
-      <c r="R48" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S48" s="5" t="inlineStr"/>
-      <c r="T48" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U48" s="5" t="inlineStr"/>
-      <c r="V48" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W48" s="5" t="inlineStr"/>
+      <c r="Q48" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R48" s="5" t="inlineStr"/>
+      <c r="S48" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T48" s="5" t="inlineStr"/>
+      <c r="U48" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V48" s="5" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
@@ -8270,60 +7943,57 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>0.9475</v>
+        <v>0.9569</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>0.9569</v>
+        <v>0.9556</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>0.9569</v>
+        <v>0.0878</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>0.0878</v>
-      </c>
-      <c r="G49" s="5" t="n">
         <v>0.0847</v>
       </c>
+      <c r="G49" s="5" t="inlineStr"/>
       <c r="H49" s="5" t="inlineStr"/>
       <c r="I49" s="5" t="inlineStr"/>
-      <c r="J49" s="5" t="inlineStr"/>
-      <c r="K49" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L49" s="5" t="inlineStr"/>
-      <c r="M49" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N49" s="5" t="inlineStr"/>
-      <c r="O49" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr"/>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M49" s="5" t="inlineStr"/>
+      <c r="N49" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O49" s="5" t="inlineStr"/>
       <c r="P49" s="5" t="inlineStr"/>
-      <c r="Q49" s="5" t="inlineStr"/>
-      <c r="R49" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S49" s="5" t="inlineStr"/>
-      <c r="T49" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U49" s="5" t="inlineStr"/>
-      <c r="V49" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W49" s="5" t="inlineStr"/>
+      <c r="Q49" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R49" s="5" t="inlineStr"/>
+      <c r="S49" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T49" s="5" t="inlineStr"/>
+      <c r="U49" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
@@ -8337,60 +8007,57 @@
         </is>
       </c>
       <c r="C50" s="5" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.9525</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>0.9525</v>
+        <v>0.9507</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>0.9519</v>
+        <v>0.1264</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>0.1264</v>
-      </c>
-      <c r="G50" s="5" t="n">
         <v>0.09810000000000001</v>
       </c>
+      <c r="G50" s="5" t="inlineStr"/>
       <c r="H50" s="5" t="inlineStr"/>
       <c r="I50" s="5" t="inlineStr"/>
-      <c r="J50" s="5" t="inlineStr"/>
-      <c r="K50" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L50" s="5" t="inlineStr"/>
-      <c r="M50" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N50" s="5" t="inlineStr"/>
-      <c r="O50" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="inlineStr"/>
+      <c r="L50" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M50" s="5" t="inlineStr"/>
+      <c r="N50" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O50" s="5" t="inlineStr"/>
       <c r="P50" s="5" t="inlineStr"/>
-      <c r="Q50" s="5" t="inlineStr"/>
-      <c r="R50" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S50" s="5" t="inlineStr"/>
-      <c r="T50" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U50" s="5" t="inlineStr"/>
-      <c r="V50" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W50" s="5" t="inlineStr"/>
+      <c r="Q50" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R50" s="5" t="inlineStr"/>
+      <c r="S50" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T50" s="5" t="inlineStr"/>
+      <c r="U50" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V50" s="5" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
@@ -8404,56 +8071,53 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>0.9993</v>
+        <v>1.0018</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>1.0018</v>
-      </c>
-      <c r="E51" s="5" t="n">
-        <v>0.9952</v>
-      </c>
+        <v>0.9949</v>
+      </c>
+      <c r="E51" s="5" t="inlineStr"/>
       <c r="F51" s="5" t="inlineStr"/>
       <c r="G51" s="5" t="inlineStr"/>
       <c r="H51" s="5" t="inlineStr"/>
       <c r="I51" s="5" t="inlineStr"/>
-      <c r="J51" s="5" t="inlineStr"/>
-      <c r="K51" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L51" s="5" t="inlineStr"/>
-      <c r="M51" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N51" s="5" t="inlineStr"/>
-      <c r="O51" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr"/>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M51" s="5" t="inlineStr"/>
+      <c r="N51" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O51" s="5" t="inlineStr"/>
       <c r="P51" s="5" t="inlineStr"/>
-      <c r="Q51" s="5" t="inlineStr"/>
-      <c r="R51" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S51" s="5" t="inlineStr"/>
-      <c r="T51" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U51" s="5" t="inlineStr"/>
-      <c r="V51" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W51" s="5" t="inlineStr"/>
+      <c r="Q51" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R51" s="5" t="inlineStr"/>
+      <c r="S51" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T51" s="5" t="inlineStr"/>
+      <c r="U51" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V51" s="5" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
@@ -8467,60 +8131,57 @@
         </is>
       </c>
       <c r="C52" s="5" t="n">
-        <v>0.9855</v>
+        <v>0.9879</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>0.9879</v>
+        <v>0.989</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0.9893999999999999</v>
+        <v>0.05</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G52" s="5" t="n">
         <v>0.0498</v>
       </c>
+      <c r="G52" s="5" t="inlineStr"/>
       <c r="H52" s="5" t="inlineStr"/>
       <c r="I52" s="5" t="inlineStr"/>
-      <c r="J52" s="5" t="inlineStr"/>
-      <c r="K52" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L52" s="5" t="inlineStr"/>
-      <c r="M52" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N52" s="5" t="inlineStr"/>
-      <c r="O52" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="inlineStr"/>
+      <c r="L52" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M52" s="5" t="inlineStr"/>
+      <c r="N52" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O52" s="5" t="inlineStr"/>
       <c r="P52" s="5" t="inlineStr"/>
-      <c r="Q52" s="5" t="inlineStr"/>
-      <c r="R52" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S52" s="5" t="inlineStr"/>
-      <c r="T52" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U52" s="5" t="inlineStr"/>
-      <c r="V52" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W52" s="5" t="inlineStr"/>
+      <c r="Q52" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R52" s="5" t="inlineStr"/>
+      <c r="S52" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T52" s="5" t="inlineStr"/>
+      <c r="U52" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V52" s="5" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
@@ -8534,60 +8195,57 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>0.9475</v>
+        <v>0.9569</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>0.9569</v>
+        <v>0.9556</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>0.9569</v>
+        <v>0.1784</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>0.1784</v>
-      </c>
-      <c r="G53" s="5" t="n">
         <v>0.2533</v>
       </c>
+      <c r="G53" s="5" t="inlineStr"/>
       <c r="H53" s="5" t="inlineStr"/>
       <c r="I53" s="5" t="inlineStr"/>
-      <c r="J53" s="5" t="inlineStr"/>
-      <c r="K53" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L53" s="5" t="inlineStr"/>
-      <c r="M53" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N53" s="5" t="inlineStr"/>
-      <c r="O53" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr"/>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M53" s="5" t="inlineStr"/>
+      <c r="N53" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O53" s="5" t="inlineStr"/>
       <c r="P53" s="5" t="inlineStr"/>
-      <c r="Q53" s="5" t="inlineStr"/>
-      <c r="R53" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S53" s="5" t="inlineStr"/>
-      <c r="T53" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U53" s="5" t="inlineStr"/>
-      <c r="V53" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W53" s="5" t="inlineStr"/>
+      <c r="Q53" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R53" s="5" t="inlineStr"/>
+      <c r="S53" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T53" s="5" t="inlineStr"/>
+      <c r="U53" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V53" s="5" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
@@ -8601,60 +8259,57 @@
         </is>
       </c>
       <c r="C54" s="5" t="n">
-        <v>0.8619</v>
+        <v>0.8817</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>0.8817</v>
+        <v>0.8824</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>0.8881</v>
+        <v>0.1857</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>0.1857</v>
-      </c>
-      <c r="G54" s="5" t="n">
         <v>0.2838</v>
       </c>
+      <c r="G54" s="5" t="inlineStr"/>
       <c r="H54" s="5" t="inlineStr"/>
       <c r="I54" s="5" t="inlineStr"/>
-      <c r="J54" s="5" t="inlineStr"/>
-      <c r="K54" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L54" s="5" t="inlineStr"/>
-      <c r="M54" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N54" s="5" t="inlineStr"/>
-      <c r="O54" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="inlineStr"/>
+      <c r="L54" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M54" s="5" t="inlineStr"/>
+      <c r="N54" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O54" s="5" t="inlineStr"/>
       <c r="P54" s="5" t="inlineStr"/>
-      <c r="Q54" s="5" t="inlineStr"/>
-      <c r="R54" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S54" s="5" t="inlineStr"/>
-      <c r="T54" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U54" s="5" t="inlineStr"/>
-      <c r="V54" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W54" s="5" t="inlineStr"/>
+      <c r="Q54" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R54" s="5" t="inlineStr"/>
+      <c r="S54" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T54" s="5" t="inlineStr"/>
+      <c r="U54" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V54" s="5" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
@@ -8668,60 +8323,57 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>0.8619</v>
+        <v>0.8817</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>0.8817</v>
+        <v>0.8824</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>0.8881</v>
+        <v>0.1619</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>0.1619</v>
-      </c>
-      <c r="G55" s="5" t="n">
         <v>0.2355</v>
       </c>
+      <c r="G55" s="5" t="inlineStr"/>
       <c r="H55" s="5" t="inlineStr"/>
       <c r="I55" s="5" t="inlineStr"/>
-      <c r="J55" s="5" t="inlineStr"/>
-      <c r="K55" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L55" s="5" t="inlineStr"/>
-      <c r="M55" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N55" s="5" t="inlineStr"/>
-      <c r="O55" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="inlineStr"/>
+      <c r="L55" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M55" s="5" t="inlineStr"/>
+      <c r="N55" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O55" s="5" t="inlineStr"/>
       <c r="P55" s="5" t="inlineStr"/>
-      <c r="Q55" s="5" t="inlineStr"/>
-      <c r="R55" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S55" s="5" t="inlineStr"/>
-      <c r="T55" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U55" s="5" t="inlineStr"/>
-      <c r="V55" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W55" s="5" t="inlineStr"/>
+      <c r="Q55" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R55" s="5" t="inlineStr"/>
+      <c r="S55" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T55" s="5" t="inlineStr"/>
+      <c r="U55" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V55" s="5" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
@@ -8735,60 +8387,57 @@
         </is>
       </c>
       <c r="C56" s="5" t="n">
-        <v>0.9993</v>
+        <v>1.0018</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>1.0018</v>
+        <v>0.9949</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>0.9952</v>
+        <v>0.0583</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>0.0583</v>
-      </c>
-      <c r="G56" s="5" t="n">
         <v>0.077</v>
       </c>
+      <c r="G56" s="5" t="inlineStr"/>
       <c r="H56" s="5" t="inlineStr"/>
       <c r="I56" s="5" t="inlineStr"/>
-      <c r="J56" s="5" t="inlineStr"/>
-      <c r="K56" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L56" s="5" t="inlineStr"/>
-      <c r="M56" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N56" s="5" t="inlineStr"/>
-      <c r="O56" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="inlineStr"/>
+      <c r="L56" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M56" s="5" t="inlineStr"/>
+      <c r="N56" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O56" s="5" t="inlineStr"/>
       <c r="P56" s="5" t="inlineStr"/>
-      <c r="Q56" s="5" t="inlineStr"/>
-      <c r="R56" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S56" s="5" t="inlineStr"/>
-      <c r="T56" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U56" s="5" t="inlineStr"/>
-      <c r="V56" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W56" s="5" t="inlineStr"/>
+      <c r="Q56" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R56" s="5" t="inlineStr"/>
+      <c r="S56" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T56" s="5" t="inlineStr"/>
+      <c r="U56" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V56" s="5" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
@@ -8802,58 +8451,55 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>0.9787</v>
+        <v>0.9875</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>0.9875</v>
-      </c>
-      <c r="E57" s="5" t="n">
-        <v>0.9837</v>
-      </c>
-      <c r="F57" s="5" t="inlineStr"/>
-      <c r="G57" s="5" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="E57" s="5" t="inlineStr"/>
+      <c r="F57" s="5" t="n">
         <v>0.0931</v>
       </c>
+      <c r="G57" s="5" t="inlineStr"/>
       <c r="H57" s="5" t="inlineStr"/>
       <c r="I57" s="5" t="inlineStr"/>
-      <c r="J57" s="5" t="inlineStr"/>
-      <c r="K57" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L57" s="5" t="inlineStr"/>
-      <c r="M57" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N57" s="5" t="inlineStr"/>
-      <c r="O57" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr"/>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M57" s="5" t="inlineStr"/>
+      <c r="N57" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O57" s="5" t="inlineStr"/>
       <c r="P57" s="5" t="inlineStr"/>
-      <c r="Q57" s="5" t="inlineStr"/>
-      <c r="R57" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S57" s="5" t="inlineStr"/>
-      <c r="T57" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U57" s="5" t="inlineStr"/>
-      <c r="V57" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W57" s="5" t="inlineStr"/>
+      <c r="Q57" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R57" s="5" t="inlineStr"/>
+      <c r="S57" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T57" s="5" t="inlineStr"/>
+      <c r="U57" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V57" s="5" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
@@ -8867,60 +8513,57 @@
         </is>
       </c>
       <c r="C58" s="5" t="n">
-        <v>0.9388</v>
+        <v>0.9519</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>0.9519</v>
+        <v>0.9499</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>0.951</v>
+        <v>0.1607</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>0.1607</v>
-      </c>
-      <c r="G58" s="5" t="n">
         <v>0.2295</v>
       </c>
+      <c r="G58" s="5" t="inlineStr"/>
       <c r="H58" s="5" t="inlineStr"/>
       <c r="I58" s="5" t="inlineStr"/>
-      <c r="J58" s="5" t="inlineStr"/>
-      <c r="K58" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L58" s="5" t="inlineStr"/>
-      <c r="M58" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N58" s="5" t="inlineStr"/>
-      <c r="O58" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="inlineStr"/>
+      <c r="L58" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M58" s="5" t="inlineStr"/>
+      <c r="N58" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O58" s="5" t="inlineStr"/>
       <c r="P58" s="5" t="inlineStr"/>
-      <c r="Q58" s="5" t="inlineStr"/>
-      <c r="R58" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S58" s="5" t="inlineStr"/>
-      <c r="T58" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U58" s="5" t="inlineStr"/>
-      <c r="V58" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W58" s="5" t="inlineStr"/>
+      <c r="Q58" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R58" s="5" t="inlineStr"/>
+      <c r="S58" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T58" s="5" t="inlineStr"/>
+      <c r="U58" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V58" s="5" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
@@ -8934,60 +8577,57 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>0.9812</v>
+        <v>0.9845</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>0.9845</v>
+        <v>0.9827</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>0.9832</v>
+        <v>0.0653</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>0.0653</v>
-      </c>
-      <c r="G59" s="5" t="n">
         <v>0.0216</v>
       </c>
+      <c r="G59" s="5" t="inlineStr"/>
       <c r="H59" s="5" t="inlineStr"/>
       <c r="I59" s="5" t="inlineStr"/>
-      <c r="J59" s="5" t="inlineStr"/>
-      <c r="K59" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L59" s="5" t="inlineStr"/>
-      <c r="M59" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N59" s="5" t="inlineStr"/>
-      <c r="O59" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr"/>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M59" s="5" t="inlineStr"/>
+      <c r="N59" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O59" s="5" t="inlineStr"/>
       <c r="P59" s="5" t="inlineStr"/>
-      <c r="Q59" s="5" t="inlineStr"/>
-      <c r="R59" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S59" s="5" t="inlineStr"/>
-      <c r="T59" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U59" s="5" t="inlineStr"/>
-      <c r="V59" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W59" s="5" t="inlineStr"/>
+      <c r="Q59" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R59" s="5" t="inlineStr"/>
+      <c r="S59" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T59" s="5" t="inlineStr"/>
+      <c r="U59" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V59" s="5" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
@@ -9001,56 +8641,53 @@
         </is>
       </c>
       <c r="C60" s="5" t="n">
-        <v>0.9993</v>
+        <v>1.0018</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>1.0018</v>
-      </c>
-      <c r="E60" s="5" t="n">
-        <v>0.9952</v>
-      </c>
+        <v>0.9949</v>
+      </c>
+      <c r="E60" s="5" t="inlineStr"/>
       <c r="F60" s="5" t="inlineStr"/>
       <c r="G60" s="5" t="inlineStr"/>
       <c r="H60" s="5" t="inlineStr"/>
       <c r="I60" s="5" t="inlineStr"/>
-      <c r="J60" s="5" t="inlineStr"/>
-      <c r="K60" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L60" s="5" t="inlineStr"/>
-      <c r="M60" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N60" s="5" t="inlineStr"/>
-      <c r="O60" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="inlineStr"/>
+      <c r="L60" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M60" s="5" t="inlineStr"/>
+      <c r="N60" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O60" s="5" t="inlineStr"/>
       <c r="P60" s="5" t="inlineStr"/>
-      <c r="Q60" s="5" t="inlineStr"/>
-      <c r="R60" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S60" s="5" t="inlineStr"/>
-      <c r="T60" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U60" s="5" t="inlineStr"/>
-      <c r="V60" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W60" s="5" t="inlineStr"/>
+      <c r="Q60" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R60" s="5" t="inlineStr"/>
+      <c r="S60" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T60" s="5" t="inlineStr"/>
+      <c r="U60" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V60" s="5" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
@@ -9064,56 +8701,53 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>0.9848</v>
+        <v>0.9862</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>0.9862</v>
-      </c>
-      <c r="E61" s="5" t="n">
-        <v>0.9913999999999999</v>
-      </c>
+        <v>0.992</v>
+      </c>
+      <c r="E61" s="5" t="inlineStr"/>
       <c r="F61" s="5" t="inlineStr"/>
       <c r="G61" s="5" t="inlineStr"/>
       <c r="H61" s="5" t="inlineStr"/>
       <c r="I61" s="5" t="inlineStr"/>
-      <c r="J61" s="5" t="inlineStr"/>
-      <c r="K61" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L61" s="5" t="inlineStr"/>
-      <c r="M61" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N61" s="5" t="inlineStr"/>
-      <c r="O61" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="inlineStr"/>
+      <c r="L61" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M61" s="5" t="inlineStr"/>
+      <c r="N61" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O61" s="5" t="inlineStr"/>
       <c r="P61" s="5" t="inlineStr"/>
-      <c r="Q61" s="5" t="inlineStr"/>
-      <c r="R61" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S61" s="5" t="inlineStr"/>
-      <c r="T61" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U61" s="5" t="inlineStr"/>
-      <c r="V61" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W61" s="5" t="inlineStr"/>
+      <c r="Q61" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R61" s="5" t="inlineStr"/>
+      <c r="S61" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T61" s="5" t="inlineStr"/>
+      <c r="U61" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V61" s="5" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
@@ -9127,56 +8761,53 @@
         </is>
       </c>
       <c r="C62" s="5" t="n">
-        <v>0.9149</v>
+        <v>0.9329</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>0.9329</v>
-      </c>
-      <c r="E62" s="5" t="n">
-        <v>0.9317</v>
-      </c>
+        <v>0.9298999999999999</v>
+      </c>
+      <c r="E62" s="5" t="inlineStr"/>
       <c r="F62" s="5" t="inlineStr"/>
       <c r="G62" s="5" t="inlineStr"/>
       <c r="H62" s="5" t="inlineStr"/>
       <c r="I62" s="5" t="inlineStr"/>
-      <c r="J62" s="5" t="inlineStr"/>
-      <c r="K62" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L62" s="5" t="inlineStr"/>
-      <c r="M62" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N62" s="5" t="inlineStr"/>
-      <c r="O62" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="inlineStr"/>
+      <c r="L62" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M62" s="5" t="inlineStr"/>
+      <c r="N62" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O62" s="5" t="inlineStr"/>
       <c r="P62" s="5" t="inlineStr"/>
-      <c r="Q62" s="5" t="inlineStr"/>
-      <c r="R62" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S62" s="5" t="inlineStr"/>
-      <c r="T62" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U62" s="5" t="inlineStr"/>
-      <c r="V62" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W62" s="5" t="inlineStr"/>
+      <c r="Q62" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R62" s="5" t="inlineStr"/>
+      <c r="S62" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T62" s="5" t="inlineStr"/>
+      <c r="U62" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V62" s="5" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
@@ -9190,56 +8821,53 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>0.9848</v>
+        <v>0.9862</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>0.9862</v>
-      </c>
-      <c r="E63" s="5" t="n">
-        <v>0.9913999999999999</v>
-      </c>
+        <v>0.992</v>
+      </c>
+      <c r="E63" s="5" t="inlineStr"/>
       <c r="F63" s="5" t="inlineStr"/>
       <c r="G63" s="5" t="inlineStr"/>
       <c r="H63" s="5" t="inlineStr"/>
       <c r="I63" s="5" t="inlineStr"/>
-      <c r="J63" s="5" t="inlineStr"/>
-      <c r="K63" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L63" s="5" t="inlineStr"/>
-      <c r="M63" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N63" s="5" t="inlineStr"/>
-      <c r="O63" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr"/>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M63" s="5" t="inlineStr"/>
+      <c r="N63" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O63" s="5" t="inlineStr"/>
       <c r="P63" s="5" t="inlineStr"/>
-      <c r="Q63" s="5" t="inlineStr"/>
-      <c r="R63" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S63" s="5" t="inlineStr"/>
-      <c r="T63" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U63" s="5" t="inlineStr"/>
-      <c r="V63" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W63" s="5" t="inlineStr"/>
+      <c r="Q63" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R63" s="5" t="inlineStr"/>
+      <c r="S63" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T63" s="5" t="inlineStr"/>
+      <c r="U63" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V63" s="5" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
@@ -9253,56 +8881,53 @@
         </is>
       </c>
       <c r="C64" s="5" t="n">
-        <v>0.9718</v>
+        <v>0.9825</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>0.9825</v>
-      </c>
-      <c r="E64" s="5" t="n">
-        <v>0.9801</v>
-      </c>
+        <v>0.9791</v>
+      </c>
+      <c r="E64" s="5" t="inlineStr"/>
       <c r="F64" s="5" t="inlineStr"/>
       <c r="G64" s="5" t="inlineStr"/>
       <c r="H64" s="5" t="inlineStr"/>
       <c r="I64" s="5" t="inlineStr"/>
-      <c r="J64" s="5" t="inlineStr"/>
-      <c r="K64" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L64" s="5" t="inlineStr"/>
-      <c r="M64" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N64" s="5" t="inlineStr"/>
-      <c r="O64" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="inlineStr"/>
+      <c r="L64" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M64" s="5" t="inlineStr"/>
+      <c r="N64" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O64" s="5" t="inlineStr"/>
       <c r="P64" s="5" t="inlineStr"/>
-      <c r="Q64" s="5" t="inlineStr"/>
-      <c r="R64" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S64" s="5" t="inlineStr"/>
-      <c r="T64" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U64" s="5" t="inlineStr"/>
-      <c r="V64" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W64" s="5" t="inlineStr"/>
+      <c r="Q64" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R64" s="5" t="inlineStr"/>
+      <c r="S64" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T64" s="5" t="inlineStr"/>
+      <c r="U64" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V64" s="5" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
@@ -9316,56 +8941,53 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>0.9993</v>
+        <v>1.0018</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>1.0018</v>
-      </c>
-      <c r="E65" s="5" t="n">
-        <v>0.9952</v>
-      </c>
+        <v>0.9949</v>
+      </c>
+      <c r="E65" s="5" t="inlineStr"/>
       <c r="F65" s="5" t="inlineStr"/>
       <c r="G65" s="5" t="inlineStr"/>
       <c r="H65" s="5" t="inlineStr"/>
       <c r="I65" s="5" t="inlineStr"/>
-      <c r="J65" s="5" t="inlineStr"/>
-      <c r="K65" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L65" s="5" t="inlineStr"/>
-      <c r="M65" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N65" s="5" t="inlineStr"/>
-      <c r="O65" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="inlineStr"/>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M65" s="5" t="inlineStr"/>
+      <c r="N65" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O65" s="5" t="inlineStr"/>
       <c r="P65" s="5" t="inlineStr"/>
-      <c r="Q65" s="5" t="inlineStr"/>
-      <c r="R65" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S65" s="5" t="inlineStr"/>
-      <c r="T65" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U65" s="5" t="inlineStr"/>
-      <c r="V65" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W65" s="5" t="inlineStr"/>
+      <c r="Q65" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R65" s="5" t="inlineStr"/>
+      <c r="S65" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T65" s="5" t="inlineStr"/>
+      <c r="U65" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V65" s="5" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
@@ -9379,56 +9001,53 @@
         </is>
       </c>
       <c r="C66" s="5" t="n">
-        <v>1.0072</v>
+        <v>1.0166</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>1.0166</v>
-      </c>
-      <c r="E66" s="5" t="n">
-        <v>1.0065</v>
-      </c>
+        <v>1.0031</v>
+      </c>
+      <c r="E66" s="5" t="inlineStr"/>
       <c r="F66" s="5" t="inlineStr"/>
       <c r="G66" s="5" t="inlineStr"/>
       <c r="H66" s="5" t="inlineStr"/>
       <c r="I66" s="5" t="inlineStr"/>
-      <c r="J66" s="5" t="inlineStr"/>
-      <c r="K66" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L66" s="5" t="inlineStr"/>
-      <c r="M66" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N66" s="5" t="inlineStr"/>
-      <c r="O66" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="inlineStr"/>
+      <c r="L66" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M66" s="5" t="inlineStr"/>
+      <c r="N66" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O66" s="5" t="inlineStr"/>
       <c r="P66" s="5" t="inlineStr"/>
-      <c r="Q66" s="5" t="inlineStr"/>
-      <c r="R66" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S66" s="5" t="inlineStr"/>
-      <c r="T66" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U66" s="5" t="inlineStr"/>
-      <c r="V66" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W66" s="5" t="inlineStr"/>
+      <c r="Q66" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R66" s="5" t="inlineStr"/>
+      <c r="S66" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T66" s="5" t="inlineStr"/>
+      <c r="U66" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V66" s="5" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
@@ -9442,60 +9061,57 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>0.9425</v>
+        <v>0.9537</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>0.9537</v>
+        <v>0.9547</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>0.9562</v>
+        <v>0.1421</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>0.1421</v>
-      </c>
-      <c r="G67" s="5" t="n">
         <v>0.1581</v>
       </c>
+      <c r="G67" s="5" t="inlineStr"/>
       <c r="H67" s="5" t="inlineStr"/>
       <c r="I67" s="5" t="inlineStr"/>
-      <c r="J67" s="5" t="inlineStr"/>
-      <c r="K67" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L67" s="5" t="inlineStr"/>
-      <c r="M67" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N67" s="5" t="inlineStr"/>
-      <c r="O67" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="inlineStr"/>
+      <c r="L67" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M67" s="5" t="inlineStr"/>
+      <c r="N67" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O67" s="5" t="inlineStr"/>
       <c r="P67" s="5" t="inlineStr"/>
-      <c r="Q67" s="5" t="inlineStr"/>
-      <c r="R67" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S67" s="5" t="inlineStr"/>
-      <c r="T67" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U67" s="5" t="inlineStr"/>
-      <c r="V67" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W67" s="5" t="inlineStr"/>
+      <c r="Q67" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R67" s="5" t="inlineStr"/>
+      <c r="S67" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T67" s="5" t="inlineStr"/>
+      <c r="U67" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V67" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C67">
@@ -9528,9 +9144,9 @@
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
         <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
         <color rgb="00F8696B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="0063BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
@@ -9738,18 +9354,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W2:W67">
-    <cfRule type="colorScale" priority="21">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/VIC_curtailment.xlsx
+++ b/outputs/VIC_curtailment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -67,7 +67,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -82,9 +82,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -456,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W67"/>
+  <dimension ref="A1:O67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -474,14 +471,6 @@
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -560,46 +549,6 @@
           <t>FY26-27</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Curt FY1</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Curt FY2</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Curt FY3</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Curt Avg</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Offl FY1</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Offl FY2</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Offl FY3</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Offl Avg</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -660,30 +609,6 @@
       </c>
       <c r="O2" s="5" t="n">
         <v>0.9092</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="Q2" s="6" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" s="6" t="n">
-        <v>0.02666666666666667</v>
-      </c>
-      <c r="T2" s="6" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="U2" s="6" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="V2" s="6" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="W2" s="6" t="n">
-        <v>0.12</v>
       </c>
     </row>
     <row r="3">
@@ -732,14 +657,6 @@
       <c r="O3" s="5" t="n">
         <v>0.8963</v>
       </c>
-      <c r="P3" s="6" t="inlineStr"/>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
-      <c r="V3" s="6" t="inlineStr"/>
-      <c r="W3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -797,30 +714,6 @@
       <c r="O4" s="5" t="n">
         <v>0.929</v>
       </c>
-      <c r="P4" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="Q4" s="6" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="6" t="n">
-        <v>0.02666666666666667</v>
-      </c>
-      <c r="T4" s="6" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="U4" s="6" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="V4" s="6" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="W4" s="6" t="n">
-        <v>0.12</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -881,30 +774,6 @@
       </c>
       <c r="O5" s="5" t="n">
         <v>0.929</v>
-      </c>
-      <c r="P5" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="Q5" s="6" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="6" t="n">
-        <v>0.02666666666666667</v>
-      </c>
-      <c r="T5" s="6" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="U5" s="6" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="V5" s="6" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="W5" s="6" t="n">
-        <v>0.12</v>
       </c>
     </row>
     <row r="6">
@@ -965,30 +834,6 @@
       <c r="O6" s="5" t="n">
         <v>0.921</v>
       </c>
-      <c r="P6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="6" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="U6" s="6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="V6" s="6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="W6" s="6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1047,30 +892,6 @@
       </c>
       <c r="O7" s="5" t="n">
         <v>0.9294</v>
-      </c>
-      <c r="P7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" s="6" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="U7" s="6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="V7" s="6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="W7" s="6" t="n">
-        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1123,14 +944,6 @@
       <c r="O8" s="5" t="n">
         <v>0.9211</v>
       </c>
-      <c r="P8" s="6" t="inlineStr"/>
-      <c r="Q8" s="6" t="inlineStr"/>
-      <c r="R8" s="6" t="inlineStr"/>
-      <c r="S8" s="6" t="inlineStr"/>
-      <c r="T8" s="6" t="inlineStr"/>
-      <c r="U8" s="6" t="inlineStr"/>
-      <c r="V8" s="6" t="inlineStr"/>
-      <c r="W8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1178,14 +991,6 @@
       <c r="O9" s="5" t="n">
         <v>0.9261</v>
       </c>
-      <c r="P9" s="6" t="inlineStr"/>
-      <c r="Q9" s="6" t="inlineStr"/>
-      <c r="R9" s="6" t="inlineStr"/>
-      <c r="S9" s="6" t="inlineStr"/>
-      <c r="T9" s="6" t="inlineStr"/>
-      <c r="U9" s="6" t="inlineStr"/>
-      <c r="V9" s="6" t="inlineStr"/>
-      <c r="W9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1246,30 +1051,6 @@
       </c>
       <c r="O10" s="5" t="n">
         <v>0.9051</v>
-      </c>
-      <c r="P10" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="Q10" s="6" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" s="6" t="n">
-        <v>0.02666666666666667</v>
-      </c>
-      <c r="T10" s="6" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="U10" s="6" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="V10" s="6" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="W10" s="6" t="n">
-        <v>0.12</v>
       </c>
     </row>
     <row r="11">
@@ -1318,14 +1099,6 @@
       <c r="O11" s="5" t="n">
         <v>0.9311</v>
       </c>
-      <c r="P11" s="6" t="inlineStr"/>
-      <c r="Q11" s="6" t="inlineStr"/>
-      <c r="R11" s="6" t="inlineStr"/>
-      <c r="S11" s="6" t="inlineStr"/>
-      <c r="T11" s="6" t="inlineStr"/>
-      <c r="U11" s="6" t="inlineStr"/>
-      <c r="V11" s="6" t="inlineStr"/>
-      <c r="W11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1386,30 +1159,6 @@
       </c>
       <c r="O12" s="5" t="n">
         <v>0.8738</v>
-      </c>
-      <c r="P12" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="Q12" s="6" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" s="6" t="n">
-        <v>0.02666666666666667</v>
-      </c>
-      <c r="T12" s="6" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="U12" s="6" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="V12" s="6" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="W12" s="6" t="n">
-        <v>0.12</v>
       </c>
     </row>
     <row r="13">
@@ -1458,14 +1207,6 @@
       <c r="O13" s="5" t="n">
         <v>0.921</v>
       </c>
-      <c r="P13" s="6" t="inlineStr"/>
-      <c r="Q13" s="6" t="inlineStr"/>
-      <c r="R13" s="6" t="inlineStr"/>
-      <c r="S13" s="6" t="inlineStr"/>
-      <c r="T13" s="6" t="inlineStr"/>
-      <c r="U13" s="6" t="inlineStr"/>
-      <c r="V13" s="6" t="inlineStr"/>
-      <c r="W13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1513,14 +1254,6 @@
       <c r="O14" s="5" t="n">
         <v>0.9257</v>
       </c>
-      <c r="P14" s="6" t="inlineStr"/>
-      <c r="Q14" s="6" t="inlineStr"/>
-      <c r="R14" s="6" t="inlineStr"/>
-      <c r="S14" s="6" t="inlineStr"/>
-      <c r="T14" s="6" t="inlineStr"/>
-      <c r="U14" s="6" t="inlineStr"/>
-      <c r="V14" s="6" t="inlineStr"/>
-      <c r="W14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1581,30 +1314,6 @@
       </c>
       <c r="O15" s="5" t="n">
         <v>0.921</v>
-      </c>
-      <c r="P15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" s="6" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="U15" s="6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="V15" s="6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="W15" s="6" t="n">
-        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1653,14 +1362,6 @@
       <c r="O16" s="5" t="n">
         <v>0.9282</v>
       </c>
-      <c r="P16" s="6" t="inlineStr"/>
-      <c r="Q16" s="6" t="inlineStr"/>
-      <c r="R16" s="6" t="inlineStr"/>
-      <c r="S16" s="6" t="inlineStr"/>
-      <c r="T16" s="6" t="inlineStr"/>
-      <c r="U16" s="6" t="inlineStr"/>
-      <c r="V16" s="6" t="inlineStr"/>
-      <c r="W16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1721,30 +1422,6 @@
       </c>
       <c r="O17" s="5" t="n">
         <v>0.9092</v>
-      </c>
-      <c r="P17" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="Q17" s="6" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" s="6" t="n">
-        <v>0.02666666666666667</v>
-      </c>
-      <c r="T17" s="6" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="U17" s="6" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="V17" s="6" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="W17" s="6" t="n">
-        <v>0.12</v>
       </c>
     </row>
     <row r="18">
@@ -1804,30 +1481,6 @@
       </c>
       <c r="O18" s="5" t="n">
         <v>0.9211</v>
-      </c>
-      <c r="P18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" s="6" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="U18" s="6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="V18" s="6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="W18" s="6" t="n">
-        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -1886,14 +1539,6 @@
       <c r="O19" s="5" t="n">
         <v>0.921</v>
       </c>
-      <c r="P19" s="6" t="inlineStr"/>
-      <c r="Q19" s="6" t="inlineStr"/>
-      <c r="R19" s="6" t="inlineStr"/>
-      <c r="S19" s="6" t="inlineStr"/>
-      <c r="T19" s="6" t="inlineStr"/>
-      <c r="U19" s="6" t="inlineStr"/>
-      <c r="V19" s="6" t="inlineStr"/>
-      <c r="W19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1954,30 +1599,6 @@
       </c>
       <c r="O20" s="5" t="n">
         <v>0.9051</v>
-      </c>
-      <c r="P20" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="Q20" s="6" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" s="6" t="n">
-        <v>0.02666666666666667</v>
-      </c>
-      <c r="T20" s="6" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="U20" s="6" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="V20" s="6" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="W20" s="6" t="n">
-        <v>0.12</v>
       </c>
     </row>
     <row r="21">
@@ -2030,14 +1651,6 @@
       <c r="O21" s="5" t="n">
         <v>0.898</v>
       </c>
-      <c r="P21" s="6" t="inlineStr"/>
-      <c r="Q21" s="6" t="inlineStr"/>
-      <c r="R21" s="6" t="inlineStr"/>
-      <c r="S21" s="6" t="inlineStr"/>
-      <c r="T21" s="6" t="inlineStr"/>
-      <c r="U21" s="6" t="inlineStr"/>
-      <c r="V21" s="6" t="inlineStr"/>
-      <c r="W21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2089,14 +1702,6 @@
       <c r="O22" s="5" t="n">
         <v>0.992</v>
       </c>
-      <c r="P22" s="6" t="inlineStr"/>
-      <c r="Q22" s="6" t="inlineStr"/>
-      <c r="R22" s="6" t="inlineStr"/>
-      <c r="S22" s="6" t="inlineStr"/>
-      <c r="T22" s="6" t="inlineStr"/>
-      <c r="U22" s="6" t="inlineStr"/>
-      <c r="V22" s="6" t="inlineStr"/>
-      <c r="W22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2148,14 +1753,6 @@
       <c r="O23" s="5" t="n">
         <v>0.9436</v>
       </c>
-      <c r="P23" s="6" t="inlineStr"/>
-      <c r="Q23" s="6" t="inlineStr"/>
-      <c r="R23" s="6" t="inlineStr"/>
-      <c r="S23" s="6" t="inlineStr"/>
-      <c r="T23" s="6" t="inlineStr"/>
-      <c r="U23" s="6" t="inlineStr"/>
-      <c r="V23" s="6" t="inlineStr"/>
-      <c r="W23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2207,14 +1804,6 @@
       <c r="O24" s="5" t="n">
         <v>0.9436</v>
       </c>
-      <c r="P24" s="6" t="inlineStr"/>
-      <c r="Q24" s="6" t="inlineStr"/>
-      <c r="R24" s="6" t="inlineStr"/>
-      <c r="S24" s="6" t="inlineStr"/>
-      <c r="T24" s="6" t="inlineStr"/>
-      <c r="U24" s="6" t="inlineStr"/>
-      <c r="V24" s="6" t="inlineStr"/>
-      <c r="W24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2266,14 +1855,6 @@
       <c r="O25" s="5" t="n">
         <v>0.8868</v>
       </c>
-      <c r="P25" s="6" t="inlineStr"/>
-      <c r="Q25" s="6" t="inlineStr"/>
-      <c r="R25" s="6" t="inlineStr"/>
-      <c r="S25" s="6" t="inlineStr"/>
-      <c r="T25" s="6" t="inlineStr"/>
-      <c r="U25" s="6" t="inlineStr"/>
-      <c r="V25" s="6" t="inlineStr"/>
-      <c r="W25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2321,14 +1902,6 @@
       <c r="O26" s="5" t="n">
         <v>0.9791</v>
       </c>
-      <c r="P26" s="6" t="inlineStr"/>
-      <c r="Q26" s="6" t="inlineStr"/>
-      <c r="R26" s="6" t="inlineStr"/>
-      <c r="S26" s="6" t="inlineStr"/>
-      <c r="T26" s="6" t="inlineStr"/>
-      <c r="U26" s="6" t="inlineStr"/>
-      <c r="V26" s="6" t="inlineStr"/>
-      <c r="W26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2374,14 +1947,6 @@
         <v>0.9825</v>
       </c>
       <c r="O27" s="5" t="inlineStr"/>
-      <c r="P27" s="6" t="inlineStr"/>
-      <c r="Q27" s="6" t="inlineStr"/>
-      <c r="R27" s="6" t="inlineStr"/>
-      <c r="S27" s="6" t="inlineStr"/>
-      <c r="T27" s="6" t="inlineStr"/>
-      <c r="U27" s="6" t="inlineStr"/>
-      <c r="V27" s="6" t="inlineStr"/>
-      <c r="W27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2433,14 +1998,6 @@
       <c r="O28" s="5" t="n">
         <v>0.9977</v>
       </c>
-      <c r="P28" s="6" t="inlineStr"/>
-      <c r="Q28" s="6" t="inlineStr"/>
-      <c r="R28" s="6" t="inlineStr"/>
-      <c r="S28" s="6" t="inlineStr"/>
-      <c r="T28" s="6" t="inlineStr"/>
-      <c r="U28" s="6" t="inlineStr"/>
-      <c r="V28" s="6" t="inlineStr"/>
-      <c r="W28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2488,14 +2045,6 @@
       <c r="O29" s="5" t="n">
         <v>0.9949</v>
       </c>
-      <c r="P29" s="6" t="inlineStr"/>
-      <c r="Q29" s="6" t="inlineStr"/>
-      <c r="R29" s="6" t="inlineStr"/>
-      <c r="S29" s="6" t="inlineStr"/>
-      <c r="T29" s="6" t="inlineStr"/>
-      <c r="U29" s="6" t="inlineStr"/>
-      <c r="V29" s="6" t="inlineStr"/>
-      <c r="W29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2543,14 +2092,6 @@
       <c r="O30" s="5" t="n">
         <v>1.0031</v>
       </c>
-      <c r="P30" s="6" t="inlineStr"/>
-      <c r="Q30" s="6" t="inlineStr"/>
-      <c r="R30" s="6" t="inlineStr"/>
-      <c r="S30" s="6" t="inlineStr"/>
-      <c r="T30" s="6" t="inlineStr"/>
-      <c r="U30" s="6" t="inlineStr"/>
-      <c r="V30" s="6" t="inlineStr"/>
-      <c r="W30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2602,14 +2143,6 @@
       <c r="O31" s="5" t="n">
         <v>0.8966</v>
       </c>
-      <c r="P31" s="6" t="inlineStr"/>
-      <c r="Q31" s="6" t="inlineStr"/>
-      <c r="R31" s="6" t="inlineStr"/>
-      <c r="S31" s="6" t="inlineStr"/>
-      <c r="T31" s="6" t="inlineStr"/>
-      <c r="U31" s="6" t="inlineStr"/>
-      <c r="V31" s="6" t="inlineStr"/>
-      <c r="W31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2657,14 +2190,6 @@
       <c r="O32" s="5" t="n">
         <v>0.8954</v>
       </c>
-      <c r="P32" s="6" t="inlineStr"/>
-      <c r="Q32" s="6" t="inlineStr"/>
-      <c r="R32" s="6" t="inlineStr"/>
-      <c r="S32" s="6" t="inlineStr"/>
-      <c r="T32" s="6" t="inlineStr"/>
-      <c r="U32" s="6" t="inlineStr"/>
-      <c r="V32" s="6" t="inlineStr"/>
-      <c r="W32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2716,14 +2241,6 @@
       <c r="O33" s="5" t="n">
         <v>0.9827</v>
       </c>
-      <c r="P33" s="6" t="inlineStr"/>
-      <c r="Q33" s="6" t="inlineStr"/>
-      <c r="R33" s="6" t="inlineStr"/>
-      <c r="S33" s="6" t="inlineStr"/>
-      <c r="T33" s="6" t="inlineStr"/>
-      <c r="U33" s="6" t="inlineStr"/>
-      <c r="V33" s="6" t="inlineStr"/>
-      <c r="W33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2775,14 +2292,6 @@
       <c r="O34" s="5" t="n">
         <v>0.9827</v>
       </c>
-      <c r="P34" s="6" t="inlineStr"/>
-      <c r="Q34" s="6" t="inlineStr"/>
-      <c r="R34" s="6" t="inlineStr"/>
-      <c r="S34" s="6" t="inlineStr"/>
-      <c r="T34" s="6" t="inlineStr"/>
-      <c r="U34" s="6" t="inlineStr"/>
-      <c r="V34" s="6" t="inlineStr"/>
-      <c r="W34" s="6" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2834,14 +2343,6 @@
       <c r="O35" s="5" t="n">
         <v>0.9827</v>
       </c>
-      <c r="P35" s="6" t="inlineStr"/>
-      <c r="Q35" s="6" t="inlineStr"/>
-      <c r="R35" s="6" t="inlineStr"/>
-      <c r="S35" s="6" t="inlineStr"/>
-      <c r="T35" s="6" t="inlineStr"/>
-      <c r="U35" s="6" t="inlineStr"/>
-      <c r="V35" s="6" t="inlineStr"/>
-      <c r="W35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2891,14 +2392,6 @@
       <c r="O36" s="5" t="n">
         <v>0.9556</v>
       </c>
-      <c r="P36" s="6" t="inlineStr"/>
-      <c r="Q36" s="6" t="inlineStr"/>
-      <c r="R36" s="6" t="inlineStr"/>
-      <c r="S36" s="6" t="inlineStr"/>
-      <c r="T36" s="6" t="inlineStr"/>
-      <c r="U36" s="6" t="inlineStr"/>
-      <c r="V36" s="6" t="inlineStr"/>
-      <c r="W36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2942,14 +2435,6 @@
       <c r="M37" s="5" t="inlineStr"/>
       <c r="N37" s="5" t="inlineStr"/>
       <c r="O37" s="5" t="inlineStr"/>
-      <c r="P37" s="6" t="inlineStr"/>
-      <c r="Q37" s="6" t="inlineStr"/>
-      <c r="R37" s="6" t="inlineStr"/>
-      <c r="S37" s="6" t="inlineStr"/>
-      <c r="T37" s="6" t="inlineStr"/>
-      <c r="U37" s="6" t="inlineStr"/>
-      <c r="V37" s="6" t="inlineStr"/>
-      <c r="W37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2997,14 +2482,6 @@
       <c r="O38" s="5" t="n">
         <v>0.9949</v>
       </c>
-      <c r="P38" s="6" t="inlineStr"/>
-      <c r="Q38" s="6" t="inlineStr"/>
-      <c r="R38" s="6" t="inlineStr"/>
-      <c r="S38" s="6" t="inlineStr"/>
-      <c r="T38" s="6" t="inlineStr"/>
-      <c r="U38" s="6" t="inlineStr"/>
-      <c r="V38" s="6" t="inlineStr"/>
-      <c r="W38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3052,14 +2529,6 @@
       <c r="O39" s="5" t="n">
         <v>0.9815</v>
       </c>
-      <c r="P39" s="6" t="inlineStr"/>
-      <c r="Q39" s="6" t="inlineStr"/>
-      <c r="R39" s="6" t="inlineStr"/>
-      <c r="S39" s="6" t="inlineStr"/>
-      <c r="T39" s="6" t="inlineStr"/>
-      <c r="U39" s="6" t="inlineStr"/>
-      <c r="V39" s="6" t="inlineStr"/>
-      <c r="W39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3107,14 +2576,6 @@
       <c r="O40" s="5" t="n">
         <v>0.9815</v>
       </c>
-      <c r="P40" s="6" t="inlineStr"/>
-      <c r="Q40" s="6" t="inlineStr"/>
-      <c r="R40" s="6" t="inlineStr"/>
-      <c r="S40" s="6" t="inlineStr"/>
-      <c r="T40" s="6" t="inlineStr"/>
-      <c r="U40" s="6" t="inlineStr"/>
-      <c r="V40" s="6" t="inlineStr"/>
-      <c r="W40" s="6" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -3162,14 +2623,6 @@
       <c r="O41" s="5" t="n">
         <v>0.9815</v>
       </c>
-      <c r="P41" s="6" t="inlineStr"/>
-      <c r="Q41" s="6" t="inlineStr"/>
-      <c r="R41" s="6" t="inlineStr"/>
-      <c r="S41" s="6" t="inlineStr"/>
-      <c r="T41" s="6" t="inlineStr"/>
-      <c r="U41" s="6" t="inlineStr"/>
-      <c r="V41" s="6" t="inlineStr"/>
-      <c r="W41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -3217,14 +2670,6 @@
       <c r="O42" s="5" t="n">
         <v>0.9823</v>
       </c>
-      <c r="P42" s="6" t="inlineStr"/>
-      <c r="Q42" s="6" t="inlineStr"/>
-      <c r="R42" s="6" t="inlineStr"/>
-      <c r="S42" s="6" t="inlineStr"/>
-      <c r="T42" s="6" t="inlineStr"/>
-      <c r="U42" s="6" t="inlineStr"/>
-      <c r="V42" s="6" t="inlineStr"/>
-      <c r="W42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3272,14 +2717,6 @@
       <c r="O43" s="5" t="n">
         <v>0.9823</v>
       </c>
-      <c r="P43" s="6" t="inlineStr"/>
-      <c r="Q43" s="6" t="inlineStr"/>
-      <c r="R43" s="6" t="inlineStr"/>
-      <c r="S43" s="6" t="inlineStr"/>
-      <c r="T43" s="6" t="inlineStr"/>
-      <c r="U43" s="6" t="inlineStr"/>
-      <c r="V43" s="6" t="inlineStr"/>
-      <c r="W43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3329,14 +2766,6 @@
       <c r="O44" s="5" t="n">
         <v>0.9822</v>
       </c>
-      <c r="P44" s="6" t="inlineStr"/>
-      <c r="Q44" s="6" t="inlineStr"/>
-      <c r="R44" s="6" t="inlineStr"/>
-      <c r="S44" s="6" t="inlineStr"/>
-      <c r="T44" s="6" t="inlineStr"/>
-      <c r="U44" s="6" t="inlineStr"/>
-      <c r="V44" s="6" t="inlineStr"/>
-      <c r="W44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3384,14 +2813,6 @@
       <c r="O45" s="5" t="n">
         <v>0.9791</v>
       </c>
-      <c r="P45" s="6" t="inlineStr"/>
-      <c r="Q45" s="6" t="inlineStr"/>
-      <c r="R45" s="6" t="inlineStr"/>
-      <c r="S45" s="6" t="inlineStr"/>
-      <c r="T45" s="6" t="inlineStr"/>
-      <c r="U45" s="6" t="inlineStr"/>
-      <c r="V45" s="6" t="inlineStr"/>
-      <c r="W45" s="6" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3443,14 +2864,6 @@
       <c r="O46" s="5" t="n">
         <v>0.8954</v>
       </c>
-      <c r="P46" s="6" t="inlineStr"/>
-      <c r="Q46" s="6" t="inlineStr"/>
-      <c r="R46" s="6" t="inlineStr"/>
-      <c r="S46" s="6" t="inlineStr"/>
-      <c r="T46" s="6" t="inlineStr"/>
-      <c r="U46" s="6" t="inlineStr"/>
-      <c r="V46" s="6" t="inlineStr"/>
-      <c r="W46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3502,14 +2915,6 @@
       <c r="O47" s="5" t="n">
         <v>0.9824000000000001</v>
       </c>
-      <c r="P47" s="6" t="inlineStr"/>
-      <c r="Q47" s="6" t="inlineStr"/>
-      <c r="R47" s="6" t="inlineStr"/>
-      <c r="S47" s="6" t="inlineStr"/>
-      <c r="T47" s="6" t="inlineStr"/>
-      <c r="U47" s="6" t="inlineStr"/>
-      <c r="V47" s="6" t="inlineStr"/>
-      <c r="W47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3557,14 +2962,6 @@
       <c r="O48" s="5" t="n">
         <v>0.9791</v>
       </c>
-      <c r="P48" s="6" t="inlineStr"/>
-      <c r="Q48" s="6" t="inlineStr"/>
-      <c r="R48" s="6" t="inlineStr"/>
-      <c r="S48" s="6" t="inlineStr"/>
-      <c r="T48" s="6" t="inlineStr"/>
-      <c r="U48" s="6" t="inlineStr"/>
-      <c r="V48" s="6" t="inlineStr"/>
-      <c r="W48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -3616,14 +3013,6 @@
       <c r="O49" s="5" t="n">
         <v>0.9556</v>
       </c>
-      <c r="P49" s="6" t="inlineStr"/>
-      <c r="Q49" s="6" t="inlineStr"/>
-      <c r="R49" s="6" t="inlineStr"/>
-      <c r="S49" s="6" t="inlineStr"/>
-      <c r="T49" s="6" t="inlineStr"/>
-      <c r="U49" s="6" t="inlineStr"/>
-      <c r="V49" s="6" t="inlineStr"/>
-      <c r="W49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3675,14 +3064,6 @@
       <c r="O50" s="5" t="n">
         <v>0.9507</v>
       </c>
-      <c r="P50" s="6" t="inlineStr"/>
-      <c r="Q50" s="6" t="inlineStr"/>
-      <c r="R50" s="6" t="inlineStr"/>
-      <c r="S50" s="6" t="inlineStr"/>
-      <c r="T50" s="6" t="inlineStr"/>
-      <c r="U50" s="6" t="inlineStr"/>
-      <c r="V50" s="6" t="inlineStr"/>
-      <c r="W50" s="6" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3730,14 +3111,6 @@
       <c r="O51" s="5" t="n">
         <v>0.9949</v>
       </c>
-      <c r="P51" s="6" t="inlineStr"/>
-      <c r="Q51" s="6" t="inlineStr"/>
-      <c r="R51" s="6" t="inlineStr"/>
-      <c r="S51" s="6" t="inlineStr"/>
-      <c r="T51" s="6" t="inlineStr"/>
-      <c r="U51" s="6" t="inlineStr"/>
-      <c r="V51" s="6" t="inlineStr"/>
-      <c r="W51" s="6" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3789,14 +3162,6 @@
       <c r="O52" s="5" t="n">
         <v>0.989</v>
       </c>
-      <c r="P52" s="6" t="inlineStr"/>
-      <c r="Q52" s="6" t="inlineStr"/>
-      <c r="R52" s="6" t="inlineStr"/>
-      <c r="S52" s="6" t="inlineStr"/>
-      <c r="T52" s="6" t="inlineStr"/>
-      <c r="U52" s="6" t="inlineStr"/>
-      <c r="V52" s="6" t="inlineStr"/>
-      <c r="W52" s="6" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -3848,14 +3213,6 @@
       <c r="O53" s="5" t="n">
         <v>0.9556</v>
       </c>
-      <c r="P53" s="6" t="inlineStr"/>
-      <c r="Q53" s="6" t="inlineStr"/>
-      <c r="R53" s="6" t="inlineStr"/>
-      <c r="S53" s="6" t="inlineStr"/>
-      <c r="T53" s="6" t="inlineStr"/>
-      <c r="U53" s="6" t="inlineStr"/>
-      <c r="V53" s="6" t="inlineStr"/>
-      <c r="W53" s="6" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -3907,14 +3264,6 @@
       <c r="O54" s="5" t="n">
         <v>0.8824</v>
       </c>
-      <c r="P54" s="6" t="inlineStr"/>
-      <c r="Q54" s="6" t="inlineStr"/>
-      <c r="R54" s="6" t="inlineStr"/>
-      <c r="S54" s="6" t="inlineStr"/>
-      <c r="T54" s="6" t="inlineStr"/>
-      <c r="U54" s="6" t="inlineStr"/>
-      <c r="V54" s="6" t="inlineStr"/>
-      <c r="W54" s="6" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3966,14 +3315,6 @@
       <c r="O55" s="5" t="n">
         <v>0.8824</v>
       </c>
-      <c r="P55" s="6" t="inlineStr"/>
-      <c r="Q55" s="6" t="inlineStr"/>
-      <c r="R55" s="6" t="inlineStr"/>
-      <c r="S55" s="6" t="inlineStr"/>
-      <c r="T55" s="6" t="inlineStr"/>
-      <c r="U55" s="6" t="inlineStr"/>
-      <c r="V55" s="6" t="inlineStr"/>
-      <c r="W55" s="6" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -4025,14 +3366,6 @@
       <c r="O56" s="5" t="n">
         <v>0.9949</v>
       </c>
-      <c r="P56" s="6" t="inlineStr"/>
-      <c r="Q56" s="6" t="inlineStr"/>
-      <c r="R56" s="6" t="inlineStr"/>
-      <c r="S56" s="6" t="inlineStr"/>
-      <c r="T56" s="6" t="inlineStr"/>
-      <c r="U56" s="6" t="inlineStr"/>
-      <c r="V56" s="6" t="inlineStr"/>
-      <c r="W56" s="6" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -4082,14 +3415,6 @@
       <c r="O57" s="5" t="n">
         <v>0.983</v>
       </c>
-      <c r="P57" s="6" t="inlineStr"/>
-      <c r="Q57" s="6" t="inlineStr"/>
-      <c r="R57" s="6" t="inlineStr"/>
-      <c r="S57" s="6" t="inlineStr"/>
-      <c r="T57" s="6" t="inlineStr"/>
-      <c r="U57" s="6" t="inlineStr"/>
-      <c r="V57" s="6" t="inlineStr"/>
-      <c r="W57" s="6" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -4141,14 +3466,6 @@
       <c r="O58" s="5" t="n">
         <v>0.9499</v>
       </c>
-      <c r="P58" s="6" t="inlineStr"/>
-      <c r="Q58" s="6" t="inlineStr"/>
-      <c r="R58" s="6" t="inlineStr"/>
-      <c r="S58" s="6" t="inlineStr"/>
-      <c r="T58" s="6" t="inlineStr"/>
-      <c r="U58" s="6" t="inlineStr"/>
-      <c r="V58" s="6" t="inlineStr"/>
-      <c r="W58" s="6" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -4200,14 +3517,6 @@
       <c r="O59" s="5" t="n">
         <v>0.9827</v>
       </c>
-      <c r="P59" s="6" t="inlineStr"/>
-      <c r="Q59" s="6" t="inlineStr"/>
-      <c r="R59" s="6" t="inlineStr"/>
-      <c r="S59" s="6" t="inlineStr"/>
-      <c r="T59" s="6" t="inlineStr"/>
-      <c r="U59" s="6" t="inlineStr"/>
-      <c r="V59" s="6" t="inlineStr"/>
-      <c r="W59" s="6" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -4255,14 +3564,6 @@
       <c r="O60" s="5" t="n">
         <v>0.9949</v>
       </c>
-      <c r="P60" s="6" t="inlineStr"/>
-      <c r="Q60" s="6" t="inlineStr"/>
-      <c r="R60" s="6" t="inlineStr"/>
-      <c r="S60" s="6" t="inlineStr"/>
-      <c r="T60" s="6" t="inlineStr"/>
-      <c r="U60" s="6" t="inlineStr"/>
-      <c r="V60" s="6" t="inlineStr"/>
-      <c r="W60" s="6" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -4310,14 +3611,6 @@
       <c r="O61" s="5" t="n">
         <v>0.992</v>
       </c>
-      <c r="P61" s="6" t="inlineStr"/>
-      <c r="Q61" s="6" t="inlineStr"/>
-      <c r="R61" s="6" t="inlineStr"/>
-      <c r="S61" s="6" t="inlineStr"/>
-      <c r="T61" s="6" t="inlineStr"/>
-      <c r="U61" s="6" t="inlineStr"/>
-      <c r="V61" s="6" t="inlineStr"/>
-      <c r="W61" s="6" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -4365,14 +3658,6 @@
       <c r="O62" s="5" t="n">
         <v>0.9298999999999999</v>
       </c>
-      <c r="P62" s="6" t="inlineStr"/>
-      <c r="Q62" s="6" t="inlineStr"/>
-      <c r="R62" s="6" t="inlineStr"/>
-      <c r="S62" s="6" t="inlineStr"/>
-      <c r="T62" s="6" t="inlineStr"/>
-      <c r="U62" s="6" t="inlineStr"/>
-      <c r="V62" s="6" t="inlineStr"/>
-      <c r="W62" s="6" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -4420,14 +3705,6 @@
       <c r="O63" s="5" t="n">
         <v>0.992</v>
       </c>
-      <c r="P63" s="6" t="inlineStr"/>
-      <c r="Q63" s="6" t="inlineStr"/>
-      <c r="R63" s="6" t="inlineStr"/>
-      <c r="S63" s="6" t="inlineStr"/>
-      <c r="T63" s="6" t="inlineStr"/>
-      <c r="U63" s="6" t="inlineStr"/>
-      <c r="V63" s="6" t="inlineStr"/>
-      <c r="W63" s="6" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -4475,14 +3752,6 @@
       <c r="O64" s="5" t="n">
         <v>0.9791</v>
       </c>
-      <c r="P64" s="6" t="inlineStr"/>
-      <c r="Q64" s="6" t="inlineStr"/>
-      <c r="R64" s="6" t="inlineStr"/>
-      <c r="S64" s="6" t="inlineStr"/>
-      <c r="T64" s="6" t="inlineStr"/>
-      <c r="U64" s="6" t="inlineStr"/>
-      <c r="V64" s="6" t="inlineStr"/>
-      <c r="W64" s="6" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -4530,14 +3799,6 @@
       <c r="O65" s="5" t="n">
         <v>0.9949</v>
       </c>
-      <c r="P65" s="6" t="inlineStr"/>
-      <c r="Q65" s="6" t="inlineStr"/>
-      <c r="R65" s="6" t="inlineStr"/>
-      <c r="S65" s="6" t="inlineStr"/>
-      <c r="T65" s="6" t="inlineStr"/>
-      <c r="U65" s="6" t="inlineStr"/>
-      <c r="V65" s="6" t="inlineStr"/>
-      <c r="W65" s="6" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -4585,14 +3846,6 @@
       <c r="O66" s="5" t="n">
         <v>1.0031</v>
       </c>
-      <c r="P66" s="6" t="inlineStr"/>
-      <c r="Q66" s="6" t="inlineStr"/>
-      <c r="R66" s="6" t="inlineStr"/>
-      <c r="S66" s="6" t="inlineStr"/>
-      <c r="T66" s="6" t="inlineStr"/>
-      <c r="U66" s="6" t="inlineStr"/>
-      <c r="V66" s="6" t="inlineStr"/>
-      <c r="W66" s="6" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -4644,14 +3897,6 @@
       <c r="O67" s="5" t="n">
         <v>0.9547</v>
       </c>
-      <c r="P67" s="6" t="inlineStr"/>
-      <c r="Q67" s="6" t="inlineStr"/>
-      <c r="R67" s="6" t="inlineStr"/>
-      <c r="S67" s="6" t="inlineStr"/>
-      <c r="T67" s="6" t="inlineStr"/>
-      <c r="U67" s="6" t="inlineStr"/>
-      <c r="V67" s="6" t="inlineStr"/>
-      <c r="W67" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4664,7 +3909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V67"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4675,141 +3920,57 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>DUID</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Fuel</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>MLF_FY25-26</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>MLF_FY26-27</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>CURTAILMENT_ACTUAL_FY23-24</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>CURTAILMENT_ACTUAL_FY24-25</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>ELI_CURTAILMENT_NEAR</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>ELI_CURTAILMENT_MED</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_FY1</t>
-        </is>
-      </c>
-      <c r="J1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_FY1_LABEL</t>
-        </is>
-      </c>
-      <c r="K1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_FY2</t>
-        </is>
-      </c>
-      <c r="L1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_FY2_LABEL</t>
-        </is>
-      </c>
-      <c r="M1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_FY3</t>
-        </is>
-      </c>
-      <c r="N1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_FY3_LABEL</t>
-        </is>
-      </c>
-      <c r="O1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_AVG</t>
-        </is>
-      </c>
-      <c r="P1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_FY1</t>
-        </is>
-      </c>
-      <c r="Q1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_FY1_LABEL</t>
-        </is>
-      </c>
-      <c r="R1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_FY2</t>
-        </is>
-      </c>
-      <c r="S1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_FY2_LABEL</t>
-        </is>
-      </c>
-      <c r="T1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_FY3</t>
-        </is>
-      </c>
-      <c r="U1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_FY3_LABEL</t>
-        </is>
-      </c>
-      <c r="V1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_AVG</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>BANN1</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4832,68 +3993,14 @@
       <c r="H2" s="5" t="n">
         <v>0.164192244302687</v>
       </c>
-      <c r="I2" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J2" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K2" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="L2" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O2" s="5" t="n">
-        <v>0.02666666666666667</v>
-      </c>
-      <c r="P2" s="5" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="Q2" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R2" s="5" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="S2" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T2" s="5" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="U2" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V2" s="5" t="n">
-        <v>0.12</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>CRWARP1</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4908,52 +4015,14 @@
       <c r="F3" s="5" t="inlineStr"/>
       <c r="G3" s="5" t="inlineStr"/>
       <c r="H3" s="5" t="inlineStr"/>
-      <c r="I3" s="5" t="inlineStr"/>
-      <c r="J3" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="inlineStr"/>
-      <c r="L3" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M3" s="5" t="inlineStr"/>
-      <c r="N3" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O3" s="5" t="inlineStr"/>
-      <c r="P3" s="5" t="inlineStr"/>
-      <c r="Q3" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R3" s="5" t="inlineStr"/>
-      <c r="S3" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T3" s="5" t="inlineStr"/>
-      <c r="U3" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>COHUNSF1</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4972,68 +4041,14 @@
       <c r="H4" s="5" t="n">
         <v>0.122422882740379</v>
       </c>
-      <c r="I4" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J4" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="L4" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O4" s="5" t="n">
-        <v>0.02666666666666667</v>
-      </c>
-      <c r="P4" s="5" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="Q4" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R4" s="5" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="S4" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T4" s="5" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="U4" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V4" s="5" t="n">
-        <v>0.12</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>GANNSF1</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5056,68 +4071,14 @@
       <c r="H5" s="5" t="n">
         <v>0.122422882740379</v>
       </c>
-      <c r="I5" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="L5" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O5" s="5" t="n">
-        <v>0.02666666666666667</v>
-      </c>
-      <c r="P5" s="5" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="Q5" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R5" s="5" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="S5" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T5" s="5" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="U5" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V5" s="5" t="n">
-        <v>0.12</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>GIRGSF</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5138,68 +4099,14 @@
       <c r="H6" s="5" t="n">
         <v>0.08205629867681941</v>
       </c>
-      <c r="I6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="5" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="Q6" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R6" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="S6" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T6" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="U6" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V6" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>GLENSF1</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5220,68 +4127,14 @@
       <c r="H7" s="5" t="n">
         <v>0.08997768712489811</v>
       </c>
-      <c r="I7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="5" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="Q7" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R7" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="S7" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T7" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="U7" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V7" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>GLRWNSF1</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5300,52 +4153,14 @@
       </c>
       <c r="G8" s="5" t="inlineStr"/>
       <c r="H8" s="5" t="inlineStr"/>
-      <c r="I8" s="5" t="inlineStr"/>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr"/>
-      <c r="L8" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M8" s="5" t="inlineStr"/>
-      <c r="N8" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O8" s="5" t="inlineStr"/>
-      <c r="P8" s="5" t="inlineStr"/>
-      <c r="Q8" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R8" s="5" t="inlineStr"/>
-      <c r="S8" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T8" s="5" t="inlineStr"/>
-      <c r="U8" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>GOESF1</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5360,52 +4175,14 @@
       <c r="F9" s="5" t="inlineStr"/>
       <c r="G9" s="5" t="inlineStr"/>
       <c r="H9" s="5" t="inlineStr"/>
-      <c r="I9" s="5" t="inlineStr"/>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr"/>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M9" s="5" t="inlineStr"/>
-      <c r="N9" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O9" s="5" t="inlineStr"/>
-      <c r="P9" s="5" t="inlineStr"/>
-      <c r="Q9" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R9" s="5" t="inlineStr"/>
-      <c r="S9" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T9" s="5" t="inlineStr"/>
-      <c r="U9" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>KARSF1</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5428,68 +4205,14 @@
       <c r="H10" s="5" t="n">
         <v>0.072415601225557</v>
       </c>
-      <c r="I10" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O10" s="5" t="n">
-        <v>0.02666666666666667</v>
-      </c>
-      <c r="P10" s="5" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="Q10" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R10" s="5" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="S10" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T10" s="5" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="U10" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V10" s="5" t="n">
-        <v>0.12</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>KERNGSP1</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5504,52 +4227,14 @@
       <c r="F11" s="5" t="inlineStr"/>
       <c r="G11" s="5" t="inlineStr"/>
       <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr"/>
-      <c r="L11" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M11" s="5" t="inlineStr"/>
-      <c r="N11" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O11" s="5" t="inlineStr"/>
-      <c r="P11" s="5" t="inlineStr"/>
-      <c r="Q11" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R11" s="5" t="inlineStr"/>
-      <c r="S11" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T11" s="5" t="inlineStr"/>
-      <c r="U11" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>KIAMSF1</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5572,68 +4257,14 @@
       <c r="H12" s="5" t="n">
         <v>0.0878331516592939</v>
       </c>
-      <c r="I12" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="L12" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O12" s="5" t="n">
-        <v>0.02666666666666667</v>
-      </c>
-      <c r="P12" s="5" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="Q12" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R12" s="5" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="S12" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T12" s="5" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="U12" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V12" s="5" t="n">
-        <v>0.12</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>LANCSF1</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5648,52 +4279,14 @@
       <c r="F13" s="5" t="inlineStr"/>
       <c r="G13" s="5" t="inlineStr"/>
       <c r="H13" s="5" t="inlineStr"/>
-      <c r="I13" s="5" t="inlineStr"/>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="inlineStr"/>
-      <c r="L13" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M13" s="5" t="inlineStr"/>
-      <c r="N13" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O13" s="5" t="inlineStr"/>
-      <c r="P13" s="5" t="inlineStr"/>
-      <c r="Q13" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R13" s="5" t="inlineStr"/>
-      <c r="S13" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T13" s="5" t="inlineStr"/>
-      <c r="U13" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>MOKOSF1</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5708,52 +4301,14 @@
       <c r="F14" s="5" t="inlineStr"/>
       <c r="G14" s="5" t="inlineStr"/>
       <c r="H14" s="5" t="inlineStr"/>
-      <c r="I14" s="5" t="inlineStr"/>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="inlineStr"/>
-      <c r="L14" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M14" s="5" t="inlineStr"/>
-      <c r="N14" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O14" s="5" t="inlineStr"/>
-      <c r="P14" s="5" t="inlineStr"/>
-      <c r="Q14" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R14" s="5" t="inlineStr"/>
-      <c r="S14" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T14" s="5" t="inlineStr"/>
-      <c r="U14" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>NUMURSF1</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5776,68 +4331,14 @@
       <c r="H15" s="5" t="n">
         <v>0.08205629867681941</v>
       </c>
-      <c r="I15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" s="5" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="Q15" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R15" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="S15" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T15" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="U15" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V15" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>WNSF1</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5852,52 +4353,14 @@
       <c r="F16" s="5" t="inlineStr"/>
       <c r="G16" s="5" t="inlineStr"/>
       <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="inlineStr"/>
-      <c r="L16" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M16" s="5" t="inlineStr"/>
-      <c r="N16" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O16" s="5" t="inlineStr"/>
-      <c r="P16" s="5" t="inlineStr"/>
-      <c r="Q16" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R16" s="5" t="inlineStr"/>
-      <c r="S16" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T16" s="5" t="inlineStr"/>
-      <c r="U16" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>WEMENSF1</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5920,68 +4383,14 @@
       <c r="H17" s="5" t="n">
         <v>0.164192244302687</v>
       </c>
-      <c r="I17" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O17" s="5" t="n">
-        <v>0.02666666666666667</v>
-      </c>
-      <c r="P17" s="5" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="Q17" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R17" s="5" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="S17" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T17" s="5" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="U17" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V17" s="5" t="n">
-        <v>0.12</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>WINTSF1</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6002,68 +4411,14 @@
       <c r="H18" s="5" t="n">
         <v>0.08997768712489811</v>
       </c>
-      <c r="I18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" s="5" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="Q18" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R18" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="S18" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T18" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="U18" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V18" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>WUNUSF1</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6082,52 +4437,14 @@
       <c r="H19" s="5" t="n">
         <v>0.08205629867681941</v>
       </c>
-      <c r="I19" s="5" t="inlineStr"/>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="inlineStr"/>
-      <c r="L19" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M19" s="5" t="inlineStr"/>
-      <c r="N19" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O19" s="5" t="inlineStr"/>
-      <c r="P19" s="5" t="inlineStr"/>
-      <c r="Q19" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R19" s="5" t="inlineStr"/>
-      <c r="S19" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T19" s="5" t="inlineStr"/>
-      <c r="U19" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>YATSF1</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6150,68 +4467,14 @@
       <c r="H20" s="5" t="n">
         <v>0.072415601225557</v>
       </c>
-      <c r="I20" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J20" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K20" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="L20" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O20" s="5" t="n">
-        <v>0.02666666666666667</v>
-      </c>
-      <c r="P20" s="5" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="Q20" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R20" s="5" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="S20" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T20" s="5" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="U20" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V20" s="5" t="n">
-        <v>0.12</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>ARWF1</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6230,52 +4493,14 @@
       </c>
       <c r="G21" s="5" t="inlineStr"/>
       <c r="H21" s="5" t="inlineStr"/>
-      <c r="I21" s="5" t="inlineStr"/>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr"/>
-      <c r="L21" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M21" s="5" t="inlineStr"/>
-      <c r="N21" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O21" s="5" t="inlineStr"/>
-      <c r="P21" s="5" t="inlineStr"/>
-      <c r="Q21" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R21" s="5" t="inlineStr"/>
-      <c r="S21" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T21" s="5" t="inlineStr"/>
-      <c r="U21" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>BALDHWF1</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6294,52 +4519,14 @@
       </c>
       <c r="G22" s="5" t="inlineStr"/>
       <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K22" s="5" t="inlineStr"/>
-      <c r="L22" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M22" s="5" t="inlineStr"/>
-      <c r="N22" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O22" s="5" t="inlineStr"/>
-      <c r="P22" s="5" t="inlineStr"/>
-      <c r="Q22" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R22" s="5" t="inlineStr"/>
-      <c r="S22" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T22" s="5" t="inlineStr"/>
-      <c r="U22" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>BRYB2WF2</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6358,52 +4545,14 @@
       </c>
       <c r="G23" s="5" t="inlineStr"/>
       <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr"/>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="inlineStr"/>
-      <c r="N23" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O23" s="5" t="inlineStr"/>
-      <c r="P23" s="5" t="inlineStr"/>
-      <c r="Q23" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R23" s="5" t="inlineStr"/>
-      <c r="S23" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T23" s="5" t="inlineStr"/>
-      <c r="U23" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>BRYB1WF1</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6422,52 +4571,14 @@
       </c>
       <c r="G24" s="5" t="inlineStr"/>
       <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K24" s="5" t="inlineStr"/>
-      <c r="L24" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M24" s="5" t="inlineStr"/>
-      <c r="N24" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O24" s="5" t="inlineStr"/>
-      <c r="P24" s="5" t="inlineStr"/>
-      <c r="Q24" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R24" s="5" t="inlineStr"/>
-      <c r="S24" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T24" s="5" t="inlineStr"/>
-      <c r="U24" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>BULGANA1</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6486,52 +4597,14 @@
       </c>
       <c r="G25" s="5" t="inlineStr"/>
       <c r="H25" s="5" t="inlineStr"/>
-      <c r="I25" s="5" t="inlineStr"/>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr"/>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr"/>
-      <c r="N25" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O25" s="5" t="inlineStr"/>
-      <c r="P25" s="5" t="inlineStr"/>
-      <c r="Q25" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R25" s="5" t="inlineStr"/>
-      <c r="S25" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T25" s="5" t="inlineStr"/>
-      <c r="U25" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>CHALLHWF</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6546,52 +4619,14 @@
       <c r="F26" s="5" t="inlineStr"/>
       <c r="G26" s="5" t="inlineStr"/>
       <c r="H26" s="5" t="inlineStr"/>
-      <c r="I26" s="5" t="inlineStr"/>
-      <c r="J26" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K26" s="5" t="inlineStr"/>
-      <c r="L26" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M26" s="5" t="inlineStr"/>
-      <c r="N26" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O26" s="5" t="inlineStr"/>
-      <c r="P26" s="5" t="inlineStr"/>
-      <c r="Q26" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R26" s="5" t="inlineStr"/>
-      <c r="S26" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T26" s="5" t="inlineStr"/>
-      <c r="U26" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>CHPSTWF1</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6604,52 +4639,14 @@
       <c r="F27" s="5" t="inlineStr"/>
       <c r="G27" s="5" t="inlineStr"/>
       <c r="H27" s="5" t="inlineStr"/>
-      <c r="I27" s="5" t="inlineStr"/>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr"/>
-      <c r="L27" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M27" s="5" t="inlineStr"/>
-      <c r="N27" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O27" s="5" t="inlineStr"/>
-      <c r="P27" s="5" t="inlineStr"/>
-      <c r="Q27" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R27" s="5" t="inlineStr"/>
-      <c r="S27" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T27" s="5" t="inlineStr"/>
-      <c r="U27" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>CHYTWF1</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6668,52 +4665,14 @@
       </c>
       <c r="G28" s="5" t="inlineStr"/>
       <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K28" s="5" t="inlineStr"/>
-      <c r="L28" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M28" s="5" t="inlineStr"/>
-      <c r="N28" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O28" s="5" t="inlineStr"/>
-      <c r="P28" s="5" t="inlineStr"/>
-      <c r="Q28" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R28" s="5" t="inlineStr"/>
-      <c r="S28" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T28" s="5" t="inlineStr"/>
-      <c r="U28" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>CODRNGTON</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6728,52 +4687,14 @@
       <c r="F29" s="5" t="inlineStr"/>
       <c r="G29" s="5" t="inlineStr"/>
       <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K29" s="5" t="inlineStr"/>
-      <c r="L29" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M29" s="5" t="inlineStr"/>
-      <c r="N29" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O29" s="5" t="inlineStr"/>
-      <c r="P29" s="5" t="inlineStr"/>
-      <c r="Q29" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R29" s="5" t="inlineStr"/>
-      <c r="S29" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T29" s="5" t="inlineStr"/>
-      <c r="U29" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>CBWF1</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6788,52 +4709,14 @@
       <c r="F30" s="5" t="inlineStr"/>
       <c r="G30" s="5" t="inlineStr"/>
       <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K30" s="5" t="inlineStr"/>
-      <c r="L30" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M30" s="5" t="inlineStr"/>
-      <c r="N30" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O30" s="5" t="inlineStr"/>
-      <c r="P30" s="5" t="inlineStr"/>
-      <c r="Q30" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R30" s="5" t="inlineStr"/>
-      <c r="S30" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T30" s="5" t="inlineStr"/>
-      <c r="U30" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>CROWLWF1</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6852,52 +4735,14 @@
       </c>
       <c r="G31" s="5" t="inlineStr"/>
       <c r="H31" s="5" t="inlineStr"/>
-      <c r="I31" s="5" t="inlineStr"/>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K31" s="5" t="inlineStr"/>
-      <c r="L31" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M31" s="5" t="inlineStr"/>
-      <c r="N31" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O31" s="5" t="inlineStr"/>
-      <c r="P31" s="5" t="inlineStr"/>
-      <c r="Q31" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R31" s="5" t="inlineStr"/>
-      <c r="S31" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T31" s="5" t="inlineStr"/>
-      <c r="U31" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>DIAPURWF1</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6912,52 +4757,14 @@
       <c r="F32" s="5" t="inlineStr"/>
       <c r="G32" s="5" t="inlineStr"/>
       <c r="H32" s="5" t="inlineStr"/>
-      <c r="I32" s="5" t="inlineStr"/>
-      <c r="J32" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K32" s="5" t="inlineStr"/>
-      <c r="L32" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M32" s="5" t="inlineStr"/>
-      <c r="N32" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O32" s="5" t="inlineStr"/>
-      <c r="P32" s="5" t="inlineStr"/>
-      <c r="Q32" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R32" s="5" t="inlineStr"/>
-      <c r="S32" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T32" s="5" t="inlineStr"/>
-      <c r="U32" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>DUNDWF1</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6976,52 +4783,14 @@
       </c>
       <c r="G33" s="5" t="inlineStr"/>
       <c r="H33" s="5" t="inlineStr"/>
-      <c r="I33" s="5" t="inlineStr"/>
-      <c r="J33" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K33" s="5" t="inlineStr"/>
-      <c r="L33" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M33" s="5" t="inlineStr"/>
-      <c r="N33" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O33" s="5" t="inlineStr"/>
-      <c r="P33" s="5" t="inlineStr"/>
-      <c r="Q33" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R33" s="5" t="inlineStr"/>
-      <c r="S33" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T33" s="5" t="inlineStr"/>
-      <c r="U33" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>DUNDWF2</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -7040,52 +4809,14 @@
       </c>
       <c r="G34" s="5" t="inlineStr"/>
       <c r="H34" s="5" t="inlineStr"/>
-      <c r="I34" s="5" t="inlineStr"/>
-      <c r="J34" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K34" s="5" t="inlineStr"/>
-      <c r="L34" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M34" s="5" t="inlineStr"/>
-      <c r="N34" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O34" s="5" t="inlineStr"/>
-      <c r="P34" s="5" t="inlineStr"/>
-      <c r="Q34" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R34" s="5" t="inlineStr"/>
-      <c r="S34" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T34" s="5" t="inlineStr"/>
-      <c r="U34" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>DUNDWF3</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -7104,52 +4835,14 @@
       </c>
       <c r="G35" s="5" t="inlineStr"/>
       <c r="H35" s="5" t="inlineStr"/>
-      <c r="I35" s="5" t="inlineStr"/>
-      <c r="J35" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K35" s="5" t="inlineStr"/>
-      <c r="L35" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M35" s="5" t="inlineStr"/>
-      <c r="N35" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O35" s="5" t="inlineStr"/>
-      <c r="P35" s="5" t="inlineStr"/>
-      <c r="Q35" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R35" s="5" t="inlineStr"/>
-      <c r="S35" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T35" s="5" t="inlineStr"/>
-      <c r="U35" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V35" s="5" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>ELAINWF1</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -7166,52 +4859,14 @@
       <c r="F36" s="5" t="inlineStr"/>
       <c r="G36" s="5" t="inlineStr"/>
       <c r="H36" s="5" t="inlineStr"/>
-      <c r="I36" s="5" t="inlineStr"/>
-      <c r="J36" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K36" s="5" t="inlineStr"/>
-      <c r="L36" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M36" s="5" t="inlineStr"/>
-      <c r="N36" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O36" s="5" t="inlineStr"/>
-      <c r="P36" s="5" t="inlineStr"/>
-      <c r="Q36" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R36" s="5" t="inlineStr"/>
-      <c r="S36" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T36" s="5" t="inlineStr"/>
-      <c r="U36" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>FNWF1</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -7222,52 +4877,14 @@
       <c r="F37" s="5" t="inlineStr"/>
       <c r="G37" s="5" t="inlineStr"/>
       <c r="H37" s="5" t="inlineStr"/>
-      <c r="I37" s="5" t="inlineStr"/>
-      <c r="J37" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K37" s="5" t="inlineStr"/>
-      <c r="L37" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M37" s="5" t="inlineStr"/>
-      <c r="N37" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O37" s="5" t="inlineStr"/>
-      <c r="P37" s="5" t="inlineStr"/>
-      <c r="Q37" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R37" s="5" t="inlineStr"/>
-      <c r="S37" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T37" s="5" t="inlineStr"/>
-      <c r="U37" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>FSWF1</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -7282,52 +4899,14 @@
       <c r="F38" s="5" t="inlineStr"/>
       <c r="G38" s="5" t="inlineStr"/>
       <c r="H38" s="5" t="inlineStr"/>
-      <c r="I38" s="5" t="inlineStr"/>
-      <c r="J38" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K38" s="5" t="inlineStr"/>
-      <c r="L38" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M38" s="5" t="inlineStr"/>
-      <c r="N38" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O38" s="5" t="inlineStr"/>
-      <c r="P38" s="5" t="inlineStr"/>
-      <c r="Q38" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R38" s="5" t="inlineStr"/>
-      <c r="S38" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T38" s="5" t="inlineStr"/>
-      <c r="U38" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>GPWFEST1</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -7342,52 +4921,14 @@
       <c r="F39" s="5" t="inlineStr"/>
       <c r="G39" s="5" t="inlineStr"/>
       <c r="H39" s="5" t="inlineStr"/>
-      <c r="I39" s="5" t="inlineStr"/>
-      <c r="J39" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K39" s="5" t="inlineStr"/>
-      <c r="L39" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M39" s="5" t="inlineStr"/>
-      <c r="N39" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O39" s="5" t="inlineStr"/>
-      <c r="P39" s="5" t="inlineStr"/>
-      <c r="Q39" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R39" s="5" t="inlineStr"/>
-      <c r="S39" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T39" s="5" t="inlineStr"/>
-      <c r="U39" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="8" t="inlineStr">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>GPWFEST2</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -7402,52 +4943,14 @@
       <c r="F40" s="5" t="inlineStr"/>
       <c r="G40" s="5" t="inlineStr"/>
       <c r="H40" s="5" t="inlineStr"/>
-      <c r="I40" s="5" t="inlineStr"/>
-      <c r="J40" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K40" s="5" t="inlineStr"/>
-      <c r="L40" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M40" s="5" t="inlineStr"/>
-      <c r="N40" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O40" s="5" t="inlineStr"/>
-      <c r="P40" s="5" t="inlineStr"/>
-      <c r="Q40" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R40" s="5" t="inlineStr"/>
-      <c r="S40" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T40" s="5" t="inlineStr"/>
-      <c r="U40" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>GPWFEST3</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -7462,52 +4965,14 @@
       <c r="F41" s="5" t="inlineStr"/>
       <c r="G41" s="5" t="inlineStr"/>
       <c r="H41" s="5" t="inlineStr"/>
-      <c r="I41" s="5" t="inlineStr"/>
-      <c r="J41" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K41" s="5" t="inlineStr"/>
-      <c r="L41" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M41" s="5" t="inlineStr"/>
-      <c r="N41" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O41" s="5" t="inlineStr"/>
-      <c r="P41" s="5" t="inlineStr"/>
-      <c r="Q41" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R41" s="5" t="inlineStr"/>
-      <c r="S41" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T41" s="5" t="inlineStr"/>
-      <c r="U41" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V41" s="5" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="inlineStr">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>GPWFWST1</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -7522,52 +4987,14 @@
       <c r="F42" s="5" t="inlineStr"/>
       <c r="G42" s="5" t="inlineStr"/>
       <c r="H42" s="5" t="inlineStr"/>
-      <c r="I42" s="5" t="inlineStr"/>
-      <c r="J42" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K42" s="5" t="inlineStr"/>
-      <c r="L42" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M42" s="5" t="inlineStr"/>
-      <c r="N42" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O42" s="5" t="inlineStr"/>
-      <c r="P42" s="5" t="inlineStr"/>
-      <c r="Q42" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R42" s="5" t="inlineStr"/>
-      <c r="S42" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T42" s="5" t="inlineStr"/>
-      <c r="U42" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>GPWFWST2</t>
         </is>
       </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -7582,52 +5009,14 @@
       <c r="F43" s="5" t="inlineStr"/>
       <c r="G43" s="5" t="inlineStr"/>
       <c r="H43" s="5" t="inlineStr"/>
-      <c r="I43" s="5" t="inlineStr"/>
-      <c r="J43" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K43" s="5" t="inlineStr"/>
-      <c r="L43" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M43" s="5" t="inlineStr"/>
-      <c r="N43" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O43" s="5" t="inlineStr"/>
-      <c r="P43" s="5" t="inlineStr"/>
-      <c r="Q43" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R43" s="5" t="inlineStr"/>
-      <c r="S43" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T43" s="5" t="inlineStr"/>
-      <c r="U43" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="8" t="inlineStr">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>HD1WF1</t>
         </is>
       </c>
-      <c r="B44" s="8" t="inlineStr">
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -7644,52 +5033,14 @@
       </c>
       <c r="G44" s="5" t="inlineStr"/>
       <c r="H44" s="5" t="inlineStr"/>
-      <c r="I44" s="5" t="inlineStr"/>
-      <c r="J44" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K44" s="5" t="inlineStr"/>
-      <c r="L44" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M44" s="5" t="inlineStr"/>
-      <c r="N44" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O44" s="5" t="inlineStr"/>
-      <c r="P44" s="5" t="inlineStr"/>
-      <c r="Q44" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R44" s="5" t="inlineStr"/>
-      <c r="S44" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T44" s="5" t="inlineStr"/>
-      <c r="U44" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V44" s="5" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="8" t="inlineStr">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>HEPWIND1</t>
         </is>
       </c>
-      <c r="B45" s="8" t="inlineStr">
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -7704,52 +5055,14 @@
       <c r="F45" s="5" t="inlineStr"/>
       <c r="G45" s="5" t="inlineStr"/>
       <c r="H45" s="5" t="inlineStr"/>
-      <c r="I45" s="5" t="inlineStr"/>
-      <c r="J45" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K45" s="5" t="inlineStr"/>
-      <c r="L45" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M45" s="5" t="inlineStr"/>
-      <c r="N45" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O45" s="5" t="inlineStr"/>
-      <c r="P45" s="5" t="inlineStr"/>
-      <c r="Q45" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R45" s="5" t="inlineStr"/>
-      <c r="S45" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T45" s="5" t="inlineStr"/>
-      <c r="U45" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V45" s="5" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="8" t="inlineStr">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>KIATAWF1</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr">
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -7768,52 +5081,14 @@
       </c>
       <c r="G46" s="5" t="inlineStr"/>
       <c r="H46" s="5" t="inlineStr"/>
-      <c r="I46" s="5" t="inlineStr"/>
-      <c r="J46" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K46" s="5" t="inlineStr"/>
-      <c r="L46" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M46" s="5" t="inlineStr"/>
-      <c r="N46" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O46" s="5" t="inlineStr"/>
-      <c r="P46" s="5" t="inlineStr"/>
-      <c r="Q46" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R46" s="5" t="inlineStr"/>
-      <c r="S46" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T46" s="5" t="inlineStr"/>
-      <c r="U46" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="8" t="inlineStr">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>MACARTH1</t>
         </is>
       </c>
-      <c r="B47" s="8" t="inlineStr">
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -7832,52 +5107,14 @@
       </c>
       <c r="G47" s="5" t="inlineStr"/>
       <c r="H47" s="5" t="inlineStr"/>
-      <c r="I47" s="5" t="inlineStr"/>
-      <c r="J47" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K47" s="5" t="inlineStr"/>
-      <c r="L47" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M47" s="5" t="inlineStr"/>
-      <c r="N47" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O47" s="5" t="inlineStr"/>
-      <c r="P47" s="5" t="inlineStr"/>
-      <c r="Q47" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R47" s="5" t="inlineStr"/>
-      <c r="S47" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T47" s="5" t="inlineStr"/>
-      <c r="U47" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V47" s="5" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="8" t="inlineStr">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>MAROOWF1</t>
         </is>
       </c>
-      <c r="B48" s="8" t="inlineStr">
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -7892,52 +5129,14 @@
       <c r="F48" s="5" t="inlineStr"/>
       <c r="G48" s="5" t="inlineStr"/>
       <c r="H48" s="5" t="inlineStr"/>
-      <c r="I48" s="5" t="inlineStr"/>
-      <c r="J48" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K48" s="5" t="inlineStr"/>
-      <c r="L48" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M48" s="5" t="inlineStr"/>
-      <c r="N48" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O48" s="5" t="inlineStr"/>
-      <c r="P48" s="5" t="inlineStr"/>
-      <c r="Q48" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R48" s="5" t="inlineStr"/>
-      <c r="S48" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T48" s="5" t="inlineStr"/>
-      <c r="U48" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V48" s="5" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="inlineStr">
+      <c r="A49" s="7" t="inlineStr">
         <is>
           <t>MOORAWF1</t>
         </is>
       </c>
-      <c r="B49" s="8" t="inlineStr">
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -7956,52 +5155,14 @@
       </c>
       <c r="G49" s="5" t="inlineStr"/>
       <c r="H49" s="5" t="inlineStr"/>
-      <c r="I49" s="5" t="inlineStr"/>
-      <c r="J49" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K49" s="5" t="inlineStr"/>
-      <c r="L49" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M49" s="5" t="inlineStr"/>
-      <c r="N49" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O49" s="5" t="inlineStr"/>
-      <c r="P49" s="5" t="inlineStr"/>
-      <c r="Q49" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R49" s="5" t="inlineStr"/>
-      <c r="S49" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T49" s="5" t="inlineStr"/>
-      <c r="U49" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="8" t="inlineStr">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t>MRTLSWF1</t>
         </is>
       </c>
-      <c r="B50" s="8" t="inlineStr">
+      <c r="B50" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -8020,52 +5181,14 @@
       </c>
       <c r="G50" s="5" t="inlineStr"/>
       <c r="H50" s="5" t="inlineStr"/>
-      <c r="I50" s="5" t="inlineStr"/>
-      <c r="J50" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K50" s="5" t="inlineStr"/>
-      <c r="L50" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M50" s="5" t="inlineStr"/>
-      <c r="N50" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O50" s="5" t="inlineStr"/>
-      <c r="P50" s="5" t="inlineStr"/>
-      <c r="Q50" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R50" s="5" t="inlineStr"/>
-      <c r="S50" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T50" s="5" t="inlineStr"/>
-      <c r="U50" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V50" s="5" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="8" t="inlineStr">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>MLWF1</t>
         </is>
       </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -8080,52 +5203,14 @@
       <c r="F51" s="5" t="inlineStr"/>
       <c r="G51" s="5" t="inlineStr"/>
       <c r="H51" s="5" t="inlineStr"/>
-      <c r="I51" s="5" t="inlineStr"/>
-      <c r="J51" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K51" s="5" t="inlineStr"/>
-      <c r="L51" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M51" s="5" t="inlineStr"/>
-      <c r="N51" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O51" s="5" t="inlineStr"/>
-      <c r="P51" s="5" t="inlineStr"/>
-      <c r="Q51" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R51" s="5" t="inlineStr"/>
-      <c r="S51" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T51" s="5" t="inlineStr"/>
-      <c r="U51" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V51" s="5" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="8" t="inlineStr">
+      <c r="A52" s="7" t="inlineStr">
         <is>
           <t>MTGELWF1</t>
         </is>
       </c>
-      <c r="B52" s="8" t="inlineStr">
+      <c r="B52" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -8144,52 +5229,14 @@
       </c>
       <c r="G52" s="5" t="inlineStr"/>
       <c r="H52" s="5" t="inlineStr"/>
-      <c r="I52" s="5" t="inlineStr"/>
-      <c r="J52" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K52" s="5" t="inlineStr"/>
-      <c r="L52" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M52" s="5" t="inlineStr"/>
-      <c r="N52" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O52" s="5" t="inlineStr"/>
-      <c r="P52" s="5" t="inlineStr"/>
-      <c r="Q52" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R52" s="5" t="inlineStr"/>
-      <c r="S52" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T52" s="5" t="inlineStr"/>
-      <c r="U52" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V52" s="5" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="8" t="inlineStr">
+      <c r="A53" s="7" t="inlineStr">
         <is>
           <t>MERCER01</t>
         </is>
       </c>
-      <c r="B53" s="8" t="inlineStr">
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -8208,52 +5255,14 @@
       </c>
       <c r="G53" s="5" t="inlineStr"/>
       <c r="H53" s="5" t="inlineStr"/>
-      <c r="I53" s="5" t="inlineStr"/>
-      <c r="J53" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K53" s="5" t="inlineStr"/>
-      <c r="L53" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M53" s="5" t="inlineStr"/>
-      <c r="N53" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O53" s="5" t="inlineStr"/>
-      <c r="P53" s="5" t="inlineStr"/>
-      <c r="Q53" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R53" s="5" t="inlineStr"/>
-      <c r="S53" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T53" s="5" t="inlineStr"/>
-      <c r="U53" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V53" s="5" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="8" t="inlineStr">
+      <c r="A54" s="7" t="inlineStr">
         <is>
           <t>MUWAWF1</t>
         </is>
       </c>
-      <c r="B54" s="8" t="inlineStr">
+      <c r="B54" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -8272,52 +5281,14 @@
       </c>
       <c r="G54" s="5" t="inlineStr"/>
       <c r="H54" s="5" t="inlineStr"/>
-      <c r="I54" s="5" t="inlineStr"/>
-      <c r="J54" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K54" s="5" t="inlineStr"/>
-      <c r="L54" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M54" s="5" t="inlineStr"/>
-      <c r="N54" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O54" s="5" t="inlineStr"/>
-      <c r="P54" s="5" t="inlineStr"/>
-      <c r="Q54" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R54" s="5" t="inlineStr"/>
-      <c r="S54" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T54" s="5" t="inlineStr"/>
-      <c r="U54" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V54" s="5" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="8" t="inlineStr">
+      <c r="A55" s="7" t="inlineStr">
         <is>
           <t>MUWAWF2</t>
         </is>
       </c>
-      <c r="B55" s="8" t="inlineStr">
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -8336,52 +5307,14 @@
       </c>
       <c r="G55" s="5" t="inlineStr"/>
       <c r="H55" s="5" t="inlineStr"/>
-      <c r="I55" s="5" t="inlineStr"/>
-      <c r="J55" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K55" s="5" t="inlineStr"/>
-      <c r="L55" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M55" s="5" t="inlineStr"/>
-      <c r="N55" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O55" s="5" t="inlineStr"/>
-      <c r="P55" s="5" t="inlineStr"/>
-      <c r="Q55" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R55" s="5" t="inlineStr"/>
-      <c r="S55" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T55" s="5" t="inlineStr"/>
-      <c r="U55" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V55" s="5" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="8" t="inlineStr">
+      <c r="A56" s="7" t="inlineStr">
         <is>
           <t>OAKLAND1</t>
         </is>
       </c>
-      <c r="B56" s="8" t="inlineStr">
+      <c r="B56" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -8400,52 +5333,14 @@
       </c>
       <c r="G56" s="5" t="inlineStr"/>
       <c r="H56" s="5" t="inlineStr"/>
-      <c r="I56" s="5" t="inlineStr"/>
-      <c r="J56" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K56" s="5" t="inlineStr"/>
-      <c r="L56" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M56" s="5" t="inlineStr"/>
-      <c r="N56" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O56" s="5" t="inlineStr"/>
-      <c r="P56" s="5" t="inlineStr"/>
-      <c r="Q56" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R56" s="5" t="inlineStr"/>
-      <c r="S56" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T56" s="5" t="inlineStr"/>
-      <c r="U56" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V56" s="5" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="8" t="inlineStr">
+      <c r="A57" s="7" t="inlineStr">
         <is>
           <t>RYANCWF1</t>
         </is>
       </c>
-      <c r="B57" s="8" t="inlineStr">
+      <c r="B57" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -8462,52 +5357,14 @@
       </c>
       <c r="G57" s="5" t="inlineStr"/>
       <c r="H57" s="5" t="inlineStr"/>
-      <c r="I57" s="5" t="inlineStr"/>
-      <c r="J57" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K57" s="5" t="inlineStr"/>
-      <c r="L57" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M57" s="5" t="inlineStr"/>
-      <c r="N57" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O57" s="5" t="inlineStr"/>
-      <c r="P57" s="5" t="inlineStr"/>
-      <c r="Q57" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R57" s="5" t="inlineStr"/>
-      <c r="S57" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T57" s="5" t="inlineStr"/>
-      <c r="U57" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V57" s="5" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="8" t="inlineStr">
+      <c r="A58" s="7" t="inlineStr">
         <is>
           <t>SALTCRK1</t>
         </is>
       </c>
-      <c r="B58" s="8" t="inlineStr">
+      <c r="B58" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -8526,52 +5383,14 @@
       </c>
       <c r="G58" s="5" t="inlineStr"/>
       <c r="H58" s="5" t="inlineStr"/>
-      <c r="I58" s="5" t="inlineStr"/>
-      <c r="J58" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K58" s="5" t="inlineStr"/>
-      <c r="L58" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M58" s="5" t="inlineStr"/>
-      <c r="N58" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O58" s="5" t="inlineStr"/>
-      <c r="P58" s="5" t="inlineStr"/>
-      <c r="Q58" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R58" s="5" t="inlineStr"/>
-      <c r="S58" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T58" s="5" t="inlineStr"/>
-      <c r="U58" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V58" s="5" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="8" t="inlineStr">
+      <c r="A59" s="7" t="inlineStr">
         <is>
           <t>STOCKYD1</t>
         </is>
       </c>
-      <c r="B59" s="8" t="inlineStr">
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -8590,52 +5409,14 @@
       </c>
       <c r="G59" s="5" t="inlineStr"/>
       <c r="H59" s="5" t="inlineStr"/>
-      <c r="I59" s="5" t="inlineStr"/>
-      <c r="J59" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K59" s="5" t="inlineStr"/>
-      <c r="L59" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M59" s="5" t="inlineStr"/>
-      <c r="N59" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O59" s="5" t="inlineStr"/>
-      <c r="P59" s="5" t="inlineStr"/>
-      <c r="Q59" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R59" s="5" t="inlineStr"/>
-      <c r="S59" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T59" s="5" t="inlineStr"/>
-      <c r="U59" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V59" s="5" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="8" t="inlineStr">
+      <c r="A60" s="7" t="inlineStr">
         <is>
           <t>TIMWEST</t>
         </is>
       </c>
-      <c r="B60" s="8" t="inlineStr">
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -8650,52 +5431,14 @@
       <c r="F60" s="5" t="inlineStr"/>
       <c r="G60" s="5" t="inlineStr"/>
       <c r="H60" s="5" t="inlineStr"/>
-      <c r="I60" s="5" t="inlineStr"/>
-      <c r="J60" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K60" s="5" t="inlineStr"/>
-      <c r="L60" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M60" s="5" t="inlineStr"/>
-      <c r="N60" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O60" s="5" t="inlineStr"/>
-      <c r="P60" s="5" t="inlineStr"/>
-      <c r="Q60" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R60" s="5" t="inlineStr"/>
-      <c r="S60" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T60" s="5" t="inlineStr"/>
-      <c r="U60" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V60" s="5" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="8" t="inlineStr">
+      <c r="A61" s="7" t="inlineStr">
         <is>
           <t>TOORAWF</t>
         </is>
       </c>
-      <c r="B61" s="8" t="inlineStr">
+      <c r="B61" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -8710,52 +5453,14 @@
       <c r="F61" s="5" t="inlineStr"/>
       <c r="G61" s="5" t="inlineStr"/>
       <c r="H61" s="5" t="inlineStr"/>
-      <c r="I61" s="5" t="inlineStr"/>
-      <c r="J61" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K61" s="5" t="inlineStr"/>
-      <c r="L61" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M61" s="5" t="inlineStr"/>
-      <c r="N61" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O61" s="5" t="inlineStr"/>
-      <c r="P61" s="5" t="inlineStr"/>
-      <c r="Q61" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R61" s="5" t="inlineStr"/>
-      <c r="S61" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T61" s="5" t="inlineStr"/>
-      <c r="U61" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V61" s="5" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="8" t="inlineStr">
+      <c r="A62" s="7" t="inlineStr">
         <is>
           <t>WAUBRAWF</t>
         </is>
       </c>
-      <c r="B62" s="8" t="inlineStr">
+      <c r="B62" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -8770,52 +5475,14 @@
       <c r="F62" s="5" t="inlineStr"/>
       <c r="G62" s="5" t="inlineStr"/>
       <c r="H62" s="5" t="inlineStr"/>
-      <c r="I62" s="5" t="inlineStr"/>
-      <c r="J62" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K62" s="5" t="inlineStr"/>
-      <c r="L62" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M62" s="5" t="inlineStr"/>
-      <c r="N62" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O62" s="5" t="inlineStr"/>
-      <c r="P62" s="5" t="inlineStr"/>
-      <c r="Q62" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R62" s="5" t="inlineStr"/>
-      <c r="S62" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T62" s="5" t="inlineStr"/>
-      <c r="U62" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V62" s="5" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="8" t="inlineStr">
+      <c r="A63" s="7" t="inlineStr">
         <is>
           <t>WONWP</t>
         </is>
       </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="B63" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -8830,52 +5497,14 @@
       <c r="F63" s="5" t="inlineStr"/>
       <c r="G63" s="5" t="inlineStr"/>
       <c r="H63" s="5" t="inlineStr"/>
-      <c r="I63" s="5" t="inlineStr"/>
-      <c r="J63" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K63" s="5" t="inlineStr"/>
-      <c r="L63" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M63" s="5" t="inlineStr"/>
-      <c r="N63" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O63" s="5" t="inlineStr"/>
-      <c r="P63" s="5" t="inlineStr"/>
-      <c r="Q63" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R63" s="5" t="inlineStr"/>
-      <c r="S63" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T63" s="5" t="inlineStr"/>
-      <c r="U63" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V63" s="5" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="8" t="inlineStr">
+      <c r="A64" s="7" t="inlineStr">
         <is>
           <t>YSWF1</t>
         </is>
       </c>
-      <c r="B64" s="8" t="inlineStr">
+      <c r="B64" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -8890,52 +5519,14 @@
       <c r="F64" s="5" t="inlineStr"/>
       <c r="G64" s="5" t="inlineStr"/>
       <c r="H64" s="5" t="inlineStr"/>
-      <c r="I64" s="5" t="inlineStr"/>
-      <c r="J64" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K64" s="5" t="inlineStr"/>
-      <c r="L64" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M64" s="5" t="inlineStr"/>
-      <c r="N64" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O64" s="5" t="inlineStr"/>
-      <c r="P64" s="5" t="inlineStr"/>
-      <c r="Q64" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R64" s="5" t="inlineStr"/>
-      <c r="S64" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T64" s="5" t="inlineStr"/>
-      <c r="U64" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V64" s="5" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="8" t="inlineStr">
+      <c r="A65" s="7" t="inlineStr">
         <is>
           <t>YAMBUKWF</t>
         </is>
       </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="B65" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -8950,52 +5541,14 @@
       <c r="F65" s="5" t="inlineStr"/>
       <c r="G65" s="5" t="inlineStr"/>
       <c r="H65" s="5" t="inlineStr"/>
-      <c r="I65" s="5" t="inlineStr"/>
-      <c r="J65" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K65" s="5" t="inlineStr"/>
-      <c r="L65" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M65" s="5" t="inlineStr"/>
-      <c r="N65" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O65" s="5" t="inlineStr"/>
-      <c r="P65" s="5" t="inlineStr"/>
-      <c r="Q65" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R65" s="5" t="inlineStr"/>
-      <c r="S65" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T65" s="5" t="inlineStr"/>
-      <c r="U65" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V65" s="5" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="8" t="inlineStr">
+      <c r="A66" s="7" t="inlineStr">
         <is>
           <t>YAWWF1</t>
         </is>
       </c>
-      <c r="B66" s="8" t="inlineStr">
+      <c r="B66" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -9010,52 +5563,14 @@
       <c r="F66" s="5" t="inlineStr"/>
       <c r="G66" s="5" t="inlineStr"/>
       <c r="H66" s="5" t="inlineStr"/>
-      <c r="I66" s="5" t="inlineStr"/>
-      <c r="J66" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K66" s="5" t="inlineStr"/>
-      <c r="L66" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M66" s="5" t="inlineStr"/>
-      <c r="N66" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O66" s="5" t="inlineStr"/>
-      <c r="P66" s="5" t="inlineStr"/>
-      <c r="Q66" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R66" s="5" t="inlineStr"/>
-      <c r="S66" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T66" s="5" t="inlineStr"/>
-      <c r="U66" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V66" s="5" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="8" t="inlineStr">
+      <c r="A67" s="7" t="inlineStr">
         <is>
           <t>YENDWF1</t>
         </is>
       </c>
-      <c r="B67" s="8" t="inlineStr">
+      <c r="B67" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -9074,44 +5589,6 @@
       </c>
       <c r="G67" s="5" t="inlineStr"/>
       <c r="H67" s="5" t="inlineStr"/>
-      <c r="I67" s="5" t="inlineStr"/>
-      <c r="J67" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K67" s="5" t="inlineStr"/>
-      <c r="L67" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M67" s="5" t="inlineStr"/>
-      <c r="N67" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O67" s="5" t="inlineStr"/>
-      <c r="P67" s="5" t="inlineStr"/>
-      <c r="Q67" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R67" s="5" t="inlineStr"/>
-      <c r="S67" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T67" s="5" t="inlineStr"/>
-      <c r="U67" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V67" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C67">
@@ -9186,174 +5663,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I67">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J67">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K67">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L67">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M67">
-    <cfRule type="colorScale" priority="11">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N67">
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O67">
-    <cfRule type="colorScale" priority="13">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P67">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q67">
-    <cfRule type="colorScale" priority="15">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R67">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S67">
-    <cfRule type="colorScale" priority="17">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T67">
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U67">
-    <cfRule type="colorScale" priority="19">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V67">
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/VIC_curtailment.xlsx
+++ b/outputs/VIC_curtailment.xlsx
@@ -67,7 +67,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -82,6 +82,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -453,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O67"/>
+  <dimension ref="A1:W67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -471,6 +474,14 @@
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -549,6 +560,46 @@
           <t>FY26-27</t>
         </is>
       </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Curt FY1</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Curt FY2</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Curt FY3</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Curt Avg</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Offl FY1</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Offl FY2</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Offl FY3</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Offl Avg</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -609,6 +660,30 @@
       </c>
       <c r="O2" s="5" t="n">
         <v>0.9092</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="6" t="n">
+        <v>0.02666666666666667</v>
+      </c>
+      <c r="T2" s="6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="U2" s="6" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="V2" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="W2" s="6" t="n">
+        <v>0.12</v>
       </c>
     </row>
     <row r="3">
@@ -657,6 +732,14 @@
       <c r="O3" s="5" t="n">
         <v>0.8963</v>
       </c>
+      <c r="P3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr"/>
+      <c r="R3" s="6" t="inlineStr"/>
+      <c r="S3" s="6" t="inlineStr"/>
+      <c r="T3" s="6" t="inlineStr"/>
+      <c r="U3" s="6" t="inlineStr"/>
+      <c r="V3" s="6" t="inlineStr"/>
+      <c r="W3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -714,6 +797,30 @@
       <c r="O4" s="5" t="n">
         <v>0.929</v>
       </c>
+      <c r="P4" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q4" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="6" t="n">
+        <v>0.02666666666666667</v>
+      </c>
+      <c r="T4" s="6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="U4" s="6" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="V4" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="W4" s="6" t="n">
+        <v>0.12</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -774,6 +881,30 @@
       </c>
       <c r="O5" s="5" t="n">
         <v>0.929</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="6" t="n">
+        <v>0.02666666666666667</v>
+      </c>
+      <c r="T5" s="6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="U5" s="6" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="V5" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="W5" s="6" t="n">
+        <v>0.12</v>
       </c>
     </row>
     <row r="6">
@@ -834,6 +965,30 @@
       <c r="O6" s="5" t="n">
         <v>0.921</v>
       </c>
+      <c r="P6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="U6" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="V6" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W6" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -892,6 +1047,30 @@
       </c>
       <c r="O7" s="5" t="n">
         <v>0.9294</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="U7" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="V7" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W7" s="6" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -944,6 +1123,14 @@
       <c r="O8" s="5" t="n">
         <v>0.9211</v>
       </c>
+      <c r="P8" s="6" t="inlineStr"/>
+      <c r="Q8" s="6" t="inlineStr"/>
+      <c r="R8" s="6" t="inlineStr"/>
+      <c r="S8" s="6" t="inlineStr"/>
+      <c r="T8" s="6" t="inlineStr"/>
+      <c r="U8" s="6" t="inlineStr"/>
+      <c r="V8" s="6" t="inlineStr"/>
+      <c r="W8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -991,6 +1178,14 @@
       <c r="O9" s="5" t="n">
         <v>0.9261</v>
       </c>
+      <c r="P9" s="6" t="inlineStr"/>
+      <c r="Q9" s="6" t="inlineStr"/>
+      <c r="R9" s="6" t="inlineStr"/>
+      <c r="S9" s="6" t="inlineStr"/>
+      <c r="T9" s="6" t="inlineStr"/>
+      <c r="U9" s="6" t="inlineStr"/>
+      <c r="V9" s="6" t="inlineStr"/>
+      <c r="W9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1051,6 +1246,30 @@
       </c>
       <c r="O10" s="5" t="n">
         <v>0.9051</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="6" t="n">
+        <v>0.02666666666666667</v>
+      </c>
+      <c r="T10" s="6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="U10" s="6" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="V10" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="W10" s="6" t="n">
+        <v>0.12</v>
       </c>
     </row>
     <row r="11">
@@ -1099,6 +1318,14 @@
       <c r="O11" s="5" t="n">
         <v>0.9311</v>
       </c>
+      <c r="P11" s="6" t="inlineStr"/>
+      <c r="Q11" s="6" t="inlineStr"/>
+      <c r="R11" s="6" t="inlineStr"/>
+      <c r="S11" s="6" t="inlineStr"/>
+      <c r="T11" s="6" t="inlineStr"/>
+      <c r="U11" s="6" t="inlineStr"/>
+      <c r="V11" s="6" t="inlineStr"/>
+      <c r="W11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1159,6 +1386,30 @@
       </c>
       <c r="O12" s="5" t="n">
         <v>0.8738</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="6" t="n">
+        <v>0.02666666666666667</v>
+      </c>
+      <c r="T12" s="6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="U12" s="6" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="V12" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="W12" s="6" t="n">
+        <v>0.12</v>
       </c>
     </row>
     <row r="13">
@@ -1207,6 +1458,14 @@
       <c r="O13" s="5" t="n">
         <v>0.921</v>
       </c>
+      <c r="P13" s="6" t="inlineStr"/>
+      <c r="Q13" s="6" t="inlineStr"/>
+      <c r="R13" s="6" t="inlineStr"/>
+      <c r="S13" s="6" t="inlineStr"/>
+      <c r="T13" s="6" t="inlineStr"/>
+      <c r="U13" s="6" t="inlineStr"/>
+      <c r="V13" s="6" t="inlineStr"/>
+      <c r="W13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1254,6 +1513,14 @@
       <c r="O14" s="5" t="n">
         <v>0.9257</v>
       </c>
+      <c r="P14" s="6" t="inlineStr"/>
+      <c r="Q14" s="6" t="inlineStr"/>
+      <c r="R14" s="6" t="inlineStr"/>
+      <c r="S14" s="6" t="inlineStr"/>
+      <c r="T14" s="6" t="inlineStr"/>
+      <c r="U14" s="6" t="inlineStr"/>
+      <c r="V14" s="6" t="inlineStr"/>
+      <c r="W14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1314,6 +1581,30 @@
       </c>
       <c r="O15" s="5" t="n">
         <v>0.921</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="U15" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="V15" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W15" s="6" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1362,6 +1653,14 @@
       <c r="O16" s="5" t="n">
         <v>0.9282</v>
       </c>
+      <c r="P16" s="6" t="inlineStr"/>
+      <c r="Q16" s="6" t="inlineStr"/>
+      <c r="R16" s="6" t="inlineStr"/>
+      <c r="S16" s="6" t="inlineStr"/>
+      <c r="T16" s="6" t="inlineStr"/>
+      <c r="U16" s="6" t="inlineStr"/>
+      <c r="V16" s="6" t="inlineStr"/>
+      <c r="W16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1422,6 +1721,30 @@
       </c>
       <c r="O17" s="5" t="n">
         <v>0.9092</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="6" t="n">
+        <v>0.02666666666666667</v>
+      </c>
+      <c r="T17" s="6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="U17" s="6" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="V17" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="W17" s="6" t="n">
+        <v>0.12</v>
       </c>
     </row>
     <row r="18">
@@ -1481,6 +1804,30 @@
       </c>
       <c r="O18" s="5" t="n">
         <v>0.9211</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="U18" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="V18" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W18" s="6" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -1539,6 +1886,14 @@
       <c r="O19" s="5" t="n">
         <v>0.921</v>
       </c>
+      <c r="P19" s="6" t="inlineStr"/>
+      <c r="Q19" s="6" t="inlineStr"/>
+      <c r="R19" s="6" t="inlineStr"/>
+      <c r="S19" s="6" t="inlineStr"/>
+      <c r="T19" s="6" t="inlineStr"/>
+      <c r="U19" s="6" t="inlineStr"/>
+      <c r="V19" s="6" t="inlineStr"/>
+      <c r="W19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1599,6 +1954,30 @@
       </c>
       <c r="O20" s="5" t="n">
         <v>0.9051</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q20" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="6" t="n">
+        <v>0.02666666666666667</v>
+      </c>
+      <c r="T20" s="6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="U20" s="6" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="V20" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="W20" s="6" t="n">
+        <v>0.12</v>
       </c>
     </row>
     <row r="21">
@@ -1651,6 +2030,14 @@
       <c r="O21" s="5" t="n">
         <v>0.898</v>
       </c>
+      <c r="P21" s="6" t="inlineStr"/>
+      <c r="Q21" s="6" t="inlineStr"/>
+      <c r="R21" s="6" t="inlineStr"/>
+      <c r="S21" s="6" t="inlineStr"/>
+      <c r="T21" s="6" t="inlineStr"/>
+      <c r="U21" s="6" t="inlineStr"/>
+      <c r="V21" s="6" t="inlineStr"/>
+      <c r="W21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1702,6 +2089,14 @@
       <c r="O22" s="5" t="n">
         <v>0.992</v>
       </c>
+      <c r="P22" s="6" t="inlineStr"/>
+      <c r="Q22" s="6" t="inlineStr"/>
+      <c r="R22" s="6" t="inlineStr"/>
+      <c r="S22" s="6" t="inlineStr"/>
+      <c r="T22" s="6" t="inlineStr"/>
+      <c r="U22" s="6" t="inlineStr"/>
+      <c r="V22" s="6" t="inlineStr"/>
+      <c r="W22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1753,6 +2148,14 @@
       <c r="O23" s="5" t="n">
         <v>0.9436</v>
       </c>
+      <c r="P23" s="6" t="inlineStr"/>
+      <c r="Q23" s="6" t="inlineStr"/>
+      <c r="R23" s="6" t="inlineStr"/>
+      <c r="S23" s="6" t="inlineStr"/>
+      <c r="T23" s="6" t="inlineStr"/>
+      <c r="U23" s="6" t="inlineStr"/>
+      <c r="V23" s="6" t="inlineStr"/>
+      <c r="W23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1804,6 +2207,14 @@
       <c r="O24" s="5" t="n">
         <v>0.9436</v>
       </c>
+      <c r="P24" s="6" t="inlineStr"/>
+      <c r="Q24" s="6" t="inlineStr"/>
+      <c r="R24" s="6" t="inlineStr"/>
+      <c r="S24" s="6" t="inlineStr"/>
+      <c r="T24" s="6" t="inlineStr"/>
+      <c r="U24" s="6" t="inlineStr"/>
+      <c r="V24" s="6" t="inlineStr"/>
+      <c r="W24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1855,6 +2266,14 @@
       <c r="O25" s="5" t="n">
         <v>0.8868</v>
       </c>
+      <c r="P25" s="6" t="inlineStr"/>
+      <c r="Q25" s="6" t="inlineStr"/>
+      <c r="R25" s="6" t="inlineStr"/>
+      <c r="S25" s="6" t="inlineStr"/>
+      <c r="T25" s="6" t="inlineStr"/>
+      <c r="U25" s="6" t="inlineStr"/>
+      <c r="V25" s="6" t="inlineStr"/>
+      <c r="W25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1902,6 +2321,14 @@
       <c r="O26" s="5" t="n">
         <v>0.9791</v>
       </c>
+      <c r="P26" s="6" t="inlineStr"/>
+      <c r="Q26" s="6" t="inlineStr"/>
+      <c r="R26" s="6" t="inlineStr"/>
+      <c r="S26" s="6" t="inlineStr"/>
+      <c r="T26" s="6" t="inlineStr"/>
+      <c r="U26" s="6" t="inlineStr"/>
+      <c r="V26" s="6" t="inlineStr"/>
+      <c r="W26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1947,6 +2374,14 @@
         <v>0.9825</v>
       </c>
       <c r="O27" s="5" t="inlineStr"/>
+      <c r="P27" s="6" t="inlineStr"/>
+      <c r="Q27" s="6" t="inlineStr"/>
+      <c r="R27" s="6" t="inlineStr"/>
+      <c r="S27" s="6" t="inlineStr"/>
+      <c r="T27" s="6" t="inlineStr"/>
+      <c r="U27" s="6" t="inlineStr"/>
+      <c r="V27" s="6" t="inlineStr"/>
+      <c r="W27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1998,6 +2433,14 @@
       <c r="O28" s="5" t="n">
         <v>0.9977</v>
       </c>
+      <c r="P28" s="6" t="inlineStr"/>
+      <c r="Q28" s="6" t="inlineStr"/>
+      <c r="R28" s="6" t="inlineStr"/>
+      <c r="S28" s="6" t="inlineStr"/>
+      <c r="T28" s="6" t="inlineStr"/>
+      <c r="U28" s="6" t="inlineStr"/>
+      <c r="V28" s="6" t="inlineStr"/>
+      <c r="W28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2045,6 +2488,14 @@
       <c r="O29" s="5" t="n">
         <v>0.9949</v>
       </c>
+      <c r="P29" s="6" t="inlineStr"/>
+      <c r="Q29" s="6" t="inlineStr"/>
+      <c r="R29" s="6" t="inlineStr"/>
+      <c r="S29" s="6" t="inlineStr"/>
+      <c r="T29" s="6" t="inlineStr"/>
+      <c r="U29" s="6" t="inlineStr"/>
+      <c r="V29" s="6" t="inlineStr"/>
+      <c r="W29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2092,6 +2543,14 @@
       <c r="O30" s="5" t="n">
         <v>1.0031</v>
       </c>
+      <c r="P30" s="6" t="inlineStr"/>
+      <c r="Q30" s="6" t="inlineStr"/>
+      <c r="R30" s="6" t="inlineStr"/>
+      <c r="S30" s="6" t="inlineStr"/>
+      <c r="T30" s="6" t="inlineStr"/>
+      <c r="U30" s="6" t="inlineStr"/>
+      <c r="V30" s="6" t="inlineStr"/>
+      <c r="W30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2143,6 +2602,14 @@
       <c r="O31" s="5" t="n">
         <v>0.8966</v>
       </c>
+      <c r="P31" s="6" t="inlineStr"/>
+      <c r="Q31" s="6" t="inlineStr"/>
+      <c r="R31" s="6" t="inlineStr"/>
+      <c r="S31" s="6" t="inlineStr"/>
+      <c r="T31" s="6" t="inlineStr"/>
+      <c r="U31" s="6" t="inlineStr"/>
+      <c r="V31" s="6" t="inlineStr"/>
+      <c r="W31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2190,6 +2657,14 @@
       <c r="O32" s="5" t="n">
         <v>0.8954</v>
       </c>
+      <c r="P32" s="6" t="inlineStr"/>
+      <c r="Q32" s="6" t="inlineStr"/>
+      <c r="R32" s="6" t="inlineStr"/>
+      <c r="S32" s="6" t="inlineStr"/>
+      <c r="T32" s="6" t="inlineStr"/>
+      <c r="U32" s="6" t="inlineStr"/>
+      <c r="V32" s="6" t="inlineStr"/>
+      <c r="W32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2241,6 +2716,14 @@
       <c r="O33" s="5" t="n">
         <v>0.9827</v>
       </c>
+      <c r="P33" s="6" t="inlineStr"/>
+      <c r="Q33" s="6" t="inlineStr"/>
+      <c r="R33" s="6" t="inlineStr"/>
+      <c r="S33" s="6" t="inlineStr"/>
+      <c r="T33" s="6" t="inlineStr"/>
+      <c r="U33" s="6" t="inlineStr"/>
+      <c r="V33" s="6" t="inlineStr"/>
+      <c r="W33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2292,6 +2775,14 @@
       <c r="O34" s="5" t="n">
         <v>0.9827</v>
       </c>
+      <c r="P34" s="6" t="inlineStr"/>
+      <c r="Q34" s="6" t="inlineStr"/>
+      <c r="R34" s="6" t="inlineStr"/>
+      <c r="S34" s="6" t="inlineStr"/>
+      <c r="T34" s="6" t="inlineStr"/>
+      <c r="U34" s="6" t="inlineStr"/>
+      <c r="V34" s="6" t="inlineStr"/>
+      <c r="W34" s="6" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2343,6 +2834,14 @@
       <c r="O35" s="5" t="n">
         <v>0.9827</v>
       </c>
+      <c r="P35" s="6" t="inlineStr"/>
+      <c r="Q35" s="6" t="inlineStr"/>
+      <c r="R35" s="6" t="inlineStr"/>
+      <c r="S35" s="6" t="inlineStr"/>
+      <c r="T35" s="6" t="inlineStr"/>
+      <c r="U35" s="6" t="inlineStr"/>
+      <c r="V35" s="6" t="inlineStr"/>
+      <c r="W35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2392,6 +2891,14 @@
       <c r="O36" s="5" t="n">
         <v>0.9556</v>
       </c>
+      <c r="P36" s="6" t="inlineStr"/>
+      <c r="Q36" s="6" t="inlineStr"/>
+      <c r="R36" s="6" t="inlineStr"/>
+      <c r="S36" s="6" t="inlineStr"/>
+      <c r="T36" s="6" t="inlineStr"/>
+      <c r="U36" s="6" t="inlineStr"/>
+      <c r="V36" s="6" t="inlineStr"/>
+      <c r="W36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2435,6 +2942,14 @@
       <c r="M37" s="5" t="inlineStr"/>
       <c r="N37" s="5" t="inlineStr"/>
       <c r="O37" s="5" t="inlineStr"/>
+      <c r="P37" s="6" t="inlineStr"/>
+      <c r="Q37" s="6" t="inlineStr"/>
+      <c r="R37" s="6" t="inlineStr"/>
+      <c r="S37" s="6" t="inlineStr"/>
+      <c r="T37" s="6" t="inlineStr"/>
+      <c r="U37" s="6" t="inlineStr"/>
+      <c r="V37" s="6" t="inlineStr"/>
+      <c r="W37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2482,6 +2997,14 @@
       <c r="O38" s="5" t="n">
         <v>0.9949</v>
       </c>
+      <c r="P38" s="6" t="inlineStr"/>
+      <c r="Q38" s="6" t="inlineStr"/>
+      <c r="R38" s="6" t="inlineStr"/>
+      <c r="S38" s="6" t="inlineStr"/>
+      <c r="T38" s="6" t="inlineStr"/>
+      <c r="U38" s="6" t="inlineStr"/>
+      <c r="V38" s="6" t="inlineStr"/>
+      <c r="W38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2529,6 +3052,14 @@
       <c r="O39" s="5" t="n">
         <v>0.9815</v>
       </c>
+      <c r="P39" s="6" t="inlineStr"/>
+      <c r="Q39" s="6" t="inlineStr"/>
+      <c r="R39" s="6" t="inlineStr"/>
+      <c r="S39" s="6" t="inlineStr"/>
+      <c r="T39" s="6" t="inlineStr"/>
+      <c r="U39" s="6" t="inlineStr"/>
+      <c r="V39" s="6" t="inlineStr"/>
+      <c r="W39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2576,6 +3107,14 @@
       <c r="O40" s="5" t="n">
         <v>0.9815</v>
       </c>
+      <c r="P40" s="6" t="inlineStr"/>
+      <c r="Q40" s="6" t="inlineStr"/>
+      <c r="R40" s="6" t="inlineStr"/>
+      <c r="S40" s="6" t="inlineStr"/>
+      <c r="T40" s="6" t="inlineStr"/>
+      <c r="U40" s="6" t="inlineStr"/>
+      <c r="V40" s="6" t="inlineStr"/>
+      <c r="W40" s="6" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2623,6 +3162,14 @@
       <c r="O41" s="5" t="n">
         <v>0.9815</v>
       </c>
+      <c r="P41" s="6" t="inlineStr"/>
+      <c r="Q41" s="6" t="inlineStr"/>
+      <c r="R41" s="6" t="inlineStr"/>
+      <c r="S41" s="6" t="inlineStr"/>
+      <c r="T41" s="6" t="inlineStr"/>
+      <c r="U41" s="6" t="inlineStr"/>
+      <c r="V41" s="6" t="inlineStr"/>
+      <c r="W41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2670,6 +3217,14 @@
       <c r="O42" s="5" t="n">
         <v>0.9823</v>
       </c>
+      <c r="P42" s="6" t="inlineStr"/>
+      <c r="Q42" s="6" t="inlineStr"/>
+      <c r="R42" s="6" t="inlineStr"/>
+      <c r="S42" s="6" t="inlineStr"/>
+      <c r="T42" s="6" t="inlineStr"/>
+      <c r="U42" s="6" t="inlineStr"/>
+      <c r="V42" s="6" t="inlineStr"/>
+      <c r="W42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2717,6 +3272,14 @@
       <c r="O43" s="5" t="n">
         <v>0.9823</v>
       </c>
+      <c r="P43" s="6" t="inlineStr"/>
+      <c r="Q43" s="6" t="inlineStr"/>
+      <c r="R43" s="6" t="inlineStr"/>
+      <c r="S43" s="6" t="inlineStr"/>
+      <c r="T43" s="6" t="inlineStr"/>
+      <c r="U43" s="6" t="inlineStr"/>
+      <c r="V43" s="6" t="inlineStr"/>
+      <c r="W43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2766,6 +3329,14 @@
       <c r="O44" s="5" t="n">
         <v>0.9822</v>
       </c>
+      <c r="P44" s="6" t="inlineStr"/>
+      <c r="Q44" s="6" t="inlineStr"/>
+      <c r="R44" s="6" t="inlineStr"/>
+      <c r="S44" s="6" t="inlineStr"/>
+      <c r="T44" s="6" t="inlineStr"/>
+      <c r="U44" s="6" t="inlineStr"/>
+      <c r="V44" s="6" t="inlineStr"/>
+      <c r="W44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -2813,6 +3384,14 @@
       <c r="O45" s="5" t="n">
         <v>0.9791</v>
       </c>
+      <c r="P45" s="6" t="inlineStr"/>
+      <c r="Q45" s="6" t="inlineStr"/>
+      <c r="R45" s="6" t="inlineStr"/>
+      <c r="S45" s="6" t="inlineStr"/>
+      <c r="T45" s="6" t="inlineStr"/>
+      <c r="U45" s="6" t="inlineStr"/>
+      <c r="V45" s="6" t="inlineStr"/>
+      <c r="W45" s="6" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2864,6 +3443,14 @@
       <c r="O46" s="5" t="n">
         <v>0.8954</v>
       </c>
+      <c r="P46" s="6" t="inlineStr"/>
+      <c r="Q46" s="6" t="inlineStr"/>
+      <c r="R46" s="6" t="inlineStr"/>
+      <c r="S46" s="6" t="inlineStr"/>
+      <c r="T46" s="6" t="inlineStr"/>
+      <c r="U46" s="6" t="inlineStr"/>
+      <c r="V46" s="6" t="inlineStr"/>
+      <c r="W46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2915,6 +3502,14 @@
       <c r="O47" s="5" t="n">
         <v>0.9824000000000001</v>
       </c>
+      <c r="P47" s="6" t="inlineStr"/>
+      <c r="Q47" s="6" t="inlineStr"/>
+      <c r="R47" s="6" t="inlineStr"/>
+      <c r="S47" s="6" t="inlineStr"/>
+      <c r="T47" s="6" t="inlineStr"/>
+      <c r="U47" s="6" t="inlineStr"/>
+      <c r="V47" s="6" t="inlineStr"/>
+      <c r="W47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2962,6 +3557,14 @@
       <c r="O48" s="5" t="n">
         <v>0.9791</v>
       </c>
+      <c r="P48" s="6" t="inlineStr"/>
+      <c r="Q48" s="6" t="inlineStr"/>
+      <c r="R48" s="6" t="inlineStr"/>
+      <c r="S48" s="6" t="inlineStr"/>
+      <c r="T48" s="6" t="inlineStr"/>
+      <c r="U48" s="6" t="inlineStr"/>
+      <c r="V48" s="6" t="inlineStr"/>
+      <c r="W48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -3013,6 +3616,14 @@
       <c r="O49" s="5" t="n">
         <v>0.9556</v>
       </c>
+      <c r="P49" s="6" t="inlineStr"/>
+      <c r="Q49" s="6" t="inlineStr"/>
+      <c r="R49" s="6" t="inlineStr"/>
+      <c r="S49" s="6" t="inlineStr"/>
+      <c r="T49" s="6" t="inlineStr"/>
+      <c r="U49" s="6" t="inlineStr"/>
+      <c r="V49" s="6" t="inlineStr"/>
+      <c r="W49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3064,6 +3675,14 @@
       <c r="O50" s="5" t="n">
         <v>0.9507</v>
       </c>
+      <c r="P50" s="6" t="inlineStr"/>
+      <c r="Q50" s="6" t="inlineStr"/>
+      <c r="R50" s="6" t="inlineStr"/>
+      <c r="S50" s="6" t="inlineStr"/>
+      <c r="T50" s="6" t="inlineStr"/>
+      <c r="U50" s="6" t="inlineStr"/>
+      <c r="V50" s="6" t="inlineStr"/>
+      <c r="W50" s="6" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3111,6 +3730,14 @@
       <c r="O51" s="5" t="n">
         <v>0.9949</v>
       </c>
+      <c r="P51" s="6" t="inlineStr"/>
+      <c r="Q51" s="6" t="inlineStr"/>
+      <c r="R51" s="6" t="inlineStr"/>
+      <c r="S51" s="6" t="inlineStr"/>
+      <c r="T51" s="6" t="inlineStr"/>
+      <c r="U51" s="6" t="inlineStr"/>
+      <c r="V51" s="6" t="inlineStr"/>
+      <c r="W51" s="6" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3162,6 +3789,14 @@
       <c r="O52" s="5" t="n">
         <v>0.989</v>
       </c>
+      <c r="P52" s="6" t="inlineStr"/>
+      <c r="Q52" s="6" t="inlineStr"/>
+      <c r="R52" s="6" t="inlineStr"/>
+      <c r="S52" s="6" t="inlineStr"/>
+      <c r="T52" s="6" t="inlineStr"/>
+      <c r="U52" s="6" t="inlineStr"/>
+      <c r="V52" s="6" t="inlineStr"/>
+      <c r="W52" s="6" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -3213,6 +3848,14 @@
       <c r="O53" s="5" t="n">
         <v>0.9556</v>
       </c>
+      <c r="P53" s="6" t="inlineStr"/>
+      <c r="Q53" s="6" t="inlineStr"/>
+      <c r="R53" s="6" t="inlineStr"/>
+      <c r="S53" s="6" t="inlineStr"/>
+      <c r="T53" s="6" t="inlineStr"/>
+      <c r="U53" s="6" t="inlineStr"/>
+      <c r="V53" s="6" t="inlineStr"/>
+      <c r="W53" s="6" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -3264,6 +3907,14 @@
       <c r="O54" s="5" t="n">
         <v>0.8824</v>
       </c>
+      <c r="P54" s="6" t="inlineStr"/>
+      <c r="Q54" s="6" t="inlineStr"/>
+      <c r="R54" s="6" t="inlineStr"/>
+      <c r="S54" s="6" t="inlineStr"/>
+      <c r="T54" s="6" t="inlineStr"/>
+      <c r="U54" s="6" t="inlineStr"/>
+      <c r="V54" s="6" t="inlineStr"/>
+      <c r="W54" s="6" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3315,6 +3966,14 @@
       <c r="O55" s="5" t="n">
         <v>0.8824</v>
       </c>
+      <c r="P55" s="6" t="inlineStr"/>
+      <c r="Q55" s="6" t="inlineStr"/>
+      <c r="R55" s="6" t="inlineStr"/>
+      <c r="S55" s="6" t="inlineStr"/>
+      <c r="T55" s="6" t="inlineStr"/>
+      <c r="U55" s="6" t="inlineStr"/>
+      <c r="V55" s="6" t="inlineStr"/>
+      <c r="W55" s="6" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3366,6 +4025,14 @@
       <c r="O56" s="5" t="n">
         <v>0.9949</v>
       </c>
+      <c r="P56" s="6" t="inlineStr"/>
+      <c r="Q56" s="6" t="inlineStr"/>
+      <c r="R56" s="6" t="inlineStr"/>
+      <c r="S56" s="6" t="inlineStr"/>
+      <c r="T56" s="6" t="inlineStr"/>
+      <c r="U56" s="6" t="inlineStr"/>
+      <c r="V56" s="6" t="inlineStr"/>
+      <c r="W56" s="6" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -3415,6 +4082,14 @@
       <c r="O57" s="5" t="n">
         <v>0.983</v>
       </c>
+      <c r="P57" s="6" t="inlineStr"/>
+      <c r="Q57" s="6" t="inlineStr"/>
+      <c r="R57" s="6" t="inlineStr"/>
+      <c r="S57" s="6" t="inlineStr"/>
+      <c r="T57" s="6" t="inlineStr"/>
+      <c r="U57" s="6" t="inlineStr"/>
+      <c r="V57" s="6" t="inlineStr"/>
+      <c r="W57" s="6" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -3466,6 +4141,14 @@
       <c r="O58" s="5" t="n">
         <v>0.9499</v>
       </c>
+      <c r="P58" s="6" t="inlineStr"/>
+      <c r="Q58" s="6" t="inlineStr"/>
+      <c r="R58" s="6" t="inlineStr"/>
+      <c r="S58" s="6" t="inlineStr"/>
+      <c r="T58" s="6" t="inlineStr"/>
+      <c r="U58" s="6" t="inlineStr"/>
+      <c r="V58" s="6" t="inlineStr"/>
+      <c r="W58" s="6" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -3517,6 +4200,14 @@
       <c r="O59" s="5" t="n">
         <v>0.9827</v>
       </c>
+      <c r="P59" s="6" t="inlineStr"/>
+      <c r="Q59" s="6" t="inlineStr"/>
+      <c r="R59" s="6" t="inlineStr"/>
+      <c r="S59" s="6" t="inlineStr"/>
+      <c r="T59" s="6" t="inlineStr"/>
+      <c r="U59" s="6" t="inlineStr"/>
+      <c r="V59" s="6" t="inlineStr"/>
+      <c r="W59" s="6" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -3564,6 +4255,14 @@
       <c r="O60" s="5" t="n">
         <v>0.9949</v>
       </c>
+      <c r="P60" s="6" t="inlineStr"/>
+      <c r="Q60" s="6" t="inlineStr"/>
+      <c r="R60" s="6" t="inlineStr"/>
+      <c r="S60" s="6" t="inlineStr"/>
+      <c r="T60" s="6" t="inlineStr"/>
+      <c r="U60" s="6" t="inlineStr"/>
+      <c r="V60" s="6" t="inlineStr"/>
+      <c r="W60" s="6" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -3611,6 +4310,14 @@
       <c r="O61" s="5" t="n">
         <v>0.992</v>
       </c>
+      <c r="P61" s="6" t="inlineStr"/>
+      <c r="Q61" s="6" t="inlineStr"/>
+      <c r="R61" s="6" t="inlineStr"/>
+      <c r="S61" s="6" t="inlineStr"/>
+      <c r="T61" s="6" t="inlineStr"/>
+      <c r="U61" s="6" t="inlineStr"/>
+      <c r="V61" s="6" t="inlineStr"/>
+      <c r="W61" s="6" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -3658,6 +4365,14 @@
       <c r="O62" s="5" t="n">
         <v>0.9298999999999999</v>
       </c>
+      <c r="P62" s="6" t="inlineStr"/>
+      <c r="Q62" s="6" t="inlineStr"/>
+      <c r="R62" s="6" t="inlineStr"/>
+      <c r="S62" s="6" t="inlineStr"/>
+      <c r="T62" s="6" t="inlineStr"/>
+      <c r="U62" s="6" t="inlineStr"/>
+      <c r="V62" s="6" t="inlineStr"/>
+      <c r="W62" s="6" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -3705,6 +4420,14 @@
       <c r="O63" s="5" t="n">
         <v>0.992</v>
       </c>
+      <c r="P63" s="6" t="inlineStr"/>
+      <c r="Q63" s="6" t="inlineStr"/>
+      <c r="R63" s="6" t="inlineStr"/>
+      <c r="S63" s="6" t="inlineStr"/>
+      <c r="T63" s="6" t="inlineStr"/>
+      <c r="U63" s="6" t="inlineStr"/>
+      <c r="V63" s="6" t="inlineStr"/>
+      <c r="W63" s="6" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -3752,6 +4475,14 @@
       <c r="O64" s="5" t="n">
         <v>0.9791</v>
       </c>
+      <c r="P64" s="6" t="inlineStr"/>
+      <c r="Q64" s="6" t="inlineStr"/>
+      <c r="R64" s="6" t="inlineStr"/>
+      <c r="S64" s="6" t="inlineStr"/>
+      <c r="T64" s="6" t="inlineStr"/>
+      <c r="U64" s="6" t="inlineStr"/>
+      <c r="V64" s="6" t="inlineStr"/>
+      <c r="W64" s="6" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -3799,6 +4530,14 @@
       <c r="O65" s="5" t="n">
         <v>0.9949</v>
       </c>
+      <c r="P65" s="6" t="inlineStr"/>
+      <c r="Q65" s="6" t="inlineStr"/>
+      <c r="R65" s="6" t="inlineStr"/>
+      <c r="S65" s="6" t="inlineStr"/>
+      <c r="T65" s="6" t="inlineStr"/>
+      <c r="U65" s="6" t="inlineStr"/>
+      <c r="V65" s="6" t="inlineStr"/>
+      <c r="W65" s="6" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -3846,6 +4585,14 @@
       <c r="O66" s="5" t="n">
         <v>1.0031</v>
       </c>
+      <c r="P66" s="6" t="inlineStr"/>
+      <c r="Q66" s="6" t="inlineStr"/>
+      <c r="R66" s="6" t="inlineStr"/>
+      <c r="S66" s="6" t="inlineStr"/>
+      <c r="T66" s="6" t="inlineStr"/>
+      <c r="U66" s="6" t="inlineStr"/>
+      <c r="V66" s="6" t="inlineStr"/>
+      <c r="W66" s="6" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -3897,6 +4644,14 @@
       <c r="O67" s="5" t="n">
         <v>0.9547</v>
       </c>
+      <c r="P67" s="6" t="inlineStr"/>
+      <c r="Q67" s="6" t="inlineStr"/>
+      <c r="R67" s="6" t="inlineStr"/>
+      <c r="S67" s="6" t="inlineStr"/>
+      <c r="T67" s="6" t="inlineStr"/>
+      <c r="U67" s="6" t="inlineStr"/>
+      <c r="V67" s="6" t="inlineStr"/>
+      <c r="W67" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3909,7 +4664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:V67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3920,57 +4675,141 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>DUID</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>Fuel</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>MLF_FY25-26</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>MLF_FY26-27</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>CURTAILMENT_ACTUAL_FY23-24</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>CURTAILMENT_ACTUAL_FY24-25</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>ELI_CURTAILMENT_NEAR</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>ELI_CURTAILMENT_MED</t>
         </is>
       </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_FY1</t>
+        </is>
+      </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_FY1_LABEL</t>
+        </is>
+      </c>
+      <c r="K1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_FY2</t>
+        </is>
+      </c>
+      <c r="L1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_FY2_LABEL</t>
+        </is>
+      </c>
+      <c r="M1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_FY3</t>
+        </is>
+      </c>
+      <c r="N1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_FY3_LABEL</t>
+        </is>
+      </c>
+      <c r="O1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_AVG</t>
+        </is>
+      </c>
+      <c r="P1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_FY1</t>
+        </is>
+      </c>
+      <c r="Q1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_FY1_LABEL</t>
+        </is>
+      </c>
+      <c r="R1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_FY2</t>
+        </is>
+      </c>
+      <c r="S1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_FY2_LABEL</t>
+        </is>
+      </c>
+      <c r="T1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_FY3</t>
+        </is>
+      </c>
+      <c r="U1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_FY3_LABEL</t>
+        </is>
+      </c>
+      <c r="V1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_AVG</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>BANN1</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3993,14 +4832,68 @@
       <c r="H2" s="5" t="n">
         <v>0.164192244302687</v>
       </c>
+      <c r="I2" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="n">
+        <v>0.02666666666666667</v>
+      </c>
+      <c r="P2" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="U2" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V2" s="5" t="n">
+        <v>0.12</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>CRWARP1</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4015,14 +4908,52 @@
       <c r="F3" s="5" t="inlineStr"/>
       <c r="G3" s="5" t="inlineStr"/>
       <c r="H3" s="5" t="inlineStr"/>
+      <c r="I3" s="5" t="inlineStr"/>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr"/>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr"/>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr"/>
+      <c r="U3" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>COHUNSF1</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4041,14 +4972,68 @@
       <c r="H4" s="5" t="n">
         <v>0.122422882740379</v>
       </c>
+      <c r="I4" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="n">
+        <v>0.02666666666666667</v>
+      </c>
+      <c r="P4" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="U4" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V4" s="5" t="n">
+        <v>0.12</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>GANNSF1</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4071,14 +5056,68 @@
       <c r="H5" s="5" t="n">
         <v>0.122422882740379</v>
       </c>
+      <c r="I5" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O5" s="5" t="n">
+        <v>0.02666666666666667</v>
+      </c>
+      <c r="P5" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R5" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="S5" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T5" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="U5" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V5" s="5" t="n">
+        <v>0.12</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>GIRGSF</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4099,14 +5138,68 @@
       <c r="H6" s="5" t="n">
         <v>0.08205629867681941</v>
       </c>
+      <c r="I6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Q6" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R6" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="S6" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T6" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="U6" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V6" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>GLENSF1</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4127,14 +5220,68 @@
       <c r="H7" s="5" t="n">
         <v>0.08997768712489811</v>
       </c>
+      <c r="I7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Q7" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R7" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="S7" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T7" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="U7" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V7" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>GLRWNSF1</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4153,14 +5300,52 @@
       </c>
       <c r="G8" s="5" t="inlineStr"/>
       <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr"/>
+      <c r="N8" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O8" s="5" t="inlineStr"/>
+      <c r="P8" s="5" t="inlineStr"/>
+      <c r="Q8" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R8" s="5" t="inlineStr"/>
+      <c r="S8" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T8" s="5" t="inlineStr"/>
+      <c r="U8" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>GOESF1</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4175,14 +5360,52 @@
       <c r="F9" s="5" t="inlineStr"/>
       <c r="G9" s="5" t="inlineStr"/>
       <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O9" s="5" t="inlineStr"/>
+      <c r="P9" s="5" t="inlineStr"/>
+      <c r="Q9" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R9" s="5" t="inlineStr"/>
+      <c r="S9" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T9" s="5" t="inlineStr"/>
+      <c r="U9" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>KARSF1</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4205,14 +5428,68 @@
       <c r="H10" s="5" t="n">
         <v>0.072415601225557</v>
       </c>
+      <c r="I10" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O10" s="5" t="n">
+        <v>0.02666666666666667</v>
+      </c>
+      <c r="P10" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Q10" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R10" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="S10" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T10" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="U10" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V10" s="5" t="n">
+        <v>0.12</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>KERNGSP1</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4227,14 +5504,52 @@
       <c r="F11" s="5" t="inlineStr"/>
       <c r="G11" s="5" t="inlineStr"/>
       <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O11" s="5" t="inlineStr"/>
+      <c r="P11" s="5" t="inlineStr"/>
+      <c r="Q11" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R11" s="5" t="inlineStr"/>
+      <c r="S11" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T11" s="5" t="inlineStr"/>
+      <c r="U11" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>KIAMSF1</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4257,14 +5572,68 @@
       <c r="H12" s="5" t="n">
         <v>0.0878331516592939</v>
       </c>
+      <c r="I12" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O12" s="5" t="n">
+        <v>0.02666666666666667</v>
+      </c>
+      <c r="P12" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Q12" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R12" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="S12" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T12" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="U12" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V12" s="5" t="n">
+        <v>0.12</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>LANCSF1</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4279,14 +5648,52 @@
       <c r="F13" s="5" t="inlineStr"/>
       <c r="G13" s="5" t="inlineStr"/>
       <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O13" s="5" t="inlineStr"/>
+      <c r="P13" s="5" t="inlineStr"/>
+      <c r="Q13" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R13" s="5" t="inlineStr"/>
+      <c r="S13" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T13" s="5" t="inlineStr"/>
+      <c r="U13" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>MOKOSF1</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4301,14 +5708,52 @@
       <c r="F14" s="5" t="inlineStr"/>
       <c r="G14" s="5" t="inlineStr"/>
       <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="inlineStr"/>
+      <c r="N14" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O14" s="5" t="inlineStr"/>
+      <c r="P14" s="5" t="inlineStr"/>
+      <c r="Q14" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R14" s="5" t="inlineStr"/>
+      <c r="S14" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T14" s="5" t="inlineStr"/>
+      <c r="U14" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>NUMURSF1</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4331,14 +5776,68 @@
       <c r="H15" s="5" t="n">
         <v>0.08205629867681941</v>
       </c>
+      <c r="I15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Q15" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R15" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="S15" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T15" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="U15" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V15" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>WNSF1</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4353,14 +5852,52 @@
       <c r="F16" s="5" t="inlineStr"/>
       <c r="G16" s="5" t="inlineStr"/>
       <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr"/>
+      <c r="N16" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O16" s="5" t="inlineStr"/>
+      <c r="P16" s="5" t="inlineStr"/>
+      <c r="Q16" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R16" s="5" t="inlineStr"/>
+      <c r="S16" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T16" s="5" t="inlineStr"/>
+      <c r="U16" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>WEMENSF1</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4383,14 +5920,68 @@
       <c r="H17" s="5" t="n">
         <v>0.164192244302687</v>
       </c>
+      <c r="I17" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O17" s="5" t="n">
+        <v>0.02666666666666667</v>
+      </c>
+      <c r="P17" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Q17" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R17" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="S17" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T17" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="U17" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V17" s="5" t="n">
+        <v>0.12</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>WINTSF1</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4411,14 +6002,68 @@
       <c r="H18" s="5" t="n">
         <v>0.08997768712489811</v>
       </c>
+      <c r="I18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Q18" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R18" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="S18" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T18" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="U18" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V18" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>WUNUSF1</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4437,14 +6082,52 @@
       <c r="H19" s="5" t="n">
         <v>0.08205629867681941</v>
       </c>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O19" s="5" t="inlineStr"/>
+      <c r="P19" s="5" t="inlineStr"/>
+      <c r="Q19" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R19" s="5" t="inlineStr"/>
+      <c r="S19" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T19" s="5" t="inlineStr"/>
+      <c r="U19" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>YATSF1</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4467,14 +6150,68 @@
       <c r="H20" s="5" t="n">
         <v>0.072415601225557</v>
       </c>
+      <c r="I20" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O20" s="5" t="n">
+        <v>0.02666666666666667</v>
+      </c>
+      <c r="P20" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Q20" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R20" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="S20" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T20" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="U20" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V20" s="5" t="n">
+        <v>0.12</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>ARWF1</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4493,14 +6230,52 @@
       </c>
       <c r="G21" s="5" t="inlineStr"/>
       <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O21" s="5" t="inlineStr"/>
+      <c r="P21" s="5" t="inlineStr"/>
+      <c r="Q21" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R21" s="5" t="inlineStr"/>
+      <c r="S21" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T21" s="5" t="inlineStr"/>
+      <c r="U21" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>BALDHWF1</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4519,14 +6294,52 @@
       </c>
       <c r="G22" s="5" t="inlineStr"/>
       <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr"/>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr"/>
+      <c r="N22" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O22" s="5" t="inlineStr"/>
+      <c r="P22" s="5" t="inlineStr"/>
+      <c r="Q22" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R22" s="5" t="inlineStr"/>
+      <c r="S22" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T22" s="5" t="inlineStr"/>
+      <c r="U22" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>BRYB2WF2</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4545,14 +6358,52 @@
       </c>
       <c r="G23" s="5" t="inlineStr"/>
       <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr"/>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O23" s="5" t="inlineStr"/>
+      <c r="P23" s="5" t="inlineStr"/>
+      <c r="Q23" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R23" s="5" t="inlineStr"/>
+      <c r="S23" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T23" s="5" t="inlineStr"/>
+      <c r="U23" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>BRYB1WF1</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4571,14 +6422,52 @@
       </c>
       <c r="G24" s="5" t="inlineStr"/>
       <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr"/>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="inlineStr"/>
+      <c r="N24" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O24" s="5" t="inlineStr"/>
+      <c r="P24" s="5" t="inlineStr"/>
+      <c r="Q24" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R24" s="5" t="inlineStr"/>
+      <c r="S24" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T24" s="5" t="inlineStr"/>
+      <c r="U24" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>BULGANA1</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4597,14 +6486,52 @@
       </c>
       <c r="G25" s="5" t="inlineStr"/>
       <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr"/>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O25" s="5" t="inlineStr"/>
+      <c r="P25" s="5" t="inlineStr"/>
+      <c r="Q25" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R25" s="5" t="inlineStr"/>
+      <c r="S25" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T25" s="5" t="inlineStr"/>
+      <c r="U25" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>CHALLHWF</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4619,14 +6546,52 @@
       <c r="F26" s="5" t="inlineStr"/>
       <c r="G26" s="5" t="inlineStr"/>
       <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr"/>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M26" s="5" t="inlineStr"/>
+      <c r="N26" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O26" s="5" t="inlineStr"/>
+      <c r="P26" s="5" t="inlineStr"/>
+      <c r="Q26" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R26" s="5" t="inlineStr"/>
+      <c r="S26" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T26" s="5" t="inlineStr"/>
+      <c r="U26" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>CHPSTWF1</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4639,14 +6604,52 @@
       <c r="F27" s="5" t="inlineStr"/>
       <c r="G27" s="5" t="inlineStr"/>
       <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O27" s="5" t="inlineStr"/>
+      <c r="P27" s="5" t="inlineStr"/>
+      <c r="Q27" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R27" s="5" t="inlineStr"/>
+      <c r="S27" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T27" s="5" t="inlineStr"/>
+      <c r="U27" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>CHYTWF1</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4665,14 +6668,52 @@
       </c>
       <c r="G28" s="5" t="inlineStr"/>
       <c r="H28" s="5" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr"/>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M28" s="5" t="inlineStr"/>
+      <c r="N28" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O28" s="5" t="inlineStr"/>
+      <c r="P28" s="5" t="inlineStr"/>
+      <c r="Q28" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R28" s="5" t="inlineStr"/>
+      <c r="S28" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T28" s="5" t="inlineStr"/>
+      <c r="U28" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>CODRNGTON</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4687,14 +6728,52 @@
       <c r="F29" s="5" t="inlineStr"/>
       <c r="G29" s="5" t="inlineStr"/>
       <c r="H29" s="5" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr"/>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O29" s="5" t="inlineStr"/>
+      <c r="P29" s="5" t="inlineStr"/>
+      <c r="Q29" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R29" s="5" t="inlineStr"/>
+      <c r="S29" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T29" s="5" t="inlineStr"/>
+      <c r="U29" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>CBWF1</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4709,14 +6788,52 @@
       <c r="F30" s="5" t="inlineStr"/>
       <c r="G30" s="5" t="inlineStr"/>
       <c r="H30" s="5" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr"/>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M30" s="5" t="inlineStr"/>
+      <c r="N30" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O30" s="5" t="inlineStr"/>
+      <c r="P30" s="5" t="inlineStr"/>
+      <c r="Q30" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R30" s="5" t="inlineStr"/>
+      <c r="S30" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T30" s="5" t="inlineStr"/>
+      <c r="U30" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>CROWLWF1</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4735,14 +6852,52 @@
       </c>
       <c r="G31" s="5" t="inlineStr"/>
       <c r="H31" s="5" t="inlineStr"/>
+      <c r="I31" s="5" t="inlineStr"/>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr"/>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr"/>
+      <c r="N31" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O31" s="5" t="inlineStr"/>
+      <c r="P31" s="5" t="inlineStr"/>
+      <c r="Q31" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R31" s="5" t="inlineStr"/>
+      <c r="S31" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T31" s="5" t="inlineStr"/>
+      <c r="U31" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>DIAPURWF1</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4757,14 +6912,52 @@
       <c r="F32" s="5" t="inlineStr"/>
       <c r="G32" s="5" t="inlineStr"/>
       <c r="H32" s="5" t="inlineStr"/>
+      <c r="I32" s="5" t="inlineStr"/>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr"/>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="inlineStr"/>
+      <c r="N32" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O32" s="5" t="inlineStr"/>
+      <c r="P32" s="5" t="inlineStr"/>
+      <c r="Q32" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R32" s="5" t="inlineStr"/>
+      <c r="S32" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T32" s="5" t="inlineStr"/>
+      <c r="U32" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>DUNDWF1</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4783,14 +6976,52 @@
       </c>
       <c r="G33" s="5" t="inlineStr"/>
       <c r="H33" s="5" t="inlineStr"/>
+      <c r="I33" s="5" t="inlineStr"/>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr"/>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr"/>
+      <c r="N33" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O33" s="5" t="inlineStr"/>
+      <c r="P33" s="5" t="inlineStr"/>
+      <c r="Q33" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R33" s="5" t="inlineStr"/>
+      <c r="S33" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T33" s="5" t="inlineStr"/>
+      <c r="U33" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>DUNDWF2</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4809,14 +7040,52 @@
       </c>
       <c r="G34" s="5" t="inlineStr"/>
       <c r="H34" s="5" t="inlineStr"/>
+      <c r="I34" s="5" t="inlineStr"/>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr"/>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M34" s="5" t="inlineStr"/>
+      <c r="N34" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O34" s="5" t="inlineStr"/>
+      <c r="P34" s="5" t="inlineStr"/>
+      <c r="Q34" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R34" s="5" t="inlineStr"/>
+      <c r="S34" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T34" s="5" t="inlineStr"/>
+      <c r="U34" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="inlineStr">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>DUNDWF3</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4835,14 +7104,52 @@
       </c>
       <c r="G35" s="5" t="inlineStr"/>
       <c r="H35" s="5" t="inlineStr"/>
+      <c r="I35" s="5" t="inlineStr"/>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr"/>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr"/>
+      <c r="N35" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O35" s="5" t="inlineStr"/>
+      <c r="P35" s="5" t="inlineStr"/>
+      <c r="Q35" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R35" s="5" t="inlineStr"/>
+      <c r="S35" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T35" s="5" t="inlineStr"/>
+      <c r="U35" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V35" s="5" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>ELAINWF1</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4859,14 +7166,52 @@
       <c r="F36" s="5" t="inlineStr"/>
       <c r="G36" s="5" t="inlineStr"/>
       <c r="H36" s="5" t="inlineStr"/>
+      <c r="I36" s="5" t="inlineStr"/>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr"/>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M36" s="5" t="inlineStr"/>
+      <c r="N36" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O36" s="5" t="inlineStr"/>
+      <c r="P36" s="5" t="inlineStr"/>
+      <c r="Q36" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R36" s="5" t="inlineStr"/>
+      <c r="S36" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T36" s="5" t="inlineStr"/>
+      <c r="U36" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="inlineStr">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>FNWF1</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4877,14 +7222,52 @@
       <c r="F37" s="5" t="inlineStr"/>
       <c r="G37" s="5" t="inlineStr"/>
       <c r="H37" s="5" t="inlineStr"/>
+      <c r="I37" s="5" t="inlineStr"/>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr"/>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr"/>
+      <c r="N37" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O37" s="5" t="inlineStr"/>
+      <c r="P37" s="5" t="inlineStr"/>
+      <c r="Q37" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R37" s="5" t="inlineStr"/>
+      <c r="S37" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T37" s="5" t="inlineStr"/>
+      <c r="U37" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="7" t="inlineStr">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>FSWF1</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4899,14 +7282,52 @@
       <c r="F38" s="5" t="inlineStr"/>
       <c r="G38" s="5" t="inlineStr"/>
       <c r="H38" s="5" t="inlineStr"/>
+      <c r="I38" s="5" t="inlineStr"/>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr"/>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M38" s="5" t="inlineStr"/>
+      <c r="N38" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O38" s="5" t="inlineStr"/>
+      <c r="P38" s="5" t="inlineStr"/>
+      <c r="Q38" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R38" s="5" t="inlineStr"/>
+      <c r="S38" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T38" s="5" t="inlineStr"/>
+      <c r="U38" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="7" t="inlineStr">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>GPWFEST1</t>
         </is>
       </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4921,14 +7342,52 @@
       <c r="F39" s="5" t="inlineStr"/>
       <c r="G39" s="5" t="inlineStr"/>
       <c r="H39" s="5" t="inlineStr"/>
+      <c r="I39" s="5" t="inlineStr"/>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr"/>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr"/>
+      <c r="N39" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O39" s="5" t="inlineStr"/>
+      <c r="P39" s="5" t="inlineStr"/>
+      <c r="Q39" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R39" s="5" t="inlineStr"/>
+      <c r="S39" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T39" s="5" t="inlineStr"/>
+      <c r="U39" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="7" t="inlineStr">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>GPWFEST2</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B40" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4943,14 +7402,52 @@
       <c r="F40" s="5" t="inlineStr"/>
       <c r="G40" s="5" t="inlineStr"/>
       <c r="H40" s="5" t="inlineStr"/>
+      <c r="I40" s="5" t="inlineStr"/>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="inlineStr"/>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M40" s="5" t="inlineStr"/>
+      <c r="N40" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O40" s="5" t="inlineStr"/>
+      <c r="P40" s="5" t="inlineStr"/>
+      <c r="Q40" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R40" s="5" t="inlineStr"/>
+      <c r="S40" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T40" s="5" t="inlineStr"/>
+      <c r="U40" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="7" t="inlineStr">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>GPWFEST3</t>
         </is>
       </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="B41" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4965,14 +7462,52 @@
       <c r="F41" s="5" t="inlineStr"/>
       <c r="G41" s="5" t="inlineStr"/>
       <c r="H41" s="5" t="inlineStr"/>
+      <c r="I41" s="5" t="inlineStr"/>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr"/>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr"/>
+      <c r="N41" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O41" s="5" t="inlineStr"/>
+      <c r="P41" s="5" t="inlineStr"/>
+      <c r="Q41" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R41" s="5" t="inlineStr"/>
+      <c r="S41" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T41" s="5" t="inlineStr"/>
+      <c r="U41" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V41" s="5" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>GPWFWST1</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B42" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4987,14 +7522,52 @@
       <c r="F42" s="5" t="inlineStr"/>
       <c r="G42" s="5" t="inlineStr"/>
       <c r="H42" s="5" t="inlineStr"/>
+      <c r="I42" s="5" t="inlineStr"/>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="inlineStr"/>
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M42" s="5" t="inlineStr"/>
+      <c r="N42" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O42" s="5" t="inlineStr"/>
+      <c r="P42" s="5" t="inlineStr"/>
+      <c r="Q42" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R42" s="5" t="inlineStr"/>
+      <c r="S42" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T42" s="5" t="inlineStr"/>
+      <c r="U42" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="7" t="inlineStr">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>GPWFWST2</t>
         </is>
       </c>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="B43" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5009,14 +7582,52 @@
       <c r="F43" s="5" t="inlineStr"/>
       <c r="G43" s="5" t="inlineStr"/>
       <c r="H43" s="5" t="inlineStr"/>
+      <c r="I43" s="5" t="inlineStr"/>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr"/>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr"/>
+      <c r="N43" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O43" s="5" t="inlineStr"/>
+      <c r="P43" s="5" t="inlineStr"/>
+      <c r="Q43" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R43" s="5" t="inlineStr"/>
+      <c r="S43" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T43" s="5" t="inlineStr"/>
+      <c r="U43" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="7" t="inlineStr">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>HD1WF1</t>
         </is>
       </c>
-      <c r="B44" s="7" t="inlineStr">
+      <c r="B44" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5033,14 +7644,52 @@
       </c>
       <c r="G44" s="5" t="inlineStr"/>
       <c r="H44" s="5" t="inlineStr"/>
+      <c r="I44" s="5" t="inlineStr"/>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="inlineStr"/>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M44" s="5" t="inlineStr"/>
+      <c r="N44" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O44" s="5" t="inlineStr"/>
+      <c r="P44" s="5" t="inlineStr"/>
+      <c r="Q44" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R44" s="5" t="inlineStr"/>
+      <c r="S44" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T44" s="5" t="inlineStr"/>
+      <c r="U44" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V44" s="5" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="7" t="inlineStr">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>HEPWIND1</t>
         </is>
       </c>
-      <c r="B45" s="7" t="inlineStr">
+      <c r="B45" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5055,14 +7704,52 @@
       <c r="F45" s="5" t="inlineStr"/>
       <c r="G45" s="5" t="inlineStr"/>
       <c r="H45" s="5" t="inlineStr"/>
+      <c r="I45" s="5" t="inlineStr"/>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr"/>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M45" s="5" t="inlineStr"/>
+      <c r="N45" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O45" s="5" t="inlineStr"/>
+      <c r="P45" s="5" t="inlineStr"/>
+      <c r="Q45" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R45" s="5" t="inlineStr"/>
+      <c r="S45" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T45" s="5" t="inlineStr"/>
+      <c r="U45" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V45" s="5" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="7" t="inlineStr">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>KIATAWF1</t>
         </is>
       </c>
-      <c r="B46" s="7" t="inlineStr">
+      <c r="B46" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5081,14 +7768,52 @@
       </c>
       <c r="G46" s="5" t="inlineStr"/>
       <c r="H46" s="5" t="inlineStr"/>
+      <c r="I46" s="5" t="inlineStr"/>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="inlineStr"/>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M46" s="5" t="inlineStr"/>
+      <c r="N46" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O46" s="5" t="inlineStr"/>
+      <c r="P46" s="5" t="inlineStr"/>
+      <c r="Q46" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R46" s="5" t="inlineStr"/>
+      <c r="S46" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T46" s="5" t="inlineStr"/>
+      <c r="U46" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="7" t="inlineStr">
+      <c r="A47" s="8" t="inlineStr">
         <is>
           <t>MACARTH1</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="B47" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5107,14 +7832,52 @@
       </c>
       <c r="G47" s="5" t="inlineStr"/>
       <c r="H47" s="5" t="inlineStr"/>
+      <c r="I47" s="5" t="inlineStr"/>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr"/>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M47" s="5" t="inlineStr"/>
+      <c r="N47" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O47" s="5" t="inlineStr"/>
+      <c r="P47" s="5" t="inlineStr"/>
+      <c r="Q47" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R47" s="5" t="inlineStr"/>
+      <c r="S47" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T47" s="5" t="inlineStr"/>
+      <c r="U47" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V47" s="5" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="7" t="inlineStr">
+      <c r="A48" s="8" t="inlineStr">
         <is>
           <t>MAROOWF1</t>
         </is>
       </c>
-      <c r="B48" s="7" t="inlineStr">
+      <c r="B48" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5129,14 +7892,52 @@
       <c r="F48" s="5" t="inlineStr"/>
       <c r="G48" s="5" t="inlineStr"/>
       <c r="H48" s="5" t="inlineStr"/>
+      <c r="I48" s="5" t="inlineStr"/>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="inlineStr"/>
+      <c r="L48" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M48" s="5" t="inlineStr"/>
+      <c r="N48" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O48" s="5" t="inlineStr"/>
+      <c r="P48" s="5" t="inlineStr"/>
+      <c r="Q48" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R48" s="5" t="inlineStr"/>
+      <c r="S48" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T48" s="5" t="inlineStr"/>
+      <c r="U48" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V48" s="5" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="7" t="inlineStr">
+      <c r="A49" s="8" t="inlineStr">
         <is>
           <t>MOORAWF1</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
+      <c r="B49" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5155,14 +7956,52 @@
       </c>
       <c r="G49" s="5" t="inlineStr"/>
       <c r="H49" s="5" t="inlineStr"/>
+      <c r="I49" s="5" t="inlineStr"/>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr"/>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M49" s="5" t="inlineStr"/>
+      <c r="N49" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O49" s="5" t="inlineStr"/>
+      <c r="P49" s="5" t="inlineStr"/>
+      <c r="Q49" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R49" s="5" t="inlineStr"/>
+      <c r="S49" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T49" s="5" t="inlineStr"/>
+      <c r="U49" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="7" t="inlineStr">
+      <c r="A50" s="8" t="inlineStr">
         <is>
           <t>MRTLSWF1</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="B50" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5181,14 +8020,52 @@
       </c>
       <c r="G50" s="5" t="inlineStr"/>
       <c r="H50" s="5" t="inlineStr"/>
+      <c r="I50" s="5" t="inlineStr"/>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="inlineStr"/>
+      <c r="L50" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M50" s="5" t="inlineStr"/>
+      <c r="N50" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O50" s="5" t="inlineStr"/>
+      <c r="P50" s="5" t="inlineStr"/>
+      <c r="Q50" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R50" s="5" t="inlineStr"/>
+      <c r="S50" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T50" s="5" t="inlineStr"/>
+      <c r="U50" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V50" s="5" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="7" t="inlineStr">
+      <c r="A51" s="8" t="inlineStr">
         <is>
           <t>MLWF1</t>
         </is>
       </c>
-      <c r="B51" s="7" t="inlineStr">
+      <c r="B51" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5203,14 +8080,52 @@
       <c r="F51" s="5" t="inlineStr"/>
       <c r="G51" s="5" t="inlineStr"/>
       <c r="H51" s="5" t="inlineStr"/>
+      <c r="I51" s="5" t="inlineStr"/>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr"/>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M51" s="5" t="inlineStr"/>
+      <c r="N51" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O51" s="5" t="inlineStr"/>
+      <c r="P51" s="5" t="inlineStr"/>
+      <c r="Q51" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R51" s="5" t="inlineStr"/>
+      <c r="S51" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T51" s="5" t="inlineStr"/>
+      <c r="U51" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V51" s="5" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="7" t="inlineStr">
+      <c r="A52" s="8" t="inlineStr">
         <is>
           <t>MTGELWF1</t>
         </is>
       </c>
-      <c r="B52" s="7" t="inlineStr">
+      <c r="B52" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5229,14 +8144,52 @@
       </c>
       <c r="G52" s="5" t="inlineStr"/>
       <c r="H52" s="5" t="inlineStr"/>
+      <c r="I52" s="5" t="inlineStr"/>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="inlineStr"/>
+      <c r="L52" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M52" s="5" t="inlineStr"/>
+      <c r="N52" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O52" s="5" t="inlineStr"/>
+      <c r="P52" s="5" t="inlineStr"/>
+      <c r="Q52" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R52" s="5" t="inlineStr"/>
+      <c r="S52" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T52" s="5" t="inlineStr"/>
+      <c r="U52" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V52" s="5" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="7" t="inlineStr">
+      <c r="A53" s="8" t="inlineStr">
         <is>
           <t>MERCER01</t>
         </is>
       </c>
-      <c r="B53" s="7" t="inlineStr">
+      <c r="B53" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5255,14 +8208,52 @@
       </c>
       <c r="G53" s="5" t="inlineStr"/>
       <c r="H53" s="5" t="inlineStr"/>
+      <c r="I53" s="5" t="inlineStr"/>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr"/>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M53" s="5" t="inlineStr"/>
+      <c r="N53" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O53" s="5" t="inlineStr"/>
+      <c r="P53" s="5" t="inlineStr"/>
+      <c r="Q53" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R53" s="5" t="inlineStr"/>
+      <c r="S53" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T53" s="5" t="inlineStr"/>
+      <c r="U53" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V53" s="5" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="7" t="inlineStr">
+      <c r="A54" s="8" t="inlineStr">
         <is>
           <t>MUWAWF1</t>
         </is>
       </c>
-      <c r="B54" s="7" t="inlineStr">
+      <c r="B54" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5281,14 +8272,52 @@
       </c>
       <c r="G54" s="5" t="inlineStr"/>
       <c r="H54" s="5" t="inlineStr"/>
+      <c r="I54" s="5" t="inlineStr"/>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="inlineStr"/>
+      <c r="L54" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M54" s="5" t="inlineStr"/>
+      <c r="N54" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O54" s="5" t="inlineStr"/>
+      <c r="P54" s="5" t="inlineStr"/>
+      <c r="Q54" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R54" s="5" t="inlineStr"/>
+      <c r="S54" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T54" s="5" t="inlineStr"/>
+      <c r="U54" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V54" s="5" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="7" t="inlineStr">
+      <c r="A55" s="8" t="inlineStr">
         <is>
           <t>MUWAWF2</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
+      <c r="B55" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5307,14 +8336,52 @@
       </c>
       <c r="G55" s="5" t="inlineStr"/>
       <c r="H55" s="5" t="inlineStr"/>
+      <c r="I55" s="5" t="inlineStr"/>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="inlineStr"/>
+      <c r="L55" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M55" s="5" t="inlineStr"/>
+      <c r="N55" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O55" s="5" t="inlineStr"/>
+      <c r="P55" s="5" t="inlineStr"/>
+      <c r="Q55" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R55" s="5" t="inlineStr"/>
+      <c r="S55" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T55" s="5" t="inlineStr"/>
+      <c r="U55" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V55" s="5" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="7" t="inlineStr">
+      <c r="A56" s="8" t="inlineStr">
         <is>
           <t>OAKLAND1</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
+      <c r="B56" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5333,14 +8400,52 @@
       </c>
       <c r="G56" s="5" t="inlineStr"/>
       <c r="H56" s="5" t="inlineStr"/>
+      <c r="I56" s="5" t="inlineStr"/>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="inlineStr"/>
+      <c r="L56" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M56" s="5" t="inlineStr"/>
+      <c r="N56" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O56" s="5" t="inlineStr"/>
+      <c r="P56" s="5" t="inlineStr"/>
+      <c r="Q56" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R56" s="5" t="inlineStr"/>
+      <c r="S56" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T56" s="5" t="inlineStr"/>
+      <c r="U56" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V56" s="5" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="7" t="inlineStr">
+      <c r="A57" s="8" t="inlineStr">
         <is>
           <t>RYANCWF1</t>
         </is>
       </c>
-      <c r="B57" s="7" t="inlineStr">
+      <c r="B57" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5357,14 +8462,52 @@
       </c>
       <c r="G57" s="5" t="inlineStr"/>
       <c r="H57" s="5" t="inlineStr"/>
+      <c r="I57" s="5" t="inlineStr"/>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr"/>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M57" s="5" t="inlineStr"/>
+      <c r="N57" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O57" s="5" t="inlineStr"/>
+      <c r="P57" s="5" t="inlineStr"/>
+      <c r="Q57" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R57" s="5" t="inlineStr"/>
+      <c r="S57" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T57" s="5" t="inlineStr"/>
+      <c r="U57" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V57" s="5" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="7" t="inlineStr">
+      <c r="A58" s="8" t="inlineStr">
         <is>
           <t>SALTCRK1</t>
         </is>
       </c>
-      <c r="B58" s="7" t="inlineStr">
+      <c r="B58" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5383,14 +8526,52 @@
       </c>
       <c r="G58" s="5" t="inlineStr"/>
       <c r="H58" s="5" t="inlineStr"/>
+      <c r="I58" s="5" t="inlineStr"/>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="inlineStr"/>
+      <c r="L58" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M58" s="5" t="inlineStr"/>
+      <c r="N58" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O58" s="5" t="inlineStr"/>
+      <c r="P58" s="5" t="inlineStr"/>
+      <c r="Q58" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R58" s="5" t="inlineStr"/>
+      <c r="S58" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T58" s="5" t="inlineStr"/>
+      <c r="U58" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V58" s="5" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="7" t="inlineStr">
+      <c r="A59" s="8" t="inlineStr">
         <is>
           <t>STOCKYD1</t>
         </is>
       </c>
-      <c r="B59" s="7" t="inlineStr">
+      <c r="B59" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5409,14 +8590,52 @@
       </c>
       <c r="G59" s="5" t="inlineStr"/>
       <c r="H59" s="5" t="inlineStr"/>
+      <c r="I59" s="5" t="inlineStr"/>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr"/>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M59" s="5" t="inlineStr"/>
+      <c r="N59" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O59" s="5" t="inlineStr"/>
+      <c r="P59" s="5" t="inlineStr"/>
+      <c r="Q59" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R59" s="5" t="inlineStr"/>
+      <c r="S59" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T59" s="5" t="inlineStr"/>
+      <c r="U59" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V59" s="5" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="7" t="inlineStr">
+      <c r="A60" s="8" t="inlineStr">
         <is>
           <t>TIMWEST</t>
         </is>
       </c>
-      <c r="B60" s="7" t="inlineStr">
+      <c r="B60" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5431,14 +8650,52 @@
       <c r="F60" s="5" t="inlineStr"/>
       <c r="G60" s="5" t="inlineStr"/>
       <c r="H60" s="5" t="inlineStr"/>
+      <c r="I60" s="5" t="inlineStr"/>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="inlineStr"/>
+      <c r="L60" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M60" s="5" t="inlineStr"/>
+      <c r="N60" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O60" s="5" t="inlineStr"/>
+      <c r="P60" s="5" t="inlineStr"/>
+      <c r="Q60" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R60" s="5" t="inlineStr"/>
+      <c r="S60" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T60" s="5" t="inlineStr"/>
+      <c r="U60" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V60" s="5" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="7" t="inlineStr">
+      <c r="A61" s="8" t="inlineStr">
         <is>
           <t>TOORAWF</t>
         </is>
       </c>
-      <c r="B61" s="7" t="inlineStr">
+      <c r="B61" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5453,14 +8710,52 @@
       <c r="F61" s="5" t="inlineStr"/>
       <c r="G61" s="5" t="inlineStr"/>
       <c r="H61" s="5" t="inlineStr"/>
+      <c r="I61" s="5" t="inlineStr"/>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="inlineStr"/>
+      <c r="L61" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M61" s="5" t="inlineStr"/>
+      <c r="N61" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O61" s="5" t="inlineStr"/>
+      <c r="P61" s="5" t="inlineStr"/>
+      <c r="Q61" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R61" s="5" t="inlineStr"/>
+      <c r="S61" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T61" s="5" t="inlineStr"/>
+      <c r="U61" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V61" s="5" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="7" t="inlineStr">
+      <c r="A62" s="8" t="inlineStr">
         <is>
           <t>WAUBRAWF</t>
         </is>
       </c>
-      <c r="B62" s="7" t="inlineStr">
+      <c r="B62" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5475,14 +8770,52 @@
       <c r="F62" s="5" t="inlineStr"/>
       <c r="G62" s="5" t="inlineStr"/>
       <c r="H62" s="5" t="inlineStr"/>
+      <c r="I62" s="5" t="inlineStr"/>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="inlineStr"/>
+      <c r="L62" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M62" s="5" t="inlineStr"/>
+      <c r="N62" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O62" s="5" t="inlineStr"/>
+      <c r="P62" s="5" t="inlineStr"/>
+      <c r="Q62" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R62" s="5" t="inlineStr"/>
+      <c r="S62" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T62" s="5" t="inlineStr"/>
+      <c r="U62" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V62" s="5" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="7" t="inlineStr">
+      <c r="A63" s="8" t="inlineStr">
         <is>
           <t>WONWP</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr">
+      <c r="B63" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5497,14 +8830,52 @@
       <c r="F63" s="5" t="inlineStr"/>
       <c r="G63" s="5" t="inlineStr"/>
       <c r="H63" s="5" t="inlineStr"/>
+      <c r="I63" s="5" t="inlineStr"/>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr"/>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M63" s="5" t="inlineStr"/>
+      <c r="N63" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O63" s="5" t="inlineStr"/>
+      <c r="P63" s="5" t="inlineStr"/>
+      <c r="Q63" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R63" s="5" t="inlineStr"/>
+      <c r="S63" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T63" s="5" t="inlineStr"/>
+      <c r="U63" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V63" s="5" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="7" t="inlineStr">
+      <c r="A64" s="8" t="inlineStr">
         <is>
           <t>YSWF1</t>
         </is>
       </c>
-      <c r="B64" s="7" t="inlineStr">
+      <c r="B64" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5519,14 +8890,52 @@
       <c r="F64" s="5" t="inlineStr"/>
       <c r="G64" s="5" t="inlineStr"/>
       <c r="H64" s="5" t="inlineStr"/>
+      <c r="I64" s="5" t="inlineStr"/>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="inlineStr"/>
+      <c r="L64" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M64" s="5" t="inlineStr"/>
+      <c r="N64" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O64" s="5" t="inlineStr"/>
+      <c r="P64" s="5" t="inlineStr"/>
+      <c r="Q64" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R64" s="5" t="inlineStr"/>
+      <c r="S64" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T64" s="5" t="inlineStr"/>
+      <c r="U64" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V64" s="5" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="7" t="inlineStr">
+      <c r="A65" s="8" t="inlineStr">
         <is>
           <t>YAMBUKWF</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
+      <c r="B65" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5541,14 +8950,52 @@
       <c r="F65" s="5" t="inlineStr"/>
       <c r="G65" s="5" t="inlineStr"/>
       <c r="H65" s="5" t="inlineStr"/>
+      <c r="I65" s="5" t="inlineStr"/>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="inlineStr"/>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M65" s="5" t="inlineStr"/>
+      <c r="N65" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O65" s="5" t="inlineStr"/>
+      <c r="P65" s="5" t="inlineStr"/>
+      <c r="Q65" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R65" s="5" t="inlineStr"/>
+      <c r="S65" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T65" s="5" t="inlineStr"/>
+      <c r="U65" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V65" s="5" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="7" t="inlineStr">
+      <c r="A66" s="8" t="inlineStr">
         <is>
           <t>YAWWF1</t>
         </is>
       </c>
-      <c r="B66" s="7" t="inlineStr">
+      <c r="B66" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5563,14 +9010,52 @@
       <c r="F66" s="5" t="inlineStr"/>
       <c r="G66" s="5" t="inlineStr"/>
       <c r="H66" s="5" t="inlineStr"/>
+      <c r="I66" s="5" t="inlineStr"/>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="inlineStr"/>
+      <c r="L66" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M66" s="5" t="inlineStr"/>
+      <c r="N66" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O66" s="5" t="inlineStr"/>
+      <c r="P66" s="5" t="inlineStr"/>
+      <c r="Q66" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R66" s="5" t="inlineStr"/>
+      <c r="S66" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T66" s="5" t="inlineStr"/>
+      <c r="U66" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V66" s="5" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="7" t="inlineStr">
+      <c r="A67" s="8" t="inlineStr">
         <is>
           <t>YENDWF1</t>
         </is>
       </c>
-      <c r="B67" s="7" t="inlineStr">
+      <c r="B67" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5589,6 +9074,44 @@
       </c>
       <c r="G67" s="5" t="inlineStr"/>
       <c r="H67" s="5" t="inlineStr"/>
+      <c r="I67" s="5" t="inlineStr"/>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="inlineStr"/>
+      <c r="L67" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M67" s="5" t="inlineStr"/>
+      <c r="N67" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O67" s="5" t="inlineStr"/>
+      <c r="P67" s="5" t="inlineStr"/>
+      <c r="Q67" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R67" s="5" t="inlineStr"/>
+      <c r="S67" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T67" s="5" t="inlineStr"/>
+      <c r="U67" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V67" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C67">
@@ -5663,6 +9186,174 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I67">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J67">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K67">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L67">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M67">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N2:N67">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O2:O67">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P2:P67">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q2:Q67">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R2:R67">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S2:S67">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T2:T67">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U2:U67">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V2:V67">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/VIC_curtailment.xlsx
+++ b/outputs/VIC_curtailment.xlsx
@@ -532,12 +532,12 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Actual FY23-24</t>
+          <t>Actual FY24-25</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Actual FY24-25</t>
+          <t>Actual FY25-26</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
@@ -644,11 +644,9 @@
         <v>66</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>0.3236</v>
-      </c>
-      <c r="K2" s="5" t="n">
         <v>0.2465</v>
       </c>
+      <c r="K2" s="5" t="inlineStr"/>
       <c r="L2" s="5" t="n">
         <v>0.833539620209753</v>
       </c>
@@ -865,11 +863,9 @@
         <v>66</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>0.0499</v>
-      </c>
-      <c r="K5" s="5" t="n">
         <v>0.054</v>
       </c>
+      <c r="K5" s="5" t="inlineStr"/>
       <c r="L5" s="5" t="n">
         <v>0.547516873654646</v>
       </c>
@@ -949,10 +945,10 @@
       <c r="I6" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="n">
+      <c r="J6" s="5" t="n">
         <v>0.2374</v>
       </c>
+      <c r="K6" s="5" t="inlineStr"/>
       <c r="L6" s="5" t="n">
         <v>0.389503957787889</v>
       </c>
@@ -1032,10 +1028,10 @@
       <c r="I7" s="2" t="n">
         <v>220</v>
       </c>
-      <c r="J7" s="5" t="inlineStr"/>
-      <c r="K7" s="5" t="n">
+      <c r="J7" s="5" t="n">
         <v>0.0688</v>
       </c>
+      <c r="K7" s="5" t="inlineStr"/>
       <c r="L7" s="5" t="n">
         <v>0.390717855103594</v>
       </c>
@@ -1110,11 +1106,9 @@
       </c>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="5" t="n">
-        <v>0.1836</v>
-      </c>
-      <c r="K8" s="5" t="n">
         <v>0.2057</v>
       </c>
+      <c r="K8" s="5" t="inlineStr"/>
       <c r="L8" s="5" t="inlineStr"/>
       <c r="M8" s="5" t="inlineStr"/>
       <c r="N8" s="5" t="n">
@@ -1230,11 +1224,9 @@
         <v>66</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>0.2761</v>
-      </c>
-      <c r="K10" s="5" t="n">
         <v>0.159</v>
       </c>
+      <c r="K10" s="5" t="inlineStr"/>
       <c r="L10" s="5" t="n">
         <v>0.8554020168196</v>
       </c>
@@ -1370,11 +1362,9 @@
         <v>220</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0.106</v>
-      </c>
-      <c r="K12" s="5" t="n">
         <v>0.1081</v>
       </c>
+      <c r="K12" s="5" t="inlineStr"/>
       <c r="L12" s="5" t="n">
         <v>0.827440107601162</v>
       </c>
@@ -1565,11 +1555,9 @@
         <v>66</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>0.2971</v>
-      </c>
-      <c r="K15" s="5" t="n">
         <v>0.1275</v>
       </c>
+      <c r="K15" s="5" t="inlineStr"/>
       <c r="L15" s="5" t="n">
         <v>0.389503957787889</v>
       </c>
@@ -1705,11 +1693,9 @@
         <v>66</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>0.3065</v>
-      </c>
-      <c r="K17" s="5" t="n">
         <v>0.2491</v>
       </c>
+      <c r="K17" s="5" t="inlineStr"/>
       <c r="L17" s="5" t="n">
         <v>0.833539620209753</v>
       </c>
@@ -1789,9 +1775,7 @@
       <c r="I18" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="J18" s="5" t="n">
-        <v>0.2227</v>
-      </c>
+      <c r="J18" s="5" t="inlineStr"/>
       <c r="K18" s="5" t="inlineStr"/>
       <c r="L18" s="5" t="n">
         <v>0.390717855103594</v>
@@ -1938,11 +1922,9 @@
         <v>66</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>0.2786</v>
-      </c>
-      <c r="K20" s="5" t="n">
         <v>0.2351</v>
       </c>
+      <c r="K20" s="5" t="inlineStr"/>
       <c r="L20" s="5" t="n">
         <v>0.8554020168196</v>
       </c>
@@ -2017,11 +1999,9 @@
       </c>
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="5" t="n">
-        <v>0.0756</v>
-      </c>
-      <c r="K21" s="5" t="n">
         <v>0.0482</v>
       </c>
+      <c r="K21" s="5" t="inlineStr"/>
       <c r="L21" s="5" t="inlineStr"/>
       <c r="M21" s="5" t="inlineStr"/>
       <c r="N21" s="5" t="n">
@@ -2076,11 +2056,9 @@
       </c>
       <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="5" t="n">
-        <v>0.0078</v>
-      </c>
-      <c r="K22" s="5" t="n">
         <v>0.0051</v>
       </c>
+      <c r="K22" s="5" t="inlineStr"/>
       <c r="L22" s="5" t="inlineStr"/>
       <c r="M22" s="5" t="inlineStr"/>
       <c r="N22" s="5" t="n">
@@ -2135,11 +2113,9 @@
       </c>
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="5" t="n">
-        <v>0.2041</v>
-      </c>
-      <c r="K23" s="5" t="n">
         <v>0.1906</v>
       </c>
+      <c r="K23" s="5" t="inlineStr"/>
       <c r="L23" s="5" t="inlineStr"/>
       <c r="M23" s="5" t="inlineStr"/>
       <c r="N23" s="5" t="n">
@@ -2194,11 +2170,9 @@
       </c>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="5" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="K24" s="5" t="n">
         <v>0.0316</v>
       </c>
+      <c r="K24" s="5" t="inlineStr"/>
       <c r="L24" s="5" t="inlineStr"/>
       <c r="M24" s="5" t="inlineStr"/>
       <c r="N24" s="5" t="n">
@@ -2253,11 +2227,9 @@
       </c>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="5" t="n">
-        <v>0.0347</v>
-      </c>
-      <c r="K25" s="5" t="n">
         <v>0.0284</v>
       </c>
+      <c r="K25" s="5" t="inlineStr"/>
       <c r="L25" s="5" t="inlineStr"/>
       <c r="M25" s="5" t="inlineStr"/>
       <c r="N25" s="5" t="n">
@@ -2420,11 +2392,9 @@
       </c>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="5" t="n">
-        <v>0.0578</v>
-      </c>
-      <c r="K28" s="5" t="n">
         <v>0.0958</v>
       </c>
+      <c r="K28" s="5" t="inlineStr"/>
       <c r="L28" s="5" t="inlineStr"/>
       <c r="M28" s="5" t="inlineStr"/>
       <c r="N28" s="5" t="n">
@@ -2589,11 +2559,9 @@
       </c>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="5" t="n">
-        <v>0.0553</v>
-      </c>
-      <c r="K31" s="5" t="n">
         <v>0.0678</v>
       </c>
+      <c r="K31" s="5" t="inlineStr"/>
       <c r="L31" s="5" t="inlineStr"/>
       <c r="M31" s="5" t="inlineStr"/>
       <c r="N31" s="5" t="n">
@@ -2703,11 +2671,9 @@
       </c>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="5" t="n">
-        <v>0.1012</v>
-      </c>
-      <c r="K33" s="5" t="n">
         <v>0.125</v>
       </c>
+      <c r="K33" s="5" t="inlineStr"/>
       <c r="L33" s="5" t="inlineStr"/>
       <c r="M33" s="5" t="inlineStr"/>
       <c r="N33" s="5" t="n">
@@ -2762,11 +2728,9 @@
       </c>
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="5" t="n">
-        <v>0.0735</v>
-      </c>
-      <c r="K34" s="5" t="n">
         <v>0.0467</v>
       </c>
+      <c r="K34" s="5" t="inlineStr"/>
       <c r="L34" s="5" t="inlineStr"/>
       <c r="M34" s="5" t="inlineStr"/>
       <c r="N34" s="5" t="n">
@@ -2821,11 +2785,9 @@
       </c>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="5" t="n">
-        <v>0.0794</v>
-      </c>
-      <c r="K35" s="5" t="n">
         <v>0.0331</v>
       </c>
+      <c r="K35" s="5" t="inlineStr"/>
       <c r="L35" s="5" t="inlineStr"/>
       <c r="M35" s="5" t="inlineStr"/>
       <c r="N35" s="5" t="n">
@@ -2879,9 +2841,7 @@
         <v>83.59999999999999</v>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="5" t="n">
-        <v>0.1555</v>
-      </c>
+      <c r="J36" s="5" t="inlineStr"/>
       <c r="K36" s="5" t="inlineStr"/>
       <c r="L36" s="5" t="inlineStr"/>
       <c r="M36" s="5" t="inlineStr"/>
@@ -3317,10 +3277,10 @@
         <v>96.59999999999999</v>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="5" t="inlineStr"/>
-      <c r="K44" s="5" t="n">
+      <c r="J44" s="5" t="n">
         <v>0.1766</v>
       </c>
+      <c r="K44" s="5" t="inlineStr"/>
       <c r="L44" s="5" t="inlineStr"/>
       <c r="M44" s="5" t="inlineStr"/>
       <c r="N44" s="5" t="n">
@@ -3430,11 +3390,9 @@
       </c>
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="5" t="n">
-        <v>0.1062</v>
-      </c>
-      <c r="K46" s="5" t="n">
         <v>0.173</v>
       </c>
+      <c r="K46" s="5" t="inlineStr"/>
       <c r="L46" s="5" t="inlineStr"/>
       <c r="M46" s="5" t="inlineStr"/>
       <c r="N46" s="5" t="n">
@@ -3489,11 +3447,9 @@
       </c>
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="5" t="n">
-        <v>0.074</v>
-      </c>
-      <c r="K47" s="5" t="n">
         <v>0.1339</v>
       </c>
+      <c r="K47" s="5" t="inlineStr"/>
       <c r="L47" s="5" t="inlineStr"/>
       <c r="M47" s="5" t="inlineStr"/>
       <c r="N47" s="5" t="n">
@@ -3603,11 +3559,9 @@
       </c>
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="5" t="n">
-        <v>0.0878</v>
-      </c>
-      <c r="K49" s="5" t="n">
         <v>0.0847</v>
       </c>
+      <c r="K49" s="5" t="inlineStr"/>
       <c r="L49" s="5" t="inlineStr"/>
       <c r="M49" s="5" t="inlineStr"/>
       <c r="N49" s="5" t="n">
@@ -3662,11 +3616,9 @@
       </c>
       <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="5" t="n">
-        <v>0.1264</v>
-      </c>
-      <c r="K50" s="5" t="n">
         <v>0.09810000000000001</v>
       </c>
+      <c r="K50" s="5" t="inlineStr"/>
       <c r="L50" s="5" t="inlineStr"/>
       <c r="M50" s="5" t="inlineStr"/>
       <c r="N50" s="5" t="n">
@@ -3776,11 +3728,9 @@
       </c>
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="5" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="K52" s="5" t="n">
         <v>0.0498</v>
       </c>
+      <c r="K52" s="5" t="inlineStr"/>
       <c r="L52" s="5" t="inlineStr"/>
       <c r="M52" s="5" t="inlineStr"/>
       <c r="N52" s="5" t="n">
@@ -3835,11 +3785,9 @@
       </c>
       <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="5" t="n">
-        <v>0.1784</v>
-      </c>
-      <c r="K53" s="5" t="n">
         <v>0.2533</v>
       </c>
+      <c r="K53" s="5" t="inlineStr"/>
       <c r="L53" s="5" t="inlineStr"/>
       <c r="M53" s="5" t="inlineStr"/>
       <c r="N53" s="5" t="n">
@@ -3894,11 +3842,9 @@
       </c>
       <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="5" t="n">
-        <v>0.1857</v>
-      </c>
-      <c r="K54" s="5" t="n">
         <v>0.2838</v>
       </c>
+      <c r="K54" s="5" t="inlineStr"/>
       <c r="L54" s="5" t="inlineStr"/>
       <c r="M54" s="5" t="inlineStr"/>
       <c r="N54" s="5" t="n">
@@ -3953,11 +3899,9 @@
       </c>
       <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="5" t="n">
-        <v>0.1619</v>
-      </c>
-      <c r="K55" s="5" t="n">
         <v>0.2355</v>
       </c>
+      <c r="K55" s="5" t="inlineStr"/>
       <c r="L55" s="5" t="inlineStr"/>
       <c r="M55" s="5" t="inlineStr"/>
       <c r="N55" s="5" t="n">
@@ -4012,11 +3956,9 @@
       </c>
       <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="5" t="n">
-        <v>0.0583</v>
-      </c>
-      <c r="K56" s="5" t="n">
         <v>0.077</v>
       </c>
+      <c r="K56" s="5" t="inlineStr"/>
       <c r="L56" s="5" t="inlineStr"/>
       <c r="M56" s="5" t="inlineStr"/>
       <c r="N56" s="5" t="n">
@@ -4070,10 +4012,10 @@
         <v>218.4</v>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="5" t="inlineStr"/>
-      <c r="K57" s="5" t="n">
+      <c r="J57" s="5" t="n">
         <v>0.0931</v>
       </c>
+      <c r="K57" s="5" t="inlineStr"/>
       <c r="L57" s="5" t="inlineStr"/>
       <c r="M57" s="5" t="inlineStr"/>
       <c r="N57" s="5" t="n">
@@ -4128,11 +4070,9 @@
       </c>
       <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="5" t="n">
-        <v>0.1607</v>
-      </c>
-      <c r="K58" s="5" t="n">
         <v>0.2295</v>
       </c>
+      <c r="K58" s="5" t="inlineStr"/>
       <c r="L58" s="5" t="inlineStr"/>
       <c r="M58" s="5" t="inlineStr"/>
       <c r="N58" s="5" t="n">
@@ -4187,11 +4127,9 @@
       </c>
       <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="5" t="n">
-        <v>0.0653</v>
-      </c>
-      <c r="K59" s="5" t="n">
         <v>0.0216</v>
       </c>
+      <c r="K59" s="5" t="inlineStr"/>
       <c r="L59" s="5" t="inlineStr"/>
       <c r="M59" s="5" t="inlineStr"/>
       <c r="N59" s="5" t="n">
@@ -4631,11 +4569,9 @@
       </c>
       <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="5" t="n">
-        <v>0.1421</v>
-      </c>
-      <c r="K67" s="5" t="n">
         <v>0.1581</v>
       </c>
+      <c r="K67" s="5" t="inlineStr"/>
       <c r="L67" s="5" t="inlineStr"/>
       <c r="M67" s="5" t="inlineStr"/>
       <c r="N67" s="5" t="n">
@@ -4714,12 +4650,12 @@
       </c>
       <c r="E1" s="7" t="inlineStr">
         <is>
-          <t>CURTAILMENT_ACTUAL_FY23-24</t>
+          <t>CURTAILMENT_ACTUAL_FY24-25</t>
         </is>
       </c>
       <c r="F1" s="7" t="inlineStr">
         <is>
-          <t>CURTAILMENT_ACTUAL_FY24-25</t>
+          <t>CURTAILMENT_ACTUAL_FY25-26</t>
         </is>
       </c>
       <c r="G1" s="7" t="inlineStr">
@@ -4821,11 +4757,9 @@
         <v>0.9092</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.3236</v>
-      </c>
-      <c r="F2" s="5" t="n">
         <v>0.2465</v>
       </c>
+      <c r="F2" s="5" t="inlineStr"/>
       <c r="G2" s="5" t="n">
         <v>0.833539620209753</v>
       </c>
@@ -5045,11 +4979,9 @@
         <v>0.929</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.0499</v>
-      </c>
-      <c r="F5" s="5" t="n">
         <v>0.054</v>
       </c>
+      <c r="F5" s="5" t="inlineStr"/>
       <c r="G5" s="5" t="n">
         <v>0.547516873654646</v>
       </c>
@@ -5128,10 +5060,10 @@
       <c r="D6" s="5" t="n">
         <v>0.921</v>
       </c>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="n">
+      <c r="E6" s="5" t="n">
         <v>0.2374</v>
       </c>
+      <c r="F6" s="5" t="inlineStr"/>
       <c r="G6" s="5" t="n">
         <v>0.389503957787889</v>
       </c>
@@ -5210,10 +5142,10 @@
       <c r="D7" s="5" t="n">
         <v>0.9294</v>
       </c>
-      <c r="E7" s="5" t="inlineStr"/>
-      <c r="F7" s="5" t="n">
+      <c r="E7" s="5" t="n">
         <v>0.0688</v>
       </c>
+      <c r="F7" s="5" t="inlineStr"/>
       <c r="G7" s="5" t="n">
         <v>0.390717855103594</v>
       </c>
@@ -5293,11 +5225,9 @@
         <v>0.9211</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.1836</v>
-      </c>
-      <c r="F8" s="5" t="n">
         <v>0.2057</v>
       </c>
+      <c r="F8" s="5" t="inlineStr"/>
       <c r="G8" s="5" t="inlineStr"/>
       <c r="H8" s="5" t="inlineStr"/>
       <c r="I8" s="5" t="inlineStr"/>
@@ -5417,11 +5347,9 @@
         <v>0.9051</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.2761</v>
-      </c>
-      <c r="F10" s="5" t="n">
         <v>0.159</v>
       </c>
+      <c r="F10" s="5" t="inlineStr"/>
       <c r="G10" s="5" t="n">
         <v>0.8554020168196</v>
       </c>
@@ -5561,11 +5489,9 @@
         <v>0.8738</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.106</v>
-      </c>
-      <c r="F12" s="5" t="n">
         <v>0.1081</v>
       </c>
+      <c r="F12" s="5" t="inlineStr"/>
       <c r="G12" s="5" t="n">
         <v>0.827440107601162</v>
       </c>
@@ -5765,11 +5691,9 @@
         <v>0.921</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.2971</v>
-      </c>
-      <c r="F15" s="5" t="n">
         <v>0.1275</v>
       </c>
+      <c r="F15" s="5" t="inlineStr"/>
       <c r="G15" s="5" t="n">
         <v>0.389503957787889</v>
       </c>
@@ -5909,11 +5833,9 @@
         <v>0.9092</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0.3065</v>
-      </c>
-      <c r="F17" s="5" t="n">
         <v>0.2491</v>
       </c>
+      <c r="F17" s="5" t="inlineStr"/>
       <c r="G17" s="5" t="n">
         <v>0.833539620209753</v>
       </c>
@@ -5992,9 +5914,7 @@
       <c r="D18" s="5" t="n">
         <v>0.9211</v>
       </c>
-      <c r="E18" s="5" t="n">
-        <v>0.2227</v>
-      </c>
+      <c r="E18" s="5" t="inlineStr"/>
       <c r="F18" s="5" t="inlineStr"/>
       <c r="G18" s="5" t="n">
         <v>0.390717855103594</v>
@@ -6139,11 +6059,9 @@
         <v>0.9051</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0.2786</v>
-      </c>
-      <c r="F20" s="5" t="n">
         <v>0.2351</v>
       </c>
+      <c r="F20" s="5" t="inlineStr"/>
       <c r="G20" s="5" t="n">
         <v>0.8554020168196</v>
       </c>
@@ -6223,11 +6141,9 @@
         <v>0.898</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0.0756</v>
-      </c>
-      <c r="F21" s="5" t="n">
         <v>0.0482</v>
       </c>
+      <c r="F21" s="5" t="inlineStr"/>
       <c r="G21" s="5" t="inlineStr"/>
       <c r="H21" s="5" t="inlineStr"/>
       <c r="I21" s="5" t="inlineStr"/>
@@ -6287,11 +6203,9 @@
         <v>0.992</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0.0078</v>
-      </c>
-      <c r="F22" s="5" t="n">
         <v>0.0051</v>
       </c>
+      <c r="F22" s="5" t="inlineStr"/>
       <c r="G22" s="5" t="inlineStr"/>
       <c r="H22" s="5" t="inlineStr"/>
       <c r="I22" s="5" t="inlineStr"/>
@@ -6351,11 +6265,9 @@
         <v>0.9436</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0.2041</v>
-      </c>
-      <c r="F23" s="5" t="n">
         <v>0.1906</v>
       </c>
+      <c r="F23" s="5" t="inlineStr"/>
       <c r="G23" s="5" t="inlineStr"/>
       <c r="H23" s="5" t="inlineStr"/>
       <c r="I23" s="5" t="inlineStr"/>
@@ -6415,11 +6327,9 @@
         <v>0.9436</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="F24" s="5" t="n">
         <v>0.0316</v>
       </c>
+      <c r="F24" s="5" t="inlineStr"/>
       <c r="G24" s="5" t="inlineStr"/>
       <c r="H24" s="5" t="inlineStr"/>
       <c r="I24" s="5" t="inlineStr"/>
@@ -6479,11 +6389,9 @@
         <v>0.8868</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>0.0347</v>
-      </c>
-      <c r="F25" s="5" t="n">
         <v>0.0284</v>
       </c>
+      <c r="F25" s="5" t="inlineStr"/>
       <c r="G25" s="5" t="inlineStr"/>
       <c r="H25" s="5" t="inlineStr"/>
       <c r="I25" s="5" t="inlineStr"/>
@@ -6661,11 +6569,9 @@
         <v>0.9977</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0.0578</v>
-      </c>
-      <c r="F28" s="5" t="n">
         <v>0.0958</v>
       </c>
+      <c r="F28" s="5" t="inlineStr"/>
       <c r="G28" s="5" t="inlineStr"/>
       <c r="H28" s="5" t="inlineStr"/>
       <c r="I28" s="5" t="inlineStr"/>
@@ -6845,11 +6751,9 @@
         <v>0.8966</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>0.0553</v>
-      </c>
-      <c r="F31" s="5" t="n">
         <v>0.0678</v>
       </c>
+      <c r="F31" s="5" t="inlineStr"/>
       <c r="G31" s="5" t="inlineStr"/>
       <c r="H31" s="5" t="inlineStr"/>
       <c r="I31" s="5" t="inlineStr"/>
@@ -6969,11 +6873,9 @@
         <v>0.9827</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0.1012</v>
-      </c>
-      <c r="F33" s="5" t="n">
         <v>0.125</v>
       </c>
+      <c r="F33" s="5" t="inlineStr"/>
       <c r="G33" s="5" t="inlineStr"/>
       <c r="H33" s="5" t="inlineStr"/>
       <c r="I33" s="5" t="inlineStr"/>
@@ -7033,11 +6935,9 @@
         <v>0.9827</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0.0735</v>
-      </c>
-      <c r="F34" s="5" t="n">
         <v>0.0467</v>
       </c>
+      <c r="F34" s="5" t="inlineStr"/>
       <c r="G34" s="5" t="inlineStr"/>
       <c r="H34" s="5" t="inlineStr"/>
       <c r="I34" s="5" t="inlineStr"/>
@@ -7097,11 +6997,9 @@
         <v>0.9827</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>0.0794</v>
-      </c>
-      <c r="F35" s="5" t="n">
         <v>0.0331</v>
       </c>
+      <c r="F35" s="5" t="inlineStr"/>
       <c r="G35" s="5" t="inlineStr"/>
       <c r="H35" s="5" t="inlineStr"/>
       <c r="I35" s="5" t="inlineStr"/>
@@ -7160,9 +7058,7 @@
       <c r="D36" s="5" t="n">
         <v>0.9556</v>
       </c>
-      <c r="E36" s="5" t="n">
-        <v>0.1555</v>
-      </c>
+      <c r="E36" s="5" t="inlineStr"/>
       <c r="F36" s="5" t="inlineStr"/>
       <c r="G36" s="5" t="inlineStr"/>
       <c r="H36" s="5" t="inlineStr"/>
@@ -7638,10 +7534,10 @@
       <c r="D44" s="5" t="n">
         <v>0.9822</v>
       </c>
-      <c r="E44" s="5" t="inlineStr"/>
-      <c r="F44" s="5" t="n">
+      <c r="E44" s="5" t="n">
         <v>0.1766</v>
       </c>
+      <c r="F44" s="5" t="inlineStr"/>
       <c r="G44" s="5" t="inlineStr"/>
       <c r="H44" s="5" t="inlineStr"/>
       <c r="I44" s="5" t="inlineStr"/>
@@ -7761,11 +7657,9 @@
         <v>0.8954</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>0.1062</v>
-      </c>
-      <c r="F46" s="5" t="n">
         <v>0.173</v>
       </c>
+      <c r="F46" s="5" t="inlineStr"/>
       <c r="G46" s="5" t="inlineStr"/>
       <c r="H46" s="5" t="inlineStr"/>
       <c r="I46" s="5" t="inlineStr"/>
@@ -7825,11 +7719,9 @@
         <v>0.9824000000000001</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0.074</v>
-      </c>
-      <c r="F47" s="5" t="n">
         <v>0.1339</v>
       </c>
+      <c r="F47" s="5" t="inlineStr"/>
       <c r="G47" s="5" t="inlineStr"/>
       <c r="H47" s="5" t="inlineStr"/>
       <c r="I47" s="5" t="inlineStr"/>
@@ -7949,11 +7841,9 @@
         <v>0.9556</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>0.0878</v>
-      </c>
-      <c r="F49" s="5" t="n">
         <v>0.0847</v>
       </c>
+      <c r="F49" s="5" t="inlineStr"/>
       <c r="G49" s="5" t="inlineStr"/>
       <c r="H49" s="5" t="inlineStr"/>
       <c r="I49" s="5" t="inlineStr"/>
@@ -8013,11 +7903,9 @@
         <v>0.9507</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>0.1264</v>
-      </c>
-      <c r="F50" s="5" t="n">
         <v>0.09810000000000001</v>
       </c>
+      <c r="F50" s="5" t="inlineStr"/>
       <c r="G50" s="5" t="inlineStr"/>
       <c r="H50" s="5" t="inlineStr"/>
       <c r="I50" s="5" t="inlineStr"/>
@@ -8137,11 +8025,9 @@
         <v>0.989</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F52" s="5" t="n">
         <v>0.0498</v>
       </c>
+      <c r="F52" s="5" t="inlineStr"/>
       <c r="G52" s="5" t="inlineStr"/>
       <c r="H52" s="5" t="inlineStr"/>
       <c r="I52" s="5" t="inlineStr"/>
@@ -8201,11 +8087,9 @@
         <v>0.9556</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>0.1784</v>
-      </c>
-      <c r="F53" s="5" t="n">
         <v>0.2533</v>
       </c>
+      <c r="F53" s="5" t="inlineStr"/>
       <c r="G53" s="5" t="inlineStr"/>
       <c r="H53" s="5" t="inlineStr"/>
       <c r="I53" s="5" t="inlineStr"/>
@@ -8265,11 +8149,9 @@
         <v>0.8824</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>0.1857</v>
-      </c>
-      <c r="F54" s="5" t="n">
         <v>0.2838</v>
       </c>
+      <c r="F54" s="5" t="inlineStr"/>
       <c r="G54" s="5" t="inlineStr"/>
       <c r="H54" s="5" t="inlineStr"/>
       <c r="I54" s="5" t="inlineStr"/>
@@ -8329,11 +8211,9 @@
         <v>0.8824</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>0.1619</v>
-      </c>
-      <c r="F55" s="5" t="n">
         <v>0.2355</v>
       </c>
+      <c r="F55" s="5" t="inlineStr"/>
       <c r="G55" s="5" t="inlineStr"/>
       <c r="H55" s="5" t="inlineStr"/>
       <c r="I55" s="5" t="inlineStr"/>
@@ -8393,11 +8273,9 @@
         <v>0.9949</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>0.0583</v>
-      </c>
-      <c r="F56" s="5" t="n">
         <v>0.077</v>
       </c>
+      <c r="F56" s="5" t="inlineStr"/>
       <c r="G56" s="5" t="inlineStr"/>
       <c r="H56" s="5" t="inlineStr"/>
       <c r="I56" s="5" t="inlineStr"/>
@@ -8456,10 +8334,10 @@
       <c r="D57" s="5" t="n">
         <v>0.983</v>
       </c>
-      <c r="E57" s="5" t="inlineStr"/>
-      <c r="F57" s="5" t="n">
+      <c r="E57" s="5" t="n">
         <v>0.0931</v>
       </c>
+      <c r="F57" s="5" t="inlineStr"/>
       <c r="G57" s="5" t="inlineStr"/>
       <c r="H57" s="5" t="inlineStr"/>
       <c r="I57" s="5" t="inlineStr"/>
@@ -8519,11 +8397,9 @@
         <v>0.9499</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>0.1607</v>
-      </c>
-      <c r="F58" s="5" t="n">
         <v>0.2295</v>
       </c>
+      <c r="F58" s="5" t="inlineStr"/>
       <c r="G58" s="5" t="inlineStr"/>
       <c r="H58" s="5" t="inlineStr"/>
       <c r="I58" s="5" t="inlineStr"/>
@@ -8583,11 +8459,9 @@
         <v>0.9827</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>0.0653</v>
-      </c>
-      <c r="F59" s="5" t="n">
         <v>0.0216</v>
       </c>
+      <c r="F59" s="5" t="inlineStr"/>
       <c r="G59" s="5" t="inlineStr"/>
       <c r="H59" s="5" t="inlineStr"/>
       <c r="I59" s="5" t="inlineStr"/>
@@ -9067,11 +8941,9 @@
         <v>0.9547</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>0.1421</v>
-      </c>
-      <c r="F67" s="5" t="n">
         <v>0.1581</v>
       </c>
+      <c r="F67" s="5" t="inlineStr"/>
       <c r="G67" s="5" t="inlineStr"/>
       <c r="H67" s="5" t="inlineStr"/>
       <c r="I67" s="5" t="inlineStr"/>

--- a/outputs/VIC_curtailment.xlsx
+++ b/outputs/VIC_curtailment.xlsx
@@ -646,7 +646,9 @@
       <c r="J2" s="5" t="n">
         <v>0.2465</v>
       </c>
-      <c r="K2" s="5" t="inlineStr"/>
+      <c r="K2" s="5" t="n">
+        <v>0.1707</v>
+      </c>
       <c r="L2" s="5" t="n">
         <v>0.833539620209753</v>
       </c>
@@ -782,7 +784,9 @@
         <v>66</v>
       </c>
       <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="n">
+        <v>0.2704</v>
+      </c>
       <c r="L4" s="5" t="n">
         <v>0.547516873654646</v>
       </c>
@@ -865,7 +869,9 @@
       <c r="J5" s="5" t="n">
         <v>0.054</v>
       </c>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="K5" s="5" t="n">
+        <v>0.0756</v>
+      </c>
       <c r="L5" s="5" t="n">
         <v>0.547516873654646</v>
       </c>
@@ -948,7 +954,9 @@
       <c r="J6" s="5" t="n">
         <v>0.2374</v>
       </c>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="n">
+        <v>0.3025</v>
+      </c>
       <c r="L6" s="5" t="n">
         <v>0.389503957787889</v>
       </c>
@@ -1031,7 +1039,9 @@
       <c r="J7" s="5" t="n">
         <v>0.0688</v>
       </c>
-      <c r="K7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="n">
+        <v>0.0226</v>
+      </c>
       <c r="L7" s="5" t="n">
         <v>0.390717855103594</v>
       </c>
@@ -1108,7 +1118,9 @@
       <c r="J8" s="5" t="n">
         <v>0.2057</v>
       </c>
-      <c r="K8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="n">
+        <v>0.3181</v>
+      </c>
       <c r="L8" s="5" t="inlineStr"/>
       <c r="M8" s="5" t="inlineStr"/>
       <c r="N8" s="5" t="n">
@@ -1226,7 +1238,9 @@
       <c r="J10" s="5" t="n">
         <v>0.159</v>
       </c>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="n">
+        <v>0.1549</v>
+      </c>
       <c r="L10" s="5" t="n">
         <v>0.8554020168196</v>
       </c>
@@ -1301,7 +1315,9 @@
       </c>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="n">
+        <v>0.1479</v>
+      </c>
       <c r="L11" s="5" t="inlineStr"/>
       <c r="M11" s="5" t="inlineStr"/>
       <c r="N11" s="5" t="n">
@@ -1364,7 +1380,9 @@
       <c r="J12" s="5" t="n">
         <v>0.1081</v>
       </c>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="n">
+        <v>0.1394</v>
+      </c>
       <c r="L12" s="5" t="n">
         <v>0.827440107601162</v>
       </c>
@@ -1494,7 +1512,9 @@
       </c>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="5" t="inlineStr"/>
-      <c r="K14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="n">
+        <v>0.3551</v>
+      </c>
       <c r="L14" s="5" t="inlineStr"/>
       <c r="M14" s="5" t="inlineStr"/>
       <c r="N14" s="5" t="n">
@@ -1557,7 +1577,9 @@
       <c r="J15" s="5" t="n">
         <v>0.1275</v>
       </c>
-      <c r="K15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="n">
+        <v>0.2606</v>
+      </c>
       <c r="L15" s="5" t="n">
         <v>0.389503957787889</v>
       </c>
@@ -1695,7 +1717,9 @@
       <c r="J17" s="5" t="n">
         <v>0.2491</v>
       </c>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="n">
+        <v>0.1566</v>
+      </c>
       <c r="L17" s="5" t="n">
         <v>0.833539620209753</v>
       </c>
@@ -1776,7 +1800,9 @@
         <v>66</v>
       </c>
       <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="n">
+        <v>0.076</v>
+      </c>
       <c r="L18" s="5" t="n">
         <v>0.390717855103594</v>
       </c>
@@ -1857,7 +1883,9 @@
         <v>66</v>
       </c>
       <c r="J19" s="5" t="inlineStr"/>
-      <c r="K19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="n">
+        <v>0.3417</v>
+      </c>
       <c r="L19" s="5" t="n">
         <v>0.389503957787889</v>
       </c>
@@ -1924,7 +1952,9 @@
       <c r="J20" s="5" t="n">
         <v>0.2351</v>
       </c>
-      <c r="K20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="n">
+        <v>0.2256</v>
+      </c>
       <c r="L20" s="5" t="n">
         <v>0.8554020168196</v>
       </c>
@@ -2001,7 +2031,9 @@
       <c r="J21" s="5" t="n">
         <v>0.0482</v>
       </c>
-      <c r="K21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="n">
+        <v>0.0603</v>
+      </c>
       <c r="L21" s="5" t="inlineStr"/>
       <c r="M21" s="5" t="inlineStr"/>
       <c r="N21" s="5" t="n">
@@ -2058,7 +2090,9 @@
       <c r="J22" s="5" t="n">
         <v>0.0051</v>
       </c>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="n">
+        <v>0.003</v>
+      </c>
       <c r="L22" s="5" t="inlineStr"/>
       <c r="M22" s="5" t="inlineStr"/>
       <c r="N22" s="5" t="n">
@@ -2115,7 +2149,9 @@
       <c r="J23" s="5" t="n">
         <v>0.1906</v>
       </c>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="K23" s="5" t="n">
+        <v>0.0784</v>
+      </c>
       <c r="L23" s="5" t="inlineStr"/>
       <c r="M23" s="5" t="inlineStr"/>
       <c r="N23" s="5" t="n">
@@ -2172,7 +2208,9 @@
       <c r="J24" s="5" t="n">
         <v>0.0316</v>
       </c>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="n">
+        <v>0.0158</v>
+      </c>
       <c r="L24" s="5" t="inlineStr"/>
       <c r="M24" s="5" t="inlineStr"/>
       <c r="N24" s="5" t="n">
@@ -2229,7 +2267,9 @@
       <c r="J25" s="5" t="n">
         <v>0.0284</v>
       </c>
-      <c r="K25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="n">
+        <v>0.0116</v>
+      </c>
       <c r="L25" s="5" t="inlineStr"/>
       <c r="M25" s="5" t="inlineStr"/>
       <c r="N25" s="5" t="n">
@@ -2394,7 +2434,9 @@
       <c r="J28" s="5" t="n">
         <v>0.0958</v>
       </c>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="n">
+        <v>0.1206</v>
+      </c>
       <c r="L28" s="5" t="inlineStr"/>
       <c r="M28" s="5" t="inlineStr"/>
       <c r="N28" s="5" t="n">
@@ -2561,7 +2603,9 @@
       <c r="J31" s="5" t="n">
         <v>0.0678</v>
       </c>
-      <c r="K31" s="5" t="inlineStr"/>
+      <c r="K31" s="5" t="n">
+        <v>0.1776</v>
+      </c>
       <c r="L31" s="5" t="inlineStr"/>
       <c r="M31" s="5" t="inlineStr"/>
       <c r="N31" s="5" t="n">
@@ -2673,7 +2717,9 @@
       <c r="J33" s="5" t="n">
         <v>0.125</v>
       </c>
-      <c r="K33" s="5" t="inlineStr"/>
+      <c r="K33" s="5" t="n">
+        <v>0.1985</v>
+      </c>
       <c r="L33" s="5" t="inlineStr"/>
       <c r="M33" s="5" t="inlineStr"/>
       <c r="N33" s="5" t="n">
@@ -2730,7 +2776,9 @@
       <c r="J34" s="5" t="n">
         <v>0.0467</v>
       </c>
-      <c r="K34" s="5" t="inlineStr"/>
+      <c r="K34" s="5" t="n">
+        <v>0.0584</v>
+      </c>
       <c r="L34" s="5" t="inlineStr"/>
       <c r="M34" s="5" t="inlineStr"/>
       <c r="N34" s="5" t="n">
@@ -2787,7 +2835,9 @@
       <c r="J35" s="5" t="n">
         <v>0.0331</v>
       </c>
-      <c r="K35" s="5" t="inlineStr"/>
+      <c r="K35" s="5" t="n">
+        <v>0.0324</v>
+      </c>
       <c r="L35" s="5" t="inlineStr"/>
       <c r="M35" s="5" t="inlineStr"/>
       <c r="N35" s="5" t="n">
@@ -2842,7 +2892,9 @@
       </c>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="5" t="inlineStr"/>
-      <c r="K36" s="5" t="inlineStr"/>
+      <c r="K36" s="5" t="n">
+        <v>0.2791</v>
+      </c>
       <c r="L36" s="5" t="inlineStr"/>
       <c r="M36" s="5" t="inlineStr"/>
       <c r="N36" s="5" t="n">
@@ -3003,7 +3055,9 @@
       </c>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="5" t="inlineStr"/>
-      <c r="K39" s="5" t="inlineStr"/>
+      <c r="K39" s="5" t="n">
+        <v>0.3008</v>
+      </c>
       <c r="L39" s="5" t="inlineStr"/>
       <c r="M39" s="5" t="inlineStr"/>
       <c r="N39" s="5" t="n">
@@ -3058,7 +3112,9 @@
       </c>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="5" t="inlineStr"/>
-      <c r="K40" s="5" t="inlineStr"/>
+      <c r="K40" s="5" t="n">
+        <v>0.3185</v>
+      </c>
       <c r="L40" s="5" t="inlineStr"/>
       <c r="M40" s="5" t="inlineStr"/>
       <c r="N40" s="5" t="n">
@@ -3113,7 +3169,9 @@
       </c>
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="5" t="inlineStr"/>
-      <c r="K41" s="5" t="inlineStr"/>
+      <c r="K41" s="5" t="n">
+        <v>0.1703</v>
+      </c>
       <c r="L41" s="5" t="inlineStr"/>
       <c r="M41" s="5" t="inlineStr"/>
       <c r="N41" s="5" t="n">
@@ -3280,7 +3338,9 @@
       <c r="J44" s="5" t="n">
         <v>0.1766</v>
       </c>
-      <c r="K44" s="5" t="inlineStr"/>
+      <c r="K44" s="5" t="n">
+        <v>0.2424</v>
+      </c>
       <c r="L44" s="5" t="inlineStr"/>
       <c r="M44" s="5" t="inlineStr"/>
       <c r="N44" s="5" t="n">
@@ -3392,7 +3452,9 @@
       <c r="J46" s="5" t="n">
         <v>0.173</v>
       </c>
-      <c r="K46" s="5" t="inlineStr"/>
+      <c r="K46" s="5" t="n">
+        <v>0.2741</v>
+      </c>
       <c r="L46" s="5" t="inlineStr"/>
       <c r="M46" s="5" t="inlineStr"/>
       <c r="N46" s="5" t="n">
@@ -3449,7 +3511,9 @@
       <c r="J47" s="5" t="n">
         <v>0.1339</v>
       </c>
-      <c r="K47" s="5" t="inlineStr"/>
+      <c r="K47" s="5" t="n">
+        <v>0.22</v>
+      </c>
       <c r="L47" s="5" t="inlineStr"/>
       <c r="M47" s="5" t="inlineStr"/>
       <c r="N47" s="5" t="n">
@@ -3561,7 +3625,9 @@
       <c r="J49" s="5" t="n">
         <v>0.0847</v>
       </c>
-      <c r="K49" s="5" t="inlineStr"/>
+      <c r="K49" s="5" t="n">
+        <v>0.0832</v>
+      </c>
       <c r="L49" s="5" t="inlineStr"/>
       <c r="M49" s="5" t="inlineStr"/>
       <c r="N49" s="5" t="n">
@@ -3618,7 +3684,9 @@
       <c r="J50" s="5" t="n">
         <v>0.09810000000000001</v>
       </c>
-      <c r="K50" s="5" t="inlineStr"/>
+      <c r="K50" s="5" t="n">
+        <v>0.0223</v>
+      </c>
       <c r="L50" s="5" t="inlineStr"/>
       <c r="M50" s="5" t="inlineStr"/>
       <c r="N50" s="5" t="n">
@@ -3730,7 +3798,9 @@
       <c r="J52" s="5" t="n">
         <v>0.0498</v>
       </c>
-      <c r="K52" s="5" t="inlineStr"/>
+      <c r="K52" s="5" t="n">
+        <v>0.0317</v>
+      </c>
       <c r="L52" s="5" t="inlineStr"/>
       <c r="M52" s="5" t="inlineStr"/>
       <c r="N52" s="5" t="n">
@@ -3787,7 +3857,9 @@
       <c r="J53" s="5" t="n">
         <v>0.2533</v>
       </c>
-      <c r="K53" s="5" t="inlineStr"/>
+      <c r="K53" s="5" t="n">
+        <v>0.149</v>
+      </c>
       <c r="L53" s="5" t="inlineStr"/>
       <c r="M53" s="5" t="inlineStr"/>
       <c r="N53" s="5" t="n">
@@ -3844,7 +3916,9 @@
       <c r="J54" s="5" t="n">
         <v>0.2838</v>
       </c>
-      <c r="K54" s="5" t="inlineStr"/>
+      <c r="K54" s="5" t="n">
+        <v>0.3998</v>
+      </c>
       <c r="L54" s="5" t="inlineStr"/>
       <c r="M54" s="5" t="inlineStr"/>
       <c r="N54" s="5" t="n">
@@ -3901,7 +3975,9 @@
       <c r="J55" s="5" t="n">
         <v>0.2355</v>
       </c>
-      <c r="K55" s="5" t="inlineStr"/>
+      <c r="K55" s="5" t="n">
+        <v>0.2821</v>
+      </c>
       <c r="L55" s="5" t="inlineStr"/>
       <c r="M55" s="5" t="inlineStr"/>
       <c r="N55" s="5" t="n">
@@ -3958,7 +4034,9 @@
       <c r="J56" s="5" t="n">
         <v>0.077</v>
       </c>
-      <c r="K56" s="5" t="inlineStr"/>
+      <c r="K56" s="5" t="n">
+        <v>0.1518</v>
+      </c>
       <c r="L56" s="5" t="inlineStr"/>
       <c r="M56" s="5" t="inlineStr"/>
       <c r="N56" s="5" t="n">
@@ -4015,7 +4093,9 @@
       <c r="J57" s="5" t="n">
         <v>0.0931</v>
       </c>
-      <c r="K57" s="5" t="inlineStr"/>
+      <c r="K57" s="5" t="n">
+        <v>0.1385</v>
+      </c>
       <c r="L57" s="5" t="inlineStr"/>
       <c r="M57" s="5" t="inlineStr"/>
       <c r="N57" s="5" t="n">
@@ -4072,7 +4152,9 @@
       <c r="J58" s="5" t="n">
         <v>0.2295</v>
       </c>
-      <c r="K58" s="5" t="inlineStr"/>
+      <c r="K58" s="5" t="n">
+        <v>0.3559</v>
+      </c>
       <c r="L58" s="5" t="inlineStr"/>
       <c r="M58" s="5" t="inlineStr"/>
       <c r="N58" s="5" t="n">
@@ -4129,7 +4211,9 @@
       <c r="J59" s="5" t="n">
         <v>0.0216</v>
       </c>
-      <c r="K59" s="5" t="inlineStr"/>
+      <c r="K59" s="5" t="n">
+        <v>0.0081</v>
+      </c>
       <c r="L59" s="5" t="inlineStr"/>
       <c r="M59" s="5" t="inlineStr"/>
       <c r="N59" s="5" t="n">
@@ -4571,7 +4655,9 @@
       <c r="J67" s="5" t="n">
         <v>0.1581</v>
       </c>
-      <c r="K67" s="5" t="inlineStr"/>
+      <c r="K67" s="5" t="n">
+        <v>0.257</v>
+      </c>
       <c r="L67" s="5" t="inlineStr"/>
       <c r="M67" s="5" t="inlineStr"/>
       <c r="N67" s="5" t="n">
@@ -4759,7 +4845,9 @@
       <c r="E2" s="5" t="n">
         <v>0.2465</v>
       </c>
-      <c r="F2" s="5" t="inlineStr"/>
+      <c r="F2" s="5" t="n">
+        <v>0.1707</v>
+      </c>
       <c r="G2" s="5" t="n">
         <v>0.833539620209753</v>
       </c>
@@ -4899,7 +4987,9 @@
         <v>0.929</v>
       </c>
       <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="n">
+        <v>0.2704</v>
+      </c>
       <c r="G4" s="5" t="n">
         <v>0.547516873654646</v>
       </c>
@@ -4981,7 +5071,9 @@
       <c r="E5" s="5" t="n">
         <v>0.054</v>
       </c>
-      <c r="F5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="n">
+        <v>0.0756</v>
+      </c>
       <c r="G5" s="5" t="n">
         <v>0.547516873654646</v>
       </c>
@@ -5063,7 +5155,9 @@
       <c r="E6" s="5" t="n">
         <v>0.2374</v>
       </c>
-      <c r="F6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="n">
+        <v>0.3025</v>
+      </c>
       <c r="G6" s="5" t="n">
         <v>0.389503957787889</v>
       </c>
@@ -5145,7 +5239,9 @@
       <c r="E7" s="5" t="n">
         <v>0.0688</v>
       </c>
-      <c r="F7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="n">
+        <v>0.0226</v>
+      </c>
       <c r="G7" s="5" t="n">
         <v>0.390717855103594</v>
       </c>
@@ -5227,7 +5323,9 @@
       <c r="E8" s="5" t="n">
         <v>0.2057</v>
       </c>
-      <c r="F8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="n">
+        <v>0.3181</v>
+      </c>
       <c r="G8" s="5" t="inlineStr"/>
       <c r="H8" s="5" t="inlineStr"/>
       <c r="I8" s="5" t="inlineStr"/>
@@ -5349,7 +5447,9 @@
       <c r="E10" s="5" t="n">
         <v>0.159</v>
       </c>
-      <c r="F10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="n">
+        <v>0.1549</v>
+      </c>
       <c r="G10" s="5" t="n">
         <v>0.8554020168196</v>
       </c>
@@ -5429,7 +5529,9 @@
         <v>0.9311</v>
       </c>
       <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="n">
+        <v>0.1479</v>
+      </c>
       <c r="G11" s="5" t="inlineStr"/>
       <c r="H11" s="5" t="inlineStr"/>
       <c r="I11" s="5" t="inlineStr"/>
@@ -5491,7 +5593,9 @@
       <c r="E12" s="5" t="n">
         <v>0.1081</v>
       </c>
-      <c r="F12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="n">
+        <v>0.1394</v>
+      </c>
       <c r="G12" s="5" t="n">
         <v>0.827440107601162</v>
       </c>
@@ -5631,7 +5735,9 @@
         <v>0.9257</v>
       </c>
       <c r="E14" s="5" t="inlineStr"/>
-      <c r="F14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="n">
+        <v>0.3551</v>
+      </c>
       <c r="G14" s="5" t="inlineStr"/>
       <c r="H14" s="5" t="inlineStr"/>
       <c r="I14" s="5" t="inlineStr"/>
@@ -5693,7 +5799,9 @@
       <c r="E15" s="5" t="n">
         <v>0.1275</v>
       </c>
-      <c r="F15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="n">
+        <v>0.2606</v>
+      </c>
       <c r="G15" s="5" t="n">
         <v>0.389503957787889</v>
       </c>
@@ -5835,7 +5943,9 @@
       <c r="E17" s="5" t="n">
         <v>0.2491</v>
       </c>
-      <c r="F17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="n">
+        <v>0.1566</v>
+      </c>
       <c r="G17" s="5" t="n">
         <v>0.833539620209753</v>
       </c>
@@ -5915,7 +6025,9 @@
         <v>0.9211</v>
       </c>
       <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="n">
+        <v>0.076</v>
+      </c>
       <c r="G18" s="5" t="n">
         <v>0.390717855103594</v>
       </c>
@@ -5995,7 +6107,9 @@
         <v>0.921</v>
       </c>
       <c r="E19" s="5" t="inlineStr"/>
-      <c r="F19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="n">
+        <v>0.3417</v>
+      </c>
       <c r="G19" s="5" t="n">
         <v>0.389503957787889</v>
       </c>
@@ -6061,7 +6175,9 @@
       <c r="E20" s="5" t="n">
         <v>0.2351</v>
       </c>
-      <c r="F20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="n">
+        <v>0.2256</v>
+      </c>
       <c r="G20" s="5" t="n">
         <v>0.8554020168196</v>
       </c>
@@ -6143,7 +6259,9 @@
       <c r="E21" s="5" t="n">
         <v>0.0482</v>
       </c>
-      <c r="F21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="n">
+        <v>0.0603</v>
+      </c>
       <c r="G21" s="5" t="inlineStr"/>
       <c r="H21" s="5" t="inlineStr"/>
       <c r="I21" s="5" t="inlineStr"/>
@@ -6205,7 +6323,9 @@
       <c r="E22" s="5" t="n">
         <v>0.0051</v>
       </c>
-      <c r="F22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="n">
+        <v>0.003</v>
+      </c>
       <c r="G22" s="5" t="inlineStr"/>
       <c r="H22" s="5" t="inlineStr"/>
       <c r="I22" s="5" t="inlineStr"/>
@@ -6267,7 +6387,9 @@
       <c r="E23" s="5" t="n">
         <v>0.1906</v>
       </c>
-      <c r="F23" s="5" t="inlineStr"/>
+      <c r="F23" s="5" t="n">
+        <v>0.0784</v>
+      </c>
       <c r="G23" s="5" t="inlineStr"/>
       <c r="H23" s="5" t="inlineStr"/>
       <c r="I23" s="5" t="inlineStr"/>
@@ -6329,7 +6451,9 @@
       <c r="E24" s="5" t="n">
         <v>0.0316</v>
       </c>
-      <c r="F24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="n">
+        <v>0.0158</v>
+      </c>
       <c r="G24" s="5" t="inlineStr"/>
       <c r="H24" s="5" t="inlineStr"/>
       <c r="I24" s="5" t="inlineStr"/>
@@ -6391,7 +6515,9 @@
       <c r="E25" s="5" t="n">
         <v>0.0284</v>
       </c>
-      <c r="F25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="n">
+        <v>0.0116</v>
+      </c>
       <c r="G25" s="5" t="inlineStr"/>
       <c r="H25" s="5" t="inlineStr"/>
       <c r="I25" s="5" t="inlineStr"/>
@@ -6571,7 +6697,9 @@
       <c r="E28" s="5" t="n">
         <v>0.0958</v>
       </c>
-      <c r="F28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="n">
+        <v>0.1206</v>
+      </c>
       <c r="G28" s="5" t="inlineStr"/>
       <c r="H28" s="5" t="inlineStr"/>
       <c r="I28" s="5" t="inlineStr"/>
@@ -6753,7 +6881,9 @@
       <c r="E31" s="5" t="n">
         <v>0.0678</v>
       </c>
-      <c r="F31" s="5" t="inlineStr"/>
+      <c r="F31" s="5" t="n">
+        <v>0.1776</v>
+      </c>
       <c r="G31" s="5" t="inlineStr"/>
       <c r="H31" s="5" t="inlineStr"/>
       <c r="I31" s="5" t="inlineStr"/>
@@ -6875,7 +7005,9 @@
       <c r="E33" s="5" t="n">
         <v>0.125</v>
       </c>
-      <c r="F33" s="5" t="inlineStr"/>
+      <c r="F33" s="5" t="n">
+        <v>0.1985</v>
+      </c>
       <c r="G33" s="5" t="inlineStr"/>
       <c r="H33" s="5" t="inlineStr"/>
       <c r="I33" s="5" t="inlineStr"/>
@@ -6937,7 +7069,9 @@
       <c r="E34" s="5" t="n">
         <v>0.0467</v>
       </c>
-      <c r="F34" s="5" t="inlineStr"/>
+      <c r="F34" s="5" t="n">
+        <v>0.0584</v>
+      </c>
       <c r="G34" s="5" t="inlineStr"/>
       <c r="H34" s="5" t="inlineStr"/>
       <c r="I34" s="5" t="inlineStr"/>
@@ -6999,7 +7133,9 @@
       <c r="E35" s="5" t="n">
         <v>0.0331</v>
       </c>
-      <c r="F35" s="5" t="inlineStr"/>
+      <c r="F35" s="5" t="n">
+        <v>0.0324</v>
+      </c>
       <c r="G35" s="5" t="inlineStr"/>
       <c r="H35" s="5" t="inlineStr"/>
       <c r="I35" s="5" t="inlineStr"/>
@@ -7059,7 +7195,9 @@
         <v>0.9556</v>
       </c>
       <c r="E36" s="5" t="inlineStr"/>
-      <c r="F36" s="5" t="inlineStr"/>
+      <c r="F36" s="5" t="n">
+        <v>0.2791</v>
+      </c>
       <c r="G36" s="5" t="inlineStr"/>
       <c r="H36" s="5" t="inlineStr"/>
       <c r="I36" s="5" t="inlineStr"/>
@@ -7235,7 +7373,9 @@
         <v>0.9815</v>
       </c>
       <c r="E39" s="5" t="inlineStr"/>
-      <c r="F39" s="5" t="inlineStr"/>
+      <c r="F39" s="5" t="n">
+        <v>0.3008</v>
+      </c>
       <c r="G39" s="5" t="inlineStr"/>
       <c r="H39" s="5" t="inlineStr"/>
       <c r="I39" s="5" t="inlineStr"/>
@@ -7295,7 +7435,9 @@
         <v>0.9815</v>
       </c>
       <c r="E40" s="5" t="inlineStr"/>
-      <c r="F40" s="5" t="inlineStr"/>
+      <c r="F40" s="5" t="n">
+        <v>0.3185</v>
+      </c>
       <c r="G40" s="5" t="inlineStr"/>
       <c r="H40" s="5" t="inlineStr"/>
       <c r="I40" s="5" t="inlineStr"/>
@@ -7355,7 +7497,9 @@
         <v>0.9815</v>
       </c>
       <c r="E41" s="5" t="inlineStr"/>
-      <c r="F41" s="5" t="inlineStr"/>
+      <c r="F41" s="5" t="n">
+        <v>0.1703</v>
+      </c>
       <c r="G41" s="5" t="inlineStr"/>
       <c r="H41" s="5" t="inlineStr"/>
       <c r="I41" s="5" t="inlineStr"/>
@@ -7537,7 +7681,9 @@
       <c r="E44" s="5" t="n">
         <v>0.1766</v>
       </c>
-      <c r="F44" s="5" t="inlineStr"/>
+      <c r="F44" s="5" t="n">
+        <v>0.2424</v>
+      </c>
       <c r="G44" s="5" t="inlineStr"/>
       <c r="H44" s="5" t="inlineStr"/>
       <c r="I44" s="5" t="inlineStr"/>
@@ -7659,7 +7805,9 @@
       <c r="E46" s="5" t="n">
         <v>0.173</v>
       </c>
-      <c r="F46" s="5" t="inlineStr"/>
+      <c r="F46" s="5" t="n">
+        <v>0.2741</v>
+      </c>
       <c r="G46" s="5" t="inlineStr"/>
       <c r="H46" s="5" t="inlineStr"/>
       <c r="I46" s="5" t="inlineStr"/>
@@ -7721,7 +7869,9 @@
       <c r="E47" s="5" t="n">
         <v>0.1339</v>
       </c>
-      <c r="F47" s="5" t="inlineStr"/>
+      <c r="F47" s="5" t="n">
+        <v>0.22</v>
+      </c>
       <c r="G47" s="5" t="inlineStr"/>
       <c r="H47" s="5" t="inlineStr"/>
       <c r="I47" s="5" t="inlineStr"/>
@@ -7843,7 +7993,9 @@
       <c r="E49" s="5" t="n">
         <v>0.0847</v>
       </c>
-      <c r="F49" s="5" t="inlineStr"/>
+      <c r="F49" s="5" t="n">
+        <v>0.0832</v>
+      </c>
       <c r="G49" s="5" t="inlineStr"/>
       <c r="H49" s="5" t="inlineStr"/>
       <c r="I49" s="5" t="inlineStr"/>
@@ -7905,7 +8057,9 @@
       <c r="E50" s="5" t="n">
         <v>0.09810000000000001</v>
       </c>
-      <c r="F50" s="5" t="inlineStr"/>
+      <c r="F50" s="5" t="n">
+        <v>0.0223</v>
+      </c>
       <c r="G50" s="5" t="inlineStr"/>
       <c r="H50" s="5" t="inlineStr"/>
       <c r="I50" s="5" t="inlineStr"/>
@@ -8027,7 +8181,9 @@
       <c r="E52" s="5" t="n">
         <v>0.0498</v>
       </c>
-      <c r="F52" s="5" t="inlineStr"/>
+      <c r="F52" s="5" t="n">
+        <v>0.0317</v>
+      </c>
       <c r="G52" s="5" t="inlineStr"/>
       <c r="H52" s="5" t="inlineStr"/>
       <c r="I52" s="5" t="inlineStr"/>
@@ -8089,7 +8245,9 @@
       <c r="E53" s="5" t="n">
         <v>0.2533</v>
       </c>
-      <c r="F53" s="5" t="inlineStr"/>
+      <c r="F53" s="5" t="n">
+        <v>0.149</v>
+      </c>
       <c r="G53" s="5" t="inlineStr"/>
       <c r="H53" s="5" t="inlineStr"/>
       <c r="I53" s="5" t="inlineStr"/>
@@ -8151,7 +8309,9 @@
       <c r="E54" s="5" t="n">
         <v>0.2838</v>
       </c>
-      <c r="F54" s="5" t="inlineStr"/>
+      <c r="F54" s="5" t="n">
+        <v>0.3998</v>
+      </c>
       <c r="G54" s="5" t="inlineStr"/>
       <c r="H54" s="5" t="inlineStr"/>
       <c r="I54" s="5" t="inlineStr"/>
@@ -8213,7 +8373,9 @@
       <c r="E55" s="5" t="n">
         <v>0.2355</v>
       </c>
-      <c r="F55" s="5" t="inlineStr"/>
+      <c r="F55" s="5" t="n">
+        <v>0.2821</v>
+      </c>
       <c r="G55" s="5" t="inlineStr"/>
       <c r="H55" s="5" t="inlineStr"/>
       <c r="I55" s="5" t="inlineStr"/>
@@ -8275,7 +8437,9 @@
       <c r="E56" s="5" t="n">
         <v>0.077</v>
       </c>
-      <c r="F56" s="5" t="inlineStr"/>
+      <c r="F56" s="5" t="n">
+        <v>0.1518</v>
+      </c>
       <c r="G56" s="5" t="inlineStr"/>
       <c r="H56" s="5" t="inlineStr"/>
       <c r="I56" s="5" t="inlineStr"/>
@@ -8337,7 +8501,9 @@
       <c r="E57" s="5" t="n">
         <v>0.0931</v>
       </c>
-      <c r="F57" s="5" t="inlineStr"/>
+      <c r="F57" s="5" t="n">
+        <v>0.1385</v>
+      </c>
       <c r="G57" s="5" t="inlineStr"/>
       <c r="H57" s="5" t="inlineStr"/>
       <c r="I57" s="5" t="inlineStr"/>
@@ -8399,7 +8565,9 @@
       <c r="E58" s="5" t="n">
         <v>0.2295</v>
       </c>
-      <c r="F58" s="5" t="inlineStr"/>
+      <c r="F58" s="5" t="n">
+        <v>0.3559</v>
+      </c>
       <c r="G58" s="5" t="inlineStr"/>
       <c r="H58" s="5" t="inlineStr"/>
       <c r="I58" s="5" t="inlineStr"/>
@@ -8461,7 +8629,9 @@
       <c r="E59" s="5" t="n">
         <v>0.0216</v>
       </c>
-      <c r="F59" s="5" t="inlineStr"/>
+      <c r="F59" s="5" t="n">
+        <v>0.0081</v>
+      </c>
       <c r="G59" s="5" t="inlineStr"/>
       <c r="H59" s="5" t="inlineStr"/>
       <c r="I59" s="5" t="inlineStr"/>
@@ -8943,7 +9113,9 @@
       <c r="E67" s="5" t="n">
         <v>0.1581</v>
       </c>
-      <c r="F67" s="5" t="inlineStr"/>
+      <c r="F67" s="5" t="n">
+        <v>0.257</v>
+      </c>
       <c r="G67" s="5" t="inlineStr"/>
       <c r="H67" s="5" t="inlineStr"/>
       <c r="I67" s="5" t="inlineStr"/>
